--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\学习专用\ark_-n\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279881E2-6B2F-499C-BF0F-42A268D42396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A9A412-5195-437B-81A0-5D6359994935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -23,18 +23,6 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -297,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="514">
   <si>
     <t>Id</t>
   </si>
@@ -1911,6 +1899,14 @@
   </si>
   <si>
     <t>Target.Hp&gt;Unit.Attack*6 + Unit.Defence</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>可无视buff抑制检测</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsCancelable</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2466,7 +2462,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
@@ -2504,48 +2500,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BS598"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1"/>
-    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="4" max="4" width="8.54296875" customWidth="1"/>
+    <col min="5" max="5" width="5.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.54296875" customWidth="1"/>
+    <col min="7" max="7" width="8.26953125" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="4.08203125" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1"/>
+    <col min="12" max="12" width="4.08984375" customWidth="1"/>
+    <col min="13" max="13" width="5.54296875" customWidth="1"/>
     <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.75" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="10.25" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1"/>
-    <col min="23" max="23" width="10.75" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1"/>
-    <col min="26" max="26" width="10.75" customWidth="1"/>
+    <col min="15" max="15" width="7.7265625" customWidth="1"/>
+    <col min="16" max="16" width="10.81640625" customWidth="1"/>
+    <col min="17" max="18" width="3.81640625" customWidth="1"/>
+    <col min="19" max="20" width="3.54296875" customWidth="1"/>
+    <col min="21" max="21" width="10.26953125" customWidth="1"/>
+    <col min="22" max="22" width="9.54296875" customWidth="1"/>
+    <col min="23" max="23" width="10.7265625" customWidth="1"/>
+    <col min="24" max="24" width="12.81640625" customWidth="1"/>
+    <col min="25" max="25" width="13.08984375" customWidth="1"/>
+    <col min="26" max="26" width="10.7265625" customWidth="1"/>
     <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1"/>
-    <col min="31" max="31" width="9.75" customWidth="1"/>
-    <col min="32" max="32" width="7.83203125" customWidth="1"/>
-    <col min="33" max="33" width="15.83203125" customWidth="1"/>
-    <col min="34" max="34" width="13.83203125" customWidth="1"/>
-    <col min="35" max="35" width="34.5" customWidth="1"/>
-    <col min="36" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
+    <col min="30" max="30" width="17.08984375" customWidth="1"/>
+    <col min="31" max="31" width="9.7265625" customWidth="1"/>
+    <col min="32" max="32" width="7.81640625" customWidth="1"/>
+    <col min="33" max="33" width="15.81640625" customWidth="1"/>
+    <col min="34" max="34" width="13.81640625" customWidth="1"/>
+    <col min="35" max="35" width="34.453125" customWidth="1"/>
+    <col min="36" max="37" width="9.81640625" customWidth="1"/>
+    <col min="43" max="43" width="12.453125" customWidth="1"/>
+    <col min="50" max="50" width="24.36328125" customWidth="1"/>
+    <col min="52" max="52" width="17.7265625" customWidth="1"/>
+    <col min="53" max="53" width="7.81640625" customWidth="1"/>
+    <col min="56" max="56" width="24.26953125" customWidth="1"/>
+    <col min="57" max="57" width="13.26953125" customWidth="1"/>
+    <col min="58" max="58" width="16.08984375" customWidth="1"/>
     <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="39.54296875" customWidth="1"/>
     <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
+    <col min="66" max="66" width="14.81640625" customWidth="1"/>
     <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="71" max="71" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.25">
@@ -3777,2755 +3773,2755 @@
       <c r="AI35" s="8"/>
       <c r="BK35" s="8"/>
     </row>
-    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D36" s="6"/>
       <c r="E36" s="1"/>
       <c r="BO36" s="7"/>
       <c r="BR36" s="7"/>
     </row>
-    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D37" s="6"/>
       <c r="E37" s="1"/>
       <c r="BO37" s="7"/>
       <c r="BR37" s="7"/>
     </row>
-    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D38" s="6"/>
       <c r="E38" s="1"/>
       <c r="BO38" s="7"/>
       <c r="BR38" s="7"/>
     </row>
-    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D39" s="6"/>
       <c r="E39" s="1"/>
       <c r="BO39" s="7"/>
       <c r="BR39" s="7"/>
     </row>
-    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D40" s="6"/>
       <c r="E40" s="1"/>
       <c r="BO40" s="7"/>
       <c r="BR40" s="7"/>
     </row>
-    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D41" s="6"/>
       <c r="E41" s="1"/>
       <c r="BO41" s="7"/>
       <c r="BR41" s="7"/>
     </row>
-    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D42" s="6"/>
       <c r="E42" s="1"/>
       <c r="BO42" s="7"/>
       <c r="BR42" s="7"/>
     </row>
-    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D43" s="6"/>
       <c r="E43" s="1"/>
       <c r="BR43" s="7"/>
     </row>
-    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D44" s="6"/>
       <c r="E44" s="1"/>
       <c r="BR44" s="7"/>
     </row>
-    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D45" s="6"/>
       <c r="E45" s="1"/>
       <c r="BR45" s="7"/>
     </row>
-    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D46" s="6"/>
       <c r="E46" s="1"/>
       <c r="BO46" s="7"/>
       <c r="BR46" s="7"/>
     </row>
-    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D47" s="6"/>
       <c r="E47" s="1"/>
       <c r="BO47" s="7"/>
       <c r="BR47" s="7"/>
     </row>
-    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D48" s="6"/>
       <c r="E48" s="1"/>
       <c r="BO48" s="7"/>
       <c r="BR48" s="7"/>
     </row>
-    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D49" s="6"/>
       <c r="E49" s="1"/>
       <c r="BO49" s="7"/>
       <c r="BR49" s="7"/>
     </row>
-    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D50" s="6"/>
       <c r="E50" s="1"/>
       <c r="BO50" s="7"/>
       <c r="BR50" s="7"/>
     </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D51" s="6"/>
       <c r="E51" s="1"/>
       <c r="BO51" s="7"/>
       <c r="BR51" s="7"/>
     </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D52" s="6"/>
       <c r="E52" s="1"/>
       <c r="BO52" s="7"/>
       <c r="BR52" s="7"/>
     </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D53" s="6"/>
       <c r="E53" s="1"/>
       <c r="BO53" s="7"/>
       <c r="BR53" s="7"/>
     </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D54" s="6"/>
       <c r="E54" s="1"/>
       <c r="BO54" s="7"/>
       <c r="BR54" s="7"/>
     </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D55" s="6"/>
       <c r="E55" s="1"/>
       <c r="BO55" s="7"/>
       <c r="BR55" s="7"/>
     </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D56" s="6"/>
       <c r="E56" s="1"/>
       <c r="BO56" s="7"/>
       <c r="BR56" s="7"/>
     </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D57" s="6"/>
       <c r="E57" s="1"/>
       <c r="BO57" s="7"/>
       <c r="BR57" s="7"/>
     </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D58" s="6"/>
       <c r="E58" s="1"/>
       <c r="BO58" s="7"/>
       <c r="BR58" s="7"/>
     </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D59" s="6"/>
       <c r="E59" s="1"/>
       <c r="BO59" s="7"/>
       <c r="BR59" s="7"/>
     </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D60" s="6"/>
       <c r="E60" s="1"/>
       <c r="BO60" s="7"/>
       <c r="BR60" s="7"/>
     </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D61" s="6"/>
       <c r="E61" s="1"/>
       <c r="BO61" s="7"/>
       <c r="BR61" s="7"/>
     </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D62" s="6"/>
       <c r="E62" s="1"/>
       <c r="BO62" s="7"/>
       <c r="BR62" s="7"/>
     </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D63" s="6"/>
       <c r="E63" s="1"/>
       <c r="BO63" s="7"/>
       <c r="BR63" s="7"/>
     </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D64" s="6"/>
       <c r="E64" s="1"/>
       <c r="BO64" s="7"/>
       <c r="BR64" s="7"/>
     </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D65" s="6"/>
       <c r="E65" s="1"/>
       <c r="BO65" s="7"/>
       <c r="BR65" s="7"/>
     </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D66" s="6"/>
       <c r="E66" s="1"/>
       <c r="BO66" s="7"/>
       <c r="BR66" s="7"/>
     </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D67" s="6"/>
       <c r="E67" s="1"/>
       <c r="BO67" s="7"/>
       <c r="BR67" s="7"/>
     </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D68" s="6"/>
       <c r="E68" s="1"/>
       <c r="BO68" s="7"/>
       <c r="BR68" s="7"/>
     </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D69" s="6"/>
       <c r="E69" s="1"/>
       <c r="BO69" s="7"/>
       <c r="BR69" s="7"/>
     </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D70" s="6"/>
       <c r="E70" s="1"/>
       <c r="BO70" s="7"/>
       <c r="BR70" s="7"/>
     </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D71" s="6"/>
       <c r="E71" s="1"/>
       <c r="BO71" s="7"/>
       <c r="BR71" s="7"/>
     </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D72" s="6"/>
       <c r="E72" s="1"/>
       <c r="BO72" s="7"/>
       <c r="BR72" s="7"/>
     </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D73" s="6"/>
       <c r="E73" s="1"/>
       <c r="BO73" s="7"/>
       <c r="BR73" s="7"/>
     </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D74" s="6"/>
       <c r="E74" s="1"/>
       <c r="BO74" s="7"/>
       <c r="BR74" s="7"/>
     </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D75" s="6"/>
       <c r="E75" s="1"/>
       <c r="BO75" s="7"/>
       <c r="BR75" s="7"/>
     </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D76" s="6"/>
       <c r="E76" s="1"/>
       <c r="BO76" s="7"/>
       <c r="BR76" s="7"/>
     </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D77" s="6"/>
       <c r="E77" s="1"/>
       <c r="BO77" s="7"/>
       <c r="BR77" s="7"/>
     </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D78" s="6"/>
       <c r="E78" s="1"/>
       <c r="BO78" s="7"/>
       <c r="BR78" s="7"/>
     </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D79" s="6"/>
       <c r="E79" s="1"/>
       <c r="BO79" s="7"/>
       <c r="BR79" s="7"/>
     </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D80" s="6"/>
       <c r="E80" s="1"/>
       <c r="BO80" s="7"/>
       <c r="BR80" s="7"/>
     </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D81" s="6"/>
       <c r="E81" s="1"/>
       <c r="BO81" s="7"/>
       <c r="BR81" s="7"/>
     </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D82" s="6"/>
       <c r="E82" s="1"/>
       <c r="BO82" s="7"/>
       <c r="BR82" s="7"/>
     </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D83" s="6"/>
       <c r="E83" s="1"/>
       <c r="BO83" s="7"/>
       <c r="BR83" s="7"/>
     </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D84" s="6"/>
       <c r="E84" s="1"/>
       <c r="BO84" s="7"/>
       <c r="BR84" s="7"/>
     </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D85" s="6"/>
       <c r="E85" s="1"/>
       <c r="BO85" s="7"/>
       <c r="BR85" s="7"/>
     </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D86" s="6"/>
       <c r="E86" s="1"/>
       <c r="BO86" s="7"/>
       <c r="BR86" s="7"/>
     </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D87" s="6"/>
       <c r="E87" s="1"/>
       <c r="BO87" s="7"/>
       <c r="BR87" s="7"/>
     </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
       <c r="E88" s="1"/>
       <c r="BO88" s="7"/>
       <c r="BR88" s="7"/>
     </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="1"/>
       <c r="BO89" s="7"/>
       <c r="BR89" s="7"/>
     </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="1"/>
       <c r="BO90" s="7"/>
       <c r="BR90" s="7"/>
     </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D91" s="6"/>
       <c r="E91" s="1"/>
       <c r="BO91" s="7"/>
       <c r="BR91" s="7"/>
     </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D92" s="6"/>
       <c r="E92" s="1"/>
       <c r="BO92" s="7"/>
       <c r="BR92" s="7"/>
     </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D93" s="6"/>
       <c r="E93" s="1"/>
       <c r="BO93" s="7"/>
       <c r="BR93" s="7"/>
     </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D94" s="6"/>
       <c r="E94" s="1"/>
       <c r="BO94" s="7"/>
       <c r="BR94" s="7"/>
     </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D95" s="6"/>
       <c r="E95" s="1"/>
       <c r="BO95" s="7"/>
       <c r="BR95" s="7"/>
     </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D96" s="6"/>
       <c r="E96" s="1"/>
       <c r="BO96" s="7"/>
       <c r="BR96" s="7"/>
     </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D97" s="6"/>
       <c r="E97" s="1"/>
       <c r="BO97" s="7"/>
       <c r="BR97" s="7"/>
     </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D98" s="6"/>
       <c r="E98" s="1"/>
       <c r="BO98" s="7"/>
       <c r="BR98" s="7"/>
     </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D99" s="6"/>
       <c r="E99" s="1"/>
       <c r="BO99" s="7"/>
       <c r="BR99" s="7"/>
     </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D100" s="6"/>
       <c r="E100" s="1"/>
       <c r="BO100" s="7"/>
       <c r="BR100" s="7"/>
     </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D101" s="6"/>
       <c r="E101" s="1"/>
       <c r="BO101" s="7"/>
       <c r="BR101" s="7"/>
     </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D102" s="6"/>
       <c r="E102" s="1"/>
       <c r="BO102" s="7"/>
       <c r="BR102" s="7"/>
     </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D103" s="6"/>
       <c r="E103" s="1"/>
       <c r="BO103" s="7"/>
       <c r="BR103" s="7"/>
     </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D104" s="6"/>
       <c r="E104" s="1"/>
       <c r="BO104" s="7"/>
       <c r="BR104" s="7"/>
     </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D105" s="6"/>
       <c r="E105" s="1"/>
       <c r="BO105" s="7"/>
       <c r="BR105" s="7"/>
     </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D106" s="6"/>
       <c r="E106" s="1"/>
       <c r="BO106" s="7"/>
       <c r="BR106" s="7"/>
     </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D107" s="6"/>
       <c r="E107" s="1"/>
       <c r="BO107" s="7"/>
       <c r="BR107" s="7"/>
     </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D108" s="6"/>
       <c r="E108" s="1"/>
       <c r="BO108" s="7"/>
       <c r="BR108" s="7"/>
     </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="1"/>
       <c r="BO109" s="7"/>
       <c r="BR109" s="7"/>
     </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="1"/>
       <c r="BO110" s="7"/>
       <c r="BR110" s="7"/>
     </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="1"/>
       <c r="BO111" s="7"/>
       <c r="BR111" s="7"/>
     </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="1"/>
       <c r="BO112" s="7"/>
       <c r="BR112" s="7"/>
     </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
       <c r="E113" s="1"/>
       <c r="BO113" s="7"/>
       <c r="BR113" s="7"/>
     </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="1"/>
       <c r="BO114" s="7"/>
       <c r="BR114" s="7"/>
     </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D115" s="6"/>
       <c r="E115" s="1"/>
       <c r="BO115" s="7"/>
       <c r="BR115" s="7"/>
     </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D116" s="6"/>
       <c r="E116" s="1"/>
       <c r="BO116" s="7"/>
       <c r="BR116" s="7"/>
     </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D117" s="6"/>
       <c r="E117" s="1"/>
       <c r="BO117" s="7"/>
       <c r="BR117" s="7"/>
     </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D118" s="6"/>
       <c r="E118" s="1"/>
       <c r="BO118" s="7"/>
       <c r="BR118" s="7"/>
     </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D119" s="6"/>
       <c r="E119" s="1"/>
       <c r="BO119" s="7"/>
       <c r="BR119" s="7"/>
     </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D120" s="6"/>
       <c r="E120" s="1"/>
       <c r="BO120" s="7"/>
       <c r="BR120" s="7"/>
     </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D121" s="6"/>
       <c r="E121" s="1"/>
       <c r="BO121" s="7"/>
       <c r="BR121" s="7"/>
     </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D122" s="6"/>
       <c r="E122" s="1"/>
       <c r="BO122" s="7"/>
       <c r="BR122" s="7"/>
     </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D123" s="6"/>
       <c r="E123" s="1"/>
       <c r="BO123" s="7"/>
       <c r="BR123" s="7"/>
     </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D124" s="6"/>
       <c r="E124" s="1"/>
       <c r="BO124" s="7"/>
       <c r="BR124" s="7"/>
     </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D125" s="6"/>
       <c r="E125" s="1"/>
       <c r="BO125" s="7"/>
       <c r="BR125" s="7"/>
     </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D126" s="6"/>
       <c r="E126" s="1"/>
       <c r="BO126" s="7"/>
       <c r="BR126" s="7"/>
     </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D127" s="6"/>
       <c r="E127" s="1"/>
       <c r="BO127" s="7"/>
       <c r="BR127" s="7"/>
     </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D128" s="6"/>
       <c r="E128" s="1"/>
       <c r="BO128" s="7"/>
       <c r="BR128" s="7"/>
     </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D129" s="6"/>
       <c r="E129" s="1"/>
       <c r="BO129" s="7"/>
       <c r="BR129" s="7"/>
     </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D130" s="6"/>
       <c r="E130" s="1"/>
       <c r="BO130" s="7"/>
       <c r="BR130" s="7"/>
     </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D131" s="6"/>
       <c r="E131" s="1"/>
       <c r="BO131" s="7"/>
       <c r="BR131" s="7"/>
     </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D132" s="6"/>
       <c r="E132" s="1"/>
       <c r="BO132" s="7"/>
       <c r="BR132" s="7"/>
     </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D133" s="6"/>
       <c r="E133" s="1"/>
       <c r="BO133" s="7"/>
       <c r="BR133" s="7"/>
     </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D134" s="6"/>
       <c r="E134" s="1"/>
       <c r="BO134" s="7"/>
       <c r="BR134" s="7"/>
     </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D135" s="6"/>
       <c r="E135" s="1"/>
       <c r="BO135" s="7"/>
       <c r="BR135" s="7"/>
     </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D136" s="6"/>
       <c r="E136" s="1"/>
       <c r="BO136" s="7"/>
       <c r="BR136" s="7"/>
     </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D137" s="6"/>
       <c r="E137" s="1"/>
       <c r="BO137" s="7"/>
       <c r="BR137" s="7"/>
     </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D138" s="6"/>
       <c r="E138" s="1"/>
       <c r="BO138" s="7"/>
       <c r="BR138" s="7"/>
     </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D139" s="6"/>
       <c r="E139" s="1"/>
       <c r="BO139" s="7"/>
       <c r="BR139" s="7"/>
     </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D140" s="6"/>
       <c r="E140" s="1"/>
       <c r="BO140" s="7"/>
       <c r="BR140" s="7"/>
     </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D141" s="6"/>
       <c r="E141" s="1"/>
       <c r="BO141" s="7"/>
       <c r="BR141" s="7"/>
     </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D142" s="6"/>
       <c r="E142" s="1"/>
       <c r="BO142" s="7"/>
       <c r="BR142" s="7"/>
     </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D143" s="6"/>
       <c r="E143" s="1"/>
       <c r="BO143" s="7"/>
       <c r="BR143" s="7"/>
     </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D144" s="6"/>
       <c r="E144" s="1"/>
       <c r="BO144" s="7"/>
       <c r="BR144" s="7"/>
     </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D145" s="6"/>
       <c r="E145" s="1"/>
       <c r="BO145" s="7"/>
       <c r="BR145" s="7"/>
     </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D146" s="6"/>
       <c r="E146" s="1"/>
       <c r="BO146" s="7"/>
       <c r="BR146" s="7"/>
     </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D147" s="6"/>
       <c r="E147" s="1"/>
       <c r="BO147" s="7"/>
       <c r="BR147" s="7"/>
     </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D148" s="6"/>
       <c r="E148" s="1"/>
       <c r="BO148" s="7"/>
       <c r="BR148" s="7"/>
     </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D149" s="6"/>
       <c r="E149" s="1"/>
       <c r="BO149" s="7"/>
       <c r="BR149" s="7"/>
     </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D150" s="6"/>
       <c r="E150" s="1"/>
       <c r="BO150" s="7"/>
       <c r="BR150" s="7"/>
     </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D151" s="6"/>
       <c r="E151" s="1"/>
       <c r="BO151" s="7"/>
       <c r="BR151" s="7"/>
     </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D152" s="6"/>
       <c r="E152" s="1"/>
       <c r="BO152" s="7"/>
       <c r="BR152" s="7"/>
     </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D153" s="6"/>
       <c r="E153" s="1"/>
       <c r="BO153" s="7"/>
       <c r="BR153" s="7"/>
     </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D154" s="6"/>
       <c r="E154" s="1"/>
       <c r="BO154" s="7"/>
       <c r="BR154" s="7"/>
     </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D155" s="6"/>
       <c r="E155" s="1"/>
       <c r="BO155" s="7"/>
       <c r="BR155" s="7"/>
     </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D156" s="6"/>
       <c r="E156" s="1"/>
       <c r="BO156" s="7"/>
       <c r="BR156" s="7"/>
     </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D157" s="6"/>
       <c r="E157" s="1"/>
       <c r="BO157" s="7"/>
       <c r="BR157" s="7"/>
     </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D158" s="6"/>
       <c r="E158" s="1"/>
       <c r="BO158" s="7"/>
       <c r="BR158" s="7"/>
     </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D159" s="6"/>
       <c r="E159" s="1"/>
       <c r="BO159" s="7"/>
       <c r="BR159" s="7"/>
     </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D160" s="6"/>
       <c r="E160" s="1"/>
       <c r="BO160" s="7"/>
       <c r="BR160" s="7"/>
     </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D161" s="6"/>
       <c r="E161" s="1"/>
       <c r="BO161" s="7"/>
       <c r="BR161" s="7"/>
     </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D162" s="6"/>
       <c r="E162" s="1"/>
       <c r="BO162" s="7"/>
       <c r="BR162" s="7"/>
     </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D163" s="6"/>
       <c r="E163" s="1"/>
       <c r="BO163" s="7"/>
       <c r="BR163" s="7"/>
     </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D164" s="6"/>
       <c r="E164" s="1"/>
       <c r="BO164" s="7"/>
       <c r="BR164" s="7"/>
     </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D165" s="6"/>
       <c r="E165" s="1"/>
       <c r="BO165" s="7"/>
       <c r="BR165" s="7"/>
     </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D166" s="6"/>
       <c r="E166" s="1"/>
       <c r="BO166" s="7"/>
       <c r="BR166" s="7"/>
     </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D167" s="6"/>
       <c r="E167" s="1"/>
       <c r="BO167" s="7"/>
       <c r="BR167" s="7"/>
     </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D168" s="6"/>
       <c r="E168" s="1"/>
       <c r="BO168" s="7"/>
       <c r="BR168" s="7"/>
     </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D169" s="6"/>
       <c r="E169" s="1"/>
       <c r="BO169" s="7"/>
       <c r="BR169" s="7"/>
     </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D170" s="6"/>
       <c r="E170" s="1"/>
       <c r="BO170" s="7"/>
       <c r="BR170" s="7"/>
     </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D171" s="6"/>
       <c r="E171" s="1"/>
       <c r="BO171" s="7"/>
       <c r="BR171" s="7"/>
     </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D172" s="6"/>
       <c r="E172" s="1"/>
       <c r="BO172" s="7"/>
       <c r="BR172" s="7"/>
     </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D173" s="6"/>
       <c r="E173" s="1"/>
       <c r="BO173" s="7"/>
       <c r="BR173" s="7"/>
     </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D174" s="6"/>
       <c r="E174" s="1"/>
       <c r="BO174" s="7"/>
       <c r="BR174" s="7"/>
     </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D175" s="6"/>
       <c r="E175" s="1"/>
       <c r="BO175" s="7"/>
       <c r="BR175" s="7"/>
     </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D176" s="6"/>
       <c r="E176" s="1"/>
       <c r="BO176" s="7"/>
       <c r="BR176" s="7"/>
     </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D177" s="6"/>
       <c r="E177" s="1"/>
       <c r="BO177" s="7"/>
       <c r="BR177" s="7"/>
     </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D178" s="6"/>
       <c r="E178" s="1"/>
       <c r="BO178" s="7"/>
       <c r="BR178" s="7"/>
     </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D179" s="6"/>
       <c r="E179" s="1"/>
       <c r="BO179" s="7"/>
       <c r="BR179" s="7"/>
     </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D180" s="6"/>
       <c r="E180" s="1"/>
       <c r="BO180" s="7"/>
       <c r="BR180" s="7"/>
     </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D181" s="6"/>
       <c r="E181" s="1"/>
       <c r="BO181" s="7"/>
       <c r="BR181" s="7"/>
     </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D182" s="6"/>
       <c r="E182" s="1"/>
       <c r="BO182" s="7"/>
       <c r="BR182" s="7"/>
     </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D183" s="6"/>
       <c r="E183" s="1"/>
       <c r="BO183" s="7"/>
       <c r="BR183" s="7"/>
     </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D184" s="6"/>
       <c r="E184" s="1"/>
       <c r="BO184" s="7"/>
       <c r="BR184" s="7"/>
     </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D185" s="6"/>
       <c r="E185" s="1"/>
       <c r="BO185" s="7"/>
       <c r="BR185" s="7"/>
     </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D186" s="6"/>
       <c r="E186" s="1"/>
       <c r="BO186" s="7"/>
       <c r="BR186" s="7"/>
     </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D187" s="6"/>
       <c r="E187" s="1"/>
       <c r="BO187" s="7"/>
       <c r="BR187" s="7"/>
     </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D188" s="6"/>
       <c r="E188" s="1"/>
       <c r="BO188" s="7"/>
       <c r="BR188" s="7"/>
     </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D189" s="6"/>
       <c r="E189" s="1"/>
       <c r="BO189" s="7"/>
       <c r="BR189" s="7"/>
     </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D190" s="6"/>
       <c r="E190" s="1"/>
       <c r="BO190" s="7"/>
       <c r="BR190" s="7"/>
     </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D191" s="6"/>
       <c r="E191" s="1"/>
       <c r="BO191" s="7"/>
       <c r="BR191" s="7"/>
     </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D192" s="6"/>
       <c r="E192" s="1"/>
       <c r="BO192" s="7"/>
       <c r="BR192" s="7"/>
     </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D193" s="6"/>
       <c r="E193" s="1"/>
       <c r="BO193" s="7"/>
       <c r="BR193" s="7"/>
     </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D194" s="6"/>
       <c r="E194" s="1"/>
       <c r="BO194" s="7"/>
       <c r="BR194" s="7"/>
     </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D195" s="6"/>
       <c r="E195" s="1"/>
       <c r="BO195" s="7"/>
       <c r="BR195" s="7"/>
     </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D196" s="6"/>
       <c r="E196" s="1"/>
       <c r="BO196" s="7"/>
       <c r="BR196" s="7"/>
     </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D197" s="6"/>
       <c r="E197" s="1"/>
       <c r="BO197" s="7"/>
       <c r="BR197" s="7"/>
     </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D198" s="6"/>
       <c r="E198" s="1"/>
       <c r="BO198" s="7"/>
       <c r="BR198" s="7"/>
     </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D199" s="6"/>
       <c r="E199" s="1"/>
       <c r="BO199" s="7"/>
       <c r="BR199" s="7"/>
     </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D200" s="6"/>
       <c r="E200" s="1"/>
       <c r="BO200" s="7"/>
       <c r="BR200" s="7"/>
     </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D201" s="6"/>
       <c r="E201" s="1"/>
       <c r="BO201" s="7"/>
       <c r="BR201" s="7"/>
     </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D202" s="6"/>
       <c r="E202" s="1"/>
       <c r="BO202" s="7"/>
       <c r="BR202" s="7"/>
     </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D203" s="6"/>
       <c r="E203" s="1"/>
       <c r="BO203" s="7"/>
       <c r="BR203" s="7"/>
     </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D204" s="6"/>
       <c r="E204" s="1"/>
       <c r="BO204" s="7"/>
       <c r="BR204" s="7"/>
     </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D205" s="6"/>
       <c r="E205" s="1"/>
       <c r="BO205" s="7"/>
       <c r="BR205" s="7"/>
     </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D206" s="6"/>
       <c r="E206" s="1"/>
       <c r="BO206" s="7"/>
       <c r="BR206" s="7"/>
     </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D207" s="6"/>
       <c r="E207" s="1"/>
       <c r="BO207" s="7"/>
       <c r="BR207" s="7"/>
     </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D208" s="6"/>
       <c r="E208" s="1"/>
       <c r="BO208" s="7"/>
       <c r="BR208" s="7"/>
     </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D209" s="6"/>
       <c r="E209" s="1"/>
       <c r="BO209" s="7"/>
       <c r="BR209" s="7"/>
     </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D210" s="6"/>
       <c r="E210" s="1"/>
       <c r="BO210" s="7"/>
       <c r="BR210" s="7"/>
     </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D211" s="6"/>
       <c r="E211" s="1"/>
       <c r="BO211" s="7"/>
       <c r="BR211" s="7"/>
     </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D212" s="6"/>
       <c r="E212" s="1"/>
       <c r="BO212" s="7"/>
       <c r="BR212" s="7"/>
     </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D213" s="6"/>
       <c r="E213" s="1"/>
       <c r="BO213" s="7"/>
       <c r="BR213" s="7"/>
     </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D214" s="6"/>
       <c r="E214" s="1"/>
       <c r="BO214" s="7"/>
       <c r="BR214" s="7"/>
     </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D215" s="6"/>
       <c r="E215" s="1"/>
       <c r="BO215" s="7"/>
       <c r="BR215" s="7"/>
     </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D216" s="6"/>
       <c r="E216" s="1"/>
       <c r="BO216" s="7"/>
       <c r="BR216" s="7"/>
     </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D217" s="6"/>
       <c r="E217" s="1"/>
       <c r="BO217" s="7"/>
       <c r="BR217" s="7"/>
     </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D218" s="6"/>
       <c r="E218" s="1"/>
       <c r="BO218" s="7"/>
       <c r="BR218" s="7"/>
     </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D219" s="6"/>
       <c r="E219" s="1"/>
       <c r="BO219" s="7"/>
       <c r="BR219" s="7"/>
     </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D220" s="6"/>
       <c r="E220" s="1"/>
       <c r="BO220" s="7"/>
       <c r="BR220" s="7"/>
     </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D221" s="6"/>
       <c r="E221" s="1"/>
       <c r="BO221" s="7"/>
       <c r="BR221" s="7"/>
     </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D222" s="6"/>
       <c r="E222" s="1"/>
       <c r="BO222" s="7"/>
       <c r="BR222" s="7"/>
     </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D223" s="6"/>
       <c r="E223" s="1"/>
       <c r="BO223" s="7"/>
       <c r="BR223" s="7"/>
     </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D224" s="6"/>
       <c r="E224" s="1"/>
       <c r="BO224" s="7"/>
       <c r="BR224" s="7"/>
     </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D225" s="6"/>
       <c r="E225" s="1"/>
       <c r="BO225" s="7"/>
       <c r="BR225" s="7"/>
     </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D226" s="6"/>
       <c r="E226" s="1"/>
       <c r="BO226" s="7"/>
       <c r="BR226" s="7"/>
     </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D227" s="6"/>
       <c r="E227" s="1"/>
       <c r="BO227" s="7"/>
       <c r="BR227" s="7"/>
     </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D228" s="6"/>
       <c r="E228" s="1"/>
       <c r="BO228" s="7"/>
       <c r="BR228" s="7"/>
     </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D229" s="6"/>
       <c r="E229" s="1"/>
       <c r="BO229" s="7"/>
       <c r="BR229" s="7"/>
     </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D230" s="6"/>
       <c r="E230" s="1"/>
       <c r="BO230" s="7"/>
       <c r="BR230" s="7"/>
     </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D231" s="6"/>
       <c r="E231" s="1"/>
       <c r="BO231" s="7"/>
       <c r="BR231" s="7"/>
     </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D232" s="6"/>
       <c r="E232" s="1"/>
       <c r="BO232" s="7"/>
       <c r="BR232" s="7"/>
     </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D233" s="6"/>
       <c r="E233" s="1"/>
       <c r="BO233" s="7"/>
       <c r="BR233" s="7"/>
     </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D234" s="6"/>
       <c r="E234" s="1"/>
       <c r="BO234" s="7"/>
       <c r="BR234" s="7"/>
     </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D235" s="6"/>
       <c r="E235" s="1"/>
       <c r="BO235" s="7"/>
       <c r="BR235" s="7"/>
     </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D236" s="6"/>
       <c r="E236" s="1"/>
       <c r="BO236" s="7"/>
       <c r="BR236" s="7"/>
     </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D237" s="6"/>
       <c r="E237" s="1"/>
       <c r="BO237" s="7"/>
       <c r="BR237" s="7"/>
     </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D238" s="6"/>
       <c r="E238" s="1"/>
       <c r="BO238" s="7"/>
       <c r="BR238" s="7"/>
     </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D239" s="6"/>
       <c r="E239" s="1"/>
       <c r="BO239" s="7"/>
       <c r="BR239" s="7"/>
     </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D240" s="6"/>
       <c r="E240" s="1"/>
       <c r="BO240" s="7"/>
       <c r="BR240" s="7"/>
     </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D241" s="6"/>
       <c r="E241" s="1"/>
       <c r="BO241" s="7"/>
       <c r="BR241" s="7"/>
     </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D242" s="6"/>
       <c r="E242" s="1"/>
       <c r="BO242" s="7"/>
       <c r="BR242" s="7"/>
     </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D243" s="6"/>
       <c r="E243" s="1"/>
       <c r="BR243" s="7"/>
     </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D244" s="6"/>
       <c r="E244" s="1"/>
       <c r="BO244" s="7"/>
       <c r="BR244" s="7"/>
     </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D245" s="6"/>
       <c r="E245" s="1"/>
       <c r="BO245" s="7"/>
       <c r="BR245" s="7"/>
     </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D246" s="6"/>
       <c r="E246" s="1"/>
       <c r="BO246" s="7"/>
       <c r="BR246" s="7"/>
     </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D247" s="6"/>
       <c r="E247" s="1"/>
       <c r="BO247" s="7"/>
       <c r="BR247" s="7"/>
     </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D248" s="6"/>
       <c r="E248" s="1"/>
       <c r="BO248" s="7"/>
       <c r="BR248" s="7"/>
     </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D249" s="6"/>
       <c r="E249" s="1"/>
       <c r="BO249" s="7"/>
       <c r="BR249" s="7"/>
     </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D250" s="6"/>
       <c r="E250" s="1"/>
       <c r="BO250" s="7"/>
       <c r="BR250" s="7"/>
     </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D251" s="6"/>
       <c r="E251" s="1"/>
       <c r="BO251" s="7"/>
       <c r="BR251" s="7"/>
     </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D252" s="6"/>
       <c r="E252" s="1"/>
       <c r="BO252" s="7"/>
       <c r="BR252" s="7"/>
     </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D253" s="6"/>
       <c r="E253" s="1"/>
       <c r="BO253" s="7"/>
       <c r="BR253" s="7"/>
     </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D254" s="6"/>
       <c r="E254" s="1"/>
       <c r="BO254" s="7"/>
       <c r="BR254" s="7"/>
     </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D255" s="6"/>
       <c r="E255" s="1"/>
       <c r="BO255" s="7"/>
       <c r="BR255" s="7"/>
     </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D256" s="6"/>
       <c r="E256" s="1"/>
       <c r="BO256" s="7"/>
       <c r="BR256" s="7"/>
     </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D257" s="6"/>
       <c r="E257" s="1"/>
       <c r="BO257" s="7"/>
       <c r="BR257" s="7"/>
     </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D258" s="6"/>
       <c r="E258" s="1"/>
       <c r="BO258" s="7"/>
       <c r="BR258" s="7"/>
     </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D259" s="6"/>
       <c r="E259" s="1"/>
       <c r="BO259" s="7"/>
       <c r="BR259" s="7"/>
     </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D260" s="6"/>
       <c r="E260" s="1"/>
       <c r="BO260" s="7"/>
       <c r="BR260" s="7"/>
     </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D261" s="6"/>
       <c r="E261" s="1"/>
       <c r="BO261" s="7"/>
       <c r="BR261" s="7"/>
     </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D262" s="6"/>
       <c r="E262" s="1"/>
       <c r="BO262" s="7"/>
       <c r="BR262" s="7"/>
     </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D263" s="6"/>
       <c r="E263" s="1"/>
       <c r="BO263" s="7"/>
       <c r="BR263" s="7"/>
     </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D264" s="6"/>
       <c r="E264" s="1"/>
       <c r="BO264" s="7"/>
       <c r="BR264" s="7"/>
     </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D265" s="6"/>
       <c r="E265" s="1"/>
       <c r="BO265" s="7"/>
       <c r="BR265" s="7"/>
     </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D266" s="6"/>
       <c r="E266" s="1"/>
       <c r="BO266" s="7"/>
       <c r="BR266" s="7"/>
     </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D267" s="6"/>
       <c r="E267" s="1"/>
       <c r="BO267" s="7"/>
       <c r="BR267" s="7"/>
     </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D268" s="6"/>
       <c r="E268" s="1"/>
       <c r="BO268" s="7"/>
       <c r="BR268" s="7"/>
     </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D269" s="6"/>
       <c r="E269" s="1"/>
       <c r="BO269" s="7"/>
       <c r="BR269" s="7"/>
     </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D270" s="6"/>
       <c r="E270" s="1"/>
       <c r="BO270" s="7"/>
       <c r="BR270" s="7"/>
     </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D271" s="6"/>
       <c r="E271" s="1"/>
       <c r="BO271" s="7"/>
       <c r="BR271" s="7"/>
     </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D272" s="6"/>
       <c r="E272" s="1"/>
       <c r="BO272" s="7"/>
       <c r="BR272" s="7"/>
     </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D273" s="6"/>
       <c r="E273" s="1"/>
       <c r="BO273" s="7"/>
       <c r="BR273" s="7"/>
     </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D274" s="6"/>
       <c r="E274" s="1"/>
       <c r="BO274" s="7"/>
       <c r="BR274" s="7"/>
     </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D275" s="6"/>
       <c r="E275" s="1"/>
       <c r="BO275" s="7"/>
       <c r="BR275" s="7"/>
     </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D276" s="6"/>
       <c r="E276" s="1"/>
       <c r="BO276" s="7"/>
       <c r="BR276" s="7"/>
     </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D277" s="6"/>
       <c r="E277" s="1"/>
       <c r="BO277" s="7"/>
       <c r="BR277" s="7"/>
     </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D278" s="6"/>
       <c r="E278" s="1"/>
       <c r="BO278" s="7"/>
       <c r="BR278" s="7"/>
     </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D279" s="6"/>
       <c r="E279" s="1"/>
       <c r="BO279" s="7"/>
       <c r="BR279" s="7"/>
     </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D280" s="6"/>
       <c r="E280" s="1"/>
       <c r="BO280" s="7"/>
       <c r="BR280" s="7"/>
     </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D281" s="6"/>
       <c r="E281" s="1"/>
       <c r="BO281" s="7"/>
       <c r="BR281" s="7"/>
     </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D282" s="6"/>
       <c r="E282" s="1"/>
       <c r="BO282" s="7"/>
       <c r="BR282" s="7"/>
     </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D283" s="6"/>
       <c r="E283" s="1"/>
       <c r="BO283" s="7"/>
       <c r="BR283" s="7"/>
     </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D284" s="6"/>
       <c r="E284" s="1"/>
       <c r="BO284" s="7"/>
       <c r="BR284" s="7"/>
     </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D285" s="6"/>
       <c r="E285" s="1"/>
       <c r="BO285" s="7"/>
       <c r="BR285" s="7"/>
     </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D286" s="6"/>
       <c r="E286" s="1"/>
       <c r="BR286" s="7"/>
     </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D287" s="6"/>
       <c r="E287" s="1"/>
       <c r="BO287" s="7"/>
       <c r="BR287" s="7"/>
     </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D288" s="6"/>
       <c r="E288" s="1"/>
       <c r="BO288" s="7"/>
       <c r="BR288" s="7"/>
     </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D289" s="6"/>
       <c r="E289" s="1"/>
       <c r="BO289" s="7"/>
       <c r="BR289" s="7"/>
     </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D290" s="6"/>
       <c r="E290" s="1"/>
       <c r="BO290" s="7"/>
       <c r="BR290" s="7"/>
     </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D291" s="6"/>
       <c r="E291" s="1"/>
       <c r="BO291" s="7"/>
       <c r="BR291" s="7"/>
     </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D292" s="6"/>
       <c r="E292" s="1"/>
       <c r="BO292" s="7"/>
       <c r="BR292" s="7"/>
     </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D293" s="6"/>
       <c r="E293" s="1"/>
       <c r="BO293" s="7"/>
       <c r="BR293" s="7"/>
     </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D294" s="6"/>
       <c r="E294" s="1"/>
       <c r="BO294" s="7"/>
       <c r="BR294" s="7"/>
     </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D295" s="6"/>
       <c r="E295" s="1"/>
       <c r="BO295" s="7"/>
       <c r="BR295" s="7"/>
     </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D296" s="6"/>
       <c r="E296" s="1"/>
       <c r="BO296" s="7"/>
       <c r="BR296" s="7"/>
     </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D297" s="6"/>
       <c r="E297" s="1"/>
       <c r="BO297" s="7"/>
       <c r="BR297" s="7"/>
     </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D298" s="6"/>
       <c r="E298" s="1"/>
       <c r="BO298" s="7"/>
       <c r="BR298" s="7"/>
     </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D299" s="6"/>
       <c r="E299" s="1"/>
       <c r="BO299" s="7"/>
       <c r="BR299" s="7"/>
     </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D300" s="6"/>
       <c r="E300" s="1"/>
       <c r="BO300" s="7"/>
       <c r="BR300" s="7"/>
     </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D301" s="6"/>
       <c r="E301" s="1"/>
       <c r="BO301" s="7"/>
       <c r="BR301" s="7"/>
     </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D302" s="6"/>
       <c r="E302" s="1"/>
       <c r="BO302" s="7"/>
       <c r="BR302" s="7"/>
     </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D303" s="6"/>
       <c r="E303" s="1"/>
       <c r="BO303" s="7"/>
       <c r="BR303" s="7"/>
     </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D304" s="6"/>
       <c r="E304" s="1"/>
       <c r="BO304" s="7"/>
       <c r="BR304" s="7"/>
     </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D305" s="6"/>
       <c r="E305" s="1"/>
       <c r="BO305" s="7"/>
       <c r="BR305" s="7"/>
     </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D306" s="6"/>
       <c r="E306" s="1"/>
       <c r="BO306" s="7"/>
       <c r="BR306" s="7"/>
     </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D307" s="6"/>
       <c r="E307" s="1"/>
       <c r="BO307" s="7"/>
       <c r="BR307" s="7"/>
     </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D308" s="6"/>
       <c r="E308" s="1"/>
       <c r="BO308" s="7"/>
       <c r="BR308" s="7"/>
     </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D309" s="6"/>
       <c r="E309" s="1"/>
       <c r="BO309" s="7"/>
       <c r="BR309" s="7"/>
     </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D310" s="6"/>
       <c r="E310" s="1"/>
       <c r="BO310" s="7"/>
       <c r="BR310" s="7"/>
     </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D311" s="6"/>
       <c r="E311" s="1"/>
       <c r="BO311" s="7"/>
       <c r="BR311" s="7"/>
     </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D312" s="6"/>
       <c r="E312" s="1"/>
       <c r="BO312" s="7"/>
       <c r="BR312" s="7"/>
     </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D313" s="6"/>
       <c r="E313" s="1"/>
       <c r="BO313" s="7"/>
       <c r="BR313" s="7"/>
     </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D314" s="6"/>
       <c r="E314" s="1"/>
       <c r="BO314" s="7"/>
       <c r="BR314" s="7"/>
     </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D315" s="6"/>
       <c r="E315" s="1"/>
       <c r="BO315" s="7"/>
       <c r="BR315" s="7"/>
     </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D316" s="6"/>
       <c r="E316" s="1"/>
       <c r="BO316" s="7"/>
       <c r="BR316" s="7"/>
     </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D317" s="6"/>
       <c r="E317" s="1"/>
       <c r="BO317" s="7"/>
       <c r="BR317" s="7"/>
     </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D318" s="6"/>
       <c r="E318" s="1"/>
       <c r="BO318" s="7"/>
       <c r="BR318" s="7"/>
     </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D319" s="6"/>
       <c r="E319" s="1"/>
       <c r="BO319" s="7"/>
       <c r="BR319" s="7"/>
     </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D320" s="6"/>
       <c r="E320" s="1"/>
       <c r="BO320" s="7"/>
       <c r="BR320" s="7"/>
     </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D321" s="6"/>
       <c r="E321" s="1"/>
       <c r="BO321" s="7"/>
       <c r="BR321" s="7"/>
     </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D322" s="6"/>
       <c r="E322" s="1"/>
       <c r="BO322" s="7"/>
       <c r="BR322" s="7"/>
     </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D323" s="6"/>
       <c r="E323" s="1"/>
       <c r="BO323" s="7"/>
       <c r="BR323" s="7"/>
     </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D324" s="6"/>
       <c r="E324" s="1"/>
       <c r="BO324" s="7"/>
       <c r="BR324" s="7"/>
     </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D325" s="6"/>
       <c r="E325" s="1"/>
       <c r="BO325" s="7"/>
       <c r="BR325" s="7"/>
     </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D326" s="6"/>
       <c r="E326" s="1"/>
       <c r="BO326" s="7"/>
       <c r="BR326" s="7"/>
     </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D327" s="6"/>
       <c r="E327" s="1"/>
       <c r="BO327" s="7"/>
       <c r="BR327" s="7"/>
     </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D328" s="6"/>
       <c r="E328" s="1"/>
       <c r="BO328" s="7"/>
       <c r="BR328" s="7"/>
     </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D329" s="6"/>
       <c r="E329" s="1"/>
       <c r="BO329" s="7"/>
       <c r="BR329" s="7"/>
     </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D330" s="6"/>
       <c r="E330" s="1"/>
       <c r="BO330" s="7"/>
       <c r="BR330" s="7"/>
     </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D331" s="6"/>
       <c r="E331" s="1"/>
       <c r="BO331" s="7"/>
       <c r="BR331" s="7"/>
     </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D332" s="6"/>
       <c r="E332" s="1"/>
       <c r="BO332" s="7"/>
       <c r="BR332" s="7"/>
     </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D333" s="6"/>
       <c r="E333" s="1"/>
       <c r="BO333" s="7"/>
       <c r="BR333" s="7"/>
     </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D334" s="6"/>
       <c r="E334" s="1"/>
       <c r="BO334" s="7"/>
       <c r="BR334" s="7"/>
     </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D335" s="6"/>
       <c r="E335" s="1"/>
       <c r="BO335" s="7"/>
       <c r="BR335" s="7"/>
     </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D336" s="6"/>
       <c r="E336" s="1"/>
       <c r="BO336" s="7"/>
       <c r="BR336" s="7"/>
     </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D337" s="6"/>
       <c r="E337" s="1"/>
       <c r="BO337" s="7"/>
       <c r="BR337" s="7"/>
     </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D338" s="6"/>
       <c r="E338" s="1"/>
       <c r="BO338" s="7"/>
       <c r="BR338" s="7"/>
     </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D339" s="6"/>
       <c r="E339" s="1"/>
       <c r="BO339" s="7"/>
       <c r="BR339" s="7"/>
     </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D340" s="6"/>
       <c r="E340" s="1"/>
       <c r="BO340" s="7"/>
       <c r="BR340" s="7"/>
     </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D341" s="6"/>
       <c r="E341" s="1"/>
       <c r="BO341" s="7"/>
       <c r="BR341" s="7"/>
     </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D342" s="6"/>
       <c r="E342" s="1"/>
       <c r="BR342" s="7"/>
     </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D343" s="6"/>
       <c r="E343" s="1"/>
       <c r="BR343" s="7"/>
     </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D344" s="6"/>
       <c r="E344" s="1"/>
       <c r="BR344" s="7"/>
     </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D345" s="6"/>
       <c r="E345" s="1"/>
       <c r="BO345" s="7"/>
       <c r="BR345" s="7"/>
     </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D346" s="6"/>
       <c r="E346" s="1"/>
       <c r="BO346" s="7"/>
       <c r="BR346" s="7"/>
     </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D347" s="6"/>
       <c r="E347" s="1"/>
       <c r="BO347" s="7"/>
       <c r="BR347" s="7"/>
     </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D348" s="6"/>
       <c r="E348" s="1"/>
       <c r="BO348" s="7"/>
       <c r="BR348" s="7"/>
     </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D349" s="6"/>
       <c r="E349" s="1"/>
       <c r="BO349" s="7"/>
       <c r="BR349" s="7"/>
     </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D350" s="6"/>
       <c r="E350" s="1"/>
       <c r="BO350" s="7"/>
       <c r="BR350" s="7"/>
     </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D351" s="6"/>
       <c r="E351" s="1"/>
       <c r="BO351" s="7"/>
       <c r="BR351" s="7"/>
     </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D352" s="6"/>
       <c r="E352" s="1"/>
       <c r="BO352" s="7"/>
       <c r="BR352" s="7"/>
     </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D353" s="6"/>
       <c r="E353" s="1"/>
       <c r="BO353" s="7"/>
       <c r="BR353" s="7"/>
     </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D354" s="6"/>
       <c r="E354" s="1"/>
       <c r="BO354" s="7"/>
       <c r="BR354" s="7"/>
     </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D355" s="6"/>
       <c r="E355" s="1"/>
       <c r="BO355" s="7"/>
       <c r="BR355" s="7"/>
     </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D356" s="6"/>
       <c r="E356" s="1"/>
       <c r="BO356" s="7"/>
       <c r="BR356" s="7"/>
     </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D357" s="6"/>
       <c r="E357" s="1"/>
       <c r="BO357" s="7"/>
       <c r="BR357" s="7"/>
     </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D358" s="6"/>
       <c r="E358" s="1"/>
       <c r="BO358" s="7"/>
       <c r="BR358" s="7"/>
     </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D359" s="6"/>
       <c r="E359" s="1"/>
       <c r="BO359" s="7"/>
       <c r="BR359" s="7"/>
     </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D360" s="6"/>
       <c r="E360" s="1"/>
       <c r="BO360" s="7"/>
       <c r="BR360" s="7"/>
     </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D361" s="6"/>
       <c r="E361" s="1"/>
       <c r="BO361" s="7"/>
       <c r="BR361" s="7"/>
     </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D362" s="6"/>
       <c r="E362" s="1"/>
       <c r="BO362" s="7"/>
       <c r="BR362" s="7"/>
     </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D363" s="6"/>
       <c r="E363" s="1"/>
       <c r="BO363" s="7"/>
       <c r="BR363" s="7"/>
     </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D364" s="6"/>
       <c r="E364" s="1"/>
       <c r="BO364" s="7"/>
       <c r="BR364" s="7"/>
     </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D365" s="6"/>
       <c r="E365" s="1"/>
       <c r="BO365" s="7"/>
       <c r="BR365" s="7"/>
     </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D366" s="6"/>
       <c r="E366" s="1"/>
       <c r="BO366" s="7"/>
       <c r="BR366" s="7"/>
     </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D367" s="6"/>
       <c r="E367" s="1"/>
       <c r="BO367" s="7"/>
       <c r="BR367" s="7"/>
     </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D368" s="6"/>
       <c r="E368" s="1"/>
       <c r="BO368" s="7"/>
       <c r="BR368" s="7"/>
     </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D369" s="6"/>
       <c r="E369" s="1"/>
       <c r="BO369" s="7"/>
       <c r="BR369" s="7"/>
     </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D370" s="6"/>
       <c r="E370" s="1"/>
       <c r="BO370" s="7"/>
       <c r="BR370" s="7"/>
     </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D371" s="6"/>
       <c r="E371" s="1"/>
       <c r="BO371" s="7"/>
       <c r="BR371" s="7"/>
     </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D372" s="6"/>
       <c r="E372" s="1"/>
       <c r="BO372" s="7"/>
       <c r="BR372" s="7"/>
     </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D373" s="6"/>
       <c r="E373" s="1"/>
       <c r="BO373" s="7"/>
       <c r="BR373" s="7"/>
     </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D374" s="6"/>
       <c r="E374" s="1"/>
       <c r="BO374" s="7"/>
       <c r="BR374" s="7"/>
     </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D375" s="6"/>
       <c r="E375" s="1"/>
       <c r="BO375" s="7"/>
       <c r="BR375" s="7"/>
     </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D376" s="6"/>
       <c r="E376" s="1"/>
       <c r="BO376" s="7"/>
       <c r="BR376" s="7"/>
     </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D377" s="6"/>
       <c r="E377" s="1"/>
       <c r="BO377" s="7"/>
       <c r="BR377" s="7"/>
     </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D378" s="6"/>
       <c r="E378" s="1"/>
       <c r="BO378" s="7"/>
       <c r="BR378" s="7"/>
     </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D379" s="6"/>
       <c r="E379" s="1"/>
       <c r="BR379" s="7"/>
     </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D380" s="6"/>
       <c r="E380" s="1"/>
       <c r="BR380" s="7"/>
     </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D381" s="6"/>
       <c r="E381" s="1"/>
       <c r="BO381" s="7"/>
       <c r="BR381" s="7"/>
     </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D382" s="6"/>
       <c r="E382" s="1"/>
       <c r="BO382" s="7"/>
       <c r="BR382" s="7"/>
     </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D383" s="6"/>
       <c r="E383" s="1"/>
       <c r="BO383" s="7"/>
       <c r="BR383" s="7"/>
     </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D384" s="6"/>
       <c r="E384" s="1"/>
       <c r="BO384" s="7"/>
       <c r="BR384" s="7"/>
     </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D385" s="6"/>
       <c r="E385" s="1"/>
       <c r="BO385" s="7"/>
       <c r="BR385" s="7"/>
     </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D386" s="6"/>
       <c r="E386" s="1"/>
       <c r="BO386" s="7"/>
       <c r="BR386" s="7"/>
     </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D387" s="6"/>
       <c r="E387" s="1"/>
       <c r="BO387" s="7"/>
       <c r="BR387" s="7"/>
     </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D388" s="6"/>
       <c r="E388" s="1"/>
       <c r="BO388" s="7"/>
       <c r="BR388" s="7"/>
     </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D389" s="6"/>
       <c r="E389" s="1"/>
       <c r="BO389" s="7"/>
       <c r="BR389" s="7"/>
     </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D390" s="6"/>
       <c r="E390" s="1"/>
       <c r="BO390" s="7"/>
       <c r="BR390" s="7"/>
     </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D391" s="6"/>
       <c r="E391" s="1"/>
       <c r="BO391" s="7"/>
       <c r="BR391" s="7"/>
     </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D392" s="6"/>
       <c r="E392" s="1"/>
       <c r="BO392" s="7"/>
       <c r="BR392" s="7"/>
     </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D393" s="6"/>
       <c r="E393" s="1"/>
       <c r="BO393" s="7"/>
       <c r="BR393" s="7"/>
     </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D394" s="6"/>
       <c r="E394" s="1"/>
       <c r="BO394" s="7"/>
       <c r="BR394" s="7"/>
     </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D395" s="6"/>
       <c r="E395" s="1"/>
       <c r="BO395" s="7"/>
       <c r="BR395" s="7"/>
     </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D396" s="6"/>
       <c r="E396" s="1"/>
       <c r="BO396" s="7"/>
       <c r="BR396" s="7"/>
     </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D397" s="6"/>
       <c r="E397" s="1"/>
       <c r="BO397" s="7"/>
       <c r="BR397" s="7"/>
     </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D398" s="6"/>
       <c r="E398" s="1"/>
       <c r="BO398" s="7"/>
       <c r="BR398" s="7"/>
     </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D399" s="6"/>
       <c r="E399" s="1"/>
       <c r="BO399" s="7"/>
       <c r="BR399" s="7"/>
     </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D400" s="6"/>
       <c r="E400" s="1"/>
       <c r="BO400" s="7"/>
       <c r="BR400" s="7"/>
     </row>
-    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D401" s="6"/>
       <c r="E401" s="1"/>
       <c r="BO401" s="7"/>
       <c r="BR401" s="7"/>
     </row>
-    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D402" s="6"/>
       <c r="E402" s="1"/>
       <c r="BO402" s="7"/>
       <c r="BR402" s="7"/>
     </row>
-    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D403" s="6"/>
       <c r="E403" s="1"/>
       <c r="BO403" s="7"/>
       <c r="BR403" s="7"/>
     </row>
-    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D404" s="6"/>
       <c r="E404" s="1"/>
       <c r="BR404" s="7"/>
     </row>
-    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D405" s="6"/>
       <c r="E405" s="1"/>
       <c r="BR405" s="7"/>
     </row>
-    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D406" s="6"/>
       <c r="E406" s="1"/>
       <c r="BO406" s="7"/>
       <c r="BR406" s="7"/>
     </row>
-    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D407" s="6"/>
       <c r="E407" s="1"/>
       <c r="BO407" s="7"/>
       <c r="BR407" s="7"/>
     </row>
-    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D408" s="6"/>
       <c r="E408" s="1"/>
       <c r="BR408" s="7"/>
     </row>
-    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D409" s="6"/>
       <c r="E409" s="1"/>
       <c r="BR409" s="7"/>
     </row>
-    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D410" s="6"/>
       <c r="E410" s="1"/>
       <c r="BO410" s="7"/>
       <c r="BR410" s="7"/>
     </row>
-    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D411" s="6"/>
       <c r="E411" s="1"/>
       <c r="BO411" s="7"/>
       <c r="BR411" s="7"/>
     </row>
-    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D412" s="6"/>
       <c r="E412" s="1"/>
       <c r="BO412" s="7"/>
       <c r="BR412" s="7"/>
     </row>
-    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D413" s="6"/>
       <c r="E413" s="1"/>
       <c r="BO413" s="7"/>
       <c r="BR413" s="7"/>
     </row>
-    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D414" s="6"/>
       <c r="E414" s="1"/>
       <c r="BO414" s="7"/>
       <c r="BR414" s="7"/>
     </row>
-    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D415" s="6"/>
       <c r="E415" s="1"/>
       <c r="BO415" s="7"/>
       <c r="BR415" s="7"/>
     </row>
-    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D416" s="6"/>
       <c r="E416" s="1"/>
       <c r="BO416" s="7"/>
       <c r="BR416" s="7"/>
     </row>
-    <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D417" s="6"/>
       <c r="E417" s="1"/>
       <c r="BO417" s="7"/>
       <c r="BR417" s="7"/>
     </row>
-    <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D418" s="6"/>
       <c r="E418" s="1"/>
       <c r="BO418" s="7"/>
       <c r="BR418" s="7"/>
     </row>
-    <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D419" s="6"/>
       <c r="E419" s="1"/>
       <c r="BO419" s="7"/>
       <c r="BR419" s="7"/>
     </row>
-    <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D420" s="6"/>
       <c r="E420" s="1"/>
       <c r="BO420" s="7"/>
       <c r="BR420" s="7"/>
     </row>
-    <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D421" s="6"/>
       <c r="E421" s="1"/>
       <c r="BO421" s="7"/>
       <c r="BR421" s="7"/>
     </row>
-    <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D422" s="6"/>
       <c r="E422" s="1"/>
       <c r="BO422" s="7"/>
       <c r="BR422" s="7"/>
     </row>
-    <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D423" s="6"/>
       <c r="E423" s="1"/>
       <c r="BO423" s="7"/>
       <c r="BR423" s="7"/>
     </row>
-    <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D424" s="6"/>
       <c r="E424" s="1"/>
       <c r="BO424" s="7"/>
       <c r="BR424" s="7"/>
     </row>
-    <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D425" s="6"/>
       <c r="E425" s="1"/>
       <c r="BO425" s="7"/>
       <c r="BR425" s="7"/>
     </row>
-    <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D426" s="6"/>
       <c r="E426" s="1"/>
       <c r="BO426" s="7"/>
       <c r="BR426" s="7"/>
     </row>
-    <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D427" s="6"/>
       <c r="E427" s="1"/>
     </row>
-    <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D428" s="6"/>
       <c r="E428" s="1"/>
     </row>
-    <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D429" s="6"/>
       <c r="E429" s="1"/>
     </row>
-    <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D430" s="6"/>
       <c r="E430" s="1"/>
     </row>
-    <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D431" s="6"/>
       <c r="E431" s="1"/>
     </row>
-    <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D432" s="6"/>
       <c r="E432" s="1"/>
     </row>
-    <row r="433" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D433" s="6"/>
       <c r="E433" s="1"/>
     </row>
-    <row r="434" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D434" s="6"/>
       <c r="E434" s="1"/>
     </row>
-    <row r="435" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D435" s="6"/>
       <c r="E435" s="1"/>
     </row>
-    <row r="436" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D436" s="6"/>
       <c r="E436" s="1"/>
     </row>
-    <row r="437" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D437" s="6"/>
       <c r="E437" s="1"/>
     </row>
-    <row r="438" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D438" s="6"/>
       <c r="E438" s="1"/>
     </row>
-    <row r="439" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D439" s="6"/>
       <c r="E439" s="1"/>
     </row>
-    <row r="440" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D440" s="6"/>
       <c r="E440" s="1"/>
     </row>
-    <row r="441" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D441" s="6"/>
       <c r="E441" s="1"/>
     </row>
-    <row r="442" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D442" s="6"/>
       <c r="E442" s="1"/>
     </row>
-    <row r="443" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D443" s="6"/>
       <c r="E443" s="1"/>
     </row>
-    <row r="444" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D444" s="6"/>
       <c r="E444" s="1"/>
     </row>
-    <row r="445" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D445" s="6"/>
       <c r="E445" s="1"/>
     </row>
-    <row r="446" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D446" s="6"/>
       <c r="E446" s="1"/>
     </row>
-    <row r="447" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D447" s="6"/>
       <c r="E447" s="1"/>
     </row>
-    <row r="448" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D448" s="6"/>
       <c r="E448" s="1"/>
     </row>
-    <row r="449" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D449" s="6"/>
       <c r="E449" s="1"/>
     </row>
-    <row r="450" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D450" s="6"/>
       <c r="E450" s="1"/>
     </row>
-    <row r="451" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D451" s="6"/>
       <c r="E451" s="1"/>
     </row>
-    <row r="452" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D452" s="6"/>
       <c r="E452" s="1"/>
     </row>
-    <row r="453" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D453" s="6"/>
       <c r="E453" s="1"/>
     </row>
-    <row r="454" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D454" s="6"/>
       <c r="E454" s="1"/>
     </row>
-    <row r="455" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D455" s="6"/>
       <c r="E455" s="1"/>
     </row>
-    <row r="456" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D456" s="6"/>
       <c r="E456" s="1"/>
     </row>
-    <row r="457" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D457" s="6"/>
       <c r="E457" s="1"/>
     </row>
-    <row r="458" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D458" s="6"/>
       <c r="E458" s="1"/>
     </row>
-    <row r="459" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D459" s="6"/>
       <c r="E459" s="1"/>
     </row>
-    <row r="460" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D460" s="6"/>
       <c r="E460" s="1"/>
     </row>
-    <row r="461" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D461" s="6"/>
       <c r="E461" s="1"/>
     </row>
-    <row r="462" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D462" s="6"/>
       <c r="E462" s="1"/>
     </row>
-    <row r="463" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D463" s="6"/>
       <c r="E463" s="1"/>
     </row>
-    <row r="464" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D464" s="6"/>
       <c r="E464" s="1"/>
     </row>
-    <row r="465" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D465" s="6"/>
       <c r="E465" s="1"/>
     </row>
-    <row r="466" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D466" s="6"/>
       <c r="E466" s="1"/>
     </row>
-    <row r="467" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D467" s="6"/>
       <c r="E467" s="1"/>
     </row>
-    <row r="468" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D468" s="6"/>
       <c r="E468" s="1"/>
     </row>
-    <row r="469" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D469" s="6"/>
       <c r="E469" s="1"/>
     </row>
-    <row r="470" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D470" s="6"/>
       <c r="E470" s="1"/>
     </row>
-    <row r="471" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D471" s="6"/>
       <c r="E471" s="1"/>
     </row>
-    <row r="472" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D472" s="6"/>
       <c r="E472" s="1"/>
     </row>
-    <row r="473" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D473" s="6"/>
       <c r="E473" s="1"/>
     </row>
-    <row r="474" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D474" s="6"/>
       <c r="E474" s="1"/>
     </row>
-    <row r="475" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D475" s="6"/>
       <c r="E475" s="1"/>
     </row>
-    <row r="476" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D476" s="6"/>
       <c r="E476" s="1"/>
     </row>
-    <row r="477" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D477" s="6"/>
       <c r="E477" s="1"/>
     </row>
-    <row r="478" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D478" s="6"/>
       <c r="E478" s="1"/>
     </row>
-    <row r="479" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D479" s="6"/>
       <c r="E479" s="1"/>
     </row>
-    <row r="480" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D480" s="6"/>
       <c r="E480" s="1"/>
     </row>
-    <row r="481" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D481" s="6"/>
       <c r="E481" s="1"/>
     </row>
-    <row r="482" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="482" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D482" s="6"/>
       <c r="E482" s="1"/>
     </row>
-    <row r="483" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="483" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D483" s="6"/>
       <c r="E483" s="1"/>
     </row>
-    <row r="484" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="484" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D484" s="6"/>
       <c r="E484" s="1"/>
     </row>
-    <row r="485" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="485" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D485" s="6"/>
       <c r="E485" s="1"/>
     </row>
-    <row r="486" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="486" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D486" s="6"/>
       <c r="E486" s="1"/>
     </row>
-    <row r="487" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="487" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D487" s="6"/>
       <c r="E487" s="1"/>
     </row>
-    <row r="488" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="488" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D488" s="6"/>
       <c r="E488" s="1"/>
     </row>
-    <row r="489" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="489" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D489" s="6"/>
       <c r="E489" s="1"/>
     </row>
-    <row r="490" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="490" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D490" s="6"/>
       <c r="E490" s="1"/>
     </row>
-    <row r="491" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="491" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D491" s="6"/>
       <c r="E491" s="1"/>
     </row>
-    <row r="492" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="492" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D492" s="6"/>
       <c r="E492" s="1"/>
     </row>
-    <row r="493" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="493" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D493" s="6"/>
       <c r="E493" s="1"/>
     </row>
-    <row r="494" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="494" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D494" s="6"/>
       <c r="E494" s="1"/>
     </row>
-    <row r="495" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="495" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D495" s="6"/>
       <c r="E495" s="1"/>
     </row>
-    <row r="496" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="496" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D496" s="6"/>
       <c r="E496" s="1"/>
     </row>
-    <row r="497" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="497" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D497" s="6"/>
       <c r="E497" s="1"/>
     </row>
-    <row r="498" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="498" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D498" s="6"/>
       <c r="E498" s="1"/>
     </row>
-    <row r="499" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="499" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D499" s="6"/>
       <c r="E499" s="1"/>
     </row>
-    <row r="500" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="500" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D500" s="6"/>
       <c r="E500" s="1"/>
     </row>
-    <row r="501" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="501" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D501" s="6"/>
       <c r="E501" s="1"/>
     </row>
-    <row r="502" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="502" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D502" s="6"/>
       <c r="E502" s="1"/>
     </row>
-    <row r="503" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="503" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D503" s="6"/>
       <c r="E503" s="1"/>
     </row>
-    <row r="504" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="504" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D504" s="6"/>
       <c r="E504" s="1"/>
     </row>
-    <row r="505" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="505" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D505" s="6"/>
       <c r="E505" s="1"/>
     </row>
-    <row r="506" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="506" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D506" s="6"/>
       <c r="E506" s="1"/>
     </row>
-    <row r="574" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="574" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D574" s="6"/>
       <c r="E574" s="1"/>
     </row>
-    <row r="575" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="575" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D575" s="6"/>
       <c r="E575" s="1"/>
     </row>
-    <row r="576" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="576" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D576" s="6"/>
       <c r="E576" s="1"/>
     </row>
-    <row r="577" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="577" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D577" s="6"/>
       <c r="E577" s="1"/>
     </row>
-    <row r="578" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="578" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D578" s="6"/>
       <c r="E578" s="1"/>
     </row>
-    <row r="579" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="579" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D579" s="6"/>
       <c r="E579" s="1"/>
     </row>
-    <row r="580" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="580" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D580" s="6"/>
       <c r="E580" s="1"/>
     </row>
-    <row r="581" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="581" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D581" s="6"/>
       <c r="E581" s="1"/>
     </row>
-    <row r="582" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="582" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D582" s="6"/>
       <c r="E582" s="1"/>
     </row>
-    <row r="583" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="583" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D583" s="6"/>
       <c r="E583" s="1"/>
     </row>
-    <row r="584" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="584" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D584" s="6"/>
       <c r="E584" s="1"/>
     </row>
-    <row r="585" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="585" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D585" s="6"/>
       <c r="E585" s="1"/>
     </row>
-    <row r="586" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="586" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D586" s="6"/>
       <c r="E586" s="1"/>
     </row>
-    <row r="587" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="587" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D587" s="6"/>
       <c r="E587" s="1"/>
     </row>
-    <row r="588" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="588" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D588" s="6"/>
       <c r="E588" s="1"/>
     </row>
-    <row r="589" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="589" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D589" s="6"/>
       <c r="E589" s="1"/>
     </row>
-    <row r="590" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="590" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D590" s="6"/>
       <c r="E590" s="1"/>
     </row>
-    <row r="591" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="591" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D591" s="6"/>
       <c r="E591" s="1"/>
     </row>
-    <row r="592" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="592" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D592" s="6"/>
       <c r="E592" s="1"/>
     </row>
-    <row r="593" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="593" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D593" s="6"/>
       <c r="E593" s="1"/>
     </row>
-    <row r="594" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="594" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D594" s="6"/>
       <c r="E594" s="1"/>
     </row>
-    <row r="595" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="595" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D595" s="6"/>
       <c r="E595" s="1"/>
     </row>
-    <row r="596" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="596" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D596" s="6"/>
       <c r="E596" s="1"/>
     </row>
-    <row r="597" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="597" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D597" s="6"/>
       <c r="E597" s="1"/>
     </row>
-    <row r="598" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="598" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D598" s="6"/>
       <c r="E598" s="1"/>
     </row>
@@ -6540,84 +6536,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:DH840"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.75" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="21.5" style="3" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" style="3" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" style="3" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" style="3" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" style="3" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" style="3" customWidth="1"/>
-    <col min="24" max="24" width="18.5" style="3" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1"/>
-    <col min="32" max="32" width="13.75" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1"/>
-    <col min="36" max="36" width="12.5" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.08984375" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="7.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" customWidth="1"/>
+    <col min="6" max="6" width="31.36328125" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.81640625" customWidth="1"/>
+    <col min="9" max="9" width="7.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="11" max="13" width="8.36328125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11.7265625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.08984375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.54296875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="21.453125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="19.81640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="16.54296875" style="3" customWidth="1"/>
+    <col min="20" max="20" width="19.08984375" style="3" customWidth="1"/>
+    <col min="21" max="21" width="18.36328125" style="3" customWidth="1"/>
+    <col min="22" max="22" width="17.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.36328125" style="3" customWidth="1"/>
+    <col min="24" max="24" width="18.453125" style="3" customWidth="1"/>
+    <col min="25" max="25" width="16.54296875" customWidth="1"/>
+    <col min="26" max="26" width="10.6328125" customWidth="1"/>
+    <col min="27" max="27" width="8.36328125" customWidth="1"/>
+    <col min="28" max="28" width="15.1796875" customWidth="1"/>
+    <col min="29" max="30" width="8.54296875" customWidth="1"/>
+    <col min="31" max="31" width="13.453125" customWidth="1"/>
+    <col min="32" max="32" width="13.7265625" customWidth="1"/>
+    <col min="33" max="33" width="14.54296875" customWidth="1"/>
+    <col min="34" max="34" width="17.453125" customWidth="1"/>
+    <col min="35" max="35" width="8.54296875" customWidth="1"/>
+    <col min="36" max="36" width="12.453125" customWidth="1"/>
+    <col min="37" max="37" width="8.54296875" customWidth="1"/>
+    <col min="38" max="39" width="8.36328125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="43" width="11.83203125" customWidth="1"/>
-    <col min="44" max="44" width="18.4140625" customWidth="1"/>
-    <col min="45" max="45" width="12.25" customWidth="1"/>
-    <col min="46" max="46" width="11.9140625" customWidth="1"/>
-    <col min="47" max="47" width="19.58203125" customWidth="1"/>
-    <col min="48" max="48" width="12.6640625" customWidth="1"/>
+    <col min="41" max="41" width="13.26953125" customWidth="1"/>
+    <col min="42" max="43" width="11.81640625" customWidth="1"/>
+    <col min="44" max="44" width="18.453125" customWidth="1"/>
+    <col min="45" max="45" width="12.26953125" customWidth="1"/>
+    <col min="46" max="46" width="11.90625" customWidth="1"/>
+    <col min="47" max="47" width="19.54296875" customWidth="1"/>
+    <col min="48" max="48" width="12.6328125" customWidth="1"/>
     <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="19.75" customWidth="1"/>
-    <col min="53" max="53" width="5.08203125" customWidth="1"/>
-    <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="55" width="13.5" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" customWidth="1"/>
-    <col min="58" max="58" width="8.25" customWidth="1"/>
-    <col min="59" max="65" width="8.33203125" customWidth="1"/>
-    <col min="66" max="68" width="11.25" customWidth="1"/>
-    <col min="69" max="69" width="6.58203125" customWidth="1"/>
+    <col min="51" max="51" width="11.7265625" customWidth="1"/>
+    <col min="52" max="52" width="19.7265625" customWidth="1"/>
+    <col min="53" max="53" width="5.08984375" customWidth="1"/>
+    <col min="54" max="54" width="8.453125" customWidth="1"/>
+    <col min="55" max="55" width="13.453125" customWidth="1"/>
+    <col min="56" max="56" width="14.6328125" customWidth="1"/>
+    <col min="57" max="57" width="10.1796875" customWidth="1"/>
+    <col min="58" max="58" width="8.26953125" customWidth="1"/>
+    <col min="59" max="65" width="8.36328125" customWidth="1"/>
+    <col min="66" max="68" width="11.26953125" customWidth="1"/>
+    <col min="69" max="69" width="6.54296875" customWidth="1"/>
     <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="4" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="4" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="4" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="4" customWidth="1"/>
-    <col min="78" max="78" width="13.5" customWidth="1"/>
-    <col min="79" max="79" width="21.1640625" customWidth="1"/>
-    <col min="80" max="80" width="15.75" customWidth="1"/>
-    <col min="81" max="81" width="15.58203125" customWidth="1"/>
-    <col min="82" max="82" width="12.83203125" customWidth="1"/>
-    <col min="83" max="83" width="16.1640625" customWidth="1"/>
+    <col min="72" max="72" width="7.36328125" style="4" customWidth="1"/>
+    <col min="73" max="74" width="8.453125" style="4" customWidth="1"/>
+    <col min="75" max="76" width="7.81640625" style="4" customWidth="1"/>
+    <col min="77" max="77" width="22.1796875" style="4" customWidth="1"/>
+    <col min="78" max="78" width="13.453125" customWidth="1"/>
+    <col min="79" max="79" width="21.1796875" customWidth="1"/>
+    <col min="80" max="80" width="15.7265625" customWidth="1"/>
+    <col min="81" max="81" width="15.54296875" customWidth="1"/>
+    <col min="82" max="82" width="12.81640625" customWidth="1"/>
+    <col min="83" max="83" width="16.1796875" customWidth="1"/>
     <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.83203125" customWidth="1"/>
-    <col min="88" max="88" width="23.58203125" customWidth="1"/>
-    <col min="89" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="17.08203125" customWidth="1"/>
+    <col min="86" max="87" width="12.81640625" customWidth="1"/>
+    <col min="88" max="88" width="23.54296875" customWidth="1"/>
+    <col min="89" max="89" width="12.81640625" customWidth="1"/>
+    <col min="90" max="90" width="17.08984375" customWidth="1"/>
     <col min="97" max="97" width="14" customWidth="1"/>
     <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08203125" customWidth="1"/>
-    <col min="101" max="101" width="13.75" customWidth="1"/>
-    <col min="108" max="108" width="15.5" customWidth="1"/>
+    <col min="100" max="100" width="11.08984375" customWidth="1"/>
+    <col min="101" max="101" width="13.7265625" customWidth="1"/>
+    <col min="108" max="108" width="15.453125" customWidth="1"/>
     <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10180,20 +10176,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08984375" customWidth="1"/>
+    <col min="15" max="15" width="9.453125" customWidth="1"/>
+    <col min="16" max="16" width="22.1796875" customWidth="1"/>
+    <col min="17" max="17" width="12.81640625" customWidth="1"/>
+    <col min="20" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10230,8 +10227,11 @@
       <c r="O1" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P1" s="8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10274,11 +10274,14 @@
       <c r="O2" t="s">
         <v>372</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q2" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10322,32 +10325,42 @@
         <v>307</v>
       </c>
       <c r="P3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P6"/>
+    </row>
+    <row r="9" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K9"/>
-    </row>
-    <row r="11" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P9"/>
+    </row>
+    <row r="11" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K11"/>
-    </row>
-    <row r="12" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P11"/>
+    </row>
+    <row r="12" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K12"/>
-    </row>
-    <row r="14" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P12"/>
+    </row>
+    <row r="14" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="J14"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P14"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C17" s="14"/>
     </row>
-    <row r="18" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="J18"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P18"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="C20" s="8"/>
-      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -10359,11 +10372,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
+    <col min="4" max="4" width="27.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10412,11 +10425,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="3" max="3" width="27.26953125" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10511,13 +10524,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1"/>
-    <col min="5" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="3" max="4" width="10.08984375" customWidth="1"/>
+    <col min="5" max="10" width="11.26953125" customWidth="1"/>
+    <col min="11" max="11" width="6.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10642,15 +10655,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A2:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1"/>
-    <col min="2" max="2" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col min="4" max="4" width="47.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\学习专用\ark_-n\Excel\Test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A9A412-5195-437B-81A0-5D6359994935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556AC661-FAD3-4723-AB45-EFA20ACEC91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -21,8 +21,21 @@
     <sheet name="BulletData" sheetId="4" r:id="rId6"/>
     <sheet name="EffectData" sheetId="9" r:id="rId7"/>
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
+    <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -285,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="530">
   <si>
     <t>Id</t>
   </si>
@@ -1902,11 +1915,75 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>可无视buff抑制检测</t>
+    <t>Id</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>IsCancelable</t>
+    <t>仅单面</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>相对路径</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>正面atlas</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>正面png</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>正面skel</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>背面atlas</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>背面png</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>背面skel</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnlyFront</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseAppHotfixResPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontAtlasPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontPngPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontSkelPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackAtlasPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackPngPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackSkelPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>string?</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2023,6 +2100,7 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2030,12 +2108,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2090,12 +2170,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2157,9 +2240,13 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{E43D54E0-90FD-4693-8244-4418D0B0692B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2462,7 +2549,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
@@ -2500,48 +2587,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BS598"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
-    <col min="4" max="4" width="8.54296875" customWidth="1"/>
-    <col min="5" max="5" width="5.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.54296875" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="4.08984375" customWidth="1"/>
-    <col min="13" max="13" width="5.54296875" customWidth="1"/>
+    <col min="12" max="12" width="4.08203125" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1"/>
     <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.7265625" customWidth="1"/>
-    <col min="16" max="16" width="10.81640625" customWidth="1"/>
-    <col min="17" max="18" width="3.81640625" customWidth="1"/>
-    <col min="19" max="20" width="3.54296875" customWidth="1"/>
-    <col min="21" max="21" width="10.26953125" customWidth="1"/>
-    <col min="22" max="22" width="9.54296875" customWidth="1"/>
-    <col min="23" max="23" width="10.7265625" customWidth="1"/>
-    <col min="24" max="24" width="12.81640625" customWidth="1"/>
-    <col min="25" max="25" width="13.08984375" customWidth="1"/>
-    <col min="26" max="26" width="10.7265625" customWidth="1"/>
+    <col min="15" max="15" width="7.75" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1"/>
+    <col min="23" max="23" width="10.75" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1"/>
+    <col min="26" max="26" width="10.75" customWidth="1"/>
     <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08984375" customWidth="1"/>
-    <col min="31" max="31" width="9.7265625" customWidth="1"/>
-    <col min="32" max="32" width="7.81640625" customWidth="1"/>
-    <col min="33" max="33" width="15.81640625" customWidth="1"/>
-    <col min="34" max="34" width="13.81640625" customWidth="1"/>
-    <col min="35" max="35" width="34.453125" customWidth="1"/>
-    <col min="36" max="37" width="9.81640625" customWidth="1"/>
-    <col min="43" max="43" width="12.453125" customWidth="1"/>
-    <col min="50" max="50" width="24.36328125" customWidth="1"/>
-    <col min="52" max="52" width="17.7265625" customWidth="1"/>
-    <col min="53" max="53" width="7.81640625" customWidth="1"/>
-    <col min="56" max="56" width="24.26953125" customWidth="1"/>
-    <col min="57" max="57" width="13.26953125" customWidth="1"/>
-    <col min="58" max="58" width="16.08984375" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1"/>
+    <col min="31" max="31" width="9.75" customWidth="1"/>
+    <col min="32" max="32" width="7.83203125" customWidth="1"/>
+    <col min="33" max="33" width="15.83203125" customWidth="1"/>
+    <col min="34" max="34" width="13.83203125" customWidth="1"/>
+    <col min="35" max="35" width="34.5" customWidth="1"/>
+    <col min="36" max="37" width="9.83203125" customWidth="1"/>
+    <col min="43" max="43" width="12.5" customWidth="1"/>
+    <col min="50" max="50" width="24.33203125" customWidth="1"/>
+    <col min="52" max="52" width="17.75" customWidth="1"/>
+    <col min="53" max="53" width="7.83203125" customWidth="1"/>
+    <col min="56" max="56" width="24.25" customWidth="1"/>
+    <col min="57" max="57" width="13.25" customWidth="1"/>
+    <col min="58" max="58" width="16.08203125" customWidth="1"/>
     <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.54296875" customWidth="1"/>
+    <col min="64" max="64" width="39.58203125" customWidth="1"/>
     <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.81640625" customWidth="1"/>
+    <col min="66" max="66" width="14.83203125" customWidth="1"/>
     <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1796875" customWidth="1"/>
+    <col min="71" max="71" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.25">
@@ -3773,2755 +3860,2755 @@
       <c r="AI35" s="8"/>
       <c r="BK35" s="8"/>
     </row>
-    <row r="36" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="6"/>
       <c r="E36" s="1"/>
       <c r="BO36" s="7"/>
       <c r="BR36" s="7"/>
     </row>
-    <row r="37" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="6"/>
       <c r="E37" s="1"/>
       <c r="BO37" s="7"/>
       <c r="BR37" s="7"/>
     </row>
-    <row r="38" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="6"/>
       <c r="E38" s="1"/>
       <c r="BO38" s="7"/>
       <c r="BR38" s="7"/>
     </row>
-    <row r="39" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="6"/>
       <c r="E39" s="1"/>
       <c r="BO39" s="7"/>
       <c r="BR39" s="7"/>
     </row>
-    <row r="40" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="6"/>
       <c r="E40" s="1"/>
       <c r="BO40" s="7"/>
       <c r="BR40" s="7"/>
     </row>
-    <row r="41" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="6"/>
       <c r="E41" s="1"/>
       <c r="BO41" s="7"/>
       <c r="BR41" s="7"/>
     </row>
-    <row r="42" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="6"/>
       <c r="E42" s="1"/>
       <c r="BO42" s="7"/>
       <c r="BR42" s="7"/>
     </row>
-    <row r="43" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="6"/>
       <c r="E43" s="1"/>
       <c r="BR43" s="7"/>
     </row>
-    <row r="44" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="6"/>
       <c r="E44" s="1"/>
       <c r="BR44" s="7"/>
     </row>
-    <row r="45" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="6"/>
       <c r="E45" s="1"/>
       <c r="BR45" s="7"/>
     </row>
-    <row r="46" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="6"/>
       <c r="E46" s="1"/>
       <c r="BO46" s="7"/>
       <c r="BR46" s="7"/>
     </row>
-    <row r="47" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="6"/>
       <c r="E47" s="1"/>
       <c r="BO47" s="7"/>
       <c r="BR47" s="7"/>
     </row>
-    <row r="48" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="6"/>
       <c r="E48" s="1"/>
       <c r="BO48" s="7"/>
       <c r="BR48" s="7"/>
     </row>
-    <row r="49" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="6"/>
       <c r="E49" s="1"/>
       <c r="BO49" s="7"/>
       <c r="BR49" s="7"/>
     </row>
-    <row r="50" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="6"/>
       <c r="E50" s="1"/>
       <c r="BO50" s="7"/>
       <c r="BR50" s="7"/>
     </row>
-    <row r="51" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="6"/>
       <c r="E51" s="1"/>
       <c r="BO51" s="7"/>
       <c r="BR51" s="7"/>
     </row>
-    <row r="52" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="6"/>
       <c r="E52" s="1"/>
       <c r="BO52" s="7"/>
       <c r="BR52" s="7"/>
     </row>
-    <row r="53" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="6"/>
       <c r="E53" s="1"/>
       <c r="BO53" s="7"/>
       <c r="BR53" s="7"/>
     </row>
-    <row r="54" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="6"/>
       <c r="E54" s="1"/>
       <c r="BO54" s="7"/>
       <c r="BR54" s="7"/>
     </row>
-    <row r="55" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="6"/>
       <c r="E55" s="1"/>
       <c r="BO55" s="7"/>
       <c r="BR55" s="7"/>
     </row>
-    <row r="56" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="6"/>
       <c r="E56" s="1"/>
       <c r="BO56" s="7"/>
       <c r="BR56" s="7"/>
     </row>
-    <row r="57" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="6"/>
       <c r="E57" s="1"/>
       <c r="BO57" s="7"/>
       <c r="BR57" s="7"/>
     </row>
-    <row r="58" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="6"/>
       <c r="E58" s="1"/>
       <c r="BO58" s="7"/>
       <c r="BR58" s="7"/>
     </row>
-    <row r="59" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="6"/>
       <c r="E59" s="1"/>
       <c r="BO59" s="7"/>
       <c r="BR59" s="7"/>
     </row>
-    <row r="60" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="6"/>
       <c r="E60" s="1"/>
       <c r="BO60" s="7"/>
       <c r="BR60" s="7"/>
     </row>
-    <row r="61" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="6"/>
       <c r="E61" s="1"/>
       <c r="BO61" s="7"/>
       <c r="BR61" s="7"/>
     </row>
-    <row r="62" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="6"/>
       <c r="E62" s="1"/>
       <c r="BO62" s="7"/>
       <c r="BR62" s="7"/>
     </row>
-    <row r="63" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="6"/>
       <c r="E63" s="1"/>
       <c r="BO63" s="7"/>
       <c r="BR63" s="7"/>
     </row>
-    <row r="64" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="6"/>
       <c r="E64" s="1"/>
       <c r="BO64" s="7"/>
       <c r="BR64" s="7"/>
     </row>
-    <row r="65" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="6"/>
       <c r="E65" s="1"/>
       <c r="BO65" s="7"/>
       <c r="BR65" s="7"/>
     </row>
-    <row r="66" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="6"/>
       <c r="E66" s="1"/>
       <c r="BO66" s="7"/>
       <c r="BR66" s="7"/>
     </row>
-    <row r="67" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="6"/>
       <c r="E67" s="1"/>
       <c r="BO67" s="7"/>
       <c r="BR67" s="7"/>
     </row>
-    <row r="68" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="6"/>
       <c r="E68" s="1"/>
       <c r="BO68" s="7"/>
       <c r="BR68" s="7"/>
     </row>
-    <row r="69" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="6"/>
       <c r="E69" s="1"/>
       <c r="BO69" s="7"/>
       <c r="BR69" s="7"/>
     </row>
-    <row r="70" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="6"/>
       <c r="E70" s="1"/>
       <c r="BO70" s="7"/>
       <c r="BR70" s="7"/>
     </row>
-    <row r="71" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="6"/>
       <c r="E71" s="1"/>
       <c r="BO71" s="7"/>
       <c r="BR71" s="7"/>
     </row>
-    <row r="72" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="6"/>
       <c r="E72" s="1"/>
       <c r="BO72" s="7"/>
       <c r="BR72" s="7"/>
     </row>
-    <row r="73" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="6"/>
       <c r="E73" s="1"/>
       <c r="BO73" s="7"/>
       <c r="BR73" s="7"/>
     </row>
-    <row r="74" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="6"/>
       <c r="E74" s="1"/>
       <c r="BO74" s="7"/>
       <c r="BR74" s="7"/>
     </row>
-    <row r="75" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="6"/>
       <c r="E75" s="1"/>
       <c r="BO75" s="7"/>
       <c r="BR75" s="7"/>
     </row>
-    <row r="76" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="6"/>
       <c r="E76" s="1"/>
       <c r="BO76" s="7"/>
       <c r="BR76" s="7"/>
     </row>
-    <row r="77" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="6"/>
       <c r="E77" s="1"/>
       <c r="BO77" s="7"/>
       <c r="BR77" s="7"/>
     </row>
-    <row r="78" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="6"/>
       <c r="E78" s="1"/>
       <c r="BO78" s="7"/>
       <c r="BR78" s="7"/>
     </row>
-    <row r="79" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="6"/>
       <c r="E79" s="1"/>
       <c r="BO79" s="7"/>
       <c r="BR79" s="7"/>
     </row>
-    <row r="80" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="6"/>
       <c r="E80" s="1"/>
       <c r="BO80" s="7"/>
       <c r="BR80" s="7"/>
     </row>
-    <row r="81" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="6"/>
       <c r="E81" s="1"/>
       <c r="BO81" s="7"/>
       <c r="BR81" s="7"/>
     </row>
-    <row r="82" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="6"/>
       <c r="E82" s="1"/>
       <c r="BO82" s="7"/>
       <c r="BR82" s="7"/>
     </row>
-    <row r="83" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="6"/>
       <c r="E83" s="1"/>
       <c r="BO83" s="7"/>
       <c r="BR83" s="7"/>
     </row>
-    <row r="84" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="6"/>
       <c r="E84" s="1"/>
       <c r="BO84" s="7"/>
       <c r="BR84" s="7"/>
     </row>
-    <row r="85" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="6"/>
       <c r="E85" s="1"/>
       <c r="BO85" s="7"/>
       <c r="BR85" s="7"/>
     </row>
-    <row r="86" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="6"/>
       <c r="E86" s="1"/>
       <c r="BO86" s="7"/>
       <c r="BR86" s="7"/>
     </row>
-    <row r="87" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="6"/>
       <c r="E87" s="1"/>
       <c r="BO87" s="7"/>
       <c r="BR87" s="7"/>
     </row>
-    <row r="88" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
       <c r="E88" s="1"/>
       <c r="BO88" s="7"/>
       <c r="BR88" s="7"/>
     </row>
-    <row r="89" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="1"/>
       <c r="BO89" s="7"/>
       <c r="BR89" s="7"/>
     </row>
-    <row r="90" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="1"/>
       <c r="BO90" s="7"/>
       <c r="BR90" s="7"/>
     </row>
-    <row r="91" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="6"/>
       <c r="E91" s="1"/>
       <c r="BO91" s="7"/>
       <c r="BR91" s="7"/>
     </row>
-    <row r="92" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="6"/>
       <c r="E92" s="1"/>
       <c r="BO92" s="7"/>
       <c r="BR92" s="7"/>
     </row>
-    <row r="93" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="6"/>
       <c r="E93" s="1"/>
       <c r="BO93" s="7"/>
       <c r="BR93" s="7"/>
     </row>
-    <row r="94" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="6"/>
       <c r="E94" s="1"/>
       <c r="BO94" s="7"/>
       <c r="BR94" s="7"/>
     </row>
-    <row r="95" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="6"/>
       <c r="E95" s="1"/>
       <c r="BO95" s="7"/>
       <c r="BR95" s="7"/>
     </row>
-    <row r="96" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="6"/>
       <c r="E96" s="1"/>
       <c r="BO96" s="7"/>
       <c r="BR96" s="7"/>
     </row>
-    <row r="97" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="6"/>
       <c r="E97" s="1"/>
       <c r="BO97" s="7"/>
       <c r="BR97" s="7"/>
     </row>
-    <row r="98" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="6"/>
       <c r="E98" s="1"/>
       <c r="BO98" s="7"/>
       <c r="BR98" s="7"/>
     </row>
-    <row r="99" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="6"/>
       <c r="E99" s="1"/>
       <c r="BO99" s="7"/>
       <c r="BR99" s="7"/>
     </row>
-    <row r="100" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="6"/>
       <c r="E100" s="1"/>
       <c r="BO100" s="7"/>
       <c r="BR100" s="7"/>
     </row>
-    <row r="101" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="6"/>
       <c r="E101" s="1"/>
       <c r="BO101" s="7"/>
       <c r="BR101" s="7"/>
     </row>
-    <row r="102" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="6"/>
       <c r="E102" s="1"/>
       <c r="BO102" s="7"/>
       <c r="BR102" s="7"/>
     </row>
-    <row r="103" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="6"/>
       <c r="E103" s="1"/>
       <c r="BO103" s="7"/>
       <c r="BR103" s="7"/>
     </row>
-    <row r="104" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="6"/>
       <c r="E104" s="1"/>
       <c r="BO104" s="7"/>
       <c r="BR104" s="7"/>
     </row>
-    <row r="105" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="6"/>
       <c r="E105" s="1"/>
       <c r="BO105" s="7"/>
       <c r="BR105" s="7"/>
     </row>
-    <row r="106" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="6"/>
       <c r="E106" s="1"/>
       <c r="BO106" s="7"/>
       <c r="BR106" s="7"/>
     </row>
-    <row r="107" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="6"/>
       <c r="E107" s="1"/>
       <c r="BO107" s="7"/>
       <c r="BR107" s="7"/>
     </row>
-    <row r="108" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="6"/>
       <c r="E108" s="1"/>
       <c r="BO108" s="7"/>
       <c r="BR108" s="7"/>
     </row>
-    <row r="109" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="1"/>
       <c r="BO109" s="7"/>
       <c r="BR109" s="7"/>
     </row>
-    <row r="110" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="1"/>
       <c r="BO110" s="7"/>
       <c r="BR110" s="7"/>
     </row>
-    <row r="111" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="1"/>
       <c r="BO111" s="7"/>
       <c r="BR111" s="7"/>
     </row>
-    <row r="112" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="1"/>
       <c r="BO112" s="7"/>
       <c r="BR112" s="7"/>
     </row>
-    <row r="113" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
       <c r="E113" s="1"/>
       <c r="BO113" s="7"/>
       <c r="BR113" s="7"/>
     </row>
-    <row r="114" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="1"/>
       <c r="BO114" s="7"/>
       <c r="BR114" s="7"/>
     </row>
-    <row r="115" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="6"/>
       <c r="E115" s="1"/>
       <c r="BO115" s="7"/>
       <c r="BR115" s="7"/>
     </row>
-    <row r="116" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="6"/>
       <c r="E116" s="1"/>
       <c r="BO116" s="7"/>
       <c r="BR116" s="7"/>
     </row>
-    <row r="117" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="6"/>
       <c r="E117" s="1"/>
       <c r="BO117" s="7"/>
       <c r="BR117" s="7"/>
     </row>
-    <row r="118" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="6"/>
       <c r="E118" s="1"/>
       <c r="BO118" s="7"/>
       <c r="BR118" s="7"/>
     </row>
-    <row r="119" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="6"/>
       <c r="E119" s="1"/>
       <c r="BO119" s="7"/>
       <c r="BR119" s="7"/>
     </row>
-    <row r="120" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="6"/>
       <c r="E120" s="1"/>
       <c r="BO120" s="7"/>
       <c r="BR120" s="7"/>
     </row>
-    <row r="121" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="6"/>
       <c r="E121" s="1"/>
       <c r="BO121" s="7"/>
       <c r="BR121" s="7"/>
     </row>
-    <row r="122" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="6"/>
       <c r="E122" s="1"/>
       <c r="BO122" s="7"/>
       <c r="BR122" s="7"/>
     </row>
-    <row r="123" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="6"/>
       <c r="E123" s="1"/>
       <c r="BO123" s="7"/>
       <c r="BR123" s="7"/>
     </row>
-    <row r="124" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="6"/>
       <c r="E124" s="1"/>
       <c r="BO124" s="7"/>
       <c r="BR124" s="7"/>
     </row>
-    <row r="125" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="6"/>
       <c r="E125" s="1"/>
       <c r="BO125" s="7"/>
       <c r="BR125" s="7"/>
     </row>
-    <row r="126" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="6"/>
       <c r="E126" s="1"/>
       <c r="BO126" s="7"/>
       <c r="BR126" s="7"/>
     </row>
-    <row r="127" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="6"/>
       <c r="E127" s="1"/>
       <c r="BO127" s="7"/>
       <c r="BR127" s="7"/>
     </row>
-    <row r="128" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="6"/>
       <c r="E128" s="1"/>
       <c r="BO128" s="7"/>
       <c r="BR128" s="7"/>
     </row>
-    <row r="129" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="6"/>
       <c r="E129" s="1"/>
       <c r="BO129" s="7"/>
       <c r="BR129" s="7"/>
     </row>
-    <row r="130" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="6"/>
       <c r="E130" s="1"/>
       <c r="BO130" s="7"/>
       <c r="BR130" s="7"/>
     </row>
-    <row r="131" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="6"/>
       <c r="E131" s="1"/>
       <c r="BO131" s="7"/>
       <c r="BR131" s="7"/>
     </row>
-    <row r="132" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="6"/>
       <c r="E132" s="1"/>
       <c r="BO132" s="7"/>
       <c r="BR132" s="7"/>
     </row>
-    <row r="133" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="6"/>
       <c r="E133" s="1"/>
       <c r="BO133" s="7"/>
       <c r="BR133" s="7"/>
     </row>
-    <row r="134" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="6"/>
       <c r="E134" s="1"/>
       <c r="BO134" s="7"/>
       <c r="BR134" s="7"/>
     </row>
-    <row r="135" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="6"/>
       <c r="E135" s="1"/>
       <c r="BO135" s="7"/>
       <c r="BR135" s="7"/>
     </row>
-    <row r="136" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="6"/>
       <c r="E136" s="1"/>
       <c r="BO136" s="7"/>
       <c r="BR136" s="7"/>
     </row>
-    <row r="137" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="6"/>
       <c r="E137" s="1"/>
       <c r="BO137" s="7"/>
       <c r="BR137" s="7"/>
     </row>
-    <row r="138" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="6"/>
       <c r="E138" s="1"/>
       <c r="BO138" s="7"/>
       <c r="BR138" s="7"/>
     </row>
-    <row r="139" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="6"/>
       <c r="E139" s="1"/>
       <c r="BO139" s="7"/>
       <c r="BR139" s="7"/>
     </row>
-    <row r="140" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="6"/>
       <c r="E140" s="1"/>
       <c r="BO140" s="7"/>
       <c r="BR140" s="7"/>
     </row>
-    <row r="141" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="6"/>
       <c r="E141" s="1"/>
       <c r="BO141" s="7"/>
       <c r="BR141" s="7"/>
     </row>
-    <row r="142" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="6"/>
       <c r="E142" s="1"/>
       <c r="BO142" s="7"/>
       <c r="BR142" s="7"/>
     </row>
-    <row r="143" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="6"/>
       <c r="E143" s="1"/>
       <c r="BO143" s="7"/>
       <c r="BR143" s="7"/>
     </row>
-    <row r="144" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="6"/>
       <c r="E144" s="1"/>
       <c r="BO144" s="7"/>
       <c r="BR144" s="7"/>
     </row>
-    <row r="145" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="6"/>
       <c r="E145" s="1"/>
       <c r="BO145" s="7"/>
       <c r="BR145" s="7"/>
     </row>
-    <row r="146" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="6"/>
       <c r="E146" s="1"/>
       <c r="BO146" s="7"/>
       <c r="BR146" s="7"/>
     </row>
-    <row r="147" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="6"/>
       <c r="E147" s="1"/>
       <c r="BO147" s="7"/>
       <c r="BR147" s="7"/>
     </row>
-    <row r="148" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="6"/>
       <c r="E148" s="1"/>
       <c r="BO148" s="7"/>
       <c r="BR148" s="7"/>
     </row>
-    <row r="149" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="6"/>
       <c r="E149" s="1"/>
       <c r="BO149" s="7"/>
       <c r="BR149" s="7"/>
     </row>
-    <row r="150" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="6"/>
       <c r="E150" s="1"/>
       <c r="BO150" s="7"/>
       <c r="BR150" s="7"/>
     </row>
-    <row r="151" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="6"/>
       <c r="E151" s="1"/>
       <c r="BO151" s="7"/>
       <c r="BR151" s="7"/>
     </row>
-    <row r="152" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="6"/>
       <c r="E152" s="1"/>
       <c r="BO152" s="7"/>
       <c r="BR152" s="7"/>
     </row>
-    <row r="153" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="6"/>
       <c r="E153" s="1"/>
       <c r="BO153" s="7"/>
       <c r="BR153" s="7"/>
     </row>
-    <row r="154" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="6"/>
       <c r="E154" s="1"/>
       <c r="BO154" s="7"/>
       <c r="BR154" s="7"/>
     </row>
-    <row r="155" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="6"/>
       <c r="E155" s="1"/>
       <c r="BO155" s="7"/>
       <c r="BR155" s="7"/>
     </row>
-    <row r="156" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="6"/>
       <c r="E156" s="1"/>
       <c r="BO156" s="7"/>
       <c r="BR156" s="7"/>
     </row>
-    <row r="157" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="6"/>
       <c r="E157" s="1"/>
       <c r="BO157" s="7"/>
       <c r="BR157" s="7"/>
     </row>
-    <row r="158" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="6"/>
       <c r="E158" s="1"/>
       <c r="BO158" s="7"/>
       <c r="BR158" s="7"/>
     </row>
-    <row r="159" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="6"/>
       <c r="E159" s="1"/>
       <c r="BO159" s="7"/>
       <c r="BR159" s="7"/>
     </row>
-    <row r="160" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="6"/>
       <c r="E160" s="1"/>
       <c r="BO160" s="7"/>
       <c r="BR160" s="7"/>
     </row>
-    <row r="161" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="6"/>
       <c r="E161" s="1"/>
       <c r="BO161" s="7"/>
       <c r="BR161" s="7"/>
     </row>
-    <row r="162" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="6"/>
       <c r="E162" s="1"/>
       <c r="BO162" s="7"/>
       <c r="BR162" s="7"/>
     </row>
-    <row r="163" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="6"/>
       <c r="E163" s="1"/>
       <c r="BO163" s="7"/>
       <c r="BR163" s="7"/>
     </row>
-    <row r="164" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="6"/>
       <c r="E164" s="1"/>
       <c r="BO164" s="7"/>
       <c r="BR164" s="7"/>
     </row>
-    <row r="165" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="6"/>
       <c r="E165" s="1"/>
       <c r="BO165" s="7"/>
       <c r="BR165" s="7"/>
     </row>
-    <row r="166" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="6"/>
       <c r="E166" s="1"/>
       <c r="BO166" s="7"/>
       <c r="BR166" s="7"/>
     </row>
-    <row r="167" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="6"/>
       <c r="E167" s="1"/>
       <c r="BO167" s="7"/>
       <c r="BR167" s="7"/>
     </row>
-    <row r="168" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="6"/>
       <c r="E168" s="1"/>
       <c r="BO168" s="7"/>
       <c r="BR168" s="7"/>
     </row>
-    <row r="169" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="6"/>
       <c r="E169" s="1"/>
       <c r="BO169" s="7"/>
       <c r="BR169" s="7"/>
     </row>
-    <row r="170" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="6"/>
       <c r="E170" s="1"/>
       <c r="BO170" s="7"/>
       <c r="BR170" s="7"/>
     </row>
-    <row r="171" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="6"/>
       <c r="E171" s="1"/>
       <c r="BO171" s="7"/>
       <c r="BR171" s="7"/>
     </row>
-    <row r="172" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="6"/>
       <c r="E172" s="1"/>
       <c r="BO172" s="7"/>
       <c r="BR172" s="7"/>
     </row>
-    <row r="173" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="6"/>
       <c r="E173" s="1"/>
       <c r="BO173" s="7"/>
       <c r="BR173" s="7"/>
     </row>
-    <row r="174" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="6"/>
       <c r="E174" s="1"/>
       <c r="BO174" s="7"/>
       <c r="BR174" s="7"/>
     </row>
-    <row r="175" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="6"/>
       <c r="E175" s="1"/>
       <c r="BO175" s="7"/>
       <c r="BR175" s="7"/>
     </row>
-    <row r="176" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="6"/>
       <c r="E176" s="1"/>
       <c r="BO176" s="7"/>
       <c r="BR176" s="7"/>
     </row>
-    <row r="177" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="6"/>
       <c r="E177" s="1"/>
       <c r="BO177" s="7"/>
       <c r="BR177" s="7"/>
     </row>
-    <row r="178" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="6"/>
       <c r="E178" s="1"/>
       <c r="BO178" s="7"/>
       <c r="BR178" s="7"/>
     </row>
-    <row r="179" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="6"/>
       <c r="E179" s="1"/>
       <c r="BO179" s="7"/>
       <c r="BR179" s="7"/>
     </row>
-    <row r="180" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="6"/>
       <c r="E180" s="1"/>
       <c r="BO180" s="7"/>
       <c r="BR180" s="7"/>
     </row>
-    <row r="181" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="6"/>
       <c r="E181" s="1"/>
       <c r="BO181" s="7"/>
       <c r="BR181" s="7"/>
     </row>
-    <row r="182" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="6"/>
       <c r="E182" s="1"/>
       <c r="BO182" s="7"/>
       <c r="BR182" s="7"/>
     </row>
-    <row r="183" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="6"/>
       <c r="E183" s="1"/>
       <c r="BO183" s="7"/>
       <c r="BR183" s="7"/>
     </row>
-    <row r="184" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="6"/>
       <c r="E184" s="1"/>
       <c r="BO184" s="7"/>
       <c r="BR184" s="7"/>
     </row>
-    <row r="185" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="6"/>
       <c r="E185" s="1"/>
       <c r="BO185" s="7"/>
       <c r="BR185" s="7"/>
     </row>
-    <row r="186" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="6"/>
       <c r="E186" s="1"/>
       <c r="BO186" s="7"/>
       <c r="BR186" s="7"/>
     </row>
-    <row r="187" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="6"/>
       <c r="E187" s="1"/>
       <c r="BO187" s="7"/>
       <c r="BR187" s="7"/>
     </row>
-    <row r="188" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="6"/>
       <c r="E188" s="1"/>
       <c r="BO188" s="7"/>
       <c r="BR188" s="7"/>
     </row>
-    <row r="189" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="6"/>
       <c r="E189" s="1"/>
       <c r="BO189" s="7"/>
       <c r="BR189" s="7"/>
     </row>
-    <row r="190" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="6"/>
       <c r="E190" s="1"/>
       <c r="BO190" s="7"/>
       <c r="BR190" s="7"/>
     </row>
-    <row r="191" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="6"/>
       <c r="E191" s="1"/>
       <c r="BO191" s="7"/>
       <c r="BR191" s="7"/>
     </row>
-    <row r="192" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="6"/>
       <c r="E192" s="1"/>
       <c r="BO192" s="7"/>
       <c r="BR192" s="7"/>
     </row>
-    <row r="193" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="6"/>
       <c r="E193" s="1"/>
       <c r="BO193" s="7"/>
       <c r="BR193" s="7"/>
     </row>
-    <row r="194" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="6"/>
       <c r="E194" s="1"/>
       <c r="BO194" s="7"/>
       <c r="BR194" s="7"/>
     </row>
-    <row r="195" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="6"/>
       <c r="E195" s="1"/>
       <c r="BO195" s="7"/>
       <c r="BR195" s="7"/>
     </row>
-    <row r="196" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="6"/>
       <c r="E196" s="1"/>
       <c r="BO196" s="7"/>
       <c r="BR196" s="7"/>
     </row>
-    <row r="197" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="6"/>
       <c r="E197" s="1"/>
       <c r="BO197" s="7"/>
       <c r="BR197" s="7"/>
     </row>
-    <row r="198" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="6"/>
       <c r="E198" s="1"/>
       <c r="BO198" s="7"/>
       <c r="BR198" s="7"/>
     </row>
-    <row r="199" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="6"/>
       <c r="E199" s="1"/>
       <c r="BO199" s="7"/>
       <c r="BR199" s="7"/>
     </row>
-    <row r="200" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="6"/>
       <c r="E200" s="1"/>
       <c r="BO200" s="7"/>
       <c r="BR200" s="7"/>
     </row>
-    <row r="201" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="6"/>
       <c r="E201" s="1"/>
       <c r="BO201" s="7"/>
       <c r="BR201" s="7"/>
     </row>
-    <row r="202" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="6"/>
       <c r="E202" s="1"/>
       <c r="BO202" s="7"/>
       <c r="BR202" s="7"/>
     </row>
-    <row r="203" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="6"/>
       <c r="E203" s="1"/>
       <c r="BO203" s="7"/>
       <c r="BR203" s="7"/>
     </row>
-    <row r="204" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="6"/>
       <c r="E204" s="1"/>
       <c r="BO204" s="7"/>
       <c r="BR204" s="7"/>
     </row>
-    <row r="205" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="6"/>
       <c r="E205" s="1"/>
       <c r="BO205" s="7"/>
       <c r="BR205" s="7"/>
     </row>
-    <row r="206" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="6"/>
       <c r="E206" s="1"/>
       <c r="BO206" s="7"/>
       <c r="BR206" s="7"/>
     </row>
-    <row r="207" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="6"/>
       <c r="E207" s="1"/>
       <c r="BO207" s="7"/>
       <c r="BR207" s="7"/>
     </row>
-    <row r="208" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="6"/>
       <c r="E208" s="1"/>
       <c r="BO208" s="7"/>
       <c r="BR208" s="7"/>
     </row>
-    <row r="209" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="6"/>
       <c r="E209" s="1"/>
       <c r="BO209" s="7"/>
       <c r="BR209" s="7"/>
     </row>
-    <row r="210" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="6"/>
       <c r="E210" s="1"/>
       <c r="BO210" s="7"/>
       <c r="BR210" s="7"/>
     </row>
-    <row r="211" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="6"/>
       <c r="E211" s="1"/>
       <c r="BO211" s="7"/>
       <c r="BR211" s="7"/>
     </row>
-    <row r="212" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="6"/>
       <c r="E212" s="1"/>
       <c r="BO212" s="7"/>
       <c r="BR212" s="7"/>
     </row>
-    <row r="213" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="6"/>
       <c r="E213" s="1"/>
       <c r="BO213" s="7"/>
       <c r="BR213" s="7"/>
     </row>
-    <row r="214" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="6"/>
       <c r="E214" s="1"/>
       <c r="BO214" s="7"/>
       <c r="BR214" s="7"/>
     </row>
-    <row r="215" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="6"/>
       <c r="E215" s="1"/>
       <c r="BO215" s="7"/>
       <c r="BR215" s="7"/>
     </row>
-    <row r="216" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="6"/>
       <c r="E216" s="1"/>
       <c r="BO216" s="7"/>
       <c r="BR216" s="7"/>
     </row>
-    <row r="217" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="6"/>
       <c r="E217" s="1"/>
       <c r="BO217" s="7"/>
       <c r="BR217" s="7"/>
     </row>
-    <row r="218" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="6"/>
       <c r="E218" s="1"/>
       <c r="BO218" s="7"/>
       <c r="BR218" s="7"/>
     </row>
-    <row r="219" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="6"/>
       <c r="E219" s="1"/>
       <c r="BO219" s="7"/>
       <c r="BR219" s="7"/>
     </row>
-    <row r="220" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="6"/>
       <c r="E220" s="1"/>
       <c r="BO220" s="7"/>
       <c r="BR220" s="7"/>
     </row>
-    <row r="221" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="6"/>
       <c r="E221" s="1"/>
       <c r="BO221" s="7"/>
       <c r="BR221" s="7"/>
     </row>
-    <row r="222" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="6"/>
       <c r="E222" s="1"/>
       <c r="BO222" s="7"/>
       <c r="BR222" s="7"/>
     </row>
-    <row r="223" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="6"/>
       <c r="E223" s="1"/>
       <c r="BO223" s="7"/>
       <c r="BR223" s="7"/>
     </row>
-    <row r="224" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="6"/>
       <c r="E224" s="1"/>
       <c r="BO224" s="7"/>
       <c r="BR224" s="7"/>
     </row>
-    <row r="225" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="6"/>
       <c r="E225" s="1"/>
       <c r="BO225" s="7"/>
       <c r="BR225" s="7"/>
     </row>
-    <row r="226" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="6"/>
       <c r="E226" s="1"/>
       <c r="BO226" s="7"/>
       <c r="BR226" s="7"/>
     </row>
-    <row r="227" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="6"/>
       <c r="E227" s="1"/>
       <c r="BO227" s="7"/>
       <c r="BR227" s="7"/>
     </row>
-    <row r="228" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="6"/>
       <c r="E228" s="1"/>
       <c r="BO228" s="7"/>
       <c r="BR228" s="7"/>
     </row>
-    <row r="229" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="6"/>
       <c r="E229" s="1"/>
       <c r="BO229" s="7"/>
       <c r="BR229" s="7"/>
     </row>
-    <row r="230" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="6"/>
       <c r="E230" s="1"/>
       <c r="BO230" s="7"/>
       <c r="BR230" s="7"/>
     </row>
-    <row r="231" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="6"/>
       <c r="E231" s="1"/>
       <c r="BO231" s="7"/>
       <c r="BR231" s="7"/>
     </row>
-    <row r="232" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="6"/>
       <c r="E232" s="1"/>
       <c r="BO232" s="7"/>
       <c r="BR232" s="7"/>
     </row>
-    <row r="233" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="6"/>
       <c r="E233" s="1"/>
       <c r="BO233" s="7"/>
       <c r="BR233" s="7"/>
     </row>
-    <row r="234" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="6"/>
       <c r="E234" s="1"/>
       <c r="BO234" s="7"/>
       <c r="BR234" s="7"/>
     </row>
-    <row r="235" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="6"/>
       <c r="E235" s="1"/>
       <c r="BO235" s="7"/>
       <c r="BR235" s="7"/>
     </row>
-    <row r="236" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="6"/>
       <c r="E236" s="1"/>
       <c r="BO236" s="7"/>
       <c r="BR236" s="7"/>
     </row>
-    <row r="237" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="6"/>
       <c r="E237" s="1"/>
       <c r="BO237" s="7"/>
       <c r="BR237" s="7"/>
     </row>
-    <row r="238" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="6"/>
       <c r="E238" s="1"/>
       <c r="BO238" s="7"/>
       <c r="BR238" s="7"/>
     </row>
-    <row r="239" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="6"/>
       <c r="E239" s="1"/>
       <c r="BO239" s="7"/>
       <c r="BR239" s="7"/>
     </row>
-    <row r="240" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="6"/>
       <c r="E240" s="1"/>
       <c r="BO240" s="7"/>
       <c r="BR240" s="7"/>
     </row>
-    <row r="241" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="6"/>
       <c r="E241" s="1"/>
       <c r="BO241" s="7"/>
       <c r="BR241" s="7"/>
     </row>
-    <row r="242" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="6"/>
       <c r="E242" s="1"/>
       <c r="BO242" s="7"/>
       <c r="BR242" s="7"/>
     </row>
-    <row r="243" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="6"/>
       <c r="E243" s="1"/>
       <c r="BR243" s="7"/>
     </row>
-    <row r="244" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="6"/>
       <c r="E244" s="1"/>
       <c r="BO244" s="7"/>
       <c r="BR244" s="7"/>
     </row>
-    <row r="245" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="6"/>
       <c r="E245" s="1"/>
       <c r="BO245" s="7"/>
       <c r="BR245" s="7"/>
     </row>
-    <row r="246" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="6"/>
       <c r="E246" s="1"/>
       <c r="BO246" s="7"/>
       <c r="BR246" s="7"/>
     </row>
-    <row r="247" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="6"/>
       <c r="E247" s="1"/>
       <c r="BO247" s="7"/>
       <c r="BR247" s="7"/>
     </row>
-    <row r="248" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="6"/>
       <c r="E248" s="1"/>
       <c r="BO248" s="7"/>
       <c r="BR248" s="7"/>
     </row>
-    <row r="249" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="6"/>
       <c r="E249" s="1"/>
       <c r="BO249" s="7"/>
       <c r="BR249" s="7"/>
     </row>
-    <row r="250" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="6"/>
       <c r="E250" s="1"/>
       <c r="BO250" s="7"/>
       <c r="BR250" s="7"/>
     </row>
-    <row r="251" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="6"/>
       <c r="E251" s="1"/>
       <c r="BO251" s="7"/>
       <c r="BR251" s="7"/>
     </row>
-    <row r="252" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="6"/>
       <c r="E252" s="1"/>
       <c r="BO252" s="7"/>
       <c r="BR252" s="7"/>
     </row>
-    <row r="253" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="6"/>
       <c r="E253" s="1"/>
       <c r="BO253" s="7"/>
       <c r="BR253" s="7"/>
     </row>
-    <row r="254" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="6"/>
       <c r="E254" s="1"/>
       <c r="BO254" s="7"/>
       <c r="BR254" s="7"/>
     </row>
-    <row r="255" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="6"/>
       <c r="E255" s="1"/>
       <c r="BO255" s="7"/>
       <c r="BR255" s="7"/>
     </row>
-    <row r="256" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="6"/>
       <c r="E256" s="1"/>
       <c r="BO256" s="7"/>
       <c r="BR256" s="7"/>
     </row>
-    <row r="257" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="6"/>
       <c r="E257" s="1"/>
       <c r="BO257" s="7"/>
       <c r="BR257" s="7"/>
     </row>
-    <row r="258" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="6"/>
       <c r="E258" s="1"/>
       <c r="BO258" s="7"/>
       <c r="BR258" s="7"/>
     </row>
-    <row r="259" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="6"/>
       <c r="E259" s="1"/>
       <c r="BO259" s="7"/>
       <c r="BR259" s="7"/>
     </row>
-    <row r="260" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="6"/>
       <c r="E260" s="1"/>
       <c r="BO260" s="7"/>
       <c r="BR260" s="7"/>
     </row>
-    <row r="261" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="6"/>
       <c r="E261" s="1"/>
       <c r="BO261" s="7"/>
       <c r="BR261" s="7"/>
     </row>
-    <row r="262" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="6"/>
       <c r="E262" s="1"/>
       <c r="BO262" s="7"/>
       <c r="BR262" s="7"/>
     </row>
-    <row r="263" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="6"/>
       <c r="E263" s="1"/>
       <c r="BO263" s="7"/>
       <c r="BR263" s="7"/>
     </row>
-    <row r="264" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="6"/>
       <c r="E264" s="1"/>
       <c r="BO264" s="7"/>
       <c r="BR264" s="7"/>
     </row>
-    <row r="265" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="6"/>
       <c r="E265" s="1"/>
       <c r="BO265" s="7"/>
       <c r="BR265" s="7"/>
     </row>
-    <row r="266" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="6"/>
       <c r="E266" s="1"/>
       <c r="BO266" s="7"/>
       <c r="BR266" s="7"/>
     </row>
-    <row r="267" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="6"/>
       <c r="E267" s="1"/>
       <c r="BO267" s="7"/>
       <c r="BR267" s="7"/>
     </row>
-    <row r="268" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="6"/>
       <c r="E268" s="1"/>
       <c r="BO268" s="7"/>
       <c r="BR268" s="7"/>
     </row>
-    <row r="269" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="6"/>
       <c r="E269" s="1"/>
       <c r="BO269" s="7"/>
       <c r="BR269" s="7"/>
     </row>
-    <row r="270" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="6"/>
       <c r="E270" s="1"/>
       <c r="BO270" s="7"/>
       <c r="BR270" s="7"/>
     </row>
-    <row r="271" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="6"/>
       <c r="E271" s="1"/>
       <c r="BO271" s="7"/>
       <c r="BR271" s="7"/>
     </row>
-    <row r="272" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="6"/>
       <c r="E272" s="1"/>
       <c r="BO272" s="7"/>
       <c r="BR272" s="7"/>
     </row>
-    <row r="273" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="6"/>
       <c r="E273" s="1"/>
       <c r="BO273" s="7"/>
       <c r="BR273" s="7"/>
     </row>
-    <row r="274" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="6"/>
       <c r="E274" s="1"/>
       <c r="BO274" s="7"/>
       <c r="BR274" s="7"/>
     </row>
-    <row r="275" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="6"/>
       <c r="E275" s="1"/>
       <c r="BO275" s="7"/>
       <c r="BR275" s="7"/>
     </row>
-    <row r="276" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="6"/>
       <c r="E276" s="1"/>
       <c r="BO276" s="7"/>
       <c r="BR276" s="7"/>
     </row>
-    <row r="277" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="6"/>
       <c r="E277" s="1"/>
       <c r="BO277" s="7"/>
       <c r="BR277" s="7"/>
     </row>
-    <row r="278" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="6"/>
       <c r="E278" s="1"/>
       <c r="BO278" s="7"/>
       <c r="BR278" s="7"/>
     </row>
-    <row r="279" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="6"/>
       <c r="E279" s="1"/>
       <c r="BO279" s="7"/>
       <c r="BR279" s="7"/>
     </row>
-    <row r="280" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="6"/>
       <c r="E280" s="1"/>
       <c r="BO280" s="7"/>
       <c r="BR280" s="7"/>
     </row>
-    <row r="281" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="6"/>
       <c r="E281" s="1"/>
       <c r="BO281" s="7"/>
       <c r="BR281" s="7"/>
     </row>
-    <row r="282" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="6"/>
       <c r="E282" s="1"/>
       <c r="BO282" s="7"/>
       <c r="BR282" s="7"/>
     </row>
-    <row r="283" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="6"/>
       <c r="E283" s="1"/>
       <c r="BO283" s="7"/>
       <c r="BR283" s="7"/>
     </row>
-    <row r="284" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="6"/>
       <c r="E284" s="1"/>
       <c r="BO284" s="7"/>
       <c r="BR284" s="7"/>
     </row>
-    <row r="285" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="6"/>
       <c r="E285" s="1"/>
       <c r="BO285" s="7"/>
       <c r="BR285" s="7"/>
     </row>
-    <row r="286" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="6"/>
       <c r="E286" s="1"/>
       <c r="BR286" s="7"/>
     </row>
-    <row r="287" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="6"/>
       <c r="E287" s="1"/>
       <c r="BO287" s="7"/>
       <c r="BR287" s="7"/>
     </row>
-    <row r="288" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="6"/>
       <c r="E288" s="1"/>
       <c r="BO288" s="7"/>
       <c r="BR288" s="7"/>
     </row>
-    <row r="289" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="6"/>
       <c r="E289" s="1"/>
       <c r="BO289" s="7"/>
       <c r="BR289" s="7"/>
     </row>
-    <row r="290" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="6"/>
       <c r="E290" s="1"/>
       <c r="BO290" s="7"/>
       <c r="BR290" s="7"/>
     </row>
-    <row r="291" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="6"/>
       <c r="E291" s="1"/>
       <c r="BO291" s="7"/>
       <c r="BR291" s="7"/>
     </row>
-    <row r="292" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="6"/>
       <c r="E292" s="1"/>
       <c r="BO292" s="7"/>
       <c r="BR292" s="7"/>
     </row>
-    <row r="293" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="6"/>
       <c r="E293" s="1"/>
       <c r="BO293" s="7"/>
       <c r="BR293" s="7"/>
     </row>
-    <row r="294" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="6"/>
       <c r="E294" s="1"/>
       <c r="BO294" s="7"/>
       <c r="BR294" s="7"/>
     </row>
-    <row r="295" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="6"/>
       <c r="E295" s="1"/>
       <c r="BO295" s="7"/>
       <c r="BR295" s="7"/>
     </row>
-    <row r="296" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="6"/>
       <c r="E296" s="1"/>
       <c r="BO296" s="7"/>
       <c r="BR296" s="7"/>
     </row>
-    <row r="297" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="6"/>
       <c r="E297" s="1"/>
       <c r="BO297" s="7"/>
       <c r="BR297" s="7"/>
     </row>
-    <row r="298" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="6"/>
       <c r="E298" s="1"/>
       <c r="BO298" s="7"/>
       <c r="BR298" s="7"/>
     </row>
-    <row r="299" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="6"/>
       <c r="E299" s="1"/>
       <c r="BO299" s="7"/>
       <c r="BR299" s="7"/>
     </row>
-    <row r="300" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="6"/>
       <c r="E300" s="1"/>
       <c r="BO300" s="7"/>
       <c r="BR300" s="7"/>
     </row>
-    <row r="301" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="6"/>
       <c r="E301" s="1"/>
       <c r="BO301" s="7"/>
       <c r="BR301" s="7"/>
     </row>
-    <row r="302" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="6"/>
       <c r="E302" s="1"/>
       <c r="BO302" s="7"/>
       <c r="BR302" s="7"/>
     </row>
-    <row r="303" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="6"/>
       <c r="E303" s="1"/>
       <c r="BO303" s="7"/>
       <c r="BR303" s="7"/>
     </row>
-    <row r="304" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="6"/>
       <c r="E304" s="1"/>
       <c r="BO304" s="7"/>
       <c r="BR304" s="7"/>
     </row>
-    <row r="305" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="6"/>
       <c r="E305" s="1"/>
       <c r="BO305" s="7"/>
       <c r="BR305" s="7"/>
     </row>
-    <row r="306" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="6"/>
       <c r="E306" s="1"/>
       <c r="BO306" s="7"/>
       <c r="BR306" s="7"/>
     </row>
-    <row r="307" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="6"/>
       <c r="E307" s="1"/>
       <c r="BO307" s="7"/>
       <c r="BR307" s="7"/>
     </row>
-    <row r="308" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="6"/>
       <c r="E308" s="1"/>
       <c r="BO308" s="7"/>
       <c r="BR308" s="7"/>
     </row>
-    <row r="309" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="6"/>
       <c r="E309" s="1"/>
       <c r="BO309" s="7"/>
       <c r="BR309" s="7"/>
     </row>
-    <row r="310" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="6"/>
       <c r="E310" s="1"/>
       <c r="BO310" s="7"/>
       <c r="BR310" s="7"/>
     </row>
-    <row r="311" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="6"/>
       <c r="E311" s="1"/>
       <c r="BO311" s="7"/>
       <c r="BR311" s="7"/>
     </row>
-    <row r="312" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="6"/>
       <c r="E312" s="1"/>
       <c r="BO312" s="7"/>
       <c r="BR312" s="7"/>
     </row>
-    <row r="313" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="6"/>
       <c r="E313" s="1"/>
       <c r="BO313" s="7"/>
       <c r="BR313" s="7"/>
     </row>
-    <row r="314" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="6"/>
       <c r="E314" s="1"/>
       <c r="BO314" s="7"/>
       <c r="BR314" s="7"/>
     </row>
-    <row r="315" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="6"/>
       <c r="E315" s="1"/>
       <c r="BO315" s="7"/>
       <c r="BR315" s="7"/>
     </row>
-    <row r="316" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="6"/>
       <c r="E316" s="1"/>
       <c r="BO316" s="7"/>
       <c r="BR316" s="7"/>
     </row>
-    <row r="317" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="6"/>
       <c r="E317" s="1"/>
       <c r="BO317" s="7"/>
       <c r="BR317" s="7"/>
     </row>
-    <row r="318" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="6"/>
       <c r="E318" s="1"/>
       <c r="BO318" s="7"/>
       <c r="BR318" s="7"/>
     </row>
-    <row r="319" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="6"/>
       <c r="E319" s="1"/>
       <c r="BO319" s="7"/>
       <c r="BR319" s="7"/>
     </row>
-    <row r="320" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="6"/>
       <c r="E320" s="1"/>
       <c r="BO320" s="7"/>
       <c r="BR320" s="7"/>
     </row>
-    <row r="321" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="6"/>
       <c r="E321" s="1"/>
       <c r="BO321" s="7"/>
       <c r="BR321" s="7"/>
     </row>
-    <row r="322" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="6"/>
       <c r="E322" s="1"/>
       <c r="BO322" s="7"/>
       <c r="BR322" s="7"/>
     </row>
-    <row r="323" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="6"/>
       <c r="E323" s="1"/>
       <c r="BO323" s="7"/>
       <c r="BR323" s="7"/>
     </row>
-    <row r="324" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="6"/>
       <c r="E324" s="1"/>
       <c r="BO324" s="7"/>
       <c r="BR324" s="7"/>
     </row>
-    <row r="325" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="6"/>
       <c r="E325" s="1"/>
       <c r="BO325" s="7"/>
       <c r="BR325" s="7"/>
     </row>
-    <row r="326" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="6"/>
       <c r="E326" s="1"/>
       <c r="BO326" s="7"/>
       <c r="BR326" s="7"/>
     </row>
-    <row r="327" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="6"/>
       <c r="E327" s="1"/>
       <c r="BO327" s="7"/>
       <c r="BR327" s="7"/>
     </row>
-    <row r="328" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="6"/>
       <c r="E328" s="1"/>
       <c r="BO328" s="7"/>
       <c r="BR328" s="7"/>
     </row>
-    <row r="329" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="6"/>
       <c r="E329" s="1"/>
       <c r="BO329" s="7"/>
       <c r="BR329" s="7"/>
     </row>
-    <row r="330" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="6"/>
       <c r="E330" s="1"/>
       <c r="BO330" s="7"/>
       <c r="BR330" s="7"/>
     </row>
-    <row r="331" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="6"/>
       <c r="E331" s="1"/>
       <c r="BO331" s="7"/>
       <c r="BR331" s="7"/>
     </row>
-    <row r="332" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="6"/>
       <c r="E332" s="1"/>
       <c r="BO332" s="7"/>
       <c r="BR332" s="7"/>
     </row>
-    <row r="333" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="6"/>
       <c r="E333" s="1"/>
       <c r="BO333" s="7"/>
       <c r="BR333" s="7"/>
     </row>
-    <row r="334" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="6"/>
       <c r="E334" s="1"/>
       <c r="BO334" s="7"/>
       <c r="BR334" s="7"/>
     </row>
-    <row r="335" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="6"/>
       <c r="E335" s="1"/>
       <c r="BO335" s="7"/>
       <c r="BR335" s="7"/>
     </row>
-    <row r="336" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="6"/>
       <c r="E336" s="1"/>
       <c r="BO336" s="7"/>
       <c r="BR336" s="7"/>
     </row>
-    <row r="337" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="6"/>
       <c r="E337" s="1"/>
       <c r="BO337" s="7"/>
       <c r="BR337" s="7"/>
     </row>
-    <row r="338" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="6"/>
       <c r="E338" s="1"/>
       <c r="BO338" s="7"/>
       <c r="BR338" s="7"/>
     </row>
-    <row r="339" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="6"/>
       <c r="E339" s="1"/>
       <c r="BO339" s="7"/>
       <c r="BR339" s="7"/>
     </row>
-    <row r="340" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="6"/>
       <c r="E340" s="1"/>
       <c r="BO340" s="7"/>
       <c r="BR340" s="7"/>
     </row>
-    <row r="341" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="6"/>
       <c r="E341" s="1"/>
       <c r="BO341" s="7"/>
       <c r="BR341" s="7"/>
     </row>
-    <row r="342" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="6"/>
       <c r="E342" s="1"/>
       <c r="BR342" s="7"/>
     </row>
-    <row r="343" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="6"/>
       <c r="E343" s="1"/>
       <c r="BR343" s="7"/>
     </row>
-    <row r="344" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="6"/>
       <c r="E344" s="1"/>
       <c r="BR344" s="7"/>
     </row>
-    <row r="345" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="6"/>
       <c r="E345" s="1"/>
       <c r="BO345" s="7"/>
       <c r="BR345" s="7"/>
     </row>
-    <row r="346" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="6"/>
       <c r="E346" s="1"/>
       <c r="BO346" s="7"/>
       <c r="BR346" s="7"/>
     </row>
-    <row r="347" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="6"/>
       <c r="E347" s="1"/>
       <c r="BO347" s="7"/>
       <c r="BR347" s="7"/>
     </row>
-    <row r="348" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="6"/>
       <c r="E348" s="1"/>
       <c r="BO348" s="7"/>
       <c r="BR348" s="7"/>
     </row>
-    <row r="349" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="6"/>
       <c r="E349" s="1"/>
       <c r="BO349" s="7"/>
       <c r="BR349" s="7"/>
     </row>
-    <row r="350" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="6"/>
       <c r="E350" s="1"/>
       <c r="BO350" s="7"/>
       <c r="BR350" s="7"/>
     </row>
-    <row r="351" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="6"/>
       <c r="E351" s="1"/>
       <c r="BO351" s="7"/>
       <c r="BR351" s="7"/>
     </row>
-    <row r="352" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="6"/>
       <c r="E352" s="1"/>
       <c r="BO352" s="7"/>
       <c r="BR352" s="7"/>
     </row>
-    <row r="353" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="6"/>
       <c r="E353" s="1"/>
       <c r="BO353" s="7"/>
       <c r="BR353" s="7"/>
     </row>
-    <row r="354" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="6"/>
       <c r="E354" s="1"/>
       <c r="BO354" s="7"/>
       <c r="BR354" s="7"/>
     </row>
-    <row r="355" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="6"/>
       <c r="E355" s="1"/>
       <c r="BO355" s="7"/>
       <c r="BR355" s="7"/>
     </row>
-    <row r="356" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="6"/>
       <c r="E356" s="1"/>
       <c r="BO356" s="7"/>
       <c r="BR356" s="7"/>
     </row>
-    <row r="357" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="6"/>
       <c r="E357" s="1"/>
       <c r="BO357" s="7"/>
       <c r="BR357" s="7"/>
     </row>
-    <row r="358" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="6"/>
       <c r="E358" s="1"/>
       <c r="BO358" s="7"/>
       <c r="BR358" s="7"/>
     </row>
-    <row r="359" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="6"/>
       <c r="E359" s="1"/>
       <c r="BO359" s="7"/>
       <c r="BR359" s="7"/>
     </row>
-    <row r="360" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="6"/>
       <c r="E360" s="1"/>
       <c r="BO360" s="7"/>
       <c r="BR360" s="7"/>
     </row>
-    <row r="361" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="6"/>
       <c r="E361" s="1"/>
       <c r="BO361" s="7"/>
       <c r="BR361" s="7"/>
     </row>
-    <row r="362" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="6"/>
       <c r="E362" s="1"/>
       <c r="BO362" s="7"/>
       <c r="BR362" s="7"/>
     </row>
-    <row r="363" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="6"/>
       <c r="E363" s="1"/>
       <c r="BO363" s="7"/>
       <c r="BR363" s="7"/>
     </row>
-    <row r="364" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="6"/>
       <c r="E364" s="1"/>
       <c r="BO364" s="7"/>
       <c r="BR364" s="7"/>
     </row>
-    <row r="365" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="6"/>
       <c r="E365" s="1"/>
       <c r="BO365" s="7"/>
       <c r="BR365" s="7"/>
     </row>
-    <row r="366" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="6"/>
       <c r="E366" s="1"/>
       <c r="BO366" s="7"/>
       <c r="BR366" s="7"/>
     </row>
-    <row r="367" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="6"/>
       <c r="E367" s="1"/>
       <c r="BO367" s="7"/>
       <c r="BR367" s="7"/>
     </row>
-    <row r="368" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="6"/>
       <c r="E368" s="1"/>
       <c r="BO368" s="7"/>
       <c r="BR368" s="7"/>
     </row>
-    <row r="369" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="6"/>
       <c r="E369" s="1"/>
       <c r="BO369" s="7"/>
       <c r="BR369" s="7"/>
     </row>
-    <row r="370" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="6"/>
       <c r="E370" s="1"/>
       <c r="BO370" s="7"/>
       <c r="BR370" s="7"/>
     </row>
-    <row r="371" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="6"/>
       <c r="E371" s="1"/>
       <c r="BO371" s="7"/>
       <c r="BR371" s="7"/>
     </row>
-    <row r="372" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="6"/>
       <c r="E372" s="1"/>
       <c r="BO372" s="7"/>
       <c r="BR372" s="7"/>
     </row>
-    <row r="373" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="6"/>
       <c r="E373" s="1"/>
       <c r="BO373" s="7"/>
       <c r="BR373" s="7"/>
     </row>
-    <row r="374" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="6"/>
       <c r="E374" s="1"/>
       <c r="BO374" s="7"/>
       <c r="BR374" s="7"/>
     </row>
-    <row r="375" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="6"/>
       <c r="E375" s="1"/>
       <c r="BO375" s="7"/>
       <c r="BR375" s="7"/>
     </row>
-    <row r="376" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="6"/>
       <c r="E376" s="1"/>
       <c r="BO376" s="7"/>
       <c r="BR376" s="7"/>
     </row>
-    <row r="377" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="6"/>
       <c r="E377" s="1"/>
       <c r="BO377" s="7"/>
       <c r="BR377" s="7"/>
     </row>
-    <row r="378" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="6"/>
       <c r="E378" s="1"/>
       <c r="BO378" s="7"/>
       <c r="BR378" s="7"/>
     </row>
-    <row r="379" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="6"/>
       <c r="E379" s="1"/>
       <c r="BR379" s="7"/>
     </row>
-    <row r="380" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="6"/>
       <c r="E380" s="1"/>
       <c r="BR380" s="7"/>
     </row>
-    <row r="381" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="6"/>
       <c r="E381" s="1"/>
       <c r="BO381" s="7"/>
       <c r="BR381" s="7"/>
     </row>
-    <row r="382" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="6"/>
       <c r="E382" s="1"/>
       <c r="BO382" s="7"/>
       <c r="BR382" s="7"/>
     </row>
-    <row r="383" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="6"/>
       <c r="E383" s="1"/>
       <c r="BO383" s="7"/>
       <c r="BR383" s="7"/>
     </row>
-    <row r="384" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="6"/>
       <c r="E384" s="1"/>
       <c r="BO384" s="7"/>
       <c r="BR384" s="7"/>
     </row>
-    <row r="385" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="6"/>
       <c r="E385" s="1"/>
       <c r="BO385" s="7"/>
       <c r="BR385" s="7"/>
     </row>
-    <row r="386" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="6"/>
       <c r="E386" s="1"/>
       <c r="BO386" s="7"/>
       <c r="BR386" s="7"/>
     </row>
-    <row r="387" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="6"/>
       <c r="E387" s="1"/>
       <c r="BO387" s="7"/>
       <c r="BR387" s="7"/>
     </row>
-    <row r="388" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="6"/>
       <c r="E388" s="1"/>
       <c r="BO388" s="7"/>
       <c r="BR388" s="7"/>
     </row>
-    <row r="389" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="6"/>
       <c r="E389" s="1"/>
       <c r="BO389" s="7"/>
       <c r="BR389" s="7"/>
     </row>
-    <row r="390" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="6"/>
       <c r="E390" s="1"/>
       <c r="BO390" s="7"/>
       <c r="BR390" s="7"/>
     </row>
-    <row r="391" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="6"/>
       <c r="E391" s="1"/>
       <c r="BO391" s="7"/>
       <c r="BR391" s="7"/>
     </row>
-    <row r="392" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="6"/>
       <c r="E392" s="1"/>
       <c r="BO392" s="7"/>
       <c r="BR392" s="7"/>
     </row>
-    <row r="393" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="6"/>
       <c r="E393" s="1"/>
       <c r="BO393" s="7"/>
       <c r="BR393" s="7"/>
     </row>
-    <row r="394" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="6"/>
       <c r="E394" s="1"/>
       <c r="BO394" s="7"/>
       <c r="BR394" s="7"/>
     </row>
-    <row r="395" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="6"/>
       <c r="E395" s="1"/>
       <c r="BO395" s="7"/>
       <c r="BR395" s="7"/>
     </row>
-    <row r="396" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="6"/>
       <c r="E396" s="1"/>
       <c r="BO396" s="7"/>
       <c r="BR396" s="7"/>
     </row>
-    <row r="397" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="6"/>
       <c r="E397" s="1"/>
       <c r="BO397" s="7"/>
       <c r="BR397" s="7"/>
     </row>
-    <row r="398" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="6"/>
       <c r="E398" s="1"/>
       <c r="BO398" s="7"/>
       <c r="BR398" s="7"/>
     </row>
-    <row r="399" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="6"/>
       <c r="E399" s="1"/>
       <c r="BO399" s="7"/>
       <c r="BR399" s="7"/>
     </row>
-    <row r="400" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="6"/>
       <c r="E400" s="1"/>
       <c r="BO400" s="7"/>
       <c r="BR400" s="7"/>
     </row>
-    <row r="401" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="6"/>
       <c r="E401" s="1"/>
       <c r="BO401" s="7"/>
       <c r="BR401" s="7"/>
     </row>
-    <row r="402" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="6"/>
       <c r="E402" s="1"/>
       <c r="BO402" s="7"/>
       <c r="BR402" s="7"/>
     </row>
-    <row r="403" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="6"/>
       <c r="E403" s="1"/>
       <c r="BO403" s="7"/>
       <c r="BR403" s="7"/>
     </row>
-    <row r="404" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="6"/>
       <c r="E404" s="1"/>
       <c r="BR404" s="7"/>
     </row>
-    <row r="405" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="6"/>
       <c r="E405" s="1"/>
       <c r="BR405" s="7"/>
     </row>
-    <row r="406" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="6"/>
       <c r="E406" s="1"/>
       <c r="BO406" s="7"/>
       <c r="BR406" s="7"/>
     </row>
-    <row r="407" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="6"/>
       <c r="E407" s="1"/>
       <c r="BO407" s="7"/>
       <c r="BR407" s="7"/>
     </row>
-    <row r="408" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="6"/>
       <c r="E408" s="1"/>
       <c r="BR408" s="7"/>
     </row>
-    <row r="409" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="6"/>
       <c r="E409" s="1"/>
       <c r="BR409" s="7"/>
     </row>
-    <row r="410" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D410" s="6"/>
       <c r="E410" s="1"/>
       <c r="BO410" s="7"/>
       <c r="BR410" s="7"/>
     </row>
-    <row r="411" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D411" s="6"/>
       <c r="E411" s="1"/>
       <c r="BO411" s="7"/>
       <c r="BR411" s="7"/>
     </row>
-    <row r="412" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D412" s="6"/>
       <c r="E412" s="1"/>
       <c r="BO412" s="7"/>
       <c r="BR412" s="7"/>
     </row>
-    <row r="413" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D413" s="6"/>
       <c r="E413" s="1"/>
       <c r="BO413" s="7"/>
       <c r="BR413" s="7"/>
     </row>
-    <row r="414" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D414" s="6"/>
       <c r="E414" s="1"/>
       <c r="BO414" s="7"/>
       <c r="BR414" s="7"/>
     </row>
-    <row r="415" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D415" s="6"/>
       <c r="E415" s="1"/>
       <c r="BO415" s="7"/>
       <c r="BR415" s="7"/>
     </row>
-    <row r="416" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D416" s="6"/>
       <c r="E416" s="1"/>
       <c r="BO416" s="7"/>
       <c r="BR416" s="7"/>
     </row>
-    <row r="417" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D417" s="6"/>
       <c r="E417" s="1"/>
       <c r="BO417" s="7"/>
       <c r="BR417" s="7"/>
     </row>
-    <row r="418" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D418" s="6"/>
       <c r="E418" s="1"/>
       <c r="BO418" s="7"/>
       <c r="BR418" s="7"/>
     </row>
-    <row r="419" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D419" s="6"/>
       <c r="E419" s="1"/>
       <c r="BO419" s="7"/>
       <c r="BR419" s="7"/>
     </row>
-    <row r="420" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D420" s="6"/>
       <c r="E420" s="1"/>
       <c r="BO420" s="7"/>
       <c r="BR420" s="7"/>
     </row>
-    <row r="421" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D421" s="6"/>
       <c r="E421" s="1"/>
       <c r="BO421" s="7"/>
       <c r="BR421" s="7"/>
     </row>
-    <row r="422" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D422" s="6"/>
       <c r="E422" s="1"/>
       <c r="BO422" s="7"/>
       <c r="BR422" s="7"/>
     </row>
-    <row r="423" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D423" s="6"/>
       <c r="E423" s="1"/>
       <c r="BO423" s="7"/>
       <c r="BR423" s="7"/>
     </row>
-    <row r="424" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D424" s="6"/>
       <c r="E424" s="1"/>
       <c r="BO424" s="7"/>
       <c r="BR424" s="7"/>
     </row>
-    <row r="425" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D425" s="6"/>
       <c r="E425" s="1"/>
       <c r="BO425" s="7"/>
       <c r="BR425" s="7"/>
     </row>
-    <row r="426" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D426" s="6"/>
       <c r="E426" s="1"/>
       <c r="BO426" s="7"/>
       <c r="BR426" s="7"/>
     </row>
-    <row r="427" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D427" s="6"/>
       <c r="E427" s="1"/>
     </row>
-    <row r="428" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D428" s="6"/>
       <c r="E428" s="1"/>
     </row>
-    <row r="429" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D429" s="6"/>
       <c r="E429" s="1"/>
     </row>
-    <row r="430" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D430" s="6"/>
       <c r="E430" s="1"/>
     </row>
-    <row r="431" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D431" s="6"/>
       <c r="E431" s="1"/>
     </row>
-    <row r="432" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D432" s="6"/>
       <c r="E432" s="1"/>
     </row>
-    <row r="433" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D433" s="6"/>
       <c r="E433" s="1"/>
     </row>
-    <row r="434" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D434" s="6"/>
       <c r="E434" s="1"/>
     </row>
-    <row r="435" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D435" s="6"/>
       <c r="E435" s="1"/>
     </row>
-    <row r="436" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D436" s="6"/>
       <c r="E436" s="1"/>
     </row>
-    <row r="437" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D437" s="6"/>
       <c r="E437" s="1"/>
     </row>
-    <row r="438" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D438" s="6"/>
       <c r="E438" s="1"/>
     </row>
-    <row r="439" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D439" s="6"/>
       <c r="E439" s="1"/>
     </row>
-    <row r="440" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D440" s="6"/>
       <c r="E440" s="1"/>
     </row>
-    <row r="441" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D441" s="6"/>
       <c r="E441" s="1"/>
     </row>
-    <row r="442" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D442" s="6"/>
       <c r="E442" s="1"/>
     </row>
-    <row r="443" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D443" s="6"/>
       <c r="E443" s="1"/>
     </row>
-    <row r="444" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D444" s="6"/>
       <c r="E444" s="1"/>
     </row>
-    <row r="445" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D445" s="6"/>
       <c r="E445" s="1"/>
     </row>
-    <row r="446" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D446" s="6"/>
       <c r="E446" s="1"/>
     </row>
-    <row r="447" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D447" s="6"/>
       <c r="E447" s="1"/>
     </row>
-    <row r="448" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D448" s="6"/>
       <c r="E448" s="1"/>
     </row>
-    <row r="449" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D449" s="6"/>
       <c r="E449" s="1"/>
     </row>
-    <row r="450" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D450" s="6"/>
       <c r="E450" s="1"/>
     </row>
-    <row r="451" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D451" s="6"/>
       <c r="E451" s="1"/>
     </row>
-    <row r="452" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D452" s="6"/>
       <c r="E452" s="1"/>
     </row>
-    <row r="453" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D453" s="6"/>
       <c r="E453" s="1"/>
     </row>
-    <row r="454" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D454" s="6"/>
       <c r="E454" s="1"/>
     </row>
-    <row r="455" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D455" s="6"/>
       <c r="E455" s="1"/>
     </row>
-    <row r="456" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D456" s="6"/>
       <c r="E456" s="1"/>
     </row>
-    <row r="457" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D457" s="6"/>
       <c r="E457" s="1"/>
     </row>
-    <row r="458" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D458" s="6"/>
       <c r="E458" s="1"/>
     </row>
-    <row r="459" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D459" s="6"/>
       <c r="E459" s="1"/>
     </row>
-    <row r="460" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D460" s="6"/>
       <c r="E460" s="1"/>
     </row>
-    <row r="461" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D461" s="6"/>
       <c r="E461" s="1"/>
     </row>
-    <row r="462" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D462" s="6"/>
       <c r="E462" s="1"/>
     </row>
-    <row r="463" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D463" s="6"/>
       <c r="E463" s="1"/>
     </row>
-    <row r="464" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D464" s="6"/>
       <c r="E464" s="1"/>
     </row>
-    <row r="465" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D465" s="6"/>
       <c r="E465" s="1"/>
     </row>
-    <row r="466" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D466" s="6"/>
       <c r="E466" s="1"/>
     </row>
-    <row r="467" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D467" s="6"/>
       <c r="E467" s="1"/>
     </row>
-    <row r="468" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D468" s="6"/>
       <c r="E468" s="1"/>
     </row>
-    <row r="469" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D469" s="6"/>
       <c r="E469" s="1"/>
     </row>
-    <row r="470" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D470" s="6"/>
       <c r="E470" s="1"/>
     </row>
-    <row r="471" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D471" s="6"/>
       <c r="E471" s="1"/>
     </row>
-    <row r="472" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D472" s="6"/>
       <c r="E472" s="1"/>
     </row>
-    <row r="473" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D473" s="6"/>
       <c r="E473" s="1"/>
     </row>
-    <row r="474" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D474" s="6"/>
       <c r="E474" s="1"/>
     </row>
-    <row r="475" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D475" s="6"/>
       <c r="E475" s="1"/>
     </row>
-    <row r="476" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D476" s="6"/>
       <c r="E476" s="1"/>
     </row>
-    <row r="477" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D477" s="6"/>
       <c r="E477" s="1"/>
     </row>
-    <row r="478" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D478" s="6"/>
       <c r="E478" s="1"/>
     </row>
-    <row r="479" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D479" s="6"/>
       <c r="E479" s="1"/>
     </row>
-    <row r="480" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D480" s="6"/>
       <c r="E480" s="1"/>
     </row>
-    <row r="481" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D481" s="6"/>
       <c r="E481" s="1"/>
     </row>
-    <row r="482" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="482" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D482" s="6"/>
       <c r="E482" s="1"/>
     </row>
-    <row r="483" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="483" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D483" s="6"/>
       <c r="E483" s="1"/>
     </row>
-    <row r="484" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="484" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D484" s="6"/>
       <c r="E484" s="1"/>
     </row>
-    <row r="485" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="485" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D485" s="6"/>
       <c r="E485" s="1"/>
     </row>
-    <row r="486" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="486" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D486" s="6"/>
       <c r="E486" s="1"/>
     </row>
-    <row r="487" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="487" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D487" s="6"/>
       <c r="E487" s="1"/>
     </row>
-    <row r="488" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="488" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D488" s="6"/>
       <c r="E488" s="1"/>
     </row>
-    <row r="489" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="489" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D489" s="6"/>
       <c r="E489" s="1"/>
     </row>
-    <row r="490" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="490" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D490" s="6"/>
       <c r="E490" s="1"/>
     </row>
-    <row r="491" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="491" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D491" s="6"/>
       <c r="E491" s="1"/>
     </row>
-    <row r="492" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="492" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D492" s="6"/>
       <c r="E492" s="1"/>
     </row>
-    <row r="493" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="493" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D493" s="6"/>
       <c r="E493" s="1"/>
     </row>
-    <row r="494" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="494" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D494" s="6"/>
       <c r="E494" s="1"/>
     </row>
-    <row r="495" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="495" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D495" s="6"/>
       <c r="E495" s="1"/>
     </row>
-    <row r="496" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="496" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D496" s="6"/>
       <c r="E496" s="1"/>
     </row>
-    <row r="497" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="497" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D497" s="6"/>
       <c r="E497" s="1"/>
     </row>
-    <row r="498" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="498" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D498" s="6"/>
       <c r="E498" s="1"/>
     </row>
-    <row r="499" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="499" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D499" s="6"/>
       <c r="E499" s="1"/>
     </row>
-    <row r="500" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="500" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D500" s="6"/>
       <c r="E500" s="1"/>
     </row>
-    <row r="501" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="501" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D501" s="6"/>
       <c r="E501" s="1"/>
     </row>
-    <row r="502" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="502" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D502" s="6"/>
       <c r="E502" s="1"/>
     </row>
-    <row r="503" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="503" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D503" s="6"/>
       <c r="E503" s="1"/>
     </row>
-    <row r="504" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="504" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D504" s="6"/>
       <c r="E504" s="1"/>
     </row>
-    <row r="505" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="505" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D505" s="6"/>
       <c r="E505" s="1"/>
     </row>
-    <row r="506" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="506" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D506" s="6"/>
       <c r="E506" s="1"/>
     </row>
-    <row r="574" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="574" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D574" s="6"/>
       <c r="E574" s="1"/>
     </row>
-    <row r="575" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="575" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D575" s="6"/>
       <c r="E575" s="1"/>
     </row>
-    <row r="576" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="576" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D576" s="6"/>
       <c r="E576" s="1"/>
     </row>
-    <row r="577" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="577" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D577" s="6"/>
       <c r="E577" s="1"/>
     </row>
-    <row r="578" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="578" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D578" s="6"/>
       <c r="E578" s="1"/>
     </row>
-    <row r="579" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="579" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D579" s="6"/>
       <c r="E579" s="1"/>
     </row>
-    <row r="580" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="580" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D580" s="6"/>
       <c r="E580" s="1"/>
     </row>
-    <row r="581" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="581" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D581" s="6"/>
       <c r="E581" s="1"/>
     </row>
-    <row r="582" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="582" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D582" s="6"/>
       <c r="E582" s="1"/>
     </row>
-    <row r="583" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="583" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D583" s="6"/>
       <c r="E583" s="1"/>
     </row>
-    <row r="584" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="584" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D584" s="6"/>
       <c r="E584" s="1"/>
     </row>
-    <row r="585" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="585" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D585" s="6"/>
       <c r="E585" s="1"/>
     </row>
-    <row r="586" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="586" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D586" s="6"/>
       <c r="E586" s="1"/>
     </row>
-    <row r="587" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="587" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D587" s="6"/>
       <c r="E587" s="1"/>
     </row>
-    <row r="588" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="588" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D588" s="6"/>
       <c r="E588" s="1"/>
     </row>
-    <row r="589" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="589" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D589" s="6"/>
       <c r="E589" s="1"/>
     </row>
-    <row r="590" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="590" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D590" s="6"/>
       <c r="E590" s="1"/>
     </row>
-    <row r="591" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="591" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D591" s="6"/>
       <c r="E591" s="1"/>
     </row>
-    <row r="592" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="592" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D592" s="6"/>
       <c r="E592" s="1"/>
     </row>
-    <row r="593" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="593" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D593" s="6"/>
       <c r="E593" s="1"/>
     </row>
-    <row r="594" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="594" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D594" s="6"/>
       <c r="E594" s="1"/>
     </row>
-    <row r="595" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="595" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D595" s="6"/>
       <c r="E595" s="1"/>
     </row>
-    <row r="596" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="596" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D596" s="6"/>
       <c r="E596" s="1"/>
     </row>
-    <row r="597" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="597" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D597" s="6"/>
       <c r="E597" s="1"/>
     </row>
-    <row r="598" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="598" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D598" s="6"/>
       <c r="E598" s="1"/>
     </row>
@@ -6536,84 +6623,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:DH840"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08984375" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="7.7265625" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" customWidth="1"/>
-    <col min="6" max="6" width="31.36328125" customWidth="1"/>
-    <col min="7" max="7" width="7.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.81640625" customWidth="1"/>
-    <col min="9" max="9" width="7.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="11" max="13" width="8.36328125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.7265625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.08984375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.54296875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="21.453125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="19.81640625" style="3" customWidth="1"/>
-    <col min="19" max="19" width="16.54296875" style="3" customWidth="1"/>
-    <col min="20" max="20" width="19.08984375" style="3" customWidth="1"/>
-    <col min="21" max="21" width="18.36328125" style="3" customWidth="1"/>
-    <col min="22" max="22" width="17.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.36328125" style="3" customWidth="1"/>
-    <col min="24" max="24" width="18.453125" style="3" customWidth="1"/>
-    <col min="25" max="25" width="16.54296875" customWidth="1"/>
-    <col min="26" max="26" width="10.6328125" customWidth="1"/>
-    <col min="27" max="27" width="8.36328125" customWidth="1"/>
-    <col min="28" max="28" width="15.1796875" customWidth="1"/>
-    <col min="29" max="30" width="8.54296875" customWidth="1"/>
-    <col min="31" max="31" width="13.453125" customWidth="1"/>
-    <col min="32" max="32" width="13.7265625" customWidth="1"/>
-    <col min="33" max="33" width="14.54296875" customWidth="1"/>
-    <col min="34" max="34" width="17.453125" customWidth="1"/>
-    <col min="35" max="35" width="8.54296875" customWidth="1"/>
-    <col min="36" max="36" width="12.453125" customWidth="1"/>
-    <col min="37" max="37" width="8.54296875" customWidth="1"/>
-    <col min="38" max="39" width="8.36328125" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11.75" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="21.5" style="3" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" style="3" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" style="3" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="3" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" style="3" customWidth="1"/>
+    <col min="24" max="24" width="18.5" style="3" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.26953125" customWidth="1"/>
-    <col min="42" max="43" width="11.81640625" customWidth="1"/>
-    <col min="44" max="44" width="18.453125" customWidth="1"/>
-    <col min="45" max="45" width="12.26953125" customWidth="1"/>
-    <col min="46" max="46" width="11.90625" customWidth="1"/>
-    <col min="47" max="47" width="19.54296875" customWidth="1"/>
-    <col min="48" max="48" width="12.6328125" customWidth="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1"/>
+    <col min="42" max="43" width="11.83203125" customWidth="1"/>
+    <col min="44" max="44" width="18.4140625" customWidth="1"/>
+    <col min="45" max="45" width="12.25" customWidth="1"/>
+    <col min="46" max="46" width="11.9140625" customWidth="1"/>
+    <col min="47" max="47" width="19.58203125" customWidth="1"/>
+    <col min="48" max="48" width="12.6640625" customWidth="1"/>
     <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.7265625" customWidth="1"/>
-    <col min="52" max="52" width="19.7265625" customWidth="1"/>
-    <col min="53" max="53" width="5.08984375" customWidth="1"/>
-    <col min="54" max="54" width="8.453125" customWidth="1"/>
-    <col min="55" max="55" width="13.453125" customWidth="1"/>
-    <col min="56" max="56" width="14.6328125" customWidth="1"/>
-    <col min="57" max="57" width="10.1796875" customWidth="1"/>
-    <col min="58" max="58" width="8.26953125" customWidth="1"/>
-    <col min="59" max="65" width="8.36328125" customWidth="1"/>
-    <col min="66" max="68" width="11.26953125" customWidth="1"/>
-    <col min="69" max="69" width="6.54296875" customWidth="1"/>
+    <col min="51" max="51" width="11.75" customWidth="1"/>
+    <col min="52" max="52" width="19.75" customWidth="1"/>
+    <col min="53" max="53" width="5.08203125" customWidth="1"/>
+    <col min="54" max="54" width="8.5" customWidth="1"/>
+    <col min="55" max="55" width="13.5" customWidth="1"/>
+    <col min="56" max="56" width="14.6640625" customWidth="1"/>
+    <col min="57" max="57" width="10.1640625" customWidth="1"/>
+    <col min="58" max="58" width="8.25" customWidth="1"/>
+    <col min="59" max="65" width="8.33203125" customWidth="1"/>
+    <col min="66" max="68" width="11.25" customWidth="1"/>
+    <col min="69" max="69" width="6.58203125" customWidth="1"/>
     <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.36328125" style="4" customWidth="1"/>
-    <col min="73" max="74" width="8.453125" style="4" customWidth="1"/>
-    <col min="75" max="76" width="7.81640625" style="4" customWidth="1"/>
-    <col min="77" max="77" width="22.1796875" style="4" customWidth="1"/>
-    <col min="78" max="78" width="13.453125" customWidth="1"/>
-    <col min="79" max="79" width="21.1796875" customWidth="1"/>
-    <col min="80" max="80" width="15.7265625" customWidth="1"/>
-    <col min="81" max="81" width="15.54296875" customWidth="1"/>
-    <col min="82" max="82" width="12.81640625" customWidth="1"/>
-    <col min="83" max="83" width="16.1796875" customWidth="1"/>
+    <col min="72" max="72" width="7.33203125" style="4" customWidth="1"/>
+    <col min="73" max="74" width="8.5" style="4" customWidth="1"/>
+    <col min="75" max="76" width="7.83203125" style="4" customWidth="1"/>
+    <col min="77" max="77" width="22.1640625" style="4" customWidth="1"/>
+    <col min="78" max="78" width="13.5" customWidth="1"/>
+    <col min="79" max="79" width="21.1640625" customWidth="1"/>
+    <col min="80" max="80" width="15.75" customWidth="1"/>
+    <col min="81" max="81" width="15.58203125" customWidth="1"/>
+    <col min="82" max="82" width="12.83203125" customWidth="1"/>
+    <col min="83" max="83" width="16.1640625" customWidth="1"/>
     <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.81640625" customWidth="1"/>
-    <col min="88" max="88" width="23.54296875" customWidth="1"/>
-    <col min="89" max="89" width="12.81640625" customWidth="1"/>
-    <col min="90" max="90" width="17.08984375" customWidth="1"/>
+    <col min="86" max="87" width="12.83203125" customWidth="1"/>
+    <col min="88" max="88" width="23.58203125" customWidth="1"/>
+    <col min="89" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="17.08203125" customWidth="1"/>
     <col min="97" max="97" width="14" customWidth="1"/>
     <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08984375" customWidth="1"/>
-    <col min="101" max="101" width="13.7265625" customWidth="1"/>
-    <col min="108" max="108" width="15.453125" customWidth="1"/>
+    <col min="100" max="100" width="11.08203125" customWidth="1"/>
+    <col min="101" max="101" width="13.75" customWidth="1"/>
+    <col min="108" max="108" width="15.5" customWidth="1"/>
     <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10176,21 +10263,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="14" max="14" width="16.08984375" customWidth="1"/>
-    <col min="15" max="15" width="9.453125" customWidth="1"/>
-    <col min="16" max="16" width="22.1796875" customWidth="1"/>
-    <col min="17" max="17" width="12.81640625" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10227,11 +10313,8 @@
       <c r="O1" t="s">
         <v>362</v>
       </c>
-      <c r="P1" s="8" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10274,14 +10357,11 @@
       <c r="O2" t="s">
         <v>372</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="P2" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10325,42 +10405,32 @@
         <v>307</v>
       </c>
       <c r="P3" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P6"/>
-    </row>
-    <row r="9" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K9"/>
-      <c r="P9"/>
-    </row>
-    <row r="11" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K11"/>
-      <c r="P11"/>
-    </row>
-    <row r="12" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K12"/>
-      <c r="P12"/>
-    </row>
-    <row r="14" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="J14"/>
-      <c r="P14"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C17" s="14"/>
     </row>
-    <row r="18" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="J18"/>
-      <c r="P18"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="C20" s="8"/>
-      <c r="Q20" s="8"/>
+      <c r="P20" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -10372,11 +10442,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" customWidth="1"/>
-    <col min="4" max="4" width="27.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10425,11 +10495,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
-    <col min="3" max="3" width="27.26953125" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10524,13 +10594,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08984375" customWidth="1"/>
-    <col min="5" max="10" width="11.26953125" customWidth="1"/>
-    <col min="11" max="11" width="6.36328125" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10655,15 +10725,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A2:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" customWidth="1"/>
-    <col min="4" max="4" width="47.81640625" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -10728,6 +10798,116 @@
       </c>
       <c r="J3" t="s">
         <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5F03AD-29EF-4E37-9DA2-4A5EEE4BA8EC}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="21"/>
+    <col min="2" max="2" width="13.83203125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="21" customWidth="1"/>
+    <col min="7" max="7" width="15" style="21" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="21" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="21" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>517</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>518</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>519</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>522</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>523</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>524</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>529</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556AC661-FAD3-4723-AB45-EFA20ACEC91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A914A4A-9674-4760-922B-5E166ED1EF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="532">
   <si>
     <t>Id</t>
   </si>
@@ -1984,6 +1984,14 @@
   </si>
   <si>
     <t>string?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>可无视buff抑制检测</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsCancelable</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -10263,7 +10271,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -10272,11 +10280,12 @@
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="14" max="14" width="16.08203125" customWidth="1"/>
     <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="9" customWidth="1"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10313,8 +10322,11 @@
       <c r="O1" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P1" s="8" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10357,11 +10369,14 @@
       <c r="O2" t="s">
         <v>372</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q2" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10405,32 +10420,42 @@
         <v>307</v>
       </c>
       <c r="P3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P6"/>
+    </row>
+    <row r="9" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K9"/>
-    </row>
-    <row r="11" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P9"/>
+    </row>
+    <row r="11" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K11"/>
-    </row>
-    <row r="12" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P11"/>
+    </row>
+    <row r="12" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K12"/>
-    </row>
-    <row r="14" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P12"/>
+    </row>
+    <row r="14" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="J14"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P14"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C17" s="14"/>
     </row>
-    <row r="18" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="J18"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P18"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="C20" s="8"/>
-      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A914A4A-9674-4760-922B-5E166ED1EF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B247D40-FF86-4C27-9C18-78DC440C46C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3338" yWindow="1421" windowWidth="17953" windowHeight="10398" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -1987,12 +1987,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>可无视buff抑制检测</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsCancelable</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>不可被抵挡</t>
+  </si>
+  <si>
+    <t>NotCancelable</t>
   </si>
 </sst>
 </file>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B247D40-FF86-4C27-9C18-78DC440C46C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD2AB6C-972D-448F-B35B-D05025FC0818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3338" yWindow="1421" windowWidth="17953" windowHeight="10398" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="537">
   <si>
     <t>Id</t>
   </si>
@@ -1520,10 +1520,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>char_263_skadi</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Hip</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -1983,14 +1979,38 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>string?</t>
+    <t>不可被抵挡</t>
+  </si>
+  <si>
+    <t>NotCancelable</t>
+  </si>
+  <si>
+    <t>丰川祥子</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>不可被抵挡</t>
-  </si>
-  <si>
-    <t>NotCancelable</t>
+    <t>/Spine/丰川祥子/front/char_4182_oblvns_avemujica_1.png</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Spine/丰川祥子/back/char_4182_oblvns_avemujica_1.png</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Spine/丰川祥子/front/char_4182_oblvns_avemujica_1.atlas.txt</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Spine/丰川祥子/front/char_4182_oblvns_avemujica_1.skel.bytes</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Spine/丰川祥子/back/char_4182_oblvns_avemujica_1.atlas.txt</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Spine/丰川祥子/back/char_4182_oblvns_avemujica_1.skel.bytes</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2578,10 +2598,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -2750,7 +2770,7 @@
         <v>39</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="BA1" t="s">
         <v>40</v>
@@ -2809,7 +2829,7 @@
         <v>56</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="P2" t="s">
         <v>57</v>
@@ -2920,7 +2940,7 @@
         <v>92</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="BA2" t="s">
         <v>93</v>
@@ -2962,7 +2982,7 @@
         <v>105</v>
       </c>
       <c r="BN2" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="BO2" t="s">
         <v>106</v>
@@ -3188,14 +3208,14 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>405</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="8" t="s">
-        <v>406</v>
+        <v>530</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3237,13 +3257,13 @@
         <v>1</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3261,44 +3281,44 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="BD5" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="BD5" s="8" t="s">
+      <c r="BE5" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="BE5" s="8" t="s">
+      <c r="BF5" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="BF5" s="8" t="s">
+      <c r="BG5" s="8" t="s">
         <v>411</v>
-      </c>
-      <c r="BG5" s="8" t="s">
-        <v>412</v>
       </c>
       <c r="BH5">
         <v>6</v>
       </c>
       <c r="BI5" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="BJ5" s="8" t="s">
         <v>413</v>
-      </c>
-      <c r="BJ5" s="8" t="s">
-        <v>414</v>
       </c>
       <c r="BK5" s="5"/>
       <c r="BM5" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="BN5" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="BN5" s="8" t="s">
+      <c r="BP5" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="BP5" s="8" t="s">
+      <c r="BQ5" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="BR5" s="8" t="s">
         <v>417</v>
-      </c>
-      <c r="BQ5" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="BR5" s="8" t="s">
-        <v>418</v>
       </c>
       <c r="BS5">
         <v>1</v>
@@ -3309,19 +3329,19 @@
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B7" t="s">
         <v>125</v>
       </c>
       <c r="D7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3367,13 +3387,13 @@
         <v>-1</v>
       </c>
       <c r="AG7" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AH7" t="s">
         <v>121</v>
       </c>
       <c r="AI7" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AK7">
         <v>3</v>
@@ -3397,10 +3417,10 @@
         <v>1</v>
       </c>
       <c r="BB7" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="BD7" t="s">
         <v>500</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>501</v>
       </c>
       <c r="BE7" t="str">
         <f t="shared" ref="BE7" si="0">"half_"&amp;D7</f>
@@ -3437,19 +3457,19 @@
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B8" t="s">
         <v>125</v>
       </c>
       <c r="D8" t="s">
+        <v>426</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3498,13 +3518,13 @@
         <v>-1</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AH8" t="s">
         <v>121</v>
       </c>
       <c r="AI8" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AK8">
         <v>3</v>
@@ -3528,10 +3548,10 @@
         <v>1</v>
       </c>
       <c r="BB8" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="BD8" t="s">
         <v>500</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>501</v>
       </c>
       <c r="BE8" t="str">
         <f t="shared" ref="BE8:BE9" si="2">"half_"&amp;D8</f>
@@ -3568,19 +3588,19 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B9" t="s">
         <v>125</v>
       </c>
       <c r="D9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="F9" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3629,13 +3649,13 @@
         <v>-1</v>
       </c>
       <c r="AG9" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AH9" t="s">
         <v>121</v>
       </c>
       <c r="AI9" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AK9">
         <v>3</v>
@@ -3662,10 +3682,10 @@
         <v>1</v>
       </c>
       <c r="BB9" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="BD9" t="s">
         <v>500</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>501</v>
       </c>
       <c r="BE9" t="str">
         <f t="shared" si="2"/>
@@ -3711,19 +3731,19 @@
     </row>
     <row r="11" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B11" t="s">
         <v>125</v>
       </c>
       <c r="D11" t="s">
+        <v>426</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="8" t="s">
         <v>428</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>429</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -3769,7 +3789,7 @@
         <v>1</v>
       </c>
       <c r="AG11" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AH11" t="s">
         <v>121</v>
@@ -3800,10 +3820,10 @@
         <v>1</v>
       </c>
       <c r="BB11" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="BD11" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="BE11" t="str">
         <f t="shared" ref="BE11" si="4">"half_"&amp;D11</f>
@@ -6727,7 +6747,7 @@
         <v>132</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I1" t="s">
         <v>133</v>
@@ -6859,7 +6879,7 @@
         <v>174</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="BA1" t="s">
         <v>175</v>
@@ -6913,10 +6933,10 @@
         <v>190</v>
       </c>
       <c r="BS1" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="BT1" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="BU1" s="4" t="s">
         <v>191</v>
@@ -6964,7 +6984,7 @@
         <v>205</v>
       </c>
       <c r="CJ1" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="CK1" t="s">
         <v>206</v>
@@ -7056,7 +7076,7 @@
         <v>51</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I2" t="s">
         <v>229</v>
@@ -7245,10 +7265,10 @@
         <v>289</v>
       </c>
       <c r="BS2" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BT2" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BU2" s="4" t="s">
         <v>290</v>
@@ -7296,7 +7316,7 @@
         <v>304</v>
       </c>
       <c r="CJ2" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="CK2" t="s">
         <v>305</v>
@@ -7388,7 +7408,7 @@
         <v>113</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I3" t="s">
         <v>111</v>
@@ -7400,7 +7420,7 @@
         <v>329</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>113</v>
@@ -7577,7 +7597,7 @@
         <v>112</v>
       </c>
       <c r="BS3" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="BT3" s="4" t="s">
         <v>112</v>
@@ -7628,7 +7648,7 @@
         <v>341</v>
       </c>
       <c r="CJ3" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="CK3" t="s">
         <v>115</v>
@@ -7715,16 +7735,16 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>404</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6"/>
@@ -7732,10 +7752,10 @@
         <v>2</v>
       </c>
       <c r="AO6" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AR6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AV6" t="s">
         <v>348</v>
@@ -7747,19 +7767,19 @@
         <v>1</v>
       </c>
       <c r="BZ6" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="CE6" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="CE6" s="8" t="s">
-        <v>424</v>
-      </c>
       <c r="CF6" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="CG6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="CJ6" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="CK6" s="8"/>
       <c r="CW6" t="s">
@@ -7768,16 +7788,16 @@
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>404</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O7"/>
       <c r="AC7">
@@ -7787,7 +7807,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -7797,26 +7817,26 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="K8" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AG8" s="8"/>
       <c r="AO8" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AX8">
         <v>0</v>
@@ -7829,12 +7849,12 @@
       </c>
       <c r="CE8" s="8"/>
       <c r="CJ8" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="CL8" s="8"/>
       <c r="CM8" s="8"/>
       <c r="CW8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
@@ -7852,16 +7872,16 @@
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AC10">
         <v>1</v>
@@ -7870,14 +7890,14 @@
         <v>1</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="BB10">
         <v>1</v>
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -7898,16 +7918,16 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>346</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AC12">
         <v>1</v>
@@ -7922,7 +7942,7 @@
       <c r="BT12"/>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
@@ -7934,7 +7954,7 @@
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>404</v>
@@ -7943,23 +7963,23 @@
         <v>1</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AC14">
         <v>1</v>
       </c>
       <c r="AG14" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AJ14" s="8"/>
       <c r="AT14">
         <v>99</v>
       </c>
       <c r="AV14" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AX14">
         <v>99999</v>
@@ -7983,10 +8003,10 @@
         <v>1</v>
       </c>
       <c r="BW14" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CE14" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="CJ14" s="3"/>
       <c r="CL14" s="8"/>
@@ -8002,28 +8022,28 @@
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>454</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>455</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AC15">
         <v>2</v>
       </c>
       <c r="AO15" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AR15" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="BB15">
         <v>4</v>
@@ -8033,10 +8053,10 @@
       </c>
       <c r="CJ15" s="3"/>
       <c r="CS15" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="CW15" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
@@ -8049,7 +8069,7 @@
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C17" t="s">
         <v>345</v>
@@ -8058,10 +8078,10 @@
         <v>1</v>
       </c>
       <c r="J17" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="K17" s="12" t="s">
         <v>488</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>489</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17"/>
@@ -8090,10 +8110,10 @@
         <v>1</v>
       </c>
       <c r="BM17" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="BN17" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="BR17">
         <v>6</v>
@@ -8108,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="BW17" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="BX17" s="13"/>
       <c r="BY17" s="13"/>
@@ -8125,7 +8145,7 @@
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>345</v>
@@ -8148,7 +8168,7 @@
         <v>350</v>
       </c>
       <c r="AV18" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AX18">
         <v>999</v>
@@ -8175,16 +8195,16 @@
     </row>
     <row r="19" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>346</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AC19">
         <v>1</v>
@@ -8199,7 +8219,7 @@
       <c r="BT19"/>
       <c r="CJ19" s="3"/>
       <c r="CS19" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
@@ -8207,16 +8227,16 @@
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C21" t="s">
         <v>345</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21"/>
@@ -8239,10 +8259,10 @@
         <v>1</v>
       </c>
       <c r="AO21" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AR21" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AV21" s="8" t="s">
         <v>349</v>
@@ -8260,7 +8280,7 @@
         <v>0.5</v>
       </c>
       <c r="BN21" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="BR21">
         <v>6</v>
@@ -8275,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="BW21" s="13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="BX21" s="13"/>
       <c r="BY21" s="13"/>
@@ -8283,11 +8303,11 @@
       <c r="CE21" s="8"/>
       <c r="CH21" s="8"/>
       <c r="CJ21" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="CK21" s="8"/>
       <c r="CL21" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="CM21">
         <v>-0.8</v>
@@ -8307,7 +8327,7 @@
     </row>
     <row r="22" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>345</v>
@@ -8327,7 +8347,7 @@
       </c>
       <c r="AJ22" s="8"/>
       <c r="AV22" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AX22">
         <v>9</v>
@@ -8372,27 +8392,27 @@
     </row>
     <row r="24" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AC24">
         <v>1</v>
       </c>
       <c r="AR24" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="BT24"/>
       <c r="CJ24" s="3"/>
       <c r="CS24" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" spans="1:110" x14ac:dyDescent="0.25">
@@ -10321,7 +10341,7 @@
         <v>362</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10368,7 +10388,7 @@
         <v>372</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q2" t="s">
         <v>313</v>
@@ -10581,18 +10601,18 @@
         <v>113</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -10601,7 +10621,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -10831,106 +10851,132 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5F03AD-29EF-4E37-9DA2-4A5EEE4BA8EC}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="21"/>
     <col min="2" max="2" width="13.83203125" style="21" customWidth="1"/>
     <col min="3" max="3" width="20.58203125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="13.1640625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="21" customWidth="1"/>
-    <col min="7" max="7" width="15" style="21" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="14.25" style="21" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="39.5" style="21" customWidth="1"/>
+    <col min="7" max="7" width="38.58203125" style="21" customWidth="1"/>
+    <col min="8" max="8" width="32.25" style="21" customWidth="1"/>
+    <col min="9" max="9" width="39.9140625" style="21" customWidth="1"/>
     <col min="10" max="16384" width="8.6640625" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
+        <v>511</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>512</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="C1" s="21" t="s">
         <v>513</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="D1" s="21" t="s">
         <v>514</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="E1" s="21" t="s">
         <v>515</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>516</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>517</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>518</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>519</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B2" s="21" t="s">
+        <v>520</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>521</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="D2" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="E2" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="F2" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="G2" s="21" t="s">
         <v>525</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="H2" s="21" t="s">
         <v>526</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="I2" s="21" t="s">
         <v>527</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>529</v>
+        <v>447</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>529</v>
+        <v>447</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>529</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="C4" s="21">
+        <v>1</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>531</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>536</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD2AB6C-972D-448F-B35B-D05025FC0818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB93AC0-DDDF-40A5-B6CE-8DD87DF8C2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3067" yWindow="1721" windowWidth="17953" windowHeight="10397" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -1741,10 +1741,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{"UseMod":"useSelfPos","ShowRange":1,"LastTime":5}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>{"UnitId":"猫牢笼","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"FixedDirection"}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2010,6 +2006,10 @@
   </si>
   <si>
     <t>/Spine/丰川祥子/back/char_4182_oblvns_avemujica_1.skel.bytes</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"UseMod":"useSelfPos","ShowRange":1,"Color":"#AD6598","Alpha":0.5,"LastTime":5}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2598,10 +2598,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -2829,7 +2829,7 @@
         <v>56</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="P2" t="s">
         <v>57</v>
@@ -3208,14 +3208,14 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>405</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="8" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3257,13 +3257,13 @@
         <v>1</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AH5" s="8" t="s">
         <v>406</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B7" t="s">
         <v>125</v>
@@ -3341,7 +3341,7 @@
         <v>427</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3387,13 +3387,13 @@
         <v>-1</v>
       </c>
       <c r="AG7" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AH7" t="s">
         <v>121</v>
       </c>
       <c r="AI7" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AK7">
         <v>3</v>
@@ -3417,10 +3417,10 @@
         <v>1</v>
       </c>
       <c r="BB7" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="BD7" t="s">
         <v>499</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>500</v>
       </c>
       <c r="BE7" t="str">
         <f t="shared" ref="BE7" si="0">"half_"&amp;D7</f>
@@ -3457,7 +3457,7 @@
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B8" t="s">
         <v>125</v>
@@ -3469,7 +3469,7 @@
         <v>427</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3518,13 +3518,13 @@
         <v>-1</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AH8" t="s">
         <v>121</v>
       </c>
       <c r="AI8" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AK8">
         <v>3</v>
@@ -3548,10 +3548,10 @@
         <v>1</v>
       </c>
       <c r="BB8" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="BD8" t="s">
         <v>499</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>500</v>
       </c>
       <c r="BE8" t="str">
         <f t="shared" ref="BE8:BE9" si="2">"half_"&amp;D8</f>
@@ -3588,7 +3588,7 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B9" t="s">
         <v>125</v>
@@ -3600,7 +3600,7 @@
         <v>427</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3649,13 +3649,13 @@
         <v>-1</v>
       </c>
       <c r="AG9" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AH9" t="s">
         <v>121</v>
       </c>
       <c r="AI9" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AK9">
         <v>3</v>
@@ -3682,10 +3682,10 @@
         <v>1</v>
       </c>
       <c r="BB9" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="BD9" t="s">
         <v>499</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>500</v>
       </c>
       <c r="BE9" t="str">
         <f t="shared" si="2"/>
@@ -6722,7 +6722,7 @@
     <col min="88" max="88" width="23.58203125" customWidth="1"/>
     <col min="89" max="89" width="12.83203125" customWidth="1"/>
     <col min="90" max="90" width="17.08203125" customWidth="1"/>
-    <col min="97" max="97" width="14" customWidth="1"/>
+    <col min="97" max="97" width="85.1640625" customWidth="1"/>
     <col min="98" max="98" width="8" customWidth="1"/>
     <col min="100" max="100" width="11.08203125" customWidth="1"/>
     <col min="101" max="101" width="13.75" customWidth="1"/>
@@ -6879,7 +6879,7 @@
         <v>174</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="BA1" t="s">
         <v>175</v>
@@ -7735,13 +7735,13 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>404</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>420</v>
@@ -7773,10 +7773,10 @@
         <v>423</v>
       </c>
       <c r="CF6" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="CG6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="CJ6" s="8" t="s">
         <v>448</v>
@@ -7788,13 +7788,13 @@
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>404</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>418</v>
@@ -7807,7 +7807,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -7817,16 +7817,16 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>481</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>482</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>418</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AC8">
         <v>2</v>
@@ -7836,7 +7836,7 @@
         <v>421</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AX8">
         <v>0</v>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="CE8" s="8"/>
       <c r="CJ8" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="CL8" s="8"/>
       <c r="CM8" s="8"/>
       <c r="CW8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -7918,10 +7918,10 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>346</v>
@@ -7942,7 +7942,7 @@
       <c r="BT12"/>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
@@ -8045,6 +8045,9 @@
       <c r="AR15" t="s">
         <v>452</v>
       </c>
+      <c r="AT15">
+        <v>2.5</v>
+      </c>
       <c r="BB15">
         <v>4</v>
       </c>
@@ -8053,7 +8056,7 @@
       </c>
       <c r="CJ15" s="3"/>
       <c r="CS15" s="8" t="s">
-        <v>463</v>
+        <v>536</v>
       </c>
       <c r="CW15" s="8" t="s">
         <v>455</v>
@@ -8069,7 +8072,7 @@
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C17" t="s">
         <v>345</v>
@@ -8078,10 +8081,10 @@
         <v>1</v>
       </c>
       <c r="J17" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="K17" s="12" t="s">
         <v>487</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>488</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17"/>
@@ -8110,10 +8113,10 @@
         <v>1</v>
       </c>
       <c r="BM17" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="BN17" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="BR17">
         <v>6</v>
@@ -8128,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="BW17" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="BX17" s="13"/>
       <c r="BY17" s="13"/>
@@ -8145,7 +8148,7 @@
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>345</v>
@@ -8168,7 +8171,7 @@
         <v>350</v>
       </c>
       <c r="AV18" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AX18">
         <v>999</v>
@@ -8195,16 +8198,16 @@
     </row>
     <row r="19" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>346</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AC19">
         <v>1</v>
@@ -8219,7 +8222,7 @@
       <c r="BT19"/>
       <c r="CJ19" s="3"/>
       <c r="CS19" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
@@ -8227,7 +8230,7 @@
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C21" t="s">
         <v>345</v>
@@ -8259,7 +8262,7 @@
         <v>1</v>
       </c>
       <c r="AO21" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AR21" t="s">
         <v>452</v>
@@ -8280,7 +8283,7 @@
         <v>0.5</v>
       </c>
       <c r="BN21" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="BR21">
         <v>6</v>
@@ -8295,7 +8298,7 @@
         <v>1</v>
       </c>
       <c r="BW21" s="13" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="BX21" s="13"/>
       <c r="BY21" s="13"/>
@@ -8303,11 +8306,11 @@
       <c r="CE21" s="8"/>
       <c r="CH21" s="8"/>
       <c r="CJ21" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="CK21" s="8"/>
       <c r="CL21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="CM21">
         <v>-0.8</v>
@@ -8327,7 +8330,7 @@
     </row>
     <row r="22" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>345</v>
@@ -8347,7 +8350,7 @@
       </c>
       <c r="AJ22" s="8"/>
       <c r="AV22" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AX22">
         <v>9</v>
@@ -8412,7 +8415,7 @@
       <c r="BT24"/>
       <c r="CJ24" s="3"/>
       <c r="CS24" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="1:110" x14ac:dyDescent="0.25">
@@ -10341,7 +10344,7 @@
         <v>362</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10388,7 +10391,7 @@
         <v>372</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q2" t="s">
         <v>313</v>
@@ -10606,10 +10609,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C4" t="s">
         <v>432</v>
@@ -10621,7 +10624,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -10868,60 +10871,60 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>511</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="C1" s="21" t="s">
         <v>512</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="D1" s="21" t="s">
         <v>513</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="E1" s="21" t="s">
         <v>514</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>515</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>516</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>517</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>518</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B2" s="21" t="s">
+        <v>519</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>520</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="D2" s="21" t="s">
         <v>521</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="E2" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="F2" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="G2" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="H2" s="21" t="s">
         <v>525</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="I2" s="21" t="s">
         <v>526</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10955,28 +10958,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C4" s="21">
         <v>1</v>
       </c>
       <c r="D4" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>533</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="G4" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="H4" s="21" t="s">
         <v>531</v>
       </c>
-      <c r="F4" s="21" t="s">
-        <v>534</v>
-      </c>
-      <c r="G4" s="21" t="s">
+      <c r="I4" s="21" t="s">
         <v>535</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>532</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>536</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0071CD-3FA9-4C84-B93C-D85C05D5633F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB786E5-BD70-4EDF-A1B5-98AACF83F1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="518">
   <si>
     <t>Id</t>
   </si>
@@ -688,9 +688,6 @@
     <t>Hip</t>
   </si>
   <si>
-    <t>CCB普攻,获取猫猫</t>
-  </si>
-  <si>
     <t>先锋</t>
   </si>
   <si>
@@ -1838,6 +1835,30 @@
   </si>
   <si>
     <t>{"UseMod":"useSelfPos","ShowRange":1,"Color":"#813C85","Alpha":0.5,"LastTime":5}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>起飞</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通技能</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己入场</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅自己</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB普攻,获取猫猫,起飞</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -3083,7 +3104,7 @@
         <v>128</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>129</v>
+        <v>517</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3101,44 +3122,44 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BD5" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="BD5" s="2" t="s">
+      <c r="BE5" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="BE5" s="2" t="s">
+      <c r="BF5" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="BF5" s="2" t="s">
+      <c r="BG5" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BG5" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BH5">
         <v>6</v>
       </c>
       <c r="BI5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="BJ5" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="BK5" s="19"/>
       <c r="BM5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="BN5" s="2" t="s">
+      <c r="BP5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="BP5" s="2" t="s">
+      <c r="BQ5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BR5" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="BQ5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="BR5" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="BS5">
         <v>1</v>
@@ -3149,19 +3170,19 @@
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
         <v>126</v>
       </c>
       <c r="D7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="F7" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3207,13 +3228,13 @@
         <v>-1</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH7" t="s">
         <v>128</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AK7">
         <v>3</v>
@@ -3237,10 +3258,10 @@
         <v>1</v>
       </c>
       <c r="BB7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BD7" t="s">
         <v>146</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>147</v>
       </c>
       <c r="BE7" t="str">
         <f t="shared" ref="BE7" si="0">"half_"&amp;D7</f>
@@ -3251,25 +3272,25 @@
         <v>otter</v>
       </c>
       <c r="BG7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BH7">
         <v>5</v>
       </c>
       <c r="BI7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BM7" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN7" t="s">
         <v>137</v>
       </c>
-      <c r="BN7" t="s">
+      <c r="BP7" t="s">
         <v>138</v>
       </c>
-      <c r="BP7" t="s">
-        <v>139</v>
-      </c>
       <c r="BQ7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BS7">
         <v>1</v>
@@ -3277,19 +3298,19 @@
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
         <v>126</v>
       </c>
       <c r="D8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="F8" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3338,13 +3359,13 @@
         <v>-1</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AH8" t="s">
         <v>128</v>
       </c>
       <c r="AI8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AK8">
         <v>3</v>
@@ -3368,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="BB8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BD8" t="s">
         <v>146</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>147</v>
       </c>
       <c r="BE8" t="str">
         <f t="shared" ref="BE8:BE9" si="2">"half_"&amp;D8</f>
@@ -3382,25 +3403,25 @@
         <v>otter</v>
       </c>
       <c r="BG8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BH8">
         <v>5</v>
       </c>
       <c r="BI8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BM8" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN8" t="s">
         <v>137</v>
       </c>
-      <c r="BN8" t="s">
+      <c r="BP8" t="s">
         <v>138</v>
       </c>
-      <c r="BP8" t="s">
-        <v>139</v>
-      </c>
       <c r="BQ8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BS8">
         <v>1</v>
@@ -3408,19 +3429,19 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
         <v>126</v>
       </c>
       <c r="D9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3469,13 +3490,13 @@
         <v>-1</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AH9" t="s">
         <v>128</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AK9">
         <v>3</v>
@@ -3502,10 +3523,10 @@
         <v>1</v>
       </c>
       <c r="BB9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BD9" t="s">
         <v>146</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>147</v>
       </c>
       <c r="BE9" t="str">
         <f t="shared" si="2"/>
@@ -3516,25 +3537,25 @@
         <v>otter</v>
       </c>
       <c r="BG9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BH9">
         <v>5</v>
       </c>
       <c r="BI9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BM9" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN9" t="s">
         <v>137</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BP9" t="s">
         <v>138</v>
       </c>
-      <c r="BP9" t="s">
-        <v>139</v>
-      </c>
       <c r="BQ9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BS9">
         <v>1</v>
@@ -3551,19 +3572,19 @@
     </row>
     <row r="11" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
         <v>126</v>
       </c>
       <c r="D11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="F11" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -3609,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AH11" t="s">
         <v>128</v>
@@ -3640,10 +3661,10 @@
         <v>1</v>
       </c>
       <c r="BB11" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BD11" t="s">
         <v>146</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>147</v>
       </c>
       <c r="BE11" t="str">
         <f t="shared" ref="BE11" si="4">"half_"&amp;D11</f>
@@ -3654,25 +3675,25 @@
         <v>otter</v>
       </c>
       <c r="BG11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BH11">
         <v>5</v>
       </c>
       <c r="BI11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BM11" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN11" t="s">
         <v>137</v>
       </c>
-      <c r="BN11" t="s">
+      <c r="BP11" t="s">
         <v>138</v>
       </c>
-      <c r="BP11" t="s">
-        <v>139</v>
-      </c>
       <c r="BQ11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BS11">
         <v>1</v>
@@ -6468,7 +6489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH840"/>
+  <dimension ref="A1:DH842"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6552,328 +6573,328 @@
   <sheetData>
     <row r="1" spans="1:111" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" t="s">
         <v>154</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>155</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>156</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>157</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>159</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>160</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="V1" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" t="s">
         <v>174</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>175</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" t="s">
         <v>177</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>178</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>179</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>180</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>181</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>182</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>183</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>184</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>185</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>186</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>187</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>188</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>189</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>190</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>191</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>192</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>193</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>194</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>195</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>196</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>197</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>198</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>199</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>200</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>202</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>203</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>204</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>205</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>206</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>207</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
+        <v>207</v>
+      </c>
+      <c r="BI1" t="s">
         <v>208</v>
       </c>
-      <c r="BH1" t="s">
-        <v>208</v>
-      </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>209</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>210</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>211</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>212</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>213</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>214</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>215</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>216</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>217</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BT1" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BU1" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BV1" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BW1" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BX1" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BY1" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="BZ1" t="s">
         <v>225</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CB1" t="s">
         <v>227</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>228</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>229</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>230</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>231</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>232</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>233</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>234</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CK1" t="s">
         <v>236</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>237</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>238</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>239</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>240</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
+        <v>217</v>
+      </c>
+      <c r="CQ1" t="s">
         <v>241</v>
       </c>
-      <c r="CP1" t="s">
-        <v>218</v>
-      </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>242</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>243</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>244</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>245</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>246</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>247</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
+        <v>246</v>
+      </c>
+      <c r="CY1" t="s">
         <v>248</v>
       </c>
-      <c r="CX1" t="s">
-        <v>247</v>
-      </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>249</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>250</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>251</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>252</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>253</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>254</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>255</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>256</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:111" x14ac:dyDescent="0.25">
@@ -6887,325 +6908,325 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" t="s">
         <v>258</v>
-      </c>
-      <c r="F2" t="s">
-        <v>259</v>
       </c>
       <c r="G2" t="s">
         <v>53</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I2" t="s">
         <v>260</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>261</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Y2" t="s">
         <v>276</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>277</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AB2" t="s">
         <v>279</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>280</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>281</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>282</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>283</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>284</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>285</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>286</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>287</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>288</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>289</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>290</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>291</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>292</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>293</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>294</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>295</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>296</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>297</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>298</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>299</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>300</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>301</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>302</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>303</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>304</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>305</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>306</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>307</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>308</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>309</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>310</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>311</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>312</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>313</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>314</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>315</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>316</v>
       </c>
       <c r="BM2" t="s">
         <v>79</v>
       </c>
       <c r="BN2" t="s">
+        <v>316</v>
+      </c>
+      <c r="BO2" t="s">
         <v>317</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BP2" t="s">
         <v>318</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BQ2" t="s">
         <v>319</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>320</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>321</v>
       </c>
       <c r="BS2" s="2" t="s">
         <v>95</v>
       </c>
       <c r="BT2" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="BU2" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BV2" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BW2" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BX2" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BZ2" t="s">
         <v>327</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
         <v>328</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CB2" t="s">
         <v>329</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>330</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>331</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>332</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>333</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>334</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>335</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>336</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CK2" t="s">
         <v>338</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CL2" t="s">
         <v>339</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CM2" t="s">
         <v>340</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CN2" t="s">
         <v>341</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CO2" t="s">
         <v>342</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
         <v>343</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CQ2" t="s">
         <v>344</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CR2" t="s">
         <v>345</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CT2" t="s">
         <v>347</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CU2" t="s">
         <v>348</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CV2" t="s">
         <v>349</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CW2" t="s">
         <v>350</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CX2" t="s">
         <v>351</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CY2" t="s">
         <v>352</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CZ2" t="s">
         <v>353</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DA2" t="s">
         <v>354</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DB2" t="s">
         <v>355</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DC2" t="s">
         <v>356</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>357</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>358</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DF2" t="s">
         <v>359</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DG2" t="s">
         <v>360</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:111" x14ac:dyDescent="0.25">
@@ -7234,13 +7255,13 @@
         <v>116</v>
       </c>
       <c r="J3" t="s">
+        <v>361</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>364</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>118</v>
@@ -7303,7 +7324,7 @@
         <v>116</v>
       </c>
       <c r="AG3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -7327,16 +7348,16 @@
         <v>116</v>
       </c>
       <c r="AO3" t="s">
+        <v>365</v>
+      </c>
+      <c r="AP3" t="s">
         <v>366</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>367</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AS3" t="s">
         <v>116</v>
@@ -7348,7 +7369,7 @@
         <v>116</v>
       </c>
       <c r="AV3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AW3" t="s">
         <v>116</v>
@@ -7378,7 +7399,7 @@
         <v>116</v>
       </c>
       <c r="BF3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="BG3" t="s">
         <v>116</v>
@@ -7405,10 +7426,10 @@
         <v>119</v>
       </c>
       <c r="BO3" t="s">
+        <v>369</v>
+      </c>
+      <c r="BP3" t="s">
         <v>370</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>371</v>
       </c>
       <c r="BQ3" t="s">
         <v>117</v>
@@ -7429,19 +7450,19 @@
         <v>118</v>
       </c>
       <c r="BW3" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="BX3" s="6" t="s">
         <v>116</v>
       </c>
       <c r="BY3" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
@@ -7453,19 +7474,19 @@
         <v>124</v>
       </c>
       <c r="CE3" t="s">
+        <v>373</v>
+      </c>
+      <c r="CF3" t="s">
         <v>374</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>375</v>
       </c>
       <c r="CG3" t="s">
         <v>2</v>
       </c>
       <c r="CH3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="CI3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="CJ3" s="2" t="s">
         <v>125</v>
@@ -7486,7 +7507,7 @@
         <v>123</v>
       </c>
       <c r="CP3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="CQ3" t="s">
         <v>123</v>
@@ -7498,28 +7519,28 @@
         <v>125</v>
       </c>
       <c r="CT3" t="s">
+        <v>376</v>
+      </c>
+      <c r="CU3" t="s">
         <v>377</v>
       </c>
-      <c r="CU3" t="s">
-        <v>378</v>
-      </c>
       <c r="CV3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="CW3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="CX3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="CY3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="CZ3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="DA3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="DB3" t="s">
         <v>116</v>
@@ -7542,7 +7563,7 @@
     </row>
     <row r="4" spans="1:111" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:111" x14ac:dyDescent="0.25">
@@ -7553,29 +7574,29 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="K6" s="5" t="s">
         <v>382</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>383</v>
       </c>
       <c r="P6"/>
       <c r="AC6">
         <v>2</v>
       </c>
       <c r="AO6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="AR6" t="s">
         <v>384</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AV6" t="s">
         <v>385</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>386</v>
       </c>
       <c r="AX6">
         <v>1</v>
@@ -7587,34 +7608,34 @@
         <v>57</v>
       </c>
       <c r="CE6" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="CF6" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="CF6" s="2" t="s">
+      <c r="CG6" t="s">
         <v>388</v>
       </c>
-      <c r="CG6" t="s">
+      <c r="CJ6" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="CJ6" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="CK6" s="2"/>
       <c r="CW6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="5" t="s">
         <v>393</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>394</v>
       </c>
       <c r="O7"/>
       <c r="AC7">
@@ -7624,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -7634,26 +7655,26 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="K8" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>397</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>398</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AG8" s="2"/>
       <c r="AO8" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AV8" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AX8">
         <v>0</v>
@@ -7666,117 +7687,85 @@
       </c>
       <c r="CE8" s="2"/>
       <c r="CJ8" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="CL8" s="2"/>
       <c r="CM8" s="2"/>
       <c r="CW8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="C9" s="2"/>
       <c r="AG9" s="2"/>
-      <c r="AJ9" s="2"/>
       <c r="AO9" s="2"/>
-      <c r="BT9"/>
-      <c r="CJ9" s="5"/>
+      <c r="AV9" s="2"/>
+      <c r="CE9" s="2"/>
+      <c r="CJ9" s="2"/>
       <c r="CL9" s="2"/>
       <c r="CM9" s="2"/>
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>401</v>
-      </c>
-      <c r="C10" t="s">
-        <v>402</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
+      <c r="A10" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>515</v>
+      </c>
       <c r="AC10">
         <v>1</v>
       </c>
-      <c r="AF10">
-        <v>1</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>404</v>
-      </c>
+      <c r="AG10" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="AO10" s="2"/>
+      <c r="AV10" s="2"/>
       <c r="BB10">
         <v>1</v>
       </c>
-      <c r="BT10" s="10"/>
-      <c r="BU10" s="10"/>
-      <c r="BV10" s="10"/>
-      <c r="BW10" s="10"/>
-      <c r="BX10" s="10"/>
-      <c r="BY10" s="10"/>
-      <c r="CJ10" s="7"/>
-      <c r="CS10" t="s">
-        <v>405</v>
-      </c>
-      <c r="DB10">
-        <v>1</v>
-      </c>
-      <c r="DE10">
-        <v>1</v>
-      </c>
-      <c r="DF10">
-        <v>1</v>
+      <c r="BR10">
+        <v>0.1</v>
+      </c>
+      <c r="CE10" s="2"/>
+      <c r="CJ10" s="2"/>
+      <c r="CL10" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="CM10" s="2"/>
+      <c r="CP10">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="BT11" s="10"/>
-      <c r="BU11" s="10"/>
-      <c r="BV11" s="10"/>
-      <c r="BW11" s="10"/>
-      <c r="BX11" s="10"/>
-      <c r="BY11" s="10"/>
-      <c r="CJ11" s="7"/>
+      <c r="A11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="AG11" s="2"/>
+      <c r="AJ11" s="2"/>
+      <c r="AO11" s="2"/>
+      <c r="BT11"/>
+      <c r="CJ11" s="5"/>
+      <c r="CL11" s="2"/>
+      <c r="CM11" s="2"/>
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>400</v>
       </c>
       <c r="C12" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -7793,13 +7782,16 @@
       <c r="AC12">
         <v>1</v>
       </c>
+      <c r="AF12">
+        <v>1</v>
+      </c>
       <c r="AG12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="BB12">
         <v>1</v>
       </c>
-      <c r="BT12"/>
+      <c r="BT12" s="10"/>
       <c r="BU12" s="10"/>
       <c r="BV12" s="10"/>
       <c r="BW12" s="10"/>
@@ -7807,25 +7799,21 @@
       <c r="BY12" s="10"/>
       <c r="CJ12" s="7"/>
       <c r="CS12" t="s">
-        <v>407</v>
+        <v>404</v>
+      </c>
+      <c r="DB12">
+        <v>1</v>
+      </c>
+      <c r="DE12">
+        <v>1</v>
+      </c>
+      <c r="DF12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" t="s">
-        <v>408</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>403</v>
-      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
@@ -7838,21 +7826,6 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="AC13">
-        <v>2</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>384</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>409</v>
-      </c>
-      <c r="BB13">
-        <v>4</v>
-      </c>
-      <c r="BR13">
-        <v>0.2</v>
-      </c>
       <c r="BT13" s="10"/>
       <c r="BU13" s="10"/>
       <c r="BV13" s="10"/>
@@ -7860,25 +7833,19 @@
       <c r="BX13" s="10"/>
       <c r="BY13" s="10"/>
       <c r="CJ13" s="7"/>
-      <c r="CS13" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="CW13" t="s">
-        <v>410</v>
-      </c>
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>411</v>
+        <v>144</v>
       </c>
       <c r="C14" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -7896,7 +7863,7 @@
         <v>1</v>
       </c>
       <c r="AG14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="BB14">
         <v>1</v>
@@ -7909,12 +7876,25 @@
       <c r="BY14" s="10"/>
       <c r="CJ14" s="7"/>
       <c r="CS14" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+      <c r="A15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" t="s">
+        <v>407</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>402</v>
+      </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -7927,6 +7907,21 @@
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
+      <c r="AC15">
+        <v>2</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>383</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>408</v>
+      </c>
+      <c r="BB15">
+        <v>4</v>
+      </c>
+      <c r="BR15">
+        <v>0.2</v>
+      </c>
       <c r="BT15" s="10"/>
       <c r="BU15" s="10"/>
       <c r="BV15" s="10"/>
@@ -7934,24 +7929,26 @@
       <c r="BX15" s="10"/>
       <c r="BY15" s="10"/>
       <c r="CJ15" s="7"/>
+      <c r="CS15" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="CW15" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C16" t="s">
-        <v>381</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="L16" s="7"/>
+        <v>393</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>402</v>
+      </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -7965,123 +7962,65 @@
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="AC16">
-        <v>2</v>
-      </c>
-      <c r="AD16">
         <v>1</v>
       </c>
-      <c r="AT16">
-        <v>0.4</v>
+      <c r="AG16" t="s">
+        <v>403</v>
       </c>
       <c r="BB16">
         <v>1</v>
       </c>
-      <c r="BM16" t="s">
-        <v>416</v>
-      </c>
-      <c r="BN16" t="s">
-        <v>417</v>
-      </c>
-      <c r="BR16">
-        <v>6</v>
-      </c>
-      <c r="BT16" s="10">
-        <v>1</v>
-      </c>
-      <c r="BU16" s="10">
-        <v>1</v>
-      </c>
-      <c r="BV16" s="10">
-        <v>1</v>
-      </c>
-      <c r="BW16" s="10" t="s">
-        <v>418</v>
-      </c>
+      <c r="BT16"/>
+      <c r="BU16" s="10"/>
+      <c r="BV16" s="10"/>
+      <c r="BW16" s="10"/>
       <c r="BX16" s="10"/>
       <c r="BY16" s="10"/>
       <c r="CJ16" s="7"/>
-      <c r="DF16">
-        <v>1</v>
+      <c r="CS16" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>417</v>
-      </c>
-      <c r="C17" t="s">
-        <v>381</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="L17" s="8"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17" s="8"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="AC17">
-        <v>1</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>404</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>419</v>
-      </c>
-      <c r="AV17" t="s">
-        <v>420</v>
-      </c>
-      <c r="AX17">
-        <v>999</v>
-      </c>
-      <c r="AZ17">
-        <v>2</v>
-      </c>
-      <c r="BB17">
-        <v>1</v>
-      </c>
-      <c r="BT17" s="11"/>
-      <c r="BU17" s="11"/>
-      <c r="BV17" s="11"/>
-      <c r="BW17" s="11"/>
-      <c r="BX17" s="11"/>
-      <c r="BY17" s="11"/>
-      <c r="DB17">
-        <v>1</v>
-      </c>
-      <c r="DE17">
-        <v>1</v>
-      </c>
-      <c r="DF17">
-        <v>1</v>
-      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="BT17" s="10"/>
+      <c r="BU17" s="10"/>
+      <c r="BV17" s="10"/>
+      <c r="BW17" s="10"/>
+      <c r="BX17" s="10"/>
+      <c r="BY17" s="10"/>
+      <c r="CJ17" s="7"/>
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C18" t="s">
-        <v>406</v>
+        <v>380</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>414</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>422</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="L18" s="7"/>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
@@ -8095,73 +8034,123 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
       <c r="AC18">
+        <v>2</v>
+      </c>
+      <c r="AD18">
         <v>1</v>
       </c>
-      <c r="AG18" t="s">
-        <v>404</v>
+      <c r="AT18">
+        <v>0.4</v>
       </c>
       <c r="BB18">
         <v>1</v>
       </c>
-      <c r="BT18"/>
-      <c r="BU18" s="10"/>
-      <c r="BV18" s="10"/>
-      <c r="BW18" s="10"/>
+      <c r="BM18" t="s">
+        <v>415</v>
+      </c>
+      <c r="BN18" t="s">
+        <v>416</v>
+      </c>
+      <c r="BR18">
+        <v>6</v>
+      </c>
+      <c r="BT18" s="10">
+        <v>1</v>
+      </c>
+      <c r="BU18" s="10">
+        <v>1</v>
+      </c>
+      <c r="BV18" s="10">
+        <v>1</v>
+      </c>
+      <c r="BW18" s="10" t="s">
+        <v>417</v>
+      </c>
       <c r="BX18" s="10"/>
       <c r="BY18" s="10"/>
       <c r="CJ18" s="7"/>
-      <c r="CS18" t="s">
-        <v>423</v>
+      <c r="DF18">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C19" t="s">
-        <v>406</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
+        <v>380</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19" s="8"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AG19" t="s">
-        <v>404</v>
+        <v>403</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>418</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>419</v>
+      </c>
+      <c r="AX19">
+        <v>999</v>
+      </c>
+      <c r="AZ19">
+        <v>2</v>
       </c>
       <c r="BB19">
         <v>1</v>
       </c>
-      <c r="BT19"/>
-      <c r="BU19" s="10"/>
-      <c r="BV19" s="10"/>
-      <c r="BW19" s="10"/>
-      <c r="BX19" s="10"/>
-      <c r="BY19" s="10"/>
-      <c r="CJ19" s="7"/>
-      <c r="CS19" t="s">
-        <v>423</v>
+      <c r="BT19" s="11"/>
+      <c r="BU19" s="11"/>
+      <c r="BV19" s="11"/>
+      <c r="BW19" s="11"/>
+      <c r="BX19" s="11"/>
+      <c r="BY19" s="11"/>
+      <c r="DB19">
+        <v>1</v>
+      </c>
+      <c r="DE19">
+        <v>1</v>
+      </c>
+      <c r="DF19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
+      <c r="A20" t="s">
+        <v>420</v>
+      </c>
+      <c r="C20" t="s">
+        <v>405</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>421</v>
+      </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
@@ -8174,113 +8163,74 @@
       <c r="V20" s="7"/>
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
-      <c r="BT20" s="10"/>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>403</v>
+      </c>
+      <c r="BB20">
+        <v>1</v>
+      </c>
+      <c r="BT20"/>
       <c r="BU20" s="10"/>
       <c r="BV20" s="10"/>
       <c r="BW20" s="10"/>
       <c r="BX20" s="10"/>
       <c r="BY20" s="10"/>
       <c r="CJ20" s="7"/>
+      <c r="CS20" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>423</v>
       </c>
       <c r="C21" t="s">
-        <v>381</v>
-      </c>
-      <c r="I21">
+        <v>405</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="AC21">
         <v>1</v>
       </c>
-      <c r="K21" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="L21" s="8" t="s">
+      <c r="AG21" t="s">
         <v>403</v>
       </c>
-      <c r="M21"/>
-      <c r="N21"/>
-      <c r="O21" s="8"/>
-      <c r="P21"/>
-      <c r="Q21"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="8"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="8">
+      <c r="BB21">
         <v>1</v>
       </c>
-      <c r="Y21" s="8"/>
-      <c r="AC21">
-        <v>2</v>
-      </c>
-      <c r="AD21">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>384</v>
-      </c>
-      <c r="AR21" t="s">
-        <v>409</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>426</v>
-      </c>
-      <c r="AX21">
-        <v>1.5</v>
-      </c>
-      <c r="BB21">
-        <v>99</v>
-      </c>
-      <c r="BC21">
-        <v>11</v>
-      </c>
-      <c r="BD21">
-        <v>0.5</v>
-      </c>
-      <c r="BM21" t="s">
-        <v>427</v>
-      </c>
-      <c r="BN21" t="s">
-        <v>428</v>
-      </c>
-      <c r="BT21" s="11"/>
-      <c r="BU21" s="11"/>
-      <c r="BV21" s="11"/>
-      <c r="BW21" s="11"/>
-      <c r="BX21" s="11"/>
-      <c r="BY21" s="11"/>
-      <c r="BZ21" t="s">
-        <v>57</v>
-      </c>
-      <c r="CE21" t="s">
-        <v>387</v>
-      </c>
-      <c r="CJ21" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="CW21" t="s">
-        <v>430</v>
+      <c r="BT21"/>
+      <c r="BU21" s="10"/>
+      <c r="BV21" s="10"/>
+      <c r="BW21" s="10"/>
+      <c r="BX21" s="10"/>
+      <c r="BY21" s="10"/>
+      <c r="CJ21" s="7"/>
+      <c r="CS21" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>427</v>
-      </c>
-      <c r="C22" t="s">
-        <v>381</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>403</v>
-      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -8292,90 +8242,66 @@
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
-      <c r="X22" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC22">
-        <v>2</v>
-      </c>
-      <c r="AD22">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="s">
-        <v>384</v>
-      </c>
-      <c r="AR22" t="s">
-        <v>409</v>
-      </c>
-      <c r="BB22">
-        <v>99</v>
-      </c>
-      <c r="BT22"/>
+      <c r="X22" s="7"/>
+      <c r="BT22" s="10"/>
       <c r="BU22" s="10"/>
       <c r="BV22" s="10"/>
       <c r="BW22" s="10"/>
       <c r="BX22" s="10"/>
       <c r="BY22" s="10"/>
       <c r="CJ22" s="7"/>
-      <c r="CL22" t="s">
-        <v>431</v>
-      </c>
-      <c r="CM22">
-        <v>-0.8</v>
-      </c>
-      <c r="CP22">
-        <v>6</v>
-      </c>
-      <c r="CW22" t="s">
-        <v>430</v>
-      </c>
     </row>
     <row r="23" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>428</v>
+        <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
+        <v>393</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23" s="8"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="8"/>
+      <c r="X23" s="8">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="8"/>
       <c r="AC23">
+        <v>2</v>
+      </c>
+      <c r="AD23">
         <v>1</v>
       </c>
-      <c r="AG23" t="s">
-        <v>404</v>
+      <c r="AO23" t="s">
+        <v>383</v>
       </c>
       <c r="AR23" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="AV23" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AX23">
-        <v>0.09</v>
-      </c>
-      <c r="AZ23">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BB23">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="BC23">
         <v>11</v>
@@ -8383,398 +8309,535 @@
       <c r="BD23">
         <v>0.5</v>
       </c>
-      <c r="BT23"/>
-      <c r="BU23" s="10"/>
-      <c r="BV23" s="10"/>
-      <c r="BW23" s="10"/>
-      <c r="BX23" s="10"/>
-      <c r="BY23" s="10"/>
-      <c r="CJ23" s="7"/>
+      <c r="BM23" t="s">
+        <v>426</v>
+      </c>
+      <c r="BN23" t="s">
+        <v>427</v>
+      </c>
+      <c r="BT23" s="11"/>
+      <c r="BU23" s="11"/>
+      <c r="BV23" s="11"/>
+      <c r="BW23" s="11"/>
+      <c r="BX23" s="11"/>
+      <c r="BY23" s="11"/>
+      <c r="BZ23" t="s">
+        <v>57</v>
+      </c>
+      <c r="CE23" t="s">
+        <v>386</v>
+      </c>
+      <c r="CJ23" s="7" t="s">
+        <v>428</v>
+      </c>
       <c r="CW23" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="24" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>426</v>
+      </c>
+      <c r="C24" t="s">
+        <v>380</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC24">
+        <v>2</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>383</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>408</v>
+      </c>
+      <c r="BB24">
+        <v>99</v>
+      </c>
+      <c r="BT24"/>
+      <c r="BU24" s="10"/>
+      <c r="BV24" s="10"/>
+      <c r="BW24" s="10"/>
+      <c r="BX24" s="10"/>
+      <c r="BY24" s="10"/>
+      <c r="CJ24" s="7"/>
+      <c r="CL24" t="s">
         <v>430</v>
       </c>
-      <c r="DB23">
-        <v>1</v>
-      </c>
-      <c r="DE23">
-        <v>1</v>
-      </c>
-      <c r="DF23">
-        <v>1</v>
+      <c r="CM24">
+        <v>-0.8</v>
+      </c>
+      <c r="CP24">
+        <v>6</v>
+      </c>
+      <c r="CW24" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="25" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>406</v>
+      <c r="A25" t="s">
+        <v>427</v>
+      </c>
+      <c r="C25" t="s">
+        <v>380</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
-      <c r="K25" s="5" t="s">
-        <v>394</v>
-      </c>
+      <c r="K25" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
       <c r="AC25">
         <v>1</v>
       </c>
-      <c r="AR25" s="2" t="s">
+      <c r="AG25" t="s">
+        <v>403</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>418</v>
+      </c>
+      <c r="AV25" t="s">
         <v>419</v>
       </c>
+      <c r="AX25">
+        <v>0.09</v>
+      </c>
+      <c r="AZ25">
+        <v>1</v>
+      </c>
+      <c r="BB25">
+        <v>1</v>
+      </c>
+      <c r="BC25">
+        <v>11</v>
+      </c>
+      <c r="BD25">
+        <v>0.5</v>
+      </c>
       <c r="BT25"/>
-      <c r="CJ25" s="5"/>
-      <c r="CS25" s="2" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="26" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="J26" s="2"/>
-      <c r="O26"/>
-      <c r="AO26" s="2"/>
-      <c r="CS26" s="2"/>
+      <c r="BU25" s="10"/>
+      <c r="BV25" s="10"/>
+      <c r="BW25" s="10"/>
+      <c r="BX25" s="10"/>
+      <c r="BY25" s="10"/>
+      <c r="CJ25" s="7"/>
+      <c r="CW25" t="s">
+        <v>429</v>
+      </c>
+      <c r="DB25">
+        <v>1</v>
+      </c>
+      <c r="DE25">
+        <v>1</v>
+      </c>
+      <c r="DF25">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="P27"/>
+      <c r="A27" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AR27" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="BT27"/>
+      <c r="CJ27" s="5"/>
+      <c r="CS27" s="2" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ28" s="5"/>
+      <c r="J28" s="2"/>
+      <c r="O28"/>
+      <c r="AO28" s="2"/>
+      <c r="CS28" s="2"/>
     </row>
     <row r="29" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29"/>
-      <c r="N29"/>
-      <c r="O29" s="9"/>
       <c r="P29"/>
-      <c r="Q29"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29"/>
-      <c r="BS29" s="12"/>
-      <c r="BT29" s="12"/>
-      <c r="BU29" s="12"/>
-      <c r="BV29" s="12"/>
-      <c r="BW29" s="12"/>
-      <c r="BX29" s="12"/>
-      <c r="BY29"/>
     </row>
     <row r="30" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30"/>
-      <c r="N30"/>
-      <c r="O30" s="9"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30"/>
-      <c r="BS30" s="12"/>
-      <c r="BT30" s="12"/>
-      <c r="BU30" s="12"/>
-      <c r="BV30" s="12"/>
-      <c r="BW30" s="12"/>
-      <c r="BX30" s="12"/>
-      <c r="BY30"/>
-      <c r="CL30" s="3"/>
+      <c r="CJ30" s="5"/>
     </row>
     <row r="31" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="AW31" s="5"/>
-      <c r="BT31"/>
-      <c r="BU31"/>
-      <c r="BV31"/>
-      <c r="BW31"/>
-      <c r="BX31"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31" s="9"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31"/>
+      <c r="BS31" s="12"/>
+      <c r="BT31" s="12"/>
+      <c r="BU31" s="12"/>
+      <c r="BV31" s="12"/>
+      <c r="BW31" s="12"/>
+      <c r="BX31" s="12"/>
       <c r="BY31"/>
-      <c r="BZ31" s="5"/>
-      <c r="CA31" s="5"/>
-      <c r="CB31" s="5"/>
-      <c r="CC31" s="5"/>
-      <c r="CD31" s="5"/>
-      <c r="CF31" s="5"/>
-      <c r="CG31" s="5"/>
-      <c r="CH31" s="5"/>
-      <c r="CI31" s="5"/>
-      <c r="CJ31" s="5"/>
-      <c r="CK31" s="5"/>
     </row>
     <row r="32" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
       <c r="M32"/>
       <c r="N32"/>
-      <c r="P32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32"/>
+      <c r="O32" s="9"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
       <c r="X32"/>
-      <c r="BT32"/>
-      <c r="BZ32" s="6"/>
+      <c r="BS32" s="12"/>
+      <c r="BT32" s="12"/>
+      <c r="BU32" s="12"/>
+      <c r="BV32" s="12"/>
+      <c r="BW32" s="12"/>
+      <c r="BX32" s="12"/>
+      <c r="BY32"/>
+      <c r="CL32" s="3"/>
     </row>
     <row r="33" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="AW33" s="5"/>
       <c r="BT33"/>
+      <c r="BU33"/>
+      <c r="BV33"/>
+      <c r="BW33"/>
+      <c r="BX33"/>
+      <c r="BY33"/>
+      <c r="BZ33" s="5"/>
+      <c r="CA33" s="5"/>
+      <c r="CB33" s="5"/>
+      <c r="CC33" s="5"/>
+      <c r="CD33" s="5"/>
+      <c r="CF33" s="5"/>
+      <c r="CG33" s="5"/>
+      <c r="CH33" s="5"/>
+      <c r="CI33" s="5"/>
+      <c r="CJ33" s="5"/>
+      <c r="CK33" s="5"/>
     </row>
     <row r="34" spans="1:90" x14ac:dyDescent="0.25">
       <c r="M34"/>
-      <c r="O34"/>
-      <c r="BM34" s="2"/>
-      <c r="BN34" s="2"/>
-      <c r="CL34" s="3"/>
+      <c r="N34"/>
+      <c r="P34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34"/>
+      <c r="X34"/>
+      <c r="BT34"/>
+      <c r="BZ34" s="6"/>
     </row>
     <row r="35" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="J35" s="5"/>
-      <c r="M35"/>
-      <c r="O35" s="3"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="CL35" s="2"/>
+      <c r="BT35"/>
     </row>
     <row r="36" spans="1:90" x14ac:dyDescent="0.25">
       <c r="M36"/>
-      <c r="BZ36" s="13"/>
+      <c r="O36"/>
+      <c r="BM36" s="2"/>
+      <c r="BN36" s="2"/>
+      <c r="CL36" s="3"/>
     </row>
     <row r="37" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="J37" s="5"/>
       <c r="M37"/>
       <c r="O37" s="3"/>
       <c r="P37"/>
       <c r="Q37"/>
+      <c r="CL37" s="2"/>
     </row>
     <row r="38" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
       <c r="M38"/>
-      <c r="O38" s="3"/>
-      <c r="P38"/>
-      <c r="Q38"/>
-      <c r="CL38" s="3"/>
+      <c r="BZ38" s="13"/>
     </row>
     <row r="39" spans="1:90" x14ac:dyDescent="0.25">
       <c r="M39"/>
-      <c r="AW39" s="5"/>
-      <c r="BT39"/>
-      <c r="BU39"/>
-      <c r="BV39"/>
-      <c r="BW39"/>
-      <c r="BX39"/>
-      <c r="BY39"/>
-      <c r="BZ39" s="5"/>
-      <c r="CA39" s="5"/>
-      <c r="CB39" s="5"/>
-      <c r="CC39" s="5"/>
-      <c r="CD39" s="5"/>
-      <c r="CF39" s="5"/>
-      <c r="CG39" s="5"/>
-      <c r="CH39" s="5"/>
-      <c r="CI39" s="5"/>
-      <c r="CL39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39"/>
+      <c r="Q39"/>
     </row>
     <row r="40" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
       <c r="M40"/>
       <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="CL40" s="3"/>
     </row>
     <row r="41" spans="1:90" x14ac:dyDescent="0.25">
       <c r="M41"/>
-      <c r="N41"/>
+      <c r="AW41" s="5"/>
       <c r="BT41"/>
+      <c r="BU41"/>
+      <c r="BV41"/>
+      <c r="BW41"/>
+      <c r="BX41"/>
+      <c r="BY41"/>
+      <c r="BZ41" s="5"/>
+      <c r="CA41" s="5"/>
+      <c r="CB41" s="5"/>
+      <c r="CC41" s="5"/>
+      <c r="CD41" s="5"/>
+      <c r="CF41" s="5"/>
       <c r="CG41" s="5"/>
       <c r="CH41" s="5"/>
+      <c r="CI41" s="5"/>
+      <c r="CL41" s="3"/>
     </row>
     <row r="42" spans="1:90" x14ac:dyDescent="0.25">
       <c r="M42"/>
-      <c r="N42"/>
-      <c r="BT42"/>
-      <c r="CH42" s="5"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
     </row>
     <row r="43" spans="1:90" x14ac:dyDescent="0.25">
       <c r="M43"/>
-      <c r="O43" s="3"/>
-      <c r="AG43" s="2"/>
-      <c r="AO43" s="2"/>
-      <c r="BM43" s="2"/>
-      <c r="BN43" s="2"/>
-      <c r="CE43" s="2"/>
-      <c r="CK43" s="2"/>
+      <c r="N43"/>
+      <c r="BT43"/>
+      <c r="CG43" s="5"/>
+      <c r="CH43" s="5"/>
     </row>
     <row r="44" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
       <c r="M44"/>
-      <c r="O44" s="3"/>
-      <c r="AG44" s="2"/>
-      <c r="AO44" s="2"/>
-      <c r="CE44" s="2"/>
+      <c r="N44"/>
+      <c r="BT44"/>
+      <c r="CH44" s="5"/>
     </row>
     <row r="45" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="BS45" s="6"/>
-      <c r="BY45"/>
+      <c r="M45"/>
+      <c r="O45" s="3"/>
+      <c r="AG45" s="2"/>
+      <c r="AO45" s="2"/>
+      <c r="BM45" s="2"/>
+      <c r="BN45" s="2"/>
+      <c r="CE45" s="2"/>
+      <c r="CK45" s="2"/>
     </row>
     <row r="46" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="E46" s="2"/>
-      <c r="O46"/>
-      <c r="W46"/>
-      <c r="X46"/>
-      <c r="BM46" s="2"/>
-      <c r="BN46" s="2"/>
-      <c r="CL46" s="3"/>
+      <c r="A46" s="2"/>
+      <c r="M46"/>
+      <c r="O46" s="3"/>
+      <c r="AG46" s="2"/>
+      <c r="AO46" s="2"/>
+      <c r="CE46" s="2"/>
     </row>
     <row r="47" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="M47"/>
-      <c r="O47" s="3"/>
-      <c r="P47"/>
-      <c r="Q47"/>
-      <c r="CL47" s="3"/>
+      <c r="BS47" s="6"/>
+      <c r="BY47"/>
     </row>
     <row r="48" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="M48"/>
-      <c r="O48" s="3"/>
-      <c r="P48"/>
-      <c r="Q48"/>
+      <c r="E48" s="2"/>
+      <c r="O48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+      <c r="BM48" s="2"/>
+      <c r="BN48" s="2"/>
       <c r="CL48" s="3"/>
     </row>
     <row r="49" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
+      <c r="M49"/>
       <c r="O49" s="3"/>
+      <c r="P49"/>
+      <c r="Q49"/>
+      <c r="CL49" s="3"/>
     </row>
     <row r="50" spans="1:97" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
-      <c r="CJ50" s="5"/>
+      <c r="M50"/>
+      <c r="O50" s="3"/>
+      <c r="P50"/>
+      <c r="Q50"/>
+      <c r="CL50" s="3"/>
     </row>
     <row r="51" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CJ51" s="5"/>
+      <c r="A51" s="2"/>
+      <c r="O51" s="3"/>
     </row>
     <row r="52" spans="1:97" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="AJ52" s="2"/>
       <c r="CJ52" s="5"/>
-      <c r="CS52" s="2"/>
     </row>
     <row r="53" spans="1:97" x14ac:dyDescent="0.25">
       <c r="CJ53" s="5"/>
     </row>
     <row r="54" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="O54"/>
-      <c r="W54"/>
-      <c r="X54"/>
-      <c r="CL54" s="3"/>
+      <c r="A54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="AJ54" s="2"/>
+      <c r="CJ54" s="5"/>
+      <c r="CS54" s="2"/>
     </row>
     <row r="55" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="O55" s="3"/>
-      <c r="X55"/>
+      <c r="CJ55" s="5"/>
     </row>
     <row r="56" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="O56" s="3"/>
-      <c r="P56"/>
-      <c r="Q56"/>
+      <c r="O56"/>
+      <c r="W56"/>
       <c r="X56"/>
+      <c r="CL56" s="3"/>
     </row>
     <row r="57" spans="1:97" x14ac:dyDescent="0.25">
       <c r="O57" s="3"/>
       <c r="X57"/>
     </row>
-    <row r="60" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CK60" s="3"/>
-      <c r="CL60" s="3"/>
+    <row r="58" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="O58" s="3"/>
+      <c r="P58"/>
+      <c r="Q58"/>
+      <c r="X58"/>
+    </row>
+    <row r="59" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="O59" s="3"/>
+      <c r="X59"/>
     </row>
     <row r="62" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="M62"/>
-      <c r="N62"/>
-      <c r="BT62"/>
-      <c r="BZ62" s="14"/>
-      <c r="CG62" s="5"/>
-      <c r="CH62" s="5"/>
-    </row>
-    <row r="63" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="M63"/>
-      <c r="N63"/>
-      <c r="BT63"/>
-      <c r="BZ63" s="14"/>
-      <c r="CH63" s="5"/>
+      <c r="CK62" s="3"/>
+      <c r="CL62" s="3"/>
     </row>
     <row r="64" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="O64"/>
-      <c r="X64"/>
-      <c r="CK64" s="3"/>
-    </row>
-    <row r="67" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ67" s="5"/>
-    </row>
-    <row r="68" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ68" s="5"/>
-    </row>
-    <row r="74" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ74" s="5"/>
-    </row>
-    <row r="75" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ75" s="5"/>
-    </row>
-    <row r="77" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="M64"/>
+      <c r="N64"/>
+      <c r="BT64"/>
+      <c r="BZ64" s="14"/>
+      <c r="CG64" s="5"/>
+      <c r="CH64" s="5"/>
+    </row>
+    <row r="65" spans="13:89" x14ac:dyDescent="0.25">
+      <c r="M65"/>
+      <c r="N65"/>
+      <c r="BT65"/>
+      <c r="BZ65" s="14"/>
+      <c r="CH65" s="5"/>
+    </row>
+    <row r="66" spans="13:89" x14ac:dyDescent="0.25">
+      <c r="O66"/>
+      <c r="X66"/>
+      <c r="CK66" s="3"/>
+    </row>
+    <row r="69" spans="13:89" x14ac:dyDescent="0.25">
+      <c r="CJ69" s="5"/>
+    </row>
+    <row r="70" spans="13:89" x14ac:dyDescent="0.25">
+      <c r="CJ70" s="5"/>
+    </row>
+    <row r="76" spans="13:89" x14ac:dyDescent="0.25">
+      <c r="CJ76" s="5"/>
+    </row>
+    <row r="77" spans="13:89" x14ac:dyDescent="0.25">
       <c r="CJ77" s="5"/>
     </row>
-    <row r="78" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ78" s="5"/>
-    </row>
-    <row r="79" spans="88:88" x14ac:dyDescent="0.25">
+    <row r="79" spans="13:89" x14ac:dyDescent="0.25">
       <c r="CJ79" s="5"/>
     </row>
-    <row r="80" spans="88:88" x14ac:dyDescent="0.25">
+    <row r="80" spans="13:89" x14ac:dyDescent="0.25">
       <c r="CJ80" s="5"/>
     </row>
     <row r="81" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT81"/>
+      <c r="CJ81" s="5"/>
     </row>
     <row r="82" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT82"/>
+      <c r="CJ82" s="5"/>
     </row>
     <row r="83" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT83"/>
-      <c r="CJ83" s="5"/>
     </row>
     <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ84" s="5"/>
+      <c r="BT84"/>
     </row>
     <row r="85" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT85"/>
       <c r="CJ85" s="5"/>
     </row>
     <row r="86" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT86"/>
+      <c r="CJ86" s="5"/>
     </row>
     <row r="87" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ87" s="5"/>
     </row>
-    <row r="91" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT91"/>
-    </row>
-    <row r="92" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ92" s="5"/>
-    </row>
-    <row r="100" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ100" s="5"/>
-    </row>
-    <row r="101" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ101" s="5"/>
+    <row r="88" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT88"/>
+    </row>
+    <row r="89" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ89" s="5"/>
+    </row>
+    <row r="93" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT93"/>
+    </row>
+    <row r="94" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ94" s="5"/>
     </row>
     <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT102"/>
-    </row>
-    <row r="107" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT107"/>
-    </row>
-    <row r="108" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT108"/>
-      <c r="CJ108" s="5"/>
+      <c r="CJ102" s="5"/>
+    </row>
+    <row r="103" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ103" s="5"/>
+    </row>
+    <row r="104" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT104"/>
     </row>
     <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ109" s="5"/>
+      <c r="BT109"/>
     </row>
     <row r="110" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT110"/>
       <c r="CJ110" s="5"/>
     </row>
     <row r="111" spans="72:88" x14ac:dyDescent="0.25">
@@ -8784,13 +8847,13 @@
       <c r="CJ112" s="5"/>
     </row>
     <row r="113" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT113"/>
+      <c r="CJ113" s="5"/>
     </row>
     <row r="114" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ114" s="5"/>
     </row>
     <row r="115" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ115" s="5"/>
+      <c r="BT115"/>
     </row>
     <row r="116" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ116" s="5"/>
@@ -8799,13 +8862,13 @@
       <c r="CJ117" s="5"/>
     </row>
     <row r="118" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT118"/>
+      <c r="CJ118" s="5"/>
     </row>
     <row r="119" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ119" s="5"/>
     </row>
     <row r="120" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ120" s="5"/>
+      <c r="BT120"/>
     </row>
     <row r="121" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ121" s="5"/>
@@ -8813,11 +8876,11 @@
     <row r="122" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ122" s="5"/>
     </row>
-    <row r="125" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ125" s="5"/>
-    </row>
-    <row r="126" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ126" s="5"/>
+    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ123" s="5"/>
+    </row>
+    <row r="124" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ124" s="5"/>
     </row>
     <row r="127" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ127" s="5"/>
@@ -8828,14 +8891,14 @@
     <row r="129" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ129" s="5"/>
     </row>
+    <row r="130" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ130" s="5"/>
+    </row>
     <row r="131" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT131"/>
-    </row>
-    <row r="132" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ132" s="5"/>
+      <c r="CJ131" s="5"/>
     </row>
     <row r="133" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ133" s="5"/>
+      <c r="BT133"/>
     </row>
     <row r="134" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ134" s="5"/>
@@ -8843,20 +8906,20 @@
     <row r="135" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ135" s="5"/>
     </row>
-    <row r="139" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ139" s="5"/>
+    <row r="136" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ136" s="5"/>
+    </row>
+    <row r="137" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ137" s="5"/>
     </row>
     <row r="141" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT141"/>
-    </row>
-    <row r="142" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT142"/>
-      <c r="CJ142" s="5"/>
+      <c r="CJ141" s="5"/>
     </row>
     <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ143" s="5"/>
+      <c r="BT143"/>
     </row>
     <row r="144" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT144"/>
       <c r="CJ144" s="5"/>
     </row>
     <row r="145" spans="72:88" x14ac:dyDescent="0.25">
@@ -8865,195 +8928,195 @@
     <row r="146" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ146" s="5"/>
     </row>
+    <row r="147" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ147" s="5"/>
+    </row>
     <row r="148" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT148"/>
-    </row>
-    <row r="149" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ149" s="5"/>
+      <c r="CJ148" s="5"/>
     </row>
     <row r="150" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ150" s="5"/>
+      <c r="BT150"/>
+    </row>
+    <row r="151" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ151" s="5"/>
     </row>
     <row r="152" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ152" s="5"/>
     </row>
-    <row r="153" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ153" s="5"/>
+    <row r="154" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ154" s="5"/>
     </row>
     <row r="155" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT155"/>
-    </row>
-    <row r="156" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ156" s="5"/>
-    </row>
-    <row r="159" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ159" s="5"/>
-    </row>
-    <row r="160" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ160" s="5"/>
-    </row>
-    <row r="163" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ163" s="5"/>
+      <c r="CJ155" s="5"/>
+    </row>
+    <row r="157" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT157"/>
+    </row>
+    <row r="158" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ158" s="5"/>
+    </row>
+    <row r="161" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ161" s="5"/>
+    </row>
+    <row r="162" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ162" s="5"/>
     </row>
     <row r="165" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ165" s="5"/>
     </row>
     <row r="167" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT167"/>
-    </row>
-    <row r="168" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ168" s="5"/>
+      <c r="CJ167" s="5"/>
     </row>
     <row r="169" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ169" s="5"/>
+      <c r="BT169"/>
+    </row>
+    <row r="170" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ170" s="5"/>
     </row>
     <row r="171" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ171" s="5"/>
     </row>
-    <row r="172" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ172" s="5"/>
-    </row>
     <row r="173" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ173" s="5"/>
     </row>
-    <row r="178" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ178" s="5"/>
-    </row>
-    <row r="179" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ179" s="5"/>
-    </row>
-    <row r="182" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ182" s="5"/>
-    </row>
-    <row r="183" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ183" s="5"/>
-    </row>
-    <row r="187" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ187" s="5"/>
-    </row>
-    <row r="191" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ191" s="5"/>
+    <row r="174" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ174" s="5"/>
+    </row>
+    <row r="175" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ175" s="5"/>
+    </row>
+    <row r="180" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ180" s="5"/>
+    </row>
+    <row r="181" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ181" s="5"/>
+    </row>
+    <row r="184" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ184" s="5"/>
+    </row>
+    <row r="185" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ185" s="5"/>
+    </row>
+    <row r="189" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ189" s="5"/>
     </row>
     <row r="193" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ193" s="5"/>
     </row>
-    <row r="194" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ194" s="5"/>
+    <row r="195" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ195" s="5"/>
     </row>
     <row r="196" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ196" s="5"/>
     </row>
-    <row r="197" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ197" s="5"/>
+    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ198" s="5"/>
     </row>
     <row r="199" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT199"/>
-    </row>
-    <row r="200" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT200"/>
-      <c r="CJ200" s="5"/>
+      <c r="CJ199" s="5"/>
     </row>
     <row r="201" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ201" s="5"/>
+      <c r="BT201"/>
+    </row>
+    <row r="202" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT202"/>
+      <c r="CJ202" s="5"/>
     </row>
     <row r="203" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ203" s="5"/>
     </row>
-    <row r="212" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT212"/>
-    </row>
-    <row r="213" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT213"/>
-      <c r="CJ213" s="5"/>
+    <row r="205" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ205" s="5"/>
     </row>
     <row r="214" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ214" s="5"/>
+      <c r="BT214"/>
     </row>
     <row r="215" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT215"/>
       <c r="CJ215" s="5"/>
     </row>
     <row r="216" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT216"/>
+      <c r="CJ216" s="5"/>
     </row>
     <row r="217" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT217"/>
       <c r="CJ217" s="5"/>
     </row>
     <row r="218" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ218" s="5"/>
+      <c r="BT218"/>
+    </row>
+    <row r="219" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT219"/>
+      <c r="CJ219" s="5"/>
     </row>
     <row r="220" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT220"/>
-    </row>
-    <row r="221" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT221"/>
-      <c r="CJ221" s="5"/>
+      <c r="CJ220" s="5"/>
     </row>
     <row r="222" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ222" s="5"/>
+      <c r="BT222"/>
+    </row>
+    <row r="223" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT223"/>
+      <c r="CJ223" s="5"/>
     </row>
     <row r="224" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT224"/>
-    </row>
-    <row r="225" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ225" s="5"/>
-    </row>
-    <row r="228" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ228" s="5"/>
-    </row>
-    <row r="232" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ232" s="5"/>
+      <c r="CJ224" s="5"/>
+    </row>
+    <row r="226" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT226"/>
+    </row>
+    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ227" s="5"/>
+    </row>
+    <row r="230" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ230" s="5"/>
     </row>
     <row r="234" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT234"/>
-    </row>
-    <row r="235" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ235" s="5"/>
-    </row>
-    <row r="242" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT242"/>
-    </row>
-    <row r="243" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ243" s="5"/>
+      <c r="CJ234" s="5"/>
+    </row>
+    <row r="236" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT236"/>
+    </row>
+    <row r="237" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ237" s="5"/>
     </row>
     <row r="244" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ244" s="5"/>
+      <c r="BT244"/>
+    </row>
+    <row r="245" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ245" s="5"/>
     </row>
     <row r="246" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT246"/>
-    </row>
-    <row r="247" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT247"/>
-      <c r="CJ247" s="5"/>
+      <c r="CJ246" s="5"/>
     </row>
     <row r="248" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ248" s="5"/>
-    </row>
-    <row r="254" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT254"/>
-    </row>
-    <row r="255" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT255"/>
-      <c r="CJ255" s="5"/>
+      <c r="BT248"/>
+    </row>
+    <row r="249" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT249"/>
+      <c r="CJ249" s="5"/>
+    </row>
+    <row r="250" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ250" s="5"/>
     </row>
     <row r="256" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT256"/>
-      <c r="CJ256" s="5"/>
     </row>
     <row r="257" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT257"/>
       <c r="CJ257" s="5"/>
     </row>
-    <row r="262" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT262"/>
-    </row>
-    <row r="263" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT263"/>
-    </row>
-    <row r="267" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT267"/>
-    </row>
-    <row r="268" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ268" s="5"/>
+    <row r="258" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT258"/>
+      <c r="CJ258" s="5"/>
+    </row>
+    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ259" s="5"/>
+    </row>
+    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT264"/>
+    </row>
+    <row r="265" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT265"/>
     </row>
     <row r="269" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT269"/>
@@ -9061,46 +9124,44 @@
     <row r="270" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ270" s="5"/>
     </row>
-    <row r="280" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT280"/>
-    </row>
-    <row r="281" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ281" s="5"/>
+    <row r="271" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT271"/>
+    </row>
+    <row r="272" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ272" s="5"/>
+    </row>
+    <row r="282" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT282"/>
     </row>
     <row r="283" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT283"/>
-    </row>
-    <row r="284" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ284" s="5"/>
-    </row>
-    <row r="292" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT292"/>
-    </row>
-    <row r="293" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ293" s="5"/>
-    </row>
-    <row r="297" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT297"/>
-    </row>
-    <row r="298" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ298" s="5"/>
+      <c r="CJ283" s="5"/>
+    </row>
+    <row r="285" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT285"/>
+    </row>
+    <row r="286" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ286" s="5"/>
+    </row>
+    <row r="294" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT294"/>
+    </row>
+    <row r="295" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ295" s="5"/>
+    </row>
+    <row r="299" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT299"/>
     </row>
     <row r="300" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT300"/>
-    </row>
-    <row r="301" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ301" s="5"/>
-    </row>
-    <row r="317" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT317"/>
-    </row>
-    <row r="318" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT318"/>
-      <c r="CJ318" s="5"/>
+      <c r="CJ300" s="5"/>
+    </row>
+    <row r="302" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT302"/>
+    </row>
+    <row r="303" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ303" s="5"/>
     </row>
     <row r="319" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT319"/>
-      <c r="CJ319" s="5"/>
     </row>
     <row r="320" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT320"/>
@@ -9108,52 +9169,54 @@
     </row>
     <row r="321" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT321"/>
+      <c r="CJ321" s="5"/>
+    </row>
+    <row r="322" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT322"/>
+      <c r="CJ322" s="5"/>
     </row>
     <row r="323" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT323"/>
     </row>
-    <row r="324" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT324"/>
-      <c r="CJ324" s="5"/>
-    </row>
     <row r="325" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT325"/>
-      <c r="CJ325" s="5"/>
     </row>
     <row r="326" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT326"/>
       <c r="CJ326" s="5"/>
     </row>
-    <row r="330" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT330"/>
-    </row>
-    <row r="331" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ331" s="5"/>
+    <row r="327" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT327"/>
+      <c r="CJ327" s="5"/>
+    </row>
+    <row r="328" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ328" s="5"/>
+    </row>
+    <row r="332" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT332"/>
     </row>
     <row r="333" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT333"/>
-    </row>
-    <row r="334" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT334"/>
-      <c r="CJ334" s="5"/>
+      <c r="CJ333" s="5"/>
     </row>
     <row r="335" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT335"/>
-      <c r="CJ335" s="5"/>
     </row>
     <row r="336" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT336"/>
       <c r="CJ336" s="5"/>
     </row>
-    <row r="352" spans="72:72" x14ac:dyDescent="0.25">
-      <c r="BT352"/>
-    </row>
-    <row r="353" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ353" s="5"/>
-    </row>
-    <row r="361" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ361" s="5"/>
-    </row>
-    <row r="362" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ362" s="5"/>
+    <row r="337" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT337"/>
+      <c r="CJ337" s="5"/>
+    </row>
+    <row r="338" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ338" s="5"/>
+    </row>
+    <row r="354" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT354"/>
+    </row>
+    <row r="355" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ355" s="5"/>
     </row>
     <row r="363" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ363" s="5"/>
@@ -9164,35 +9227,38 @@
     <row r="365" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ365" s="5"/>
     </row>
+    <row r="366" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ366" s="5"/>
+    </row>
     <row r="367" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT367"/>
-    </row>
-    <row r="368" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ368" s="5"/>
+      <c r="CJ367" s="5"/>
     </row>
     <row r="369" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT369"/>
     </row>
     <row r="370" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT370"/>
       <c r="CJ370" s="5"/>
     </row>
     <row r="371" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ371" s="5"/>
+      <c r="BT371"/>
+    </row>
+    <row r="372" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT372"/>
+      <c r="CJ372" s="5"/>
     </row>
     <row r="373" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT373"/>
-    </row>
-    <row r="374" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT374"/>
-      <c r="CJ374" s="5"/>
+      <c r="CJ373" s="5"/>
     </row>
     <row r="375" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT375"/>
-      <c r="CJ375" s="5"/>
     </row>
     <row r="376" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT376"/>
       <c r="CJ376" s="5"/>
+    </row>
+    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT377"/>
+      <c r="CJ377" s="5"/>
     </row>
     <row r="378" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ378" s="5"/>
@@ -9203,11 +9269,8 @@
     <row r="382" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ382" s="5"/>
     </row>
-    <row r="385" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ385" s="5"/>
-    </row>
-    <row r="386" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ386" s="5"/>
+    <row r="384" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ384" s="5"/>
     </row>
     <row r="387" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ387" s="5"/>
@@ -9222,20 +9285,20 @@
       <c r="CJ390" s="5"/>
     </row>
     <row r="391" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT391"/>
+      <c r="CJ391" s="5"/>
     </row>
     <row r="392" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT392"/>
       <c r="CJ392" s="5"/>
     </row>
     <row r="393" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT393"/>
-      <c r="CJ393" s="5"/>
     </row>
     <row r="394" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT394"/>
       <c r="CJ394" s="5"/>
     </row>
     <row r="395" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT395"/>
       <c r="CJ395" s="5"/>
     </row>
     <row r="396" spans="72:88" x14ac:dyDescent="0.25">
@@ -9244,72 +9307,75 @@
     <row r="397" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ397" s="5"/>
     </row>
+    <row r="398" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ398" s="5"/>
+    </row>
     <row r="399" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ399" s="5"/>
     </row>
-    <row r="400" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ400" s="5"/>
-    </row>
     <row r="401" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT401"/>
+      <c r="CJ401" s="5"/>
     </row>
     <row r="402" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT402"/>
       <c r="CJ402" s="5"/>
     </row>
     <row r="403" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT403"/>
-      <c r="CJ403" s="5"/>
     </row>
     <row r="404" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT404"/>
       <c r="CJ404" s="5"/>
     </row>
     <row r="405" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT405"/>
       <c r="CJ405" s="5"/>
+    </row>
+    <row r="406" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ406" s="5"/>
     </row>
     <row r="407" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ407" s="5"/>
     </row>
-    <row r="408" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ408" s="5"/>
-    </row>
     <row r="409" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT409"/>
       <c r="CJ409" s="5"/>
     </row>
     <row r="410" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT410"/>
       <c r="CJ410" s="5"/>
     </row>
     <row r="411" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT411"/>
       <c r="CJ411" s="5"/>
     </row>
     <row r="412" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT412"/>
       <c r="CJ412" s="5"/>
     </row>
     <row r="413" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ413" s="5"/>
     </row>
+    <row r="414" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ414" s="5"/>
+    </row>
     <row r="415" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT415"/>
       <c r="CJ415" s="5"/>
     </row>
-    <row r="416" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ416" s="5"/>
-    </row>
     <row r="417" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT417"/>
       <c r="CJ417" s="5"/>
     </row>
+    <row r="418" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ418" s="5"/>
+    </row>
     <row r="419" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT419"/>
       <c r="CJ419" s="5"/>
     </row>
-    <row r="420" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT420"/>
-      <c r="CJ420" s="5"/>
-    </row>
     <row r="421" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT421"/>
       <c r="CJ421" s="5"/>
+    </row>
+    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT422"/>
+      <c r="CJ422" s="5"/>
     </row>
     <row r="423" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ423" s="5"/>
@@ -9317,47 +9383,44 @@
     <row r="425" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ425" s="5"/>
     </row>
-    <row r="428" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ428" s="5"/>
-    </row>
-    <row r="429" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ429" s="5"/>
-    </row>
-    <row r="433" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT433"/>
-    </row>
-    <row r="434" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT434"/>
-      <c r="CJ434" s="5"/>
+    <row r="427" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ427" s="5"/>
+    </row>
+    <row r="430" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ430" s="5"/>
+    </row>
+    <row r="431" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ431" s="5"/>
     </row>
     <row r="435" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT435"/>
-      <c r="CJ435" s="5"/>
     </row>
     <row r="436" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT436"/>
       <c r="CJ436" s="5"/>
     </row>
     <row r="437" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT437"/>
       <c r="CJ437" s="5"/>
     </row>
     <row r="438" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT438"/>
+      <c r="CJ438" s="5"/>
     </row>
     <row r="439" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ439" s="5"/>
     </row>
+    <row r="440" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT440"/>
+    </row>
     <row r="441" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ441" s="5"/>
     </row>
-    <row r="442" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ442" s="5"/>
+    <row r="443" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ443" s="5"/>
     </row>
     <row r="444" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ444" s="5"/>
     </row>
-    <row r="445" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ445" s="5"/>
-    </row>
     <row r="446" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ446" s="5"/>
     </row>
@@ -9373,79 +9436,77 @@
     <row r="450" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ450" s="5"/>
     </row>
+    <row r="451" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ451" s="5"/>
+    </row>
     <row r="452" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT452"/>
-    </row>
-    <row r="453" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ453" s="5"/>
+      <c r="CJ452" s="5"/>
     </row>
     <row r="454" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ454" s="5"/>
-    </row>
-    <row r="487" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS487" s="15"/>
-      <c r="BT487" s="16"/>
-    </row>
-    <row r="488" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H488" s="15"/>
-      <c r="CJ488" s="15"/>
-    </row>
-    <row r="494" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT494"/>
-    </row>
-    <row r="495" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT495"/>
-      <c r="CJ495" s="5"/>
+      <c r="BT454"/>
+    </row>
+    <row r="455" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ455" s="5"/>
+    </row>
+    <row r="456" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ456" s="5"/>
+    </row>
+    <row r="489" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS489" s="15"/>
+      <c r="BT489" s="16"/>
+    </row>
+    <row r="490" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H490" s="15"/>
+      <c r="CJ490" s="15"/>
     </row>
     <row r="496" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT496"/>
-      <c r="CJ496" s="5"/>
-    </row>
-    <row r="497" spans="88:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="497" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT497"/>
       <c r="CJ497" s="5"/>
     </row>
-    <row r="514" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT514"/>
-    </row>
-    <row r="515" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ515" s="5"/>
-    </row>
-    <row r="547" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT547"/>
-    </row>
-    <row r="548" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT548"/>
-      <c r="CJ548" s="5"/>
+    <row r="498" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT498"/>
+      <c r="CJ498" s="5"/>
+    </row>
+    <row r="499" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ499" s="5"/>
+    </row>
+    <row r="516" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT516"/>
+    </row>
+    <row r="517" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ517" s="5"/>
     </row>
     <row r="549" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ549" s="5"/>
-    </row>
-    <row r="565" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT565"/>
-    </row>
-    <row r="566" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ566" s="5"/>
-    </row>
-    <row r="572" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT572"/>
-    </row>
-    <row r="573" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT573"/>
-      <c r="CJ573" s="5"/>
+      <c r="BT549"/>
+    </row>
+    <row r="550" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT550"/>
+      <c r="CJ550" s="5"/>
+    </row>
+    <row r="551" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ551" s="5"/>
+    </row>
+    <row r="567" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT567"/>
+    </row>
+    <row r="568" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ568" s="5"/>
     </row>
     <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ574" s="5"/>
-    </row>
-    <row r="579" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT579"/>
-    </row>
-    <row r="580" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT580"/>
-      <c r="CJ580" s="5"/>
+      <c r="BT574"/>
+    </row>
+    <row r="575" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT575"/>
+      <c r="CJ575" s="5"/>
+    </row>
+    <row r="576" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ576" s="5"/>
     </row>
     <row r="581" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT581"/>
-      <c r="CJ581" s="5"/>
     </row>
     <row r="582" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT582"/>
@@ -9500,44 +9561,44 @@
       <c r="CJ594" s="5"/>
     </row>
     <row r="595" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT595"/>
       <c r="CJ595" s="5"/>
     </row>
-    <row r="599" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT599"/>
-    </row>
-    <row r="600" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT600"/>
-      <c r="CJ600" s="5"/>
+    <row r="596" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT596"/>
+      <c r="CJ596" s="5"/>
+    </row>
+    <row r="597" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ597" s="5"/>
     </row>
     <row r="601" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ601" s="5"/>
+      <c r="BT601"/>
     </row>
     <row r="602" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT602"/>
+      <c r="CJ602" s="5"/>
     </row>
     <row r="603" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ603" s="5"/>
     </row>
-    <row r="606" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT606"/>
-    </row>
-    <row r="607" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT607"/>
-      <c r="CJ607" s="5"/>
+    <row r="604" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT604"/>
+    </row>
+    <row r="605" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ605" s="5"/>
     </row>
     <row r="608" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ608" s="5"/>
-    </row>
-    <row r="639" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT639"/>
-    </row>
-    <row r="640" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT640"/>
-      <c r="CJ640" s="5"/>
+      <c r="BT608"/>
+    </row>
+    <row r="609" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT609"/>
+      <c r="CJ609" s="5"/>
+    </row>
+    <row r="610" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ610" s="5"/>
     </row>
     <row r="641" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT641"/>
-      <c r="CJ641" s="5"/>
     </row>
     <row r="642" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT642"/>
@@ -9560,132 +9621,132 @@
       <c r="CJ646" s="5"/>
     </row>
     <row r="647" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT647"/>
       <c r="CJ647" s="5"/>
     </row>
+    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT648"/>
+      <c r="CJ648" s="5"/>
+    </row>
     <row r="649" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT649"/>
-    </row>
-    <row r="650" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ650" s="5"/>
-    </row>
-    <row r="654" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT654"/>
-    </row>
-    <row r="655" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ655" s="5"/>
-    </row>
-    <row r="658" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT658"/>
-    </row>
-    <row r="659" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT659"/>
-      <c r="CJ659" s="5"/>
+      <c r="CJ649" s="5"/>
+    </row>
+    <row r="651" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT651"/>
+    </row>
+    <row r="652" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ652" s="5"/>
+    </row>
+    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT656"/>
+    </row>
+    <row r="657" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ657" s="5"/>
     </row>
     <row r="660" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT660"/>
-      <c r="CJ660" s="5"/>
     </row>
     <row r="661" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT661"/>
       <c r="CJ661" s="5"/>
     </row>
     <row r="662" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT662"/>
       <c r="CJ662" s="5"/>
     </row>
-    <row r="669" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT669"/>
-    </row>
-    <row r="670" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ670" s="5"/>
-    </row>
-    <row r="673" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT673"/>
-    </row>
-    <row r="674" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT674"/>
-      <c r="CJ674" s="5"/>
+    <row r="663" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT663"/>
+      <c r="CJ663" s="5"/>
+    </row>
+    <row r="664" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ664" s="5"/>
+    </row>
+    <row r="671" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT671"/>
+    </row>
+    <row r="672" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ672" s="5"/>
     </row>
     <row r="675" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT675"/>
-      <c r="CJ675" s="5"/>
     </row>
     <row r="676" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT676"/>
       <c r="CJ676" s="5"/>
     </row>
     <row r="677" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT677"/>
       <c r="CJ677" s="5"/>
     </row>
+    <row r="678" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT678"/>
+      <c r="CJ678" s="5"/>
+    </row>
     <row r="679" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT679"/>
-    </row>
-    <row r="680" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT680"/>
-      <c r="CJ680" s="5"/>
+      <c r="CJ679" s="5"/>
     </row>
     <row r="681" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ681" s="5"/>
+      <c r="BT681"/>
     </row>
     <row r="682" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ682">
-        <v>0.15</v>
-      </c>
+      <c r="BT682"/>
+      <c r="CJ682" s="5"/>
+    </row>
+    <row r="683" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ683" s="5"/>
     </row>
     <row r="684" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ684">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="686" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ686">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="685" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ685">
-        <v>0.1</v>
       </c>
     </row>
     <row r="687" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ687">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="689" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ689">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="694" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ694">
-        <v>1</v>
       </c>
     </row>
     <row r="696" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ696">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ698">
         <v>0.4</v>
       </c>
     </row>
-    <row r="697" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ697">
+    <row r="699" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ699">
         <v>0.6</v>
-      </c>
-    </row>
-    <row r="700" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ700">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="701" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ701">
-        <v>0.66700000000000004</v>
       </c>
     </row>
     <row r="702" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ702">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="703" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ703">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="704" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ704">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="705" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT705"/>
-    </row>
-    <row r="706" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT706"/>
-      <c r="CJ706" s="5"/>
     </row>
     <row r="707" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT707"/>
-      <c r="CJ707" s="5"/>
     </row>
     <row r="708" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT708"/>
@@ -9712,24 +9773,24 @@
       <c r="CJ713" s="5"/>
     </row>
     <row r="714" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT714"/>
       <c r="CJ714" s="5"/>
     </row>
     <row r="715" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT715"/>
+      <c r="CJ715" s="5"/>
     </row>
     <row r="716" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ716" s="5"/>
     </row>
-    <row r="725" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT725"/>
-    </row>
-    <row r="726" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT726"/>
-      <c r="CJ726" s="5"/>
+    <row r="717" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT717"/>
+    </row>
+    <row r="718" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ718" s="5"/>
     </row>
     <row r="727" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT727"/>
-      <c r="CJ727" s="5"/>
     </row>
     <row r="728" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT728"/>
@@ -9752,124 +9813,124 @@
       <c r="CJ732" s="5"/>
     </row>
     <row r="733" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT733"/>
       <c r="CJ733" s="5"/>
     </row>
     <row r="734" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT734"/>
+      <c r="CJ734" s="5"/>
     </row>
     <row r="735" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ735" s="5"/>
     </row>
-    <row r="740" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT740"/>
-    </row>
-    <row r="741" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT741"/>
-      <c r="CJ741" s="5"/>
+    <row r="736" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT736"/>
+    </row>
+    <row r="737" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ737" s="5"/>
     </row>
     <row r="742" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ742" s="5"/>
+      <c r="BT742"/>
     </row>
     <row r="743" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT743"/>
+      <c r="CJ743" s="5"/>
     </row>
     <row r="744" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT744"/>
       <c r="CJ744" s="5"/>
     </row>
     <row r="745" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ745" s="5"/>
+      <c r="BT745"/>
     </row>
     <row r="746" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT746"/>
+      <c r="CJ746" s="5"/>
     </row>
     <row r="747" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT747"/>
       <c r="CJ747" s="5"/>
     </row>
     <row r="748" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT748"/>
-      <c r="CJ748" s="5"/>
     </row>
     <row r="749" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT749"/>
       <c r="CJ749" s="5"/>
     </row>
     <row r="750" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT750"/>
       <c r="CJ750" s="5"/>
     </row>
-    <row r="754" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT754"/>
-    </row>
-    <row r="755" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT755"/>
-      <c r="CJ755" s="5"/>
+    <row r="751" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT751"/>
+      <c r="CJ751" s="5"/>
+    </row>
+    <row r="752" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ752" s="5"/>
     </row>
     <row r="756" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT756"/>
-      <c r="CJ756" s="5"/>
     </row>
     <row r="757" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT757"/>
       <c r="CJ757" s="5"/>
     </row>
     <row r="758" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT758"/>
+      <c r="CJ758" s="5"/>
     </row>
     <row r="759" spans="8:88" x14ac:dyDescent="0.25">
       <c r="CJ759" s="5"/>
     </row>
     <row r="760" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS760" s="15"/>
-      <c r="BT760" s="16"/>
+      <c r="BT760"/>
     </row>
     <row r="761" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H761" s="15"/>
-      <c r="CJ761" s="15"/>
-    </row>
-    <row r="778" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT778"/>
-    </row>
-    <row r="779" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT779"/>
-      <c r="CJ779" s="5"/>
+      <c r="CJ761" s="5"/>
+    </row>
+    <row r="762" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS762" s="15"/>
+      <c r="BT762" s="16"/>
+    </row>
+    <row r="763" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H763" s="15"/>
+      <c r="CJ763" s="15"/>
     </row>
     <row r="780" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT780"/>
-      <c r="CJ780" s="5"/>
     </row>
     <row r="781" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT781"/>
       <c r="CJ781" s="5"/>
     </row>
     <row r="782" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT782"/>
       <c r="CJ782" s="5"/>
     </row>
     <row r="783" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT783"/>
+      <c r="CJ783" s="5"/>
     </row>
     <row r="784" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT784"/>
       <c r="CJ784" s="5"/>
     </row>
     <row r="785" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS785" s="15"/>
-      <c r="BT785" s="16"/>
-      <c r="CJ785" s="5"/>
+      <c r="BT785"/>
     </row>
     <row r="786" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H786" s="15"/>
-      <c r="CJ786" s="15"/>
-    </row>
-    <row r="789" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT789"/>
-    </row>
-    <row r="790" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT790"/>
-      <c r="CJ790" s="5"/>
+      <c r="BT786"/>
+      <c r="CJ786" s="5"/>
+    </row>
+    <row r="787" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS787" s="15"/>
+      <c r="BT787" s="16"/>
+      <c r="CJ787" s="5"/>
+    </row>
+    <row r="788" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H788" s="15"/>
+      <c r="CJ788" s="15"/>
     </row>
     <row r="791" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT791"/>
-      <c r="CJ791" s="5"/>
     </row>
     <row r="792" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT792"/>
@@ -9892,18 +9953,18 @@
       <c r="CJ796" s="5"/>
     </row>
     <row r="797" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT797"/>
       <c r="CJ797" s="5"/>
     </row>
+    <row r="798" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT798"/>
+      <c r="CJ798" s="5"/>
+    </row>
     <row r="799" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT799"/>
-    </row>
-    <row r="800" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT800"/>
-      <c r="CJ800" s="5"/>
+      <c r="CJ799" s="5"/>
     </row>
     <row r="801" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT801"/>
-      <c r="CJ801" s="5"/>
     </row>
     <row r="802" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT802"/>
@@ -9918,18 +9979,18 @@
       <c r="CJ804" s="5"/>
     </row>
     <row r="805" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT805"/>
       <c r="CJ805" s="5"/>
     </row>
     <row r="806" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT806"/>
+      <c r="CJ806" s="5"/>
     </row>
     <row r="807" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT807"/>
       <c r="CJ807" s="5"/>
     </row>
     <row r="808" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT808"/>
-      <c r="CJ808" s="5"/>
     </row>
     <row r="809" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT809"/>
@@ -10040,21 +10101,29 @@
       <c r="CJ835" s="5"/>
     </row>
     <row r="836" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT836"/>
       <c r="CJ836" s="5"/>
     </row>
     <row r="837" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT837"/>
+      <c r="CJ837" s="5"/>
     </row>
     <row r="838" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT838"/>
       <c r="CJ838" s="5"/>
     </row>
     <row r="839" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT839"/>
-      <c r="CJ839" s="5"/>
     </row>
     <row r="840" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT840"/>
       <c r="CJ840" s="5"/>
+    </row>
+    <row r="841" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT841"/>
+      <c r="CJ841" s="5"/>
+    </row>
+    <row r="842" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ842" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -10088,37 +10157,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1" t="s">
         <v>434</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>435</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>436</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>437</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>438</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>439</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>440</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>441</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>442</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10132,43 +10201,43 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F2" t="s">
         <v>445</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>446</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>447</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>448</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>449</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>450</v>
-      </c>
-      <c r="K2" t="s">
-        <v>451</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
+        <v>451</v>
+      </c>
+      <c r="N2" t="s">
         <v>452</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>453</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>455</v>
-      </c>
       <c r="Q2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -10197,13 +10266,13 @@
         <v>116</v>
       </c>
       <c r="J3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K3" t="s">
         <v>117</v>
       </c>
       <c r="L3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M3" t="s">
         <v>116</v>
@@ -10212,7 +10281,7 @@
         <v>116</v>
       </c>
       <c r="O3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P3" t="s">
         <v>116</v>
@@ -10274,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10285,10 +10354,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10299,7 +10368,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D3" t="s">
         <v>125</v>
@@ -10334,22 +10403,22 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
+        <v>458</v>
+      </c>
+      <c r="G2" t="s">
         <v>459</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>460</v>
       </c>
-      <c r="H2" t="s">
-        <v>461</v>
-      </c>
       <c r="I2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10383,13 +10452,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C4" t="s">
         <v>462</v>
-      </c>
-      <c r="C4" t="s">
-        <v>463</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -10398,7 +10467,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -10428,34 +10497,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C1" t="s">
         <v>465</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>466</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>467</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>468</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>469</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>470</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>471</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>472</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>473</v>
-      </c>
-      <c r="L1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10463,34 +10532,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C2" t="s">
         <v>475</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>476</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>477</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>478</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>479</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>480</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>481</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>482</v>
       </c>
-      <c r="J2" t="s">
-        <v>483</v>
-      </c>
       <c r="K2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L2" t="s">
         <v>97</v>
@@ -10507,7 +10576,7 @@
         <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -10561,28 +10630,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
         <v>77</v>
       </c>
       <c r="D2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E2" t="s">
         <v>485</v>
-      </c>
-      <c r="E2" t="s">
-        <v>486</v>
       </c>
       <c r="F2" t="s">
         <v>79</v>
       </c>
       <c r="G2" t="s">
+        <v>486</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
         <v>487</v>
-      </c>
-      <c r="H2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I2" t="s">
-        <v>488</v>
       </c>
       <c r="J2" t="s">
         <v>54</v>
@@ -10611,7 +10680,7 @@
         <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I3" t="s">
         <v>118</v>
@@ -10648,28 +10717,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -10677,28 +10746,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10738,22 +10807,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>511</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB786E5-BD70-4EDF-A1B5-98AACF83F1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B209C00-D3E4-4E0F-B448-E9E347C6D9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="471">
   <si>
     <t>Id</t>
   </si>
@@ -721,45 +721,6 @@
     <t>Skill</t>
   </si>
   <si>
-    <t>本能的召唤</t>
-  </si>
-  <si>
-    <t>otter</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>token_10004_otter_motter</t>
-  </si>
-  <si>
-    <t>部署猫</t>
-  </si>
-  <si>
-    <t>特种</t>
-  </si>
-  <si>
-    <t>头像_召唤物_机械水獭</t>
-  </si>
-  <si>
-    <t>猫诱导</t>
-  </si>
-  <si>
-    <t>猫索敌,猫诱导,猫自杀</t>
-  </si>
-  <si>
-    <t>猫诱导后续</t>
-  </si>
-  <si>
-    <t>猫爆炸</t>
-  </si>
-  <si>
-    <t>猫牢笼</t>
-  </si>
-  <si>
-    <t>猫</t>
-  </si>
-  <si>
     <t>#备注</t>
   </si>
   <si>
@@ -1444,9 +1405,6 @@
     <t>普通技能</t>
   </si>
   <si>
-    <t>Target.Hp&gt;Unit.Attack*6 + Unit.Defence</t>
-  </si>
-  <si>
     <t>自动</t>
   </si>
   <si>
@@ -1501,105 +1459,6 @@
     <t>治疗2</t>
   </si>
   <si>
-    <t>获取猫猫</t>
-  </si>
-  <si>
-    <t>获取单位</t>
-  </si>
-  <si>
-    <t>自己入场</t>
-  </si>
-  <si>
-    <t>仅自己</t>
-  </si>
-  <si>
-    <t>{"Count":1,"UnitId":"本能的召唤"}</t>
-  </si>
-  <si>
-    <t>部署干员</t>
-  </si>
-  <si>
-    <t>{"UnitId":"猫诱导","TargetPos":"useSelfPos","SetMod":"Replace","UseMod":"UserDirection","UserName":"本能的召唤"}</t>
-  </si>
-  <si>
-    <t>尝试插入临时路径点</t>
-  </si>
-  <si>
-    <t>0,0#0,-2#-1,-1#0,-1#1,-1#-2,0#-1,0#1,0#2,0#-1,1#0,1#1,1#0,2</t>
-  </si>
-  <si>
-    <t>诅咒</t>
-  </si>
-  <si>
-    <t>猫自杀</t>
-  </si>
-  <si>
-    <t>强制撤退</t>
-  </si>
-  <si>
-    <t>{"Time":10}</t>
-  </si>
-  <si>
-    <t>猫索敌</t>
-  </si>
-  <si>
-    <t>充能释放</t>
-  </si>
-  <si>
-    <t>部署猫后续,部署猫后续2</t>
-  </si>
-  <si>
-    <t>猫死亡</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>Real</t>
-  </si>
-  <si>
-    <t>部署猫后续</t>
-  </si>
-  <si>
-    <t>离场</t>
-  </si>
-  <si>
-    <t>{"UnitId":"猫诱导后续","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"猫诱导"}</t>
-  </si>
-  <si>
-    <t>部署猫后续2</t>
-  </si>
-  <si>
-    <t>撤退</t>
-  </si>
-  <si>
-    <t>Magic</t>
-  </si>
-  <si>
-    <t>猫停顿</t>
-  </si>
-  <si>
-    <t>猫后续死亡</t>
-  </si>
-  <si>
-    <t>{"Sanity":0.25}</t>
-  </si>
-  <si>
-    <t>凛冬击中</t>
-  </si>
-  <si>
-    <t>减速</t>
-  </si>
-  <si>
-    <t>生成囚笼</t>
-  </si>
-  <si>
-    <t>{"UnitId":"猫牢笼","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"FixedDirection"}</t>
-  </si>
-  <si>
     <t>阻挡小于</t>
   </si>
   <si>
@@ -1832,10 +1691,6 @@
   </si>
   <si>
     <t>/Spine/丰川祥子/back/char_4182_oblvns_avemujica_1.skel.bytes</t>
-  </si>
-  <si>
-    <t>{"UseMod":"useSelfPos","ShowRange":1,"Color":"#813C85","Alpha":0.5,"LastTime":5}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>起飞</t>
@@ -1858,7 +1713,11 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>CCB普攻,获取猫猫,起飞</t>
+    <t>Target.Hp &gt;= 10 and Target.Hp &lt;= 100</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB普攻,起飞</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -3104,7 +2963,7 @@
         <v>128</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>517</v>
+        <v>470</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3169,397 +3028,30 @@
       <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>90</v>
-      </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>553</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>10</v>
-      </c>
-      <c r="Y7">
-        <v>0.05</v>
-      </c>
-      <c r="Z7">
-        <v>1</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>-1</v>
-      </c>
-      <c r="AG7" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>128</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="AK7">
-        <v>3</v>
-      </c>
-      <c r="AL7">
-        <v>-0.5</v>
-      </c>
-      <c r="AN7">
-        <v>1</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>1</v>
-      </c>
-      <c r="BB7" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>146</v>
-      </c>
-      <c r="BE7" t="str">
-        <f t="shared" ref="BE7" si="0">"half_"&amp;D7</f>
-        <v>half_otter</v>
-      </c>
-      <c r="BF7" t="str">
-        <f t="shared" ref="BF7" si="1">D7</f>
-        <v>otter</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>133</v>
-      </c>
-      <c r="BH7">
-        <v>5</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>134</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>136</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>137</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>138</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>138</v>
-      </c>
-      <c r="BS7">
-        <v>1</v>
-      </c>
+      <c r="AG7" s="2"/>
+      <c r="AI7" s="2"/>
+      <c r="BB7" s="2"/>
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="J8">
-        <v>90</v>
-      </c>
-      <c r="K8">
-        <v>100</v>
-      </c>
-      <c r="M8">
-        <v>553</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8">
-        <v>100</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>10</v>
-      </c>
-      <c r="Y8">
-        <v>0.05</v>
-      </c>
-      <c r="Z8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
-        <v>-1</v>
-      </c>
-      <c r="AG8" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>128</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>148</v>
-      </c>
-      <c r="AK8">
-        <v>3</v>
-      </c>
-      <c r="AL8">
-        <v>-0.5</v>
-      </c>
-      <c r="AN8">
-        <v>1</v>
-      </c>
-      <c r="AO8">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>1</v>
-      </c>
-      <c r="BB8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>146</v>
-      </c>
-      <c r="BE8" t="str">
-        <f t="shared" ref="BE8:BE9" si="2">"half_"&amp;D8</f>
-        <v>half_otter</v>
-      </c>
-      <c r="BF8" t="str">
-        <f t="shared" ref="BF8:BF9" si="3">D8</f>
-        <v>otter</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>133</v>
-      </c>
-      <c r="BH8">
-        <v>5</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>134</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>136</v>
-      </c>
-      <c r="BN8" t="s">
-        <v>137</v>
-      </c>
-      <c r="BP8" t="s">
-        <v>138</v>
-      </c>
-      <c r="BQ8" t="s">
-        <v>138</v>
-      </c>
-      <c r="BS8">
-        <v>1</v>
-      </c>
+      <c r="AG8" s="2"/>
+      <c r="BB8" s="2"/>
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>90</v>
-      </c>
-      <c r="K9">
-        <v>100</v>
-      </c>
-      <c r="M9">
-        <v>553</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9">
-        <v>100</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>10</v>
-      </c>
-      <c r="Y9">
-        <v>0.05</v>
-      </c>
-      <c r="Z9">
-        <v>999</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>1</v>
-      </c>
-      <c r="AE9">
-        <v>-1</v>
-      </c>
-      <c r="AG9" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>128</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AK9">
-        <v>3</v>
-      </c>
-      <c r="AL9">
-        <v>-0.5</v>
-      </c>
-      <c r="AN9">
-        <v>1</v>
-      </c>
-      <c r="AO9">
-        <v>0</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>1</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>1</v>
-      </c>
-      <c r="BB9" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>146</v>
-      </c>
-      <c r="BE9" t="str">
-        <f t="shared" si="2"/>
-        <v>half_otter</v>
-      </c>
-      <c r="BF9" t="str">
-        <f t="shared" si="3"/>
-        <v>otter</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>133</v>
-      </c>
-      <c r="BH9">
-        <v>5</v>
-      </c>
-      <c r="BI9" t="s">
-        <v>134</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>136</v>
-      </c>
-      <c r="BN9" t="s">
-        <v>137</v>
-      </c>
-      <c r="BP9" t="s">
-        <v>138</v>
-      </c>
-      <c r="BQ9" t="s">
-        <v>138</v>
-      </c>
-      <c r="BS9">
-        <v>1</v>
-      </c>
+      <c r="AG9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="BB9" s="2"/>
     </row>
     <row r="10" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
@@ -3571,133 +3063,13 @@
       <c r="BB10" s="2"/>
     </row>
     <row r="11" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <v>90</v>
-      </c>
-      <c r="K11">
-        <v>3</v>
-      </c>
-      <c r="M11">
-        <v>1000</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11">
-        <v>100</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>10</v>
-      </c>
-      <c r="Y11">
-        <v>0.05</v>
-      </c>
-      <c r="Z11">
-        <v>1</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>128</v>
-      </c>
+      <c r="AG11" s="2"/>
       <c r="AI11" s="2"/>
-      <c r="AK11">
-        <v>3</v>
-      </c>
-      <c r="AL11">
-        <v>-0.5</v>
-      </c>
-      <c r="AN11">
-        <v>1</v>
-      </c>
-      <c r="AO11">
-        <v>99</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>1</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>1</v>
-      </c>
-      <c r="BB11" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>146</v>
-      </c>
-      <c r="BE11" t="str">
-        <f t="shared" ref="BE11" si="4">"half_"&amp;D11</f>
-        <v>half_otter</v>
-      </c>
-      <c r="BF11" t="str">
-        <f t="shared" ref="BF11" si="5">D11</f>
-        <v>otter</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>133</v>
-      </c>
-      <c r="BH11">
-        <v>5</v>
-      </c>
-      <c r="BI11" t="s">
-        <v>134</v>
-      </c>
-      <c r="BM11" t="s">
-        <v>136</v>
-      </c>
-      <c r="BN11" t="s">
-        <v>137</v>
-      </c>
-      <c r="BP11" t="s">
-        <v>138</v>
-      </c>
-      <c r="BQ11" t="s">
-        <v>138</v>
-      </c>
-      <c r="BS11">
-        <v>1</v>
-      </c>
+      <c r="BB11" s="2"/>
     </row>
     <row r="13" spans="1:71" x14ac:dyDescent="0.25">
       <c r="E13" s="17"/>
@@ -6499,8 +5871,8 @@
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
     <col min="6" max="6" width="31.33203125" customWidth="1"/>
     <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1"/>
+    <col min="9" max="9" width="10.75" customWidth="1"/>
     <col min="10" max="10" width="15.75" customWidth="1"/>
     <col min="11" max="13" width="8.33203125" style="5" customWidth="1"/>
     <col min="14" max="14" width="11.75" style="5" customWidth="1"/>
@@ -6573,328 +5945,328 @@
   <sheetData>
     <row r="1" spans="1:111" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D1" t="s">
+      <c r="Q1" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E1" t="s">
+      <c r="R1" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="F1" t="s">
+      <c r="S1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G1" t="s">
+      <c r="T1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="U1" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="V1" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="I1" t="s">
+      <c r="W1" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="J1" t="s">
+      <c r="X1" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="Y1" t="s">
         <v>161</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="Z1" t="s">
         <v>162</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="AB1" t="s">
         <v>164</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="AC1" t="s">
         <v>165</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="AD1" t="s">
         <v>166</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="AE1" t="s">
         <v>167</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="AF1" t="s">
         <v>168</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="AG1" t="s">
         <v>169</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="AH1" t="s">
         <v>170</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="V1" s="5" t="s">
+      <c r="AI1" t="s">
         <v>171</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="AJ1" t="s">
         <v>172</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="AK1" t="s">
         <v>173</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AL1" t="s">
         <v>174</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AM1" t="s">
         <v>175</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AN1" t="s">
         <v>176</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AO1" t="s">
         <v>177</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AP1" t="s">
         <v>178</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AQ1" t="s">
         <v>179</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AR1" t="s">
         <v>180</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AS1" t="s">
         <v>181</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AT1" t="s">
         <v>182</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AU1" t="s">
         <v>183</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AV1" t="s">
         <v>184</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AW1" t="s">
         <v>185</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AX1" t="s">
         <v>186</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AY1" t="s">
         <v>187</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="BA1" t="s">
         <v>189</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="BB1" t="s">
         <v>190</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="BC1" t="s">
         <v>191</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="BD1" t="s">
         <v>192</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="BE1" t="s">
         <v>193</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="BF1" t="s">
         <v>194</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="BH1" t="s">
+        <v>194</v>
+      </c>
+      <c r="BI1" t="s">
         <v>195</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="BJ1" t="s">
         <v>196</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="BK1" t="s">
         <v>197</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BL1" t="s">
         <v>198</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BM1" t="s">
         <v>199</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BN1" t="s">
         <v>200</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BO1" t="s">
         <v>201</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BP1" t="s">
         <v>202</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BQ1" t="s">
         <v>203</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BR1" t="s">
         <v>204</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BT1" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BU1" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="BH1" t="s">
-        <v>207</v>
-      </c>
-      <c r="BI1" t="s">
+      <c r="BV1" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BW1" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BX1" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BY1" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BZ1" t="s">
         <v>212</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="CA1" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="CB1" t="s">
         <v>214</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="CC1" t="s">
         <v>215</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="CD1" t="s">
         <v>216</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="CE1" t="s">
         <v>217</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="CF1" t="s">
         <v>218</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="CG1" t="s">
         <v>219</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="CH1" t="s">
         <v>220</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="CI1" t="s">
         <v>221</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="CK1" t="s">
         <v>223</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="CL1" t="s">
         <v>224</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CM1" t="s">
         <v>225</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CN1" t="s">
         <v>226</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CO1" t="s">
         <v>227</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CP1" t="s">
+        <v>204</v>
+      </c>
+      <c r="CQ1" t="s">
         <v>228</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CR1" t="s">
         <v>229</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CS1" t="s">
         <v>230</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CT1" t="s">
         <v>231</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CU1" t="s">
         <v>232</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CV1" t="s">
         <v>233</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CW1" t="s">
         <v>234</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CX1" t="s">
+        <v>233</v>
+      </c>
+      <c r="CY1" t="s">
         <v>235</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CZ1" t="s">
         <v>236</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="DA1" t="s">
         <v>237</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="DB1" t="s">
         <v>238</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="DC1" t="s">
         <v>239</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="DD1" t="s">
         <v>240</v>
       </c>
-      <c r="CP1" t="s">
-        <v>217</v>
-      </c>
-      <c r="CQ1" t="s">
+      <c r="DE1" t="s">
         <v>241</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="DF1" t="s">
         <v>242</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="DG1" t="s">
         <v>243</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>244</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>245</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>247</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>248</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>249</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>250</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>251</v>
-      </c>
-      <c r="DC1" t="s">
-        <v>252</v>
-      </c>
-      <c r="DD1" t="s">
-        <v>253</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>254</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>255</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:111" x14ac:dyDescent="0.25">
@@ -6908,325 +6280,325 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="F2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="G2" t="s">
         <v>53</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="U2" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="I2" t="s">
+      <c r="V2" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="J2" t="s">
+      <c r="W2" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="Y2" t="s">
         <v>263</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="Z2" t="s">
         <v>264</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="AB2" t="s">
         <v>266</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="AC2" t="s">
         <v>267</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="AD2" t="s">
         <v>268</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="AE2" t="s">
         <v>269</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="AF2" t="s">
         <v>270</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="AG2" t="s">
         <v>271</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="AH2" t="s">
         <v>272</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="AI2" t="s">
         <v>273</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="AJ2" t="s">
         <v>274</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="AK2" t="s">
         <v>275</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AL2" t="s">
         <v>276</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AM2" t="s">
         <v>277</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AN2" t="s">
         <v>278</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AO2" t="s">
         <v>279</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AP2" t="s">
         <v>280</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AQ2" t="s">
         <v>281</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AR2" t="s">
         <v>282</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AS2" t="s">
         <v>283</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AT2" t="s">
         <v>284</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AU2" t="s">
         <v>285</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AV2" t="s">
         <v>286</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AW2" t="s">
         <v>287</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AX2" t="s">
         <v>288</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AY2" t="s">
         <v>289</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AZ2" t="s">
         <v>290</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="BA2" t="s">
         <v>291</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="BB2" t="s">
         <v>292</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="BC2" t="s">
         <v>293</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="BD2" t="s">
         <v>294</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="BE2" t="s">
         <v>295</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="BF2" t="s">
         <v>296</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="BG2" t="s">
         <v>297</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="BH2" t="s">
         <v>298</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="BI2" t="s">
         <v>299</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="BJ2" t="s">
         <v>300</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BK2" t="s">
         <v>301</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BL2" t="s">
         <v>302</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>303</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>304</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>305</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>309</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>310</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>311</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>312</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>313</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>314</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>315</v>
       </c>
       <c r="BM2" t="s">
         <v>79</v>
       </c>
       <c r="BN2" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="BO2" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="BP2" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="BQ2" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="BR2" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="BS2" s="2" t="s">
         <v>95</v>
       </c>
       <c r="BT2" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU2" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="BV2" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="BW2" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="BX2" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="BY2" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>314</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>315</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>316</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>317</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>318</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>319</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>320</v>
+      </c>
+      <c r="CG2" t="s">
         <v>321</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="CH2" t="s">
         <v>322</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="CI2" t="s">
         <v>323</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="CJ2" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="CK2" t="s">
         <v>325</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="CL2" t="s">
         <v>326</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CM2" t="s">
         <v>327</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CN2" t="s">
         <v>328</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CO2" t="s">
         <v>329</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CP2" t="s">
         <v>330</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CQ2" t="s">
         <v>331</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CR2" t="s">
         <v>332</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CS2" t="s">
         <v>333</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CT2" t="s">
         <v>334</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CU2" t="s">
         <v>335</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CV2" t="s">
         <v>336</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CW2" t="s">
         <v>337</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CX2" t="s">
         <v>338</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CY2" t="s">
         <v>339</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CZ2" t="s">
         <v>340</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="DA2" t="s">
         <v>341</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="DB2" t="s">
         <v>342</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="DC2" t="s">
         <v>343</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="DD2" t="s">
         <v>344</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="DE2" t="s">
         <v>345</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="DF2" t="s">
         <v>346</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="DG2" t="s">
         <v>347</v>
-      </c>
-      <c r="CU2" t="s">
-        <v>348</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>349</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>350</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>351</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>352</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>353</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>354</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>355</v>
-      </c>
-      <c r="DC2" t="s">
-        <v>356</v>
-      </c>
-      <c r="DD2" t="s">
-        <v>357</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>358</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>359</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:111" x14ac:dyDescent="0.25">
@@ -7255,13 +6627,13 @@
         <v>116</v>
       </c>
       <c r="J3" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>118</v>
@@ -7324,7 +6696,7 @@
         <v>116</v>
       </c>
       <c r="AG3" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -7348,16 +6720,16 @@
         <v>116</v>
       </c>
       <c r="AO3" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="AP3" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="AS3" t="s">
         <v>116</v>
@@ -7369,7 +6741,7 @@
         <v>116</v>
       </c>
       <c r="AV3" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="AW3" t="s">
         <v>116</v>
@@ -7399,7 +6771,7 @@
         <v>116</v>
       </c>
       <c r="BF3" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="BG3" t="s">
         <v>116</v>
@@ -7426,10 +6798,10 @@
         <v>119</v>
       </c>
       <c r="BO3" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="BP3" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="BQ3" t="s">
         <v>117</v>
@@ -7450,19 +6822,19 @@
         <v>118</v>
       </c>
       <c r="BW3" s="6" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="BX3" s="6" t="s">
         <v>116</v>
       </c>
       <c r="BY3" s="6" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
@@ -7474,19 +6846,19 @@
         <v>124</v>
       </c>
       <c r="CE3" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="CF3" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="CG3" t="s">
         <v>2</v>
       </c>
       <c r="CH3" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="CI3" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="CJ3" s="2" t="s">
         <v>125</v>
@@ -7507,7 +6879,7 @@
         <v>123</v>
       </c>
       <c r="CP3" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="CQ3" t="s">
         <v>123</v>
@@ -7519,28 +6891,28 @@
         <v>125</v>
       </c>
       <c r="CT3" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="CU3" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="CV3" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="CW3" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="CX3" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="CY3" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="CZ3" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="DA3" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="DB3" t="s">
         <v>116</v>
@@ -7563,7 +6935,7 @@
     </row>
     <row r="4" spans="1:111" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:111" x14ac:dyDescent="0.25">
@@ -7574,29 +6946,29 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>381</v>
+        <v>469</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="P6"/>
       <c r="AC6">
         <v>2</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="AR6" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="AV6" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AX6">
         <v>1</v>
@@ -7608,34 +6980,34 @@
         <v>57</v>
       </c>
       <c r="CE6" s="2" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="CF6" s="2" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="CG6" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="CJ6" s="2" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="CK6" s="2"/>
       <c r="CW6" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="O7"/>
       <c r="AC7">
@@ -7645,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -7655,26 +7027,26 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AG8" s="2"/>
       <c r="AO8" s="2" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="AV8" s="2" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AX8">
         <v>0</v>
@@ -7687,12 +7059,12 @@
       </c>
       <c r="CE8" s="2"/>
       <c r="CJ8" s="2" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="CL8" s="2"/>
       <c r="CM8" s="2"/>
       <c r="CW8" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
@@ -7708,22 +7080,22 @@
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>512</v>
+        <v>464</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>513</v>
+        <v>465</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>514</v>
+        <v>466</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>515</v>
+        <v>467</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>516</v>
+        <v>468</v>
       </c>
       <c r="AO10" s="2"/>
       <c r="AV10" s="2"/>
@@ -7736,7 +7108,7 @@
       <c r="CE10" s="2"/>
       <c r="CJ10" s="2"/>
       <c r="CL10" s="2" t="s">
-        <v>512</v>
+        <v>464</v>
       </c>
       <c r="CM10" s="2"/>
       <c r="CP10">
@@ -7755,18 +7127,8 @@
       <c r="CM11" s="2"/>
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>400</v>
-      </c>
-      <c r="C12" t="s">
-        <v>401</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>402</v>
-      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
@@ -7779,18 +7141,6 @@
       <c r="V12" s="7"/>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
-      <c r="AC12">
-        <v>1</v>
-      </c>
-      <c r="AF12">
-        <v>1</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>403</v>
-      </c>
-      <c r="BB12">
-        <v>1</v>
-      </c>
       <c r="BT12" s="10"/>
       <c r="BU12" s="10"/>
       <c r="BV12" s="10"/>
@@ -7798,18 +7148,6 @@
       <c r="BX12" s="10"/>
       <c r="BY12" s="10"/>
       <c r="CJ12" s="7"/>
-      <c r="CS12" t="s">
-        <v>404</v>
-      </c>
-      <c r="DB12">
-        <v>1</v>
-      </c>
-      <c r="DE12">
-        <v>1</v>
-      </c>
-      <c r="DF12">
-        <v>1</v>
-      </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
       <c r="K13" s="7"/>
@@ -7835,18 +7173,8 @@
       <c r="CJ13" s="7"/>
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>144</v>
-      </c>
-      <c r="C14" t="s">
-        <v>405</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>402</v>
-      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
@@ -7859,15 +7187,6 @@
       <c r="V14" s="7"/>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
-      <c r="AC14">
-        <v>1</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>403</v>
-      </c>
-      <c r="BB14">
-        <v>1</v>
-      </c>
       <c r="BT14"/>
       <c r="BU14" s="10"/>
       <c r="BV14" s="10"/>
@@ -7875,26 +7194,10 @@
       <c r="BX14" s="10"/>
       <c r="BY14" s="10"/>
       <c r="CJ14" s="7"/>
-      <c r="CS14" t="s">
-        <v>406</v>
-      </c>
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" t="s">
-        <v>407</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>402</v>
-      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -7907,21 +7210,6 @@
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="AC15">
-        <v>2</v>
-      </c>
-      <c r="AO15" t="s">
-        <v>383</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>408</v>
-      </c>
-      <c r="BB15">
-        <v>4</v>
-      </c>
-      <c r="BR15">
-        <v>0.2</v>
-      </c>
       <c r="BT15" s="10"/>
       <c r="BU15" s="10"/>
       <c r="BV15" s="10"/>
@@ -7929,26 +7217,11 @@
       <c r="BX15" s="10"/>
       <c r="BY15" s="10"/>
       <c r="CJ15" s="7"/>
-      <c r="CS15" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="CW15" t="s">
-        <v>409</v>
-      </c>
+      <c r="CS15" s="2"/>
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>410</v>
-      </c>
-      <c r="C16" t="s">
-        <v>411</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>402</v>
-      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -7961,15 +7234,6 @@
       <c r="V16" s="7"/>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
-      <c r="AC16">
-        <v>1</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>403</v>
-      </c>
-      <c r="BB16">
-        <v>1</v>
-      </c>
       <c r="BT16"/>
       <c r="BU16" s="10"/>
       <c r="BV16" s="10"/>
@@ -7977,11 +7241,8 @@
       <c r="BX16" s="10"/>
       <c r="BY16" s="10"/>
       <c r="CJ16" s="7"/>
-      <c r="CS16" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="17" spans="1:110" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:97" x14ac:dyDescent="0.25">
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
@@ -8004,22 +7265,8 @@
       <c r="BY17" s="10"/>
       <c r="CJ17" s="7"/>
     </row>
-    <row r="18" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>413</v>
-      </c>
-      <c r="C18" t="s">
-        <v>380</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18" t="s">
-        <v>414</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>382</v>
-      </c>
+    <row r="18" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
@@ -8033,60 +7280,17 @@
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
-      <c r="AC18">
-        <v>2</v>
-      </c>
-      <c r="AD18">
-        <v>1</v>
-      </c>
-      <c r="AT18">
-        <v>0.4</v>
-      </c>
-      <c r="BB18">
-        <v>1</v>
-      </c>
-      <c r="BM18" t="s">
-        <v>415</v>
-      </c>
-      <c r="BN18" t="s">
-        <v>416</v>
-      </c>
-      <c r="BR18">
-        <v>6</v>
-      </c>
-      <c r="BT18" s="10">
-        <v>1</v>
-      </c>
-      <c r="BU18" s="10">
-        <v>1</v>
-      </c>
-      <c r="BV18" s="10">
-        <v>1</v>
-      </c>
-      <c r="BW18" s="10" t="s">
-        <v>417</v>
-      </c>
+      <c r="BT18" s="10"/>
+      <c r="BU18" s="10"/>
+      <c r="BV18" s="10"/>
+      <c r="BW18" s="10"/>
       <c r="BX18" s="10"/>
       <c r="BY18" s="10"/>
       <c r="CJ18" s="7"/>
-      <c r="DF18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C19" t="s">
-        <v>380</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="19" spans="1:97" x14ac:dyDescent="0.25">
       <c r="J19" s="8"/>
-      <c r="K19" s="8" t="s">
-        <v>393</v>
-      </c>
+      <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19"/>
       <c r="N19"/>
@@ -8101,56 +7305,16 @@
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
       <c r="Y19" s="8"/>
-      <c r="AC19">
-        <v>1</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>403</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>418</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>419</v>
-      </c>
-      <c r="AX19">
-        <v>999</v>
-      </c>
-      <c r="AZ19">
-        <v>2</v>
-      </c>
-      <c r="BB19">
-        <v>1</v>
-      </c>
       <c r="BT19" s="11"/>
       <c r="BU19" s="11"/>
       <c r="BV19" s="11"/>
       <c r="BW19" s="11"/>
       <c r="BX19" s="11"/>
       <c r="BY19" s="11"/>
-      <c r="DB19">
-        <v>1</v>
-      </c>
-      <c r="DE19">
-        <v>1</v>
-      </c>
-      <c r="DF19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>420</v>
-      </c>
-      <c r="C20" t="s">
-        <v>405</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>421</v>
-      </c>
+    </row>
+    <row r="20" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
@@ -8163,15 +7327,6 @@
       <c r="V20" s="7"/>
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
-      <c r="AC20">
-        <v>1</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>403</v>
-      </c>
-      <c r="BB20">
-        <v>1</v>
-      </c>
       <c r="BT20"/>
       <c r="BU20" s="10"/>
       <c r="BV20" s="10"/>
@@ -8179,23 +7334,10 @@
       <c r="BX20" s="10"/>
       <c r="BY20" s="10"/>
       <c r="CJ20" s="7"/>
-      <c r="CS20" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="21" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>423</v>
-      </c>
-      <c r="C21" t="s">
-        <v>405</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>424</v>
-      </c>
+    </row>
+    <row r="21" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
@@ -8208,15 +7350,6 @@
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
-      <c r="AC21">
-        <v>1</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>403</v>
-      </c>
-      <c r="BB21">
-        <v>1</v>
-      </c>
       <c r="BT21"/>
       <c r="BU21" s="10"/>
       <c r="BV21" s="10"/>
@@ -8224,11 +7357,8 @@
       <c r="BX21" s="10"/>
       <c r="BY21" s="10"/>
       <c r="CJ21" s="7"/>
-      <c r="CS21" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="22" spans="1:110" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:97" x14ac:dyDescent="0.25">
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
@@ -8251,22 +7381,9 @@
       <c r="BY22" s="10"/>
       <c r="CJ22" s="7"/>
     </row>
-    <row r="23" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C23" t="s">
-        <v>380</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>402</v>
-      </c>
+    <row r="23" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="K23" s="7"/>
+      <c r="L23" s="8"/>
       <c r="M23"/>
       <c r="N23"/>
       <c r="O23" s="8"/>
@@ -8278,78 +7395,19 @@
       <c r="U23" s="8"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
-      <c r="X23" s="8">
-        <v>1</v>
-      </c>
+      <c r="X23" s="8"/>
       <c r="Y23" s="8"/>
-      <c r="AC23">
-        <v>2</v>
-      </c>
-      <c r="AD23">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="s">
-        <v>383</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>408</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>425</v>
-      </c>
-      <c r="AX23">
-        <v>1.5</v>
-      </c>
-      <c r="BB23">
-        <v>99</v>
-      </c>
-      <c r="BC23">
-        <v>11</v>
-      </c>
-      <c r="BD23">
-        <v>0.5</v>
-      </c>
-      <c r="BM23" t="s">
-        <v>426</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>427</v>
-      </c>
       <c r="BT23" s="11"/>
       <c r="BU23" s="11"/>
       <c r="BV23" s="11"/>
       <c r="BW23" s="11"/>
       <c r="BX23" s="11"/>
       <c r="BY23" s="11"/>
-      <c r="BZ23" t="s">
-        <v>57</v>
-      </c>
-      <c r="CE23" t="s">
-        <v>386</v>
-      </c>
-      <c r="CJ23" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="CW23" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="24" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>426</v>
-      </c>
-      <c r="C24" t="s">
-        <v>380</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>402</v>
-      </c>
+      <c r="CJ23" s="7"/>
+    </row>
+    <row r="24" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
@@ -8361,24 +7419,7 @@
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
       <c r="W24" s="7"/>
-      <c r="X24" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC24">
-        <v>2</v>
-      </c>
-      <c r="AD24">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="s">
-        <v>383</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>408</v>
-      </c>
-      <c r="BB24">
-        <v>99</v>
-      </c>
+      <c r="X24" s="7"/>
       <c r="BT24"/>
       <c r="BU24" s="10"/>
       <c r="BV24" s="10"/>
@@ -8386,32 +7427,9 @@
       <c r="BX24" s="10"/>
       <c r="BY24" s="10"/>
       <c r="CJ24" s="7"/>
-      <c r="CL24" t="s">
-        <v>430</v>
-      </c>
-      <c r="CM24">
-        <v>-0.8</v>
-      </c>
-      <c r="CP24">
-        <v>6</v>
-      </c>
-      <c r="CW24" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="25" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>427</v>
-      </c>
-      <c r="C25" t="s">
-        <v>380</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>393</v>
-      </c>
+    </row>
+    <row r="25" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
@@ -8425,33 +7443,6 @@
       <c r="V25" s="7"/>
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
-      <c r="AC25">
-        <v>1</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>403</v>
-      </c>
-      <c r="AR25" t="s">
-        <v>418</v>
-      </c>
-      <c r="AV25" t="s">
-        <v>419</v>
-      </c>
-      <c r="AX25">
-        <v>0.09</v>
-      </c>
-      <c r="AZ25">
-        <v>1</v>
-      </c>
-      <c r="BB25">
-        <v>1</v>
-      </c>
-      <c r="BC25">
-        <v>11</v>
-      </c>
-      <c r="BD25">
-        <v>0.5</v>
-      </c>
       <c r="BT25"/>
       <c r="BU25" s="10"/>
       <c r="BV25" s="10"/>
@@ -8459,57 +7450,28 @@
       <c r="BX25" s="10"/>
       <c r="BY25" s="10"/>
       <c r="CJ25" s="7"/>
-      <c r="CW25" t="s">
-        <v>429</v>
-      </c>
-      <c r="DB25">
-        <v>1</v>
-      </c>
-      <c r="DE25">
-        <v>1</v>
-      </c>
-      <c r="DF25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="AC27">
-        <v>1</v>
-      </c>
-      <c r="AR27" s="2" t="s">
-        <v>418</v>
-      </c>
+    </row>
+    <row r="27" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="AR27" s="2"/>
       <c r="BT27"/>
       <c r="CJ27" s="5"/>
-      <c r="CS27" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="28" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CS27" s="2"/>
+    </row>
+    <row r="28" spans="1:97" x14ac:dyDescent="0.25">
       <c r="J28" s="2"/>
       <c r="O28"/>
       <c r="AO28" s="2"/>
       <c r="CS28" s="2"/>
     </row>
-    <row r="29" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:97" x14ac:dyDescent="0.25">
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:97" x14ac:dyDescent="0.25">
       <c r="CJ30" s="5"/>
     </row>
-    <row r="31" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:97" x14ac:dyDescent="0.25">
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
       <c r="M31"/>
@@ -8532,7 +7494,7 @@
       <c r="BX31" s="12"/>
       <c r="BY31"/>
     </row>
-    <row r="32" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:97" x14ac:dyDescent="0.25">
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32"/>
@@ -10157,37 +9119,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>433</v>
+        <v>386</v>
       </c>
       <c r="F1" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="G1" t="s">
-        <v>435</v>
+        <v>388</v>
       </c>
       <c r="H1" t="s">
-        <v>436</v>
+        <v>389</v>
       </c>
       <c r="I1" t="s">
-        <v>437</v>
+        <v>390</v>
       </c>
       <c r="J1" t="s">
-        <v>438</v>
+        <v>391</v>
       </c>
       <c r="L1" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="M1" t="s">
-        <v>440</v>
+        <v>393</v>
       </c>
       <c r="N1" t="s">
-        <v>441</v>
+        <v>394</v>
       </c>
       <c r="O1" t="s">
-        <v>442</v>
+        <v>395</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>443</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10201,43 +9163,43 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>444</v>
+        <v>397</v>
       </c>
       <c r="F2" t="s">
-        <v>445</v>
+        <v>398</v>
       </c>
       <c r="G2" t="s">
-        <v>446</v>
+        <v>399</v>
       </c>
       <c r="H2" t="s">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="I2" t="s">
-        <v>448</v>
+        <v>401</v>
       </c>
       <c r="J2" t="s">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="K2" t="s">
-        <v>450</v>
+        <v>403</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
-        <v>451</v>
+        <v>404</v>
       </c>
       <c r="N2" t="s">
-        <v>452</v>
+        <v>405</v>
       </c>
       <c r="O2" t="s">
-        <v>453</v>
+        <v>406</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>454</v>
+        <v>407</v>
       </c>
       <c r="Q2" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -10266,13 +9228,13 @@
         <v>116</v>
       </c>
       <c r="J3" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="K3" t="s">
         <v>117</v>
       </c>
       <c r="L3" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="M3" t="s">
         <v>116</v>
@@ -10281,7 +9243,7 @@
         <v>116</v>
       </c>
       <c r="O3" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="P3" t="s">
         <v>116</v>
@@ -10343,7 +9305,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>455</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10354,10 +9316,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10368,7 +9330,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="D3" t="s">
         <v>125</v>
@@ -10403,22 +9365,22 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>458</v>
+        <v>411</v>
       </c>
       <c r="G2" t="s">
-        <v>459</v>
+        <v>412</v>
       </c>
       <c r="H2" t="s">
-        <v>460</v>
+        <v>413</v>
       </c>
       <c r="I2" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10452,13 +9414,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>461</v>
+        <v>414</v>
       </c>
       <c r="C4" t="s">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -10467,7 +9429,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>463</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -10497,34 +9459,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>464</v>
+        <v>417</v>
       </c>
       <c r="C1" t="s">
-        <v>465</v>
+        <v>418</v>
       </c>
       <c r="D1" t="s">
-        <v>466</v>
+        <v>419</v>
       </c>
       <c r="E1" t="s">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="F1" t="s">
-        <v>468</v>
+        <v>421</v>
       </c>
       <c r="H1" t="s">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="I1" t="s">
-        <v>470</v>
+        <v>423</v>
       </c>
       <c r="J1" t="s">
-        <v>471</v>
+        <v>424</v>
       </c>
       <c r="K1" t="s">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="L1" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10532,34 +9494,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>474</v>
+        <v>427</v>
       </c>
       <c r="C2" t="s">
-        <v>475</v>
+        <v>428</v>
       </c>
       <c r="D2" t="s">
-        <v>476</v>
+        <v>429</v>
       </c>
       <c r="E2" t="s">
-        <v>477</v>
+        <v>430</v>
       </c>
       <c r="F2" t="s">
-        <v>478</v>
+        <v>431</v>
       </c>
       <c r="G2" t="s">
-        <v>479</v>
+        <v>432</v>
       </c>
       <c r="H2" t="s">
-        <v>480</v>
+        <v>433</v>
       </c>
       <c r="I2" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
       <c r="J2" t="s">
-        <v>482</v>
+        <v>435</v>
       </c>
       <c r="K2" t="s">
-        <v>458</v>
+        <v>411</v>
       </c>
       <c r="L2" t="s">
         <v>97</v>
@@ -10576,7 +9538,7 @@
         <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>483</v>
+        <v>436</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -10630,28 +9592,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>484</v>
+        <v>437</v>
       </c>
       <c r="E2" t="s">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="F2" t="s">
         <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>486</v>
+        <v>439</v>
       </c>
       <c r="H2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="I2" t="s">
-        <v>487</v>
+        <v>440</v>
       </c>
       <c r="J2" t="s">
         <v>54</v>
@@ -10680,7 +9642,7 @@
         <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>488</v>
+        <v>441</v>
       </c>
       <c r="I3" t="s">
         <v>118</v>
@@ -10717,28 +9679,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>489</v>
+        <v>442</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>491</v>
+        <v>444</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>493</v>
+        <v>446</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>494</v>
+        <v>447</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>496</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -10746,28 +9708,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>497</v>
+        <v>450</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>498</v>
+        <v>451</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>499</v>
+        <v>452</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>500</v>
+        <v>453</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>502</v>
+        <v>455</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>503</v>
+        <v>456</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>504</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10807,22 +9769,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>505</v>
+        <v>458</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>506</v>
+        <v>459</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>507</v>
+        <v>460</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>508</v>
+        <v>461</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>509</v>
+        <v>462</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>510</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B209C00-D3E4-4E0F-B448-E9E347C6D9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFDB20D-6154-41ED-A6A3-A919BA7914EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="474">
   <si>
     <t>Id</t>
   </si>
@@ -1411,9 +1411,6 @@
     <t>终点距离</t>
   </si>
   <si>
-    <t>0,0#1,0#2,0</t>
-  </si>
-  <si>
     <t>Normal</t>
   </si>
   <si>
@@ -1424,9 +1421,6 @@
   </si>
   <si>
     <t>Muzzle</t>
-  </si>
-  <si>
-    <t>{"Sanity":600}</t>
   </si>
   <si>
     <t>拉普兰德近战击中</t>
@@ -1705,19 +1699,38 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>自己入场</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>仅自己</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>Target.Hp &gt;= 10 and Target.Hp &lt;= 100</t>
+    <t>CCB普攻,起飞</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>CCB普攻,起飞</t>
+    <t>落地</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>红门</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>大飞镖</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>真言天赋弹道</t>
+  </si>
+  <si>
+    <t>真言天赋弹道</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"LifeTime":99999,"Radius":0.5,"Trigger":0.02,"MoveHeight":2,"TriggerTimes":9999,"TargetTeam":2,"MaxTargetCount":9999}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>神经损伤麻痹</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -2963,7 +2976,7 @@
         <v>128</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -6951,27 +6964,34 @@
       <c r="C6" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>469</v>
-      </c>
+      <c r="H6" s="2"/>
       <c r="K6" s="5" t="s">
         <v>368</v>
       </c>
       <c r="P6"/>
       <c r="AC6">
+        <v>4</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AT6">
+        <v>15</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
         <v>2</v>
-      </c>
-      <c r="AO6" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>370</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>371</v>
-      </c>
-      <c r="AX6">
-        <v>1</v>
       </c>
       <c r="BB6">
         <v>1</v>
@@ -6980,34 +7000,35 @@
         <v>57</v>
       </c>
       <c r="CE6" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="CF6" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="CG6" t="s">
         <v>373</v>
       </c>
-      <c r="CG6" t="s">
+      <c r="CJ6" s="2"/>
+      <c r="CK6" s="2"/>
+      <c r="CL6" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="CW6" t="s">
         <v>374</v>
-      </c>
-      <c r="CJ6" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="CK6" s="2"/>
-      <c r="CW6" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>367</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="O7"/>
       <c r="AC7">
@@ -7017,7 +7038,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -7027,16 +7048,16 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>381</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>383</v>
       </c>
       <c r="AC8">
         <v>2</v>
@@ -7046,7 +7067,7 @@
         <v>369</v>
       </c>
       <c r="AV8" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AX8">
         <v>0</v>
@@ -7059,12 +7080,12 @@
       </c>
       <c r="CE8" s="2"/>
       <c r="CJ8" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="CL8" s="2"/>
       <c r="CM8" s="2"/>
       <c r="CW8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
@@ -7080,13 +7101,13 @@
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>464</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>466</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>467</v>
@@ -7095,7 +7116,7 @@
         <v>1</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AO10" s="2"/>
       <c r="AV10" s="2"/>
@@ -7108,7 +7129,7 @@
       <c r="CE10" s="2"/>
       <c r="CJ10" s="2"/>
       <c r="CL10" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="CM10" s="2"/>
       <c r="CP10">
@@ -9119,37 +9140,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G1" t="s">
         <v>386</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>387</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>388</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>389</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>390</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>391</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>392</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>393</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="O1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -9163,40 +9184,40 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G2" t="s">
         <v>397</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>398</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>399</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>400</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>401</v>
-      </c>
-      <c r="J2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K2" t="s">
-        <v>403</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
+        <v>402</v>
+      </c>
+      <c r="N2" t="s">
+        <v>403</v>
+      </c>
+      <c r="O2" t="s">
         <v>404</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="O2" t="s">
-        <v>406</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="Q2" t="s">
         <v>333</v>
@@ -9305,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9316,7 +9337,7 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -9365,19 +9386,19 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G2" t="s">
+        <v>410</v>
+      </c>
+      <c r="H2" t="s">
         <v>411</v>
-      </c>
-      <c r="G2" t="s">
-        <v>412</v>
-      </c>
-      <c r="H2" t="s">
-        <v>413</v>
       </c>
       <c r="I2" t="s">
         <v>333</v>
@@ -9414,13 +9435,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -9429,11 +9450,25 @@
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>472</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -9459,34 +9494,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1" t="s">
         <v>417</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>418</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>419</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>420</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>421</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>422</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>423</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>424</v>
-      </c>
-      <c r="K1" t="s">
-        <v>425</v>
-      </c>
-      <c r="L1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9494,34 +9529,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D2" t="s">
         <v>427</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>428</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>429</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>430</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>431</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>432</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>433</v>
       </c>
-      <c r="I2" t="s">
-        <v>434</v>
-      </c>
-      <c r="J2" t="s">
-        <v>435</v>
-      </c>
       <c r="K2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L2" t="s">
         <v>97</v>
@@ -9538,7 +9573,7 @@
         <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -9598,22 +9633,22 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F2" t="s">
         <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H2" t="s">
         <v>273</v>
       </c>
       <c r="I2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J2" t="s">
         <v>54</v>
@@ -9642,7 +9677,7 @@
         <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I3" t="s">
         <v>118</v>
@@ -9679,28 +9714,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -9708,28 +9743,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9769,22 +9804,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFDB20D-6154-41ED-A6A3-A919BA7914EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6A2BA8-9B2C-4E82-8B14-90F9E2F9C4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,7 +105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="BB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -132,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BP1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="BR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -156,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="CT1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="482">
   <si>
     <t>Id</t>
   </si>
@@ -1163,9 +1163,6 @@
   </si>
   <si>
     <t>IfHeal</t>
-  </si>
-  <si>
-    <t>DamageRate</t>
   </si>
   <si>
     <t>DamageWithFrameRate</t>
@@ -1731,6 +1728,42 @@
   </si>
   <si>
     <t>神经损伤麻痹</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试buff</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值变化依表达式</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageRate</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Expression":"Buff.Skill.SkillData.DamageRate = Buff.Duration.value"}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先Buff</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义优先级</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderBuff</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderExpression</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -2976,7 +3009,7 @@
         <v>128</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -5874,7 +5907,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH842"/>
+  <dimension ref="A1:DJ842"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -5914,49 +5947,49 @@
     <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
     <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="43" width="11.83203125" customWidth="1"/>
-    <col min="44" max="44" width="18.4140625" customWidth="1"/>
-    <col min="45" max="45" width="12.25" customWidth="1"/>
-    <col min="46" max="46" width="11.9140625" customWidth="1"/>
-    <col min="47" max="47" width="19.58203125" customWidth="1"/>
-    <col min="48" max="48" width="12.6640625" customWidth="1"/>
-    <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="19.75" customWidth="1"/>
-    <col min="53" max="53" width="5.08203125" customWidth="1"/>
-    <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="55" width="13.5" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" customWidth="1"/>
-    <col min="58" max="58" width="8.25" customWidth="1"/>
-    <col min="59" max="65" width="8.33203125" customWidth="1"/>
-    <col min="66" max="68" width="11.25" customWidth="1"/>
-    <col min="69" max="69" width="6.58203125" customWidth="1"/>
-    <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="6" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="6" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="6" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="6" customWidth="1"/>
-    <col min="78" max="78" width="13.5" customWidth="1"/>
-    <col min="79" max="79" width="21.1640625" customWidth="1"/>
-    <col min="80" max="80" width="15.75" customWidth="1"/>
-    <col min="81" max="81" width="15.58203125" customWidth="1"/>
-    <col min="82" max="82" width="12.83203125" customWidth="1"/>
-    <col min="83" max="83" width="16.1640625" customWidth="1"/>
-    <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.83203125" customWidth="1"/>
-    <col min="88" max="88" width="23.58203125" customWidth="1"/>
-    <col min="89" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="17.08203125" customWidth="1"/>
-    <col min="97" max="97" width="14" customWidth="1"/>
-    <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08203125" customWidth="1"/>
-    <col min="101" max="101" width="13.75" customWidth="1"/>
-    <col min="108" max="108" width="15.5" customWidth="1"/>
-    <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" style="6" customWidth="1"/>
+    <col min="75" max="76" width="8.5" style="6" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" style="6" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" style="6" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="114" max="114" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>140</v>
       </c>
@@ -6080,209 +6113,215 @@
       <c r="AQ1" t="s">
         <v>179</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="AT1" t="s">
         <v>180</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>181</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>182</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>183</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>184</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>185</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>186</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>187</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BB1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>189</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>190</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>191</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>192</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>193</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>194</v>
       </c>
       <c r="BH1" t="s">
         <v>194</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
+        <v>194</v>
+      </c>
+      <c r="BK1" t="s">
         <v>195</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>196</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>197</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>198</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>199</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>200</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>201</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>202</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>203</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>204</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BU1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BV1" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BW1" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BX1" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BY1" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="CA1" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CB1" t="s">
         <v>212</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CC1" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>214</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CE1" t="s">
         <v>215</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>216</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>217</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>218</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>219</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>220</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>221</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CL1" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CM1" t="s">
         <v>223</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CN1" t="s">
         <v>224</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CO1" t="s">
         <v>225</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CP1" t="s">
         <v>226</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>227</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
         <v>204</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CS1" t="s">
         <v>228</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CT1" t="s">
         <v>229</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>230</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>231</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>232</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>233</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>234</v>
       </c>
       <c r="CX1" t="s">
         <v>233</v>
       </c>
       <c r="CY1" t="s">
+        <v>234</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>233</v>
+      </c>
+      <c r="DA1" t="s">
         <v>235</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DB1" t="s">
         <v>236</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DC1" t="s">
         <v>237</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DD1" t="s">
         <v>238</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DE1" t="s">
         <v>239</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DF1" t="s">
         <v>240</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DG1" t="s">
         <v>241</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>242</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="2" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6409,212 +6448,218 @@
       <c r="AQ2" t="s">
         <v>281</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="AT2" t="s">
         <v>282</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AU2" t="s">
         <v>283</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>284</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>285</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>286</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>287</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="BA2" t="s">
         <v>288</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>289</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BC2" t="s">
         <v>290</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>291</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>292</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>293</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>294</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>295</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>296</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>297</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>298</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>299</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" t="s">
         <v>300</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>301</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
+        <v>79</v>
+      </c>
+      <c r="BP2" t="s">
         <v>302</v>
       </c>
-      <c r="BM2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN2" t="s">
+      <c r="BQ2" t="s">
         <v>303</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>304</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BS2" t="s">
         <v>305</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BT2" t="s">
         <v>306</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="BV2" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="BS2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BT2" s="6" t="s">
+      <c r="BW2" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BX2" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="CB2" t="s">
         <v>313</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CC2" t="s">
         <v>314</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CD2" t="s">
         <v>315</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CE2" t="s">
         <v>316</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CF2" t="s">
         <v>317</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CG2" t="s">
         <v>318</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CH2" t="s">
         <v>319</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CI2" t="s">
         <v>320</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CJ2" t="s">
         <v>321</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CK2" t="s">
         <v>322</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CM2" t="s">
         <v>324</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CN2" t="s">
         <v>325</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CO2" t="s">
         <v>326</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CP2" t="s">
         <v>327</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CQ2" t="s">
         <v>328</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CR2" t="s">
         <v>329</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CS2" t="s">
         <v>330</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CT2" t="s">
         <v>331</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CU2" t="s">
         <v>332</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CV2" t="s">
         <v>333</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CW2" t="s">
         <v>334</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CX2" t="s">
         <v>335</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CY2" t="s">
         <v>336</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CZ2" t="s">
         <v>337</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DA2" t="s">
         <v>338</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DB2" t="s">
         <v>339</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DC2" t="s">
         <v>340</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DD2" t="s">
         <v>341</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DE2" t="s">
         <v>342</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DF2" t="s">
         <v>343</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DG2" t="s">
         <v>344</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DH2" t="s">
         <v>345</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DI2" t="s">
         <v>346</v>
       </c>
-      <c r="DG2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" spans="1:111" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6640,13 +6685,13 @@
         <v>116</v>
       </c>
       <c r="J3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>349</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>350</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>118</v>
@@ -6709,7 +6754,7 @@
         <v>116</v>
       </c>
       <c r="AG3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -6733,184 +6778,184 @@
         <v>116</v>
       </c>
       <c r="AO3" t="s">
+        <v>351</v>
+      </c>
+      <c r="AP3" t="s">
         <v>352</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>353</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" t="s">
-        <v>354</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>116</v>
+      <c r="AR3" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>481</v>
       </c>
       <c r="AT3" t="s">
-        <v>117</v>
+        <v>353</v>
       </c>
       <c r="AU3" t="s">
         <v>116</v>
       </c>
       <c r="AV3" t="s">
-        <v>355</v>
+        <v>117</v>
       </c>
       <c r="AW3" t="s">
         <v>116</v>
       </c>
       <c r="AX3" t="s">
-        <v>117</v>
+        <v>354</v>
       </c>
       <c r="AY3" t="s">
         <v>116</v>
       </c>
       <c r="AZ3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BB3" t="s">
         <v>118</v>
       </c>
       <c r="BC3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD3" t="s">
         <v>118</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BE3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF3" t="s">
         <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>354</v>
       </c>
       <c r="BG3" t="s">
         <v>116</v>
       </c>
       <c r="BH3" t="s">
-        <v>117</v>
+        <v>353</v>
       </c>
       <c r="BI3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BJ3" t="s">
         <v>117</v>
       </c>
       <c r="BK3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM3" t="s">
         <v>118</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BN3" t="s">
         <v>118</v>
       </c>
-      <c r="BM3" t="s">
+      <c r="BO3" t="s">
         <v>119</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BP3" t="s">
         <v>119</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BQ3" t="s">
+        <v>355</v>
+      </c>
+      <c r="BR3" t="s">
         <v>356</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BS3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV3" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW3" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="BX3" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY3" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="BQ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BS3" s="2" t="s">
+      <c r="BZ3" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="BT3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="BV3" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="BW3" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="BX3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BY3" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>359</v>
+      <c r="CA3" s="6" t="s">
+        <v>357</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
       </c>
       <c r="CC3" t="s">
-        <v>124</v>
+        <v>358</v>
       </c>
       <c r="CD3" t="s">
         <v>124</v>
       </c>
       <c r="CE3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>359</v>
+      </c>
+      <c r="CH3" t="s">
         <v>360</v>
       </c>
-      <c r="CF3" t="s">
+      <c r="CI3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" t="s">
         <v>361</v>
       </c>
-      <c r="CG3" t="s">
-        <v>2</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>362</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>362</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
+      <c r="CK3" t="s">
+        <v>361</v>
+      </c>
+      <c r="CL3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="CM3" t="s">
         <v>120</v>
       </c>
-      <c r="CL3" t="s">
+      <c r="CN3" t="s">
         <v>120</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>123</v>
       </c>
       <c r="CO3" t="s">
         <v>123</v>
       </c>
       <c r="CP3" t="s">
-        <v>359</v>
+        <v>123</v>
       </c>
       <c r="CQ3" t="s">
         <v>123</v>
       </c>
       <c r="CR3" t="s">
+        <v>358</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CT3" t="s">
         <v>116</v>
       </c>
-      <c r="CS3" t="s">
+      <c r="CU3" t="s">
         <v>125</v>
       </c>
-      <c r="CT3" t="s">
-        <v>363</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>364</v>
-      </c>
       <c r="CV3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="CW3" t="s">
         <v>363</v>
@@ -6919,19 +6964,19 @@
         <v>363</v>
       </c>
       <c r="CY3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="CZ3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="DA3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="DB3" t="s">
-        <v>116</v>
+        <v>362</v>
       </c>
       <c r="DC3" t="s">
-        <v>116</v>
+        <v>362</v>
       </c>
       <c r="DD3" t="s">
         <v>116</v>
@@ -6945,90 +6990,96 @@
       <c r="DG3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="4" spans="1:111" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="DH3" t="s">
+        <v>116</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:111" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="BM5" s="2"/>
-      <c r="CS5" s="2"/>
-    </row>
-    <row r="6" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BO5" s="2"/>
+      <c r="CU5" s="2"/>
+    </row>
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="H6" s="2"/>
       <c r="K6" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P6"/>
       <c r="AC6">
         <v>4</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AN6">
         <v>1</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AT6">
+        <v>377</v>
+      </c>
+      <c r="AV6">
         <v>15</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AX6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>2</v>
+      </c>
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="CB6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="CG6" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>2</v>
-      </c>
-      <c r="BB6">
-        <v>1</v>
-      </c>
-      <c r="BZ6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="CE6" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="CF6" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="CG6" t="s">
+      <c r="CH6" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>372</v>
+      </c>
+      <c r="CL6" s="2"/>
+      <c r="CM6" s="2"/>
+      <c r="CN6" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="CY6" t="s">
         <v>373</v>
       </c>
-      <c r="CJ6" s="2"/>
-      <c r="CK6" s="2"/>
-      <c r="CL6" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="CW6" t="s">
+    </row>
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="7" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="5" t="s">
         <v>376</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>377</v>
       </c>
       <c r="O7"/>
       <c r="AC7">
@@ -7038,116 +7089,113 @@
         <v>1</v>
       </c>
       <c r="AO7" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AV7">
+        <v>2.5</v>
+      </c>
+      <c r="CB7" s="2"/>
+      <c r="CG7" s="2"/>
+    </row>
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="AT7">
-        <v>2.5</v>
-      </c>
-      <c r="BZ7" s="2"/>
-      <c r="CE7" s="2"/>
-    </row>
-    <row r="8" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="K8" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>380</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>381</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AG8" s="2"/>
       <c r="AO8" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="AX8" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="AV8" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="AX8">
+      <c r="AZ8">
         <v>0</v>
       </c>
-      <c r="AZ8">
+      <c r="BB8">
         <v>2</v>
       </c>
-      <c r="BB8">
+      <c r="BD8">
         <v>1</v>
       </c>
-      <c r="CE8" s="2"/>
-      <c r="CJ8" s="2" t="s">
+      <c r="CG8" s="2"/>
+      <c r="CL8" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="CN8" s="2"/>
+      <c r="CO8" s="2"/>
+      <c r="CY8" t="s">
         <v>382</v>
       </c>
-      <c r="CL8" s="2"/>
-      <c r="CM8" s="2"/>
-      <c r="CW8" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="9" spans="1:111" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="C9" s="2"/>
       <c r="AG9" s="2"/>
       <c r="AO9" s="2"/>
-      <c r="AV9" s="2"/>
-      <c r="CE9" s="2"/>
-      <c r="CJ9" s="2"/>
+      <c r="AX9" s="2"/>
+      <c r="CG9" s="2"/>
       <c r="CL9" s="2"/>
-      <c r="CM9" s="2"/>
-    </row>
-    <row r="10" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="CN9" s="2"/>
+      <c r="CO9" s="2"/>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="K10" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>464</v>
-      </c>
       <c r="L10" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO10" s="2"/>
-      <c r="AV10" s="2"/>
-      <c r="BB10">
+      <c r="AX10" s="2"/>
+      <c r="BD10">
         <v>1</v>
       </c>
-      <c r="BR10">
+      <c r="BT10">
         <v>0.1</v>
       </c>
-      <c r="CE10" s="2"/>
-      <c r="CJ10" s="2"/>
-      <c r="CL10" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="CM10" s="2"/>
-      <c r="CP10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="CG10" s="2"/>
+      <c r="CL10" s="2"/>
+      <c r="CN10" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="CO10" s="2"/>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="C11" s="2"/>
       <c r="AG11" s="2"/>
       <c r="AJ11" s="2"/>
       <c r="AO11" s="2"/>
-      <c r="BT11"/>
-      <c r="CJ11" s="5"/>
-      <c r="CL11" s="2"/>
-      <c r="CM11" s="2"/>
-    </row>
-    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BV11"/>
+      <c r="CL11" s="5"/>
+      <c r="CN11" s="2"/>
+      <c r="CO11" s="2"/>
+    </row>
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
@@ -7162,15 +7210,15 @@
       <c r="V12" s="7"/>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
-      <c r="BT12" s="10"/>
-      <c r="BU12" s="10"/>
       <c r="BV12" s="10"/>
       <c r="BW12" s="10"/>
       <c r="BX12" s="10"/>
       <c r="BY12" s="10"/>
-      <c r="CJ12" s="7"/>
-    </row>
-    <row r="13" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BZ12" s="10"/>
+      <c r="CA12" s="10"/>
+      <c r="CL12" s="7"/>
+    </row>
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
@@ -7185,15 +7233,15 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="BT13" s="10"/>
-      <c r="BU13" s="10"/>
       <c r="BV13" s="10"/>
       <c r="BW13" s="10"/>
       <c r="BX13" s="10"/>
       <c r="BY13" s="10"/>
-      <c r="CJ13" s="7"/>
-    </row>
-    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BZ13" s="10"/>
+      <c r="CA13" s="10"/>
+      <c r="CL13" s="7"/>
+    </row>
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
@@ -7208,15 +7256,15 @@
       <c r="V14" s="7"/>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
-      <c r="BT14"/>
-      <c r="BU14" s="10"/>
-      <c r="BV14" s="10"/>
+      <c r="BV14"/>
       <c r="BW14" s="10"/>
       <c r="BX14" s="10"/>
       <c r="BY14" s="10"/>
-      <c r="CJ14" s="7"/>
-    </row>
-    <row r="15" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BZ14" s="10"/>
+      <c r="CA14" s="10"/>
+      <c r="CL14" s="7"/>
+    </row>
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
@@ -7231,16 +7279,16 @@
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="BT15" s="10"/>
-      <c r="BU15" s="10"/>
       <c r="BV15" s="10"/>
       <c r="BW15" s="10"/>
       <c r="BX15" s="10"/>
       <c r="BY15" s="10"/>
-      <c r="CJ15" s="7"/>
-      <c r="CS15" s="2"/>
-    </row>
-    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BZ15" s="10"/>
+      <c r="CA15" s="10"/>
+      <c r="CL15" s="7"/>
+      <c r="CU15" s="2"/>
+    </row>
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
@@ -7255,15 +7303,15 @@
       <c r="V16" s="7"/>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
-      <c r="BT16"/>
-      <c r="BU16" s="10"/>
-      <c r="BV16" s="10"/>
+      <c r="BV16"/>
       <c r="BW16" s="10"/>
       <c r="BX16" s="10"/>
       <c r="BY16" s="10"/>
-      <c r="CJ16" s="7"/>
-    </row>
-    <row r="17" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ16" s="10"/>
+      <c r="CA16" s="10"/>
+      <c r="CL16" s="7"/>
+    </row>
+    <row r="17" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
@@ -7278,15 +7326,15 @@
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-      <c r="BT17" s="10"/>
-      <c r="BU17" s="10"/>
       <c r="BV17" s="10"/>
       <c r="BW17" s="10"/>
       <c r="BX17" s="10"/>
       <c r="BY17" s="10"/>
-      <c r="CJ17" s="7"/>
-    </row>
-    <row r="18" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ17" s="10"/>
+      <c r="CA17" s="10"/>
+      <c r="CL17" s="7"/>
+    </row>
+    <row r="18" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
@@ -7301,15 +7349,15 @@
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
-      <c r="BT18" s="10"/>
-      <c r="BU18" s="10"/>
       <c r="BV18" s="10"/>
       <c r="BW18" s="10"/>
       <c r="BX18" s="10"/>
       <c r="BY18" s="10"/>
-      <c r="CJ18" s="7"/>
-    </row>
-    <row r="19" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ18" s="10"/>
+      <c r="CA18" s="10"/>
+      <c r="CL18" s="7"/>
+    </row>
+    <row r="19" spans="1:99" x14ac:dyDescent="0.25">
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
@@ -7326,14 +7374,14 @@
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
       <c r="Y19" s="8"/>
-      <c r="BT19" s="11"/>
-      <c r="BU19" s="11"/>
       <c r="BV19" s="11"/>
       <c r="BW19" s="11"/>
       <c r="BX19" s="11"/>
       <c r="BY19" s="11"/>
-    </row>
-    <row r="20" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ19" s="11"/>
+      <c r="CA19" s="11"/>
+    </row>
+    <row r="20" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
@@ -7348,15 +7396,15 @@
       <c r="V20" s="7"/>
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
-      <c r="BT20"/>
-      <c r="BU20" s="10"/>
-      <c r="BV20" s="10"/>
+      <c r="BV20"/>
       <c r="BW20" s="10"/>
       <c r="BX20" s="10"/>
       <c r="BY20" s="10"/>
-      <c r="CJ20" s="7"/>
-    </row>
-    <row r="21" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ20" s="10"/>
+      <c r="CA20" s="10"/>
+      <c r="CL20" s="7"/>
+    </row>
+    <row r="21" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
@@ -7371,15 +7419,15 @@
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
-      <c r="BT21"/>
-      <c r="BU21" s="10"/>
-      <c r="BV21" s="10"/>
+      <c r="BV21"/>
       <c r="BW21" s="10"/>
       <c r="BX21" s="10"/>
       <c r="BY21" s="10"/>
-      <c r="CJ21" s="7"/>
-    </row>
-    <row r="22" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ21" s="10"/>
+      <c r="CA21" s="10"/>
+      <c r="CL21" s="7"/>
+    </row>
+    <row r="22" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
@@ -7394,15 +7442,15 @@
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
-      <c r="BT22" s="10"/>
-      <c r="BU22" s="10"/>
       <c r="BV22" s="10"/>
       <c r="BW22" s="10"/>
       <c r="BX22" s="10"/>
       <c r="BY22" s="10"/>
-      <c r="CJ22" s="7"/>
-    </row>
-    <row r="23" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ22" s="10"/>
+      <c r="CA22" s="10"/>
+      <c r="CL22" s="7"/>
+    </row>
+    <row r="23" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K23" s="7"/>
       <c r="L23" s="8"/>
       <c r="M23"/>
@@ -7418,15 +7466,15 @@
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
       <c r="Y23" s="8"/>
-      <c r="BT23" s="11"/>
-      <c r="BU23" s="11"/>
       <c r="BV23" s="11"/>
       <c r="BW23" s="11"/>
       <c r="BX23" s="11"/>
       <c r="BY23" s="11"/>
-      <c r="CJ23" s="7"/>
-    </row>
-    <row r="24" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ23" s="11"/>
+      <c r="CA23" s="11"/>
+      <c r="CL23" s="7"/>
+    </row>
+    <row r="24" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
@@ -7441,15 +7489,15 @@
       <c r="V24" s="7"/>
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
-      <c r="BT24"/>
-      <c r="BU24" s="10"/>
-      <c r="BV24" s="10"/>
+      <c r="BV24"/>
       <c r="BW24" s="10"/>
       <c r="BX24" s="10"/>
       <c r="BY24" s="10"/>
-      <c r="CJ24" s="7"/>
-    </row>
-    <row r="25" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ24" s="10"/>
+      <c r="CA24" s="10"/>
+      <c r="CL24" s="7"/>
+    </row>
+    <row r="25" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
@@ -7464,35 +7512,35 @@
       <c r="V25" s="7"/>
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
-      <c r="BT25"/>
-      <c r="BU25" s="10"/>
-      <c r="BV25" s="10"/>
+      <c r="BV25"/>
       <c r="BW25" s="10"/>
       <c r="BX25" s="10"/>
       <c r="BY25" s="10"/>
-      <c r="CJ25" s="7"/>
-    </row>
-    <row r="27" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ25" s="10"/>
+      <c r="CA25" s="10"/>
+      <c r="CL25" s="7"/>
+    </row>
+    <row r="27" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="AR27" s="2"/>
-      <c r="BT27"/>
-      <c r="CJ27" s="5"/>
-      <c r="CS27" s="2"/>
-    </row>
-    <row r="28" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="AT27" s="2"/>
+      <c r="BV27"/>
+      <c r="CL27" s="5"/>
+      <c r="CU27" s="2"/>
+    </row>
+    <row r="28" spans="1:99" x14ac:dyDescent="0.25">
       <c r="J28" s="2"/>
       <c r="O28"/>
       <c r="AO28" s="2"/>
-      <c r="CS28" s="2"/>
-    </row>
-    <row r="29" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CU28" s="2"/>
+    </row>
+    <row r="29" spans="1:99" x14ac:dyDescent="0.25">
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CJ30" s="5"/>
-    </row>
-    <row r="31" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CL30" s="5"/>
+    </row>
+    <row r="31" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
       <c r="M31"/>
@@ -7507,15 +7555,15 @@
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
       <c r="X31"/>
-      <c r="BS31" s="12"/>
-      <c r="BT31" s="12"/>
       <c r="BU31" s="12"/>
       <c r="BV31" s="12"/>
       <c r="BW31" s="12"/>
       <c r="BX31" s="12"/>
-      <c r="BY31"/>
-    </row>
-    <row r="32" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BY31" s="12"/>
+      <c r="BZ31" s="12"/>
+      <c r="CA31"/>
+    </row>
+    <row r="32" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32"/>
@@ -7530,1583 +7578,1583 @@
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
       <c r="X32"/>
-      <c r="BS32" s="12"/>
-      <c r="BT32" s="12"/>
       <c r="BU32" s="12"/>
       <c r="BV32" s="12"/>
       <c r="BW32" s="12"/>
       <c r="BX32" s="12"/>
-      <c r="BY32"/>
-      <c r="CL32" s="3"/>
-    </row>
-    <row r="33" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="AW33" s="5"/>
-      <c r="BT33"/>
-      <c r="BU33"/>
+      <c r="BY32" s="12"/>
+      <c r="BZ32" s="12"/>
+      <c r="CA32"/>
+      <c r="CN32" s="3"/>
+    </row>
+    <row r="33" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="AY33" s="5"/>
       <c r="BV33"/>
       <c r="BW33"/>
       <c r="BX33"/>
       <c r="BY33"/>
-      <c r="BZ33" s="5"/>
-      <c r="CA33" s="5"/>
+      <c r="BZ33"/>
+      <c r="CA33"/>
       <c r="CB33" s="5"/>
       <c r="CC33" s="5"/>
       <c r="CD33" s="5"/>
+      <c r="CE33" s="5"/>
       <c r="CF33" s="5"/>
-      <c r="CG33" s="5"/>
       <c r="CH33" s="5"/>
       <c r="CI33" s="5"/>
       <c r="CJ33" s="5"/>
       <c r="CK33" s="5"/>
-    </row>
-    <row r="34" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CL33" s="5"/>
+      <c r="CM33" s="5"/>
+    </row>
+    <row r="34" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M34"/>
       <c r="N34"/>
       <c r="P34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34"/>
       <c r="X34"/>
-      <c r="BT34"/>
-      <c r="BZ34" s="6"/>
-    </row>
-    <row r="35" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="BT35"/>
-    </row>
-    <row r="36" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BV34"/>
+      <c r="CB34" s="6"/>
+    </row>
+    <row r="35" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="BV35"/>
+    </row>
+    <row r="36" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M36"/>
       <c r="O36"/>
-      <c r="BM36" s="2"/>
-      <c r="BN36" s="2"/>
-      <c r="CL36" s="3"/>
-    </row>
-    <row r="37" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BO36" s="2"/>
+      <c r="BP36" s="2"/>
+      <c r="CN36" s="3"/>
+    </row>
+    <row r="37" spans="1:92" x14ac:dyDescent="0.25">
       <c r="J37" s="5"/>
       <c r="M37"/>
       <c r="O37" s="3"/>
       <c r="P37"/>
       <c r="Q37"/>
-      <c r="CL37" s="2"/>
-    </row>
-    <row r="38" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CN37" s="2"/>
+    </row>
+    <row r="38" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M38"/>
-      <c r="BZ38" s="13"/>
-    </row>
-    <row r="39" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CB38" s="13"/>
+    </row>
+    <row r="39" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M39"/>
       <c r="O39" s="3"/>
       <c r="P39"/>
       <c r="Q39"/>
     </row>
-    <row r="40" spans="1:90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="M40"/>
       <c r="O40" s="3"/>
       <c r="P40"/>
       <c r="Q40"/>
-      <c r="CL40" s="3"/>
-    </row>
-    <row r="41" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CN40" s="3"/>
+    </row>
+    <row r="41" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M41"/>
-      <c r="AW41" s="5"/>
-      <c r="BT41"/>
-      <c r="BU41"/>
+      <c r="AY41" s="5"/>
       <c r="BV41"/>
       <c r="BW41"/>
       <c r="BX41"/>
       <c r="BY41"/>
-      <c r="BZ41" s="5"/>
-      <c r="CA41" s="5"/>
+      <c r="BZ41"/>
+      <c r="CA41"/>
       <c r="CB41" s="5"/>
       <c r="CC41" s="5"/>
       <c r="CD41" s="5"/>
+      <c r="CE41" s="5"/>
       <c r="CF41" s="5"/>
-      <c r="CG41" s="5"/>
       <c r="CH41" s="5"/>
       <c r="CI41" s="5"/>
-      <c r="CL41" s="3"/>
-    </row>
-    <row r="42" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CJ41" s="5"/>
+      <c r="CK41" s="5"/>
+      <c r="CN41" s="3"/>
+    </row>
+    <row r="42" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M42"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="1:90" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M43"/>
       <c r="N43"/>
-      <c r="BT43"/>
-      <c r="CG43" s="5"/>
-      <c r="CH43" s="5"/>
-    </row>
-    <row r="44" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BV43"/>
+      <c r="CI43" s="5"/>
+      <c r="CJ43" s="5"/>
+    </row>
+    <row r="44" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M44"/>
       <c r="N44"/>
-      <c r="BT44"/>
-      <c r="CH44" s="5"/>
-    </row>
-    <row r="45" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BV44"/>
+      <c r="CJ44" s="5"/>
+    </row>
+    <row r="45" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M45"/>
       <c r="O45" s="3"/>
       <c r="AG45" s="2"/>
       <c r="AO45" s="2"/>
-      <c r="BM45" s="2"/>
-      <c r="BN45" s="2"/>
-      <c r="CE45" s="2"/>
-      <c r="CK45" s="2"/>
-    </row>
-    <row r="46" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BO45" s="2"/>
+      <c r="BP45" s="2"/>
+      <c r="CG45" s="2"/>
+      <c r="CM45" s="2"/>
+    </row>
+    <row r="46" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="M46"/>
       <c r="O46" s="3"/>
       <c r="AG46" s="2"/>
       <c r="AO46" s="2"/>
-      <c r="CE46" s="2"/>
-    </row>
-    <row r="47" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="BS47" s="6"/>
-      <c r="BY47"/>
-    </row>
-    <row r="48" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CG46" s="2"/>
+    </row>
+    <row r="47" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="BU47" s="6"/>
+      <c r="CA47"/>
+    </row>
+    <row r="48" spans="1:92" x14ac:dyDescent="0.25">
       <c r="E48" s="2"/>
       <c r="O48"/>
       <c r="W48"/>
       <c r="X48"/>
-      <c r="BM48" s="2"/>
-      <c r="BN48" s="2"/>
-      <c r="CL48" s="3"/>
-    </row>
-    <row r="49" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BO48" s="2"/>
+      <c r="BP48" s="2"/>
+      <c r="CN48" s="3"/>
+    </row>
+    <row r="49" spans="1:99" x14ac:dyDescent="0.25">
       <c r="M49"/>
       <c r="O49" s="3"/>
       <c r="P49"/>
       <c r="Q49"/>
-      <c r="CL49" s="3"/>
-    </row>
-    <row r="50" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CN49" s="3"/>
+    </row>
+    <row r="50" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="M50"/>
       <c r="O50" s="3"/>
       <c r="P50"/>
       <c r="Q50"/>
-      <c r="CL50" s="3"/>
-    </row>
-    <row r="51" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CN50" s="3"/>
+    </row>
+    <row r="51" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="O51" s="3"/>
     </row>
-    <row r="52" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
-      <c r="CJ52" s="5"/>
-    </row>
-    <row r="53" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CJ53" s="5"/>
-    </row>
-    <row r="54" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CL52" s="5"/>
+    </row>
+    <row r="53" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CL53" s="5"/>
+    </row>
+    <row r="54" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="C54" s="2"/>
       <c r="J54" s="2"/>
       <c r="AJ54" s="2"/>
-      <c r="CJ54" s="5"/>
-      <c r="CS54" s="2"/>
-    </row>
-    <row r="55" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CJ55" s="5"/>
-    </row>
-    <row r="56" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CL54" s="5"/>
+      <c r="CU54" s="2"/>
+    </row>
+    <row r="55" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CL55" s="5"/>
+    </row>
+    <row r="56" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O56"/>
       <c r="W56"/>
       <c r="X56"/>
-      <c r="CL56" s="3"/>
-    </row>
-    <row r="57" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CN56" s="3"/>
+    </row>
+    <row r="57" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O57" s="3"/>
       <c r="X57"/>
     </row>
-    <row r="58" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O58" s="3"/>
       <c r="P58"/>
       <c r="Q58"/>
       <c r="X58"/>
     </row>
-    <row r="59" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O59" s="3"/>
       <c r="X59"/>
     </row>
-    <row r="62" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CK62" s="3"/>
-      <c r="CL62" s="3"/>
-    </row>
-    <row r="64" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CM62" s="3"/>
+      <c r="CN62" s="3"/>
+    </row>
+    <row r="64" spans="1:99" x14ac:dyDescent="0.25">
       <c r="M64"/>
       <c r="N64"/>
-      <c r="BT64"/>
-      <c r="BZ64" s="14"/>
-      <c r="CG64" s="5"/>
-      <c r="CH64" s="5"/>
-    </row>
-    <row r="65" spans="13:89" x14ac:dyDescent="0.25">
+      <c r="BV64"/>
+      <c r="CB64" s="14"/>
+      <c r="CI64" s="5"/>
+      <c r="CJ64" s="5"/>
+    </row>
+    <row r="65" spans="13:91" x14ac:dyDescent="0.25">
       <c r="M65"/>
       <c r="N65"/>
-      <c r="BT65"/>
-      <c r="BZ65" s="14"/>
-      <c r="CH65" s="5"/>
-    </row>
-    <row r="66" spans="13:89" x14ac:dyDescent="0.25">
+      <c r="BV65"/>
+      <c r="CB65" s="14"/>
+      <c r="CJ65" s="5"/>
+    </row>
+    <row r="66" spans="13:91" x14ac:dyDescent="0.25">
       <c r="O66"/>
       <c r="X66"/>
-      <c r="CK66" s="3"/>
-    </row>
-    <row r="69" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ69" s="5"/>
-    </row>
-    <row r="70" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ70" s="5"/>
-    </row>
-    <row r="76" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ76" s="5"/>
-    </row>
-    <row r="77" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ77" s="5"/>
-    </row>
-    <row r="79" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ79" s="5"/>
-    </row>
-    <row r="80" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ80" s="5"/>
-    </row>
-    <row r="81" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ81" s="5"/>
-    </row>
-    <row r="82" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ82" s="5"/>
-    </row>
-    <row r="83" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT83"/>
-    </row>
-    <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT84"/>
-    </row>
-    <row r="85" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT85"/>
-      <c r="CJ85" s="5"/>
-    </row>
-    <row r="86" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ86" s="5"/>
-    </row>
-    <row r="87" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ87" s="5"/>
-    </row>
-    <row r="88" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT88"/>
-    </row>
-    <row r="89" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ89" s="5"/>
-    </row>
-    <row r="93" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT93"/>
-    </row>
-    <row r="94" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ94" s="5"/>
-    </row>
-    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ102" s="5"/>
-    </row>
-    <row r="103" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ103" s="5"/>
-    </row>
-    <row r="104" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT104"/>
-    </row>
-    <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT109"/>
-    </row>
-    <row r="110" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT110"/>
-      <c r="CJ110" s="5"/>
-    </row>
-    <row r="111" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ111" s="5"/>
-    </row>
-    <row r="112" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ112" s="5"/>
-    </row>
-    <row r="113" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ113" s="5"/>
-    </row>
-    <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ114" s="5"/>
-    </row>
-    <row r="115" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT115"/>
-    </row>
-    <row r="116" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ116" s="5"/>
-    </row>
-    <row r="117" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ117" s="5"/>
-    </row>
-    <row r="118" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ118" s="5"/>
-    </row>
-    <row r="119" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ119" s="5"/>
-    </row>
-    <row r="120" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT120"/>
-    </row>
-    <row r="121" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ121" s="5"/>
-    </row>
-    <row r="122" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ122" s="5"/>
-    </row>
-    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ123" s="5"/>
-    </row>
-    <row r="124" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ124" s="5"/>
-    </row>
-    <row r="127" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ127" s="5"/>
-    </row>
-    <row r="128" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ128" s="5"/>
-    </row>
-    <row r="129" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ129" s="5"/>
-    </row>
-    <row r="130" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ130" s="5"/>
-    </row>
-    <row r="131" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ131" s="5"/>
-    </row>
-    <row r="133" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT133"/>
-    </row>
-    <row r="134" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ134" s="5"/>
-    </row>
-    <row r="135" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ135" s="5"/>
-    </row>
-    <row r="136" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ136" s="5"/>
-    </row>
-    <row r="137" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ137" s="5"/>
-    </row>
-    <row r="141" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ141" s="5"/>
-    </row>
-    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT143"/>
-    </row>
-    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT144"/>
-      <c r="CJ144" s="5"/>
-    </row>
-    <row r="145" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ145" s="5"/>
-    </row>
-    <row r="146" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ146" s="5"/>
-    </row>
-    <row r="147" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ147" s="5"/>
-    </row>
-    <row r="148" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ148" s="5"/>
-    </row>
-    <row r="150" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT150"/>
-    </row>
-    <row r="151" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ151" s="5"/>
-    </row>
-    <row r="152" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ152" s="5"/>
-    </row>
-    <row r="154" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ154" s="5"/>
-    </row>
-    <row r="155" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ155" s="5"/>
-    </row>
-    <row r="157" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT157"/>
-    </row>
-    <row r="158" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ158" s="5"/>
-    </row>
-    <row r="161" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ161" s="5"/>
-    </row>
-    <row r="162" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ162" s="5"/>
-    </row>
-    <row r="165" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ165" s="5"/>
-    </row>
-    <row r="167" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ167" s="5"/>
-    </row>
-    <row r="169" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT169"/>
-    </row>
-    <row r="170" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ170" s="5"/>
-    </row>
-    <row r="171" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ171" s="5"/>
-    </row>
-    <row r="173" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ173" s="5"/>
-    </row>
-    <row r="174" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ174" s="5"/>
-    </row>
-    <row r="175" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ175" s="5"/>
-    </row>
-    <row r="180" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ180" s="5"/>
-    </row>
-    <row r="181" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ181" s="5"/>
-    </row>
-    <row r="184" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ184" s="5"/>
-    </row>
-    <row r="185" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ185" s="5"/>
-    </row>
-    <row r="189" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ189" s="5"/>
-    </row>
-    <row r="193" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ193" s="5"/>
-    </row>
-    <row r="195" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ195" s="5"/>
-    </row>
-    <row r="196" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ196" s="5"/>
-    </row>
-    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ198" s="5"/>
-    </row>
-    <row r="199" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ199" s="5"/>
-    </row>
-    <row r="201" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT201"/>
-    </row>
-    <row r="202" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT202"/>
-      <c r="CJ202" s="5"/>
-    </row>
-    <row r="203" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ203" s="5"/>
-    </row>
-    <row r="205" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ205" s="5"/>
-    </row>
-    <row r="214" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT214"/>
-    </row>
-    <row r="215" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT215"/>
-      <c r="CJ215" s="5"/>
-    </row>
-    <row r="216" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ216" s="5"/>
-    </row>
-    <row r="217" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ217" s="5"/>
-    </row>
-    <row r="218" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT218"/>
-    </row>
-    <row r="219" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT219"/>
-      <c r="CJ219" s="5"/>
-    </row>
-    <row r="220" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ220" s="5"/>
-    </row>
-    <row r="222" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT222"/>
-    </row>
-    <row r="223" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT223"/>
-      <c r="CJ223" s="5"/>
-    </row>
-    <row r="224" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ224" s="5"/>
-    </row>
-    <row r="226" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT226"/>
-    </row>
-    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ227" s="5"/>
-    </row>
-    <row r="230" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ230" s="5"/>
-    </row>
-    <row r="234" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ234" s="5"/>
-    </row>
-    <row r="236" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT236"/>
-    </row>
-    <row r="237" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ237" s="5"/>
-    </row>
-    <row r="244" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT244"/>
-    </row>
-    <row r="245" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ245" s="5"/>
-    </row>
-    <row r="246" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ246" s="5"/>
-    </row>
-    <row r="248" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT248"/>
-    </row>
-    <row r="249" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT249"/>
-      <c r="CJ249" s="5"/>
-    </row>
-    <row r="250" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ250" s="5"/>
-    </row>
-    <row r="256" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT256"/>
-    </row>
-    <row r="257" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT257"/>
-      <c r="CJ257" s="5"/>
-    </row>
-    <row r="258" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT258"/>
-      <c r="CJ258" s="5"/>
-    </row>
-    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ259" s="5"/>
-    </row>
-    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT264"/>
-    </row>
-    <row r="265" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT265"/>
-    </row>
-    <row r="269" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT269"/>
-    </row>
-    <row r="270" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ270" s="5"/>
-    </row>
-    <row r="271" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT271"/>
-    </row>
-    <row r="272" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ272" s="5"/>
-    </row>
-    <row r="282" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT282"/>
-    </row>
-    <row r="283" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ283" s="5"/>
-    </row>
-    <row r="285" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT285"/>
-    </row>
-    <row r="286" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ286" s="5"/>
-    </row>
-    <row r="294" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT294"/>
-    </row>
-    <row r="295" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ295" s="5"/>
-    </row>
-    <row r="299" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT299"/>
-    </row>
-    <row r="300" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ300" s="5"/>
-    </row>
-    <row r="302" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT302"/>
-    </row>
-    <row r="303" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ303" s="5"/>
-    </row>
-    <row r="319" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT319"/>
-    </row>
-    <row r="320" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT320"/>
-      <c r="CJ320" s="5"/>
-    </row>
-    <row r="321" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT321"/>
-      <c r="CJ321" s="5"/>
-    </row>
-    <row r="322" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT322"/>
-      <c r="CJ322" s="5"/>
-    </row>
-    <row r="323" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT323"/>
-    </row>
-    <row r="325" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT325"/>
-    </row>
-    <row r="326" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT326"/>
-      <c r="CJ326" s="5"/>
-    </row>
-    <row r="327" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT327"/>
-      <c r="CJ327" s="5"/>
-    </row>
-    <row r="328" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ328" s="5"/>
-    </row>
-    <row r="332" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT332"/>
-    </row>
-    <row r="333" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ333" s="5"/>
-    </row>
-    <row r="335" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT335"/>
-    </row>
-    <row r="336" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT336"/>
-      <c r="CJ336" s="5"/>
-    </row>
-    <row r="337" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT337"/>
-      <c r="CJ337" s="5"/>
-    </row>
-    <row r="338" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ338" s="5"/>
-    </row>
-    <row r="354" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT354"/>
-    </row>
-    <row r="355" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ355" s="5"/>
-    </row>
-    <row r="363" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ363" s="5"/>
-    </row>
-    <row r="364" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ364" s="5"/>
-    </row>
-    <row r="365" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ365" s="5"/>
-    </row>
-    <row r="366" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ366" s="5"/>
-    </row>
-    <row r="367" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ367" s="5"/>
-    </row>
-    <row r="369" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT369"/>
-    </row>
-    <row r="370" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ370" s="5"/>
-    </row>
-    <row r="371" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT371"/>
-    </row>
-    <row r="372" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT372"/>
-      <c r="CJ372" s="5"/>
-    </row>
-    <row r="373" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ373" s="5"/>
-    </row>
-    <row r="375" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT375"/>
-    </row>
-    <row r="376" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT376"/>
-      <c r="CJ376" s="5"/>
-    </row>
-    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT377"/>
-      <c r="CJ377" s="5"/>
-    </row>
-    <row r="378" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ378" s="5"/>
-    </row>
-    <row r="380" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ380" s="5"/>
-    </row>
-    <row r="382" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ382" s="5"/>
-    </row>
-    <row r="384" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ384" s="5"/>
-    </row>
-    <row r="387" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ387" s="5"/>
-    </row>
-    <row r="388" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ388" s="5"/>
-    </row>
-    <row r="389" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ389" s="5"/>
-    </row>
-    <row r="390" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ390" s="5"/>
-    </row>
-    <row r="391" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ391" s="5"/>
-    </row>
-    <row r="392" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ392" s="5"/>
-    </row>
-    <row r="393" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT393"/>
-    </row>
-    <row r="394" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT394"/>
-      <c r="CJ394" s="5"/>
-    </row>
-    <row r="395" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT395"/>
-      <c r="CJ395" s="5"/>
-    </row>
-    <row r="396" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ396" s="5"/>
-    </row>
-    <row r="397" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ397" s="5"/>
-    </row>
-    <row r="398" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ398" s="5"/>
-    </row>
-    <row r="399" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ399" s="5"/>
-    </row>
-    <row r="401" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ401" s="5"/>
-    </row>
-    <row r="402" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ402" s="5"/>
-    </row>
-    <row r="403" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT403"/>
-    </row>
-    <row r="404" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT404"/>
-      <c r="CJ404" s="5"/>
-    </row>
-    <row r="405" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT405"/>
-      <c r="CJ405" s="5"/>
-    </row>
-    <row r="406" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ406" s="5"/>
-    </row>
-    <row r="407" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ407" s="5"/>
-    </row>
-    <row r="409" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ409" s="5"/>
-    </row>
-    <row r="410" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ410" s="5"/>
-    </row>
-    <row r="411" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT411"/>
-      <c r="CJ411" s="5"/>
-    </row>
-    <row r="412" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT412"/>
-      <c r="CJ412" s="5"/>
-    </row>
-    <row r="413" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ413" s="5"/>
-    </row>
-    <row r="414" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ414" s="5"/>
-    </row>
-    <row r="415" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ415" s="5"/>
-    </row>
-    <row r="417" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT417"/>
-      <c r="CJ417" s="5"/>
-    </row>
-    <row r="418" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ418" s="5"/>
-    </row>
-    <row r="419" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ419" s="5"/>
-    </row>
-    <row r="421" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT421"/>
-      <c r="CJ421" s="5"/>
-    </row>
-    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT422"/>
-      <c r="CJ422" s="5"/>
-    </row>
-    <row r="423" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ423" s="5"/>
-    </row>
-    <row r="425" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ425" s="5"/>
-    </row>
-    <row r="427" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ427" s="5"/>
-    </row>
-    <row r="430" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ430" s="5"/>
-    </row>
-    <row r="431" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ431" s="5"/>
-    </row>
-    <row r="435" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT435"/>
-    </row>
-    <row r="436" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT436"/>
-      <c r="CJ436" s="5"/>
-    </row>
-    <row r="437" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT437"/>
-      <c r="CJ437" s="5"/>
-    </row>
-    <row r="438" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ438" s="5"/>
-    </row>
-    <row r="439" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ439" s="5"/>
-    </row>
-    <row r="440" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT440"/>
-    </row>
-    <row r="441" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ441" s="5"/>
-    </row>
-    <row r="443" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ443" s="5"/>
-    </row>
-    <row r="444" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ444" s="5"/>
-    </row>
-    <row r="446" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ446" s="5"/>
-    </row>
-    <row r="447" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ447" s="5"/>
-    </row>
-    <row r="448" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ448" s="5"/>
-    </row>
-    <row r="449" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ449" s="5"/>
-    </row>
-    <row r="450" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ450" s="5"/>
-    </row>
-    <row r="451" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ451" s="5"/>
-    </row>
-    <row r="452" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ452" s="5"/>
-    </row>
-    <row r="454" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT454"/>
-    </row>
-    <row r="455" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ455" s="5"/>
-    </row>
-    <row r="456" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ456" s="5"/>
-    </row>
-    <row r="489" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS489" s="15"/>
-      <c r="BT489" s="16"/>
-    </row>
-    <row r="490" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CM66" s="3"/>
+    </row>
+    <row r="69" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL69" s="5"/>
+    </row>
+    <row r="70" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL70" s="5"/>
+    </row>
+    <row r="76" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL76" s="5"/>
+    </row>
+    <row r="77" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL77" s="5"/>
+    </row>
+    <row r="79" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL79" s="5"/>
+    </row>
+    <row r="80" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL80" s="5"/>
+    </row>
+    <row r="81" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL81" s="5"/>
+    </row>
+    <row r="82" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL82" s="5"/>
+    </row>
+    <row r="83" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV83"/>
+    </row>
+    <row r="84" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV84"/>
+    </row>
+    <row r="85" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV85"/>
+      <c r="CL85" s="5"/>
+    </row>
+    <row r="86" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL86" s="5"/>
+    </row>
+    <row r="87" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL87" s="5"/>
+    </row>
+    <row r="88" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV88"/>
+    </row>
+    <row r="89" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL89" s="5"/>
+    </row>
+    <row r="93" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV93"/>
+    </row>
+    <row r="94" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL94" s="5"/>
+    </row>
+    <row r="102" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL102" s="5"/>
+    </row>
+    <row r="103" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL103" s="5"/>
+    </row>
+    <row r="104" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV104"/>
+    </row>
+    <row r="109" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV109"/>
+    </row>
+    <row r="110" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV110"/>
+      <c r="CL110" s="5"/>
+    </row>
+    <row r="111" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL111" s="5"/>
+    </row>
+    <row r="112" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL112" s="5"/>
+    </row>
+    <row r="113" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL113" s="5"/>
+    </row>
+    <row r="114" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL114" s="5"/>
+    </row>
+    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV115"/>
+    </row>
+    <row r="116" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL116" s="5"/>
+    </row>
+    <row r="117" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL117" s="5"/>
+    </row>
+    <row r="118" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL118" s="5"/>
+    </row>
+    <row r="119" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL119" s="5"/>
+    </row>
+    <row r="120" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV120"/>
+    </row>
+    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL121" s="5"/>
+    </row>
+    <row r="122" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL122" s="5"/>
+    </row>
+    <row r="123" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL123" s="5"/>
+    </row>
+    <row r="124" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL124" s="5"/>
+    </row>
+    <row r="127" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL127" s="5"/>
+    </row>
+    <row r="128" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL128" s="5"/>
+    </row>
+    <row r="129" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL129" s="5"/>
+    </row>
+    <row r="130" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL130" s="5"/>
+    </row>
+    <row r="131" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL131" s="5"/>
+    </row>
+    <row r="133" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV133"/>
+    </row>
+    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL134" s="5"/>
+    </row>
+    <row r="135" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL135" s="5"/>
+    </row>
+    <row r="136" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL136" s="5"/>
+    </row>
+    <row r="137" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL137" s="5"/>
+    </row>
+    <row r="141" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL141" s="5"/>
+    </row>
+    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV143"/>
+    </row>
+    <row r="144" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV144"/>
+      <c r="CL144" s="5"/>
+    </row>
+    <row r="145" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL145" s="5"/>
+    </row>
+    <row r="146" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL146" s="5"/>
+    </row>
+    <row r="147" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL147" s="5"/>
+    </row>
+    <row r="148" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL148" s="5"/>
+    </row>
+    <row r="150" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV150"/>
+    </row>
+    <row r="151" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL151" s="5"/>
+    </row>
+    <row r="152" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL152" s="5"/>
+    </row>
+    <row r="154" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL154" s="5"/>
+    </row>
+    <row r="155" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL155" s="5"/>
+    </row>
+    <row r="157" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV157"/>
+    </row>
+    <row r="158" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL158" s="5"/>
+    </row>
+    <row r="161" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL161" s="5"/>
+    </row>
+    <row r="162" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL162" s="5"/>
+    </row>
+    <row r="165" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL165" s="5"/>
+    </row>
+    <row r="167" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL167" s="5"/>
+    </row>
+    <row r="169" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV169"/>
+    </row>
+    <row r="170" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL170" s="5"/>
+    </row>
+    <row r="171" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL171" s="5"/>
+    </row>
+    <row r="173" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL173" s="5"/>
+    </row>
+    <row r="174" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL174" s="5"/>
+    </row>
+    <row r="175" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL175" s="5"/>
+    </row>
+    <row r="180" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL180" s="5"/>
+    </row>
+    <row r="181" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL181" s="5"/>
+    </row>
+    <row r="184" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL184" s="5"/>
+    </row>
+    <row r="185" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL185" s="5"/>
+    </row>
+    <row r="189" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL189" s="5"/>
+    </row>
+    <row r="193" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL193" s="5"/>
+    </row>
+    <row r="195" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL195" s="5"/>
+    </row>
+    <row r="196" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL196" s="5"/>
+    </row>
+    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL198" s="5"/>
+    </row>
+    <row r="199" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL199" s="5"/>
+    </row>
+    <row r="201" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV201"/>
+    </row>
+    <row r="202" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV202"/>
+      <c r="CL202" s="5"/>
+    </row>
+    <row r="203" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL203" s="5"/>
+    </row>
+    <row r="205" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL205" s="5"/>
+    </row>
+    <row r="214" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV214"/>
+    </row>
+    <row r="215" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV215"/>
+      <c r="CL215" s="5"/>
+    </row>
+    <row r="216" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL216" s="5"/>
+    </row>
+    <row r="217" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL217" s="5"/>
+    </row>
+    <row r="218" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV218"/>
+    </row>
+    <row r="219" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV219"/>
+      <c r="CL219" s="5"/>
+    </row>
+    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL220" s="5"/>
+    </row>
+    <row r="222" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV222"/>
+    </row>
+    <row r="223" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV223"/>
+      <c r="CL223" s="5"/>
+    </row>
+    <row r="224" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL224" s="5"/>
+    </row>
+    <row r="226" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV226"/>
+    </row>
+    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL227" s="5"/>
+    </row>
+    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL230" s="5"/>
+    </row>
+    <row r="234" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL234" s="5"/>
+    </row>
+    <row r="236" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV236"/>
+    </row>
+    <row r="237" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL237" s="5"/>
+    </row>
+    <row r="244" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV244"/>
+    </row>
+    <row r="245" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL245" s="5"/>
+    </row>
+    <row r="246" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL246" s="5"/>
+    </row>
+    <row r="248" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV248"/>
+    </row>
+    <row r="249" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV249"/>
+      <c r="CL249" s="5"/>
+    </row>
+    <row r="250" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL250" s="5"/>
+    </row>
+    <row r="256" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV256"/>
+    </row>
+    <row r="257" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV257"/>
+      <c r="CL257" s="5"/>
+    </row>
+    <row r="258" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV258"/>
+      <c r="CL258" s="5"/>
+    </row>
+    <row r="259" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL259" s="5"/>
+    </row>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV264"/>
+    </row>
+    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV265"/>
+    </row>
+    <row r="269" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV269"/>
+    </row>
+    <row r="270" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL270" s="5"/>
+    </row>
+    <row r="271" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV271"/>
+    </row>
+    <row r="272" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL272" s="5"/>
+    </row>
+    <row r="282" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV282"/>
+    </row>
+    <row r="283" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL283" s="5"/>
+    </row>
+    <row r="285" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV285"/>
+    </row>
+    <row r="286" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL286" s="5"/>
+    </row>
+    <row r="294" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV294"/>
+    </row>
+    <row r="295" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL295" s="5"/>
+    </row>
+    <row r="299" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV299"/>
+    </row>
+    <row r="300" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL300" s="5"/>
+    </row>
+    <row r="302" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV302"/>
+    </row>
+    <row r="303" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL303" s="5"/>
+    </row>
+    <row r="319" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV319"/>
+    </row>
+    <row r="320" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV320"/>
+      <c r="CL320" s="5"/>
+    </row>
+    <row r="321" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV321"/>
+      <c r="CL321" s="5"/>
+    </row>
+    <row r="322" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV322"/>
+      <c r="CL322" s="5"/>
+    </row>
+    <row r="323" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV323"/>
+    </row>
+    <row r="325" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV325"/>
+    </row>
+    <row r="326" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV326"/>
+      <c r="CL326" s="5"/>
+    </row>
+    <row r="327" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV327"/>
+      <c r="CL327" s="5"/>
+    </row>
+    <row r="328" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL328" s="5"/>
+    </row>
+    <row r="332" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV332"/>
+    </row>
+    <row r="333" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL333" s="5"/>
+    </row>
+    <row r="335" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV335"/>
+    </row>
+    <row r="336" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV336"/>
+      <c r="CL336" s="5"/>
+    </row>
+    <row r="337" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV337"/>
+      <c r="CL337" s="5"/>
+    </row>
+    <row r="338" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL338" s="5"/>
+    </row>
+    <row r="354" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV354"/>
+    </row>
+    <row r="355" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL355" s="5"/>
+    </row>
+    <row r="363" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL363" s="5"/>
+    </row>
+    <row r="364" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL364" s="5"/>
+    </row>
+    <row r="365" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL365" s="5"/>
+    </row>
+    <row r="366" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL366" s="5"/>
+    </row>
+    <row r="367" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL367" s="5"/>
+    </row>
+    <row r="369" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV369"/>
+    </row>
+    <row r="370" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL370" s="5"/>
+    </row>
+    <row r="371" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV371"/>
+    </row>
+    <row r="372" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV372"/>
+      <c r="CL372" s="5"/>
+    </row>
+    <row r="373" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL373" s="5"/>
+    </row>
+    <row r="375" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV375"/>
+    </row>
+    <row r="376" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV376"/>
+      <c r="CL376" s="5"/>
+    </row>
+    <row r="377" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV377"/>
+      <c r="CL377" s="5"/>
+    </row>
+    <row r="378" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL378" s="5"/>
+    </row>
+    <row r="380" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL380" s="5"/>
+    </row>
+    <row r="382" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL382" s="5"/>
+    </row>
+    <row r="384" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL384" s="5"/>
+    </row>
+    <row r="387" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL387" s="5"/>
+    </row>
+    <row r="388" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL388" s="5"/>
+    </row>
+    <row r="389" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL389" s="5"/>
+    </row>
+    <row r="390" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL390" s="5"/>
+    </row>
+    <row r="391" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL391" s="5"/>
+    </row>
+    <row r="392" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL392" s="5"/>
+    </row>
+    <row r="393" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV393"/>
+    </row>
+    <row r="394" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV394"/>
+      <c r="CL394" s="5"/>
+    </row>
+    <row r="395" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV395"/>
+      <c r="CL395" s="5"/>
+    </row>
+    <row r="396" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL396" s="5"/>
+    </row>
+    <row r="397" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL397" s="5"/>
+    </row>
+    <row r="398" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL398" s="5"/>
+    </row>
+    <row r="399" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL399" s="5"/>
+    </row>
+    <row r="401" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL401" s="5"/>
+    </row>
+    <row r="402" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL402" s="5"/>
+    </row>
+    <row r="403" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV403"/>
+    </row>
+    <row r="404" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV404"/>
+      <c r="CL404" s="5"/>
+    </row>
+    <row r="405" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV405"/>
+      <c r="CL405" s="5"/>
+    </row>
+    <row r="406" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL406" s="5"/>
+    </row>
+    <row r="407" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL407" s="5"/>
+    </row>
+    <row r="409" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL409" s="5"/>
+    </row>
+    <row r="410" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL410" s="5"/>
+    </row>
+    <row r="411" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV411"/>
+      <c r="CL411" s="5"/>
+    </row>
+    <row r="412" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV412"/>
+      <c r="CL412" s="5"/>
+    </row>
+    <row r="413" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL413" s="5"/>
+    </row>
+    <row r="414" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL414" s="5"/>
+    </row>
+    <row r="415" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL415" s="5"/>
+    </row>
+    <row r="417" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV417"/>
+      <c r="CL417" s="5"/>
+    </row>
+    <row r="418" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL418" s="5"/>
+    </row>
+    <row r="419" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL419" s="5"/>
+    </row>
+    <row r="421" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV421"/>
+      <c r="CL421" s="5"/>
+    </row>
+    <row r="422" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV422"/>
+      <c r="CL422" s="5"/>
+    </row>
+    <row r="423" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL423" s="5"/>
+    </row>
+    <row r="425" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL425" s="5"/>
+    </row>
+    <row r="427" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL427" s="5"/>
+    </row>
+    <row r="430" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL430" s="5"/>
+    </row>
+    <row r="431" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL431" s="5"/>
+    </row>
+    <row r="435" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV435"/>
+    </row>
+    <row r="436" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV436"/>
+      <c r="CL436" s="5"/>
+    </row>
+    <row r="437" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV437"/>
+      <c r="CL437" s="5"/>
+    </row>
+    <row r="438" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL438" s="5"/>
+    </row>
+    <row r="439" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL439" s="5"/>
+    </row>
+    <row r="440" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV440"/>
+    </row>
+    <row r="441" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL441" s="5"/>
+    </row>
+    <row r="443" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL443" s="5"/>
+    </row>
+    <row r="444" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL444" s="5"/>
+    </row>
+    <row r="446" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL446" s="5"/>
+    </row>
+    <row r="447" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL447" s="5"/>
+    </row>
+    <row r="448" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL448" s="5"/>
+    </row>
+    <row r="449" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL449" s="5"/>
+    </row>
+    <row r="450" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL450" s="5"/>
+    </row>
+    <row r="451" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL451" s="5"/>
+    </row>
+    <row r="452" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL452" s="5"/>
+    </row>
+    <row r="454" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV454"/>
+    </row>
+    <row r="455" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL455" s="5"/>
+    </row>
+    <row r="456" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL456" s="5"/>
+    </row>
+    <row r="489" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU489" s="15"/>
+      <c r="BV489" s="16"/>
+    </row>
+    <row r="490" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H490" s="15"/>
-      <c r="CJ490" s="15"/>
-    </row>
-    <row r="496" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT496"/>
-    </row>
-    <row r="497" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT497"/>
-      <c r="CJ497" s="5"/>
-    </row>
-    <row r="498" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT498"/>
-      <c r="CJ498" s="5"/>
-    </row>
-    <row r="499" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ499" s="5"/>
-    </row>
-    <row r="516" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT516"/>
-    </row>
-    <row r="517" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ517" s="5"/>
-    </row>
-    <row r="549" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT549"/>
-    </row>
-    <row r="550" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT550"/>
-      <c r="CJ550" s="5"/>
-    </row>
-    <row r="551" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ551" s="5"/>
-    </row>
-    <row r="567" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT567"/>
-    </row>
-    <row r="568" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ568" s="5"/>
-    </row>
-    <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT574"/>
-    </row>
-    <row r="575" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT575"/>
-      <c r="CJ575" s="5"/>
-    </row>
-    <row r="576" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ576" s="5"/>
-    </row>
-    <row r="581" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT581"/>
-    </row>
-    <row r="582" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT582"/>
-      <c r="CJ582" s="5"/>
-    </row>
-    <row r="583" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT583"/>
-      <c r="CJ583" s="5"/>
-    </row>
-    <row r="584" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT584"/>
-      <c r="CJ584" s="5"/>
-    </row>
-    <row r="585" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT585"/>
-      <c r="CJ585" s="5"/>
-    </row>
-    <row r="586" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT586"/>
-      <c r="CJ586" s="5"/>
-    </row>
-    <row r="587" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT587"/>
-      <c r="CJ587" s="5"/>
-    </row>
-    <row r="588" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT588"/>
-      <c r="CJ588" s="5"/>
-    </row>
-    <row r="589" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT589"/>
-      <c r="CJ589" s="5"/>
-    </row>
-    <row r="590" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT590"/>
-      <c r="CJ590" s="5"/>
-    </row>
-    <row r="591" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT591"/>
-      <c r="CJ591" s="5"/>
-    </row>
-    <row r="592" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT592"/>
-      <c r="CJ592" s="5"/>
-    </row>
-    <row r="593" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT593"/>
-      <c r="CJ593" s="5"/>
-    </row>
-    <row r="594" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT594"/>
-      <c r="CJ594" s="5"/>
-    </row>
-    <row r="595" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT595"/>
-      <c r="CJ595" s="5"/>
-    </row>
-    <row r="596" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT596"/>
-      <c r="CJ596" s="5"/>
-    </row>
-    <row r="597" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ597" s="5"/>
-    </row>
-    <row r="601" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT601"/>
-    </row>
-    <row r="602" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT602"/>
-      <c r="CJ602" s="5"/>
-    </row>
-    <row r="603" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ603" s="5"/>
-    </row>
-    <row r="604" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT604"/>
-    </row>
-    <row r="605" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ605" s="5"/>
-    </row>
-    <row r="608" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT608"/>
-    </row>
-    <row r="609" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT609"/>
-      <c r="CJ609" s="5"/>
-    </row>
-    <row r="610" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ610" s="5"/>
-    </row>
-    <row r="641" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT641"/>
-    </row>
-    <row r="642" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT642"/>
-      <c r="CJ642" s="5"/>
-    </row>
-    <row r="643" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT643"/>
-      <c r="CJ643" s="5"/>
-    </row>
-    <row r="644" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT644"/>
-      <c r="CJ644" s="5"/>
-    </row>
-    <row r="645" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT645"/>
-      <c r="CJ645" s="5"/>
-    </row>
-    <row r="646" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT646"/>
-      <c r="CJ646" s="5"/>
-    </row>
-    <row r="647" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT647"/>
-      <c r="CJ647" s="5"/>
-    </row>
-    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT648"/>
-      <c r="CJ648" s="5"/>
-    </row>
-    <row r="649" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ649" s="5"/>
-    </row>
-    <row r="651" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT651"/>
-    </row>
-    <row r="652" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ652" s="5"/>
-    </row>
-    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT656"/>
-    </row>
-    <row r="657" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ657" s="5"/>
-    </row>
-    <row r="660" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT660"/>
-    </row>
-    <row r="661" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT661"/>
-      <c r="CJ661" s="5"/>
-    </row>
-    <row r="662" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT662"/>
-      <c r="CJ662" s="5"/>
-    </row>
-    <row r="663" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT663"/>
-      <c r="CJ663" s="5"/>
-    </row>
-    <row r="664" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ664" s="5"/>
-    </row>
-    <row r="671" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT671"/>
-    </row>
-    <row r="672" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ672" s="5"/>
-    </row>
-    <row r="675" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT675"/>
-    </row>
-    <row r="676" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT676"/>
-      <c r="CJ676" s="5"/>
-    </row>
-    <row r="677" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT677"/>
-      <c r="CJ677" s="5"/>
-    </row>
-    <row r="678" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT678"/>
-      <c r="CJ678" s="5"/>
-    </row>
-    <row r="679" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ679" s="5"/>
-    </row>
-    <row r="681" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT681"/>
-    </row>
-    <row r="682" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT682"/>
-      <c r="CJ682" s="5"/>
-    </row>
-    <row r="683" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ683" s="5"/>
-    </row>
-    <row r="684" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ684">
+      <c r="CL490" s="15"/>
+    </row>
+    <row r="496" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV496"/>
+    </row>
+    <row r="497" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV497"/>
+      <c r="CL497" s="5"/>
+    </row>
+    <row r="498" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV498"/>
+      <c r="CL498" s="5"/>
+    </row>
+    <row r="499" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL499" s="5"/>
+    </row>
+    <row r="516" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV516"/>
+    </row>
+    <row r="517" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL517" s="5"/>
+    </row>
+    <row r="549" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV549"/>
+    </row>
+    <row r="550" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV550"/>
+      <c r="CL550" s="5"/>
+    </row>
+    <row r="551" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL551" s="5"/>
+    </row>
+    <row r="567" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV567"/>
+    </row>
+    <row r="568" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL568" s="5"/>
+    </row>
+    <row r="574" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV574"/>
+    </row>
+    <row r="575" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV575"/>
+      <c r="CL575" s="5"/>
+    </row>
+    <row r="576" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL576" s="5"/>
+    </row>
+    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV581"/>
+    </row>
+    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV582"/>
+      <c r="CL582" s="5"/>
+    </row>
+    <row r="583" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV583"/>
+      <c r="CL583" s="5"/>
+    </row>
+    <row r="584" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV584"/>
+      <c r="CL584" s="5"/>
+    </row>
+    <row r="585" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV585"/>
+      <c r="CL585" s="5"/>
+    </row>
+    <row r="586" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV586"/>
+      <c r="CL586" s="5"/>
+    </row>
+    <row r="587" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV587"/>
+      <c r="CL587" s="5"/>
+    </row>
+    <row r="588" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV588"/>
+      <c r="CL588" s="5"/>
+    </row>
+    <row r="589" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV589"/>
+      <c r="CL589" s="5"/>
+    </row>
+    <row r="590" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV590"/>
+      <c r="CL590" s="5"/>
+    </row>
+    <row r="591" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV591"/>
+      <c r="CL591" s="5"/>
+    </row>
+    <row r="592" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV592"/>
+      <c r="CL592" s="5"/>
+    </row>
+    <row r="593" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV593"/>
+      <c r="CL593" s="5"/>
+    </row>
+    <row r="594" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV594"/>
+      <c r="CL594" s="5"/>
+    </row>
+    <row r="595" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV595"/>
+      <c r="CL595" s="5"/>
+    </row>
+    <row r="596" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV596"/>
+      <c r="CL596" s="5"/>
+    </row>
+    <row r="597" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL597" s="5"/>
+    </row>
+    <row r="601" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV601"/>
+    </row>
+    <row r="602" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV602"/>
+      <c r="CL602" s="5"/>
+    </row>
+    <row r="603" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL603" s="5"/>
+    </row>
+    <row r="604" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV604"/>
+    </row>
+    <row r="605" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL605" s="5"/>
+    </row>
+    <row r="608" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV608"/>
+    </row>
+    <row r="609" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV609"/>
+      <c r="CL609" s="5"/>
+    </row>
+    <row r="610" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL610" s="5"/>
+    </row>
+    <row r="641" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV641"/>
+    </row>
+    <row r="642" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV642"/>
+      <c r="CL642" s="5"/>
+    </row>
+    <row r="643" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV643"/>
+      <c r="CL643" s="5"/>
+    </row>
+    <row r="644" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV644"/>
+      <c r="CL644" s="5"/>
+    </row>
+    <row r="645" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV645"/>
+      <c r="CL645" s="5"/>
+    </row>
+    <row r="646" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV646"/>
+      <c r="CL646" s="5"/>
+    </row>
+    <row r="647" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV647"/>
+      <c r="CL647" s="5"/>
+    </row>
+    <row r="648" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV648"/>
+      <c r="CL648" s="5"/>
+    </row>
+    <row r="649" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL649" s="5"/>
+    </row>
+    <row r="651" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV651"/>
+    </row>
+    <row r="652" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL652" s="5"/>
+    </row>
+    <row r="656" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV656"/>
+    </row>
+    <row r="657" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL657" s="5"/>
+    </row>
+    <row r="660" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV660"/>
+    </row>
+    <row r="661" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV661"/>
+      <c r="CL661" s="5"/>
+    </row>
+    <row r="662" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV662"/>
+      <c r="CL662" s="5"/>
+    </row>
+    <row r="663" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV663"/>
+      <c r="CL663" s="5"/>
+    </row>
+    <row r="664" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL664" s="5"/>
+    </row>
+    <row r="671" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV671"/>
+    </row>
+    <row r="672" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL672" s="5"/>
+    </row>
+    <row r="675" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV675"/>
+    </row>
+    <row r="676" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV676"/>
+      <c r="CL676" s="5"/>
+    </row>
+    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV677"/>
+      <c r="CL677" s="5"/>
+    </row>
+    <row r="678" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV678"/>
+      <c r="CL678" s="5"/>
+    </row>
+    <row r="679" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL679" s="5"/>
+    </row>
+    <row r="681" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV681"/>
+    </row>
+    <row r="682" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV682"/>
+      <c r="CL682" s="5"/>
+    </row>
+    <row r="683" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL683" s="5"/>
+    </row>
+    <row r="684" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL684">
         <v>0.15</v>
       </c>
     </row>
-    <row r="686" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ686">
+    <row r="686" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL686">
         <v>0.2</v>
       </c>
     </row>
-    <row r="687" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ687">
+    <row r="687" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL687">
         <v>0.1</v>
       </c>
     </row>
-    <row r="689" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ689">
+    <row r="689" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL689">
         <v>0.2</v>
       </c>
     </row>
-    <row r="696" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ696">
+    <row r="696" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL696">
         <v>1</v>
       </c>
     </row>
-    <row r="698" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ698">
+    <row r="698" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL698">
         <v>0.4</v>
       </c>
     </row>
-    <row r="699" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ699">
+    <row r="699" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL699">
         <v>0.6</v>
       </c>
     </row>
-    <row r="702" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ702">
+    <row r="702" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL702">
         <v>0.5</v>
       </c>
     </row>
-    <row r="703" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ703">
+    <row r="703" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL703">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="704" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ704">
+    <row r="704" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL704">
         <v>0.2</v>
       </c>
     </row>
-    <row r="707" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT707"/>
-    </row>
-    <row r="708" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT708"/>
-      <c r="CJ708" s="5"/>
-    </row>
-    <row r="709" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT709"/>
-      <c r="CJ709" s="5"/>
-    </row>
-    <row r="710" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT710"/>
-      <c r="CJ710" s="5"/>
-    </row>
-    <row r="711" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT711"/>
-      <c r="CJ711" s="5"/>
-    </row>
-    <row r="712" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT712"/>
-      <c r="CJ712" s="5"/>
-    </row>
-    <row r="713" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT713"/>
-      <c r="CJ713" s="5"/>
-    </row>
-    <row r="714" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT714"/>
-      <c r="CJ714" s="5"/>
-    </row>
-    <row r="715" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT715"/>
-      <c r="CJ715" s="5"/>
-    </row>
-    <row r="716" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ716" s="5"/>
-    </row>
-    <row r="717" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT717"/>
-    </row>
-    <row r="718" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ718" s="5"/>
-    </row>
-    <row r="727" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT727"/>
-    </row>
-    <row r="728" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT728"/>
-      <c r="CJ728" s="5"/>
-    </row>
-    <row r="729" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT729"/>
-      <c r="CJ729" s="5"/>
-    </row>
-    <row r="730" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT730"/>
-      <c r="CJ730" s="5"/>
-    </row>
-    <row r="731" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT731"/>
-      <c r="CJ731" s="5"/>
-    </row>
-    <row r="732" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT732"/>
-      <c r="CJ732" s="5"/>
-    </row>
-    <row r="733" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT733"/>
-      <c r="CJ733" s="5"/>
-    </row>
-    <row r="734" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT734"/>
-      <c r="CJ734" s="5"/>
-    </row>
-    <row r="735" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ735" s="5"/>
-    </row>
-    <row r="736" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT736"/>
-    </row>
-    <row r="737" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ737" s="5"/>
-    </row>
-    <row r="742" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT742"/>
-    </row>
-    <row r="743" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT743"/>
-      <c r="CJ743" s="5"/>
-    </row>
-    <row r="744" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ744" s="5"/>
-    </row>
-    <row r="745" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT745"/>
-    </row>
-    <row r="746" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT746"/>
-      <c r="CJ746" s="5"/>
-    </row>
-    <row r="747" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ747" s="5"/>
-    </row>
-    <row r="748" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT748"/>
-    </row>
-    <row r="749" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT749"/>
-      <c r="CJ749" s="5"/>
-    </row>
-    <row r="750" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT750"/>
-      <c r="CJ750" s="5"/>
-    </row>
-    <row r="751" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT751"/>
-      <c r="CJ751" s="5"/>
-    </row>
-    <row r="752" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ752" s="5"/>
-    </row>
-    <row r="756" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT756"/>
-    </row>
-    <row r="757" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT757"/>
-      <c r="CJ757" s="5"/>
-    </row>
-    <row r="758" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT758"/>
-      <c r="CJ758" s="5"/>
-    </row>
-    <row r="759" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ759" s="5"/>
-    </row>
-    <row r="760" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT760"/>
-    </row>
-    <row r="761" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ761" s="5"/>
-    </row>
-    <row r="762" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS762" s="15"/>
-      <c r="BT762" s="16"/>
-    </row>
-    <row r="763" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV707"/>
+    </row>
+    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV708"/>
+      <c r="CL708" s="5"/>
+    </row>
+    <row r="709" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV709"/>
+      <c r="CL709" s="5"/>
+    </row>
+    <row r="710" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV710"/>
+      <c r="CL710" s="5"/>
+    </row>
+    <row r="711" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV711"/>
+      <c r="CL711" s="5"/>
+    </row>
+    <row r="712" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV712"/>
+      <c r="CL712" s="5"/>
+    </row>
+    <row r="713" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV713"/>
+      <c r="CL713" s="5"/>
+    </row>
+    <row r="714" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV714"/>
+      <c r="CL714" s="5"/>
+    </row>
+    <row r="715" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV715"/>
+      <c r="CL715" s="5"/>
+    </row>
+    <row r="716" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL716" s="5"/>
+    </row>
+    <row r="717" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV717"/>
+    </row>
+    <row r="718" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL718" s="5"/>
+    </row>
+    <row r="727" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV727"/>
+    </row>
+    <row r="728" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV728"/>
+      <c r="CL728" s="5"/>
+    </row>
+    <row r="729" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV729"/>
+      <c r="CL729" s="5"/>
+    </row>
+    <row r="730" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV730"/>
+      <c r="CL730" s="5"/>
+    </row>
+    <row r="731" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV731"/>
+      <c r="CL731" s="5"/>
+    </row>
+    <row r="732" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV732"/>
+      <c r="CL732" s="5"/>
+    </row>
+    <row r="733" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV733"/>
+      <c r="CL733" s="5"/>
+    </row>
+    <row r="734" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV734"/>
+      <c r="CL734" s="5"/>
+    </row>
+    <row r="735" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL735" s="5"/>
+    </row>
+    <row r="736" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV736"/>
+    </row>
+    <row r="737" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL737" s="5"/>
+    </row>
+    <row r="742" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV742"/>
+    </row>
+    <row r="743" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV743"/>
+      <c r="CL743" s="5"/>
+    </row>
+    <row r="744" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL744" s="5"/>
+    </row>
+    <row r="745" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV745"/>
+    </row>
+    <row r="746" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV746"/>
+      <c r="CL746" s="5"/>
+    </row>
+    <row r="747" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL747" s="5"/>
+    </row>
+    <row r="748" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV748"/>
+    </row>
+    <row r="749" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV749"/>
+      <c r="CL749" s="5"/>
+    </row>
+    <row r="750" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV750"/>
+      <c r="CL750" s="5"/>
+    </row>
+    <row r="751" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV751"/>
+      <c r="CL751" s="5"/>
+    </row>
+    <row r="752" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL752" s="5"/>
+    </row>
+    <row r="756" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV756"/>
+    </row>
+    <row r="757" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV757"/>
+      <c r="CL757" s="5"/>
+    </row>
+    <row r="758" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV758"/>
+      <c r="CL758" s="5"/>
+    </row>
+    <row r="759" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL759" s="5"/>
+    </row>
+    <row r="760" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV760"/>
+    </row>
+    <row r="761" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL761" s="5"/>
+    </row>
+    <row r="762" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU762" s="15"/>
+      <c r="BV762" s="16"/>
+    </row>
+    <row r="763" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H763" s="15"/>
-      <c r="CJ763" s="15"/>
-    </row>
-    <row r="780" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT780"/>
-    </row>
-    <row r="781" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT781"/>
-      <c r="CJ781" s="5"/>
-    </row>
-    <row r="782" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT782"/>
-      <c r="CJ782" s="5"/>
-    </row>
-    <row r="783" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT783"/>
-      <c r="CJ783" s="5"/>
-    </row>
-    <row r="784" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ784" s="5"/>
-    </row>
-    <row r="785" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT785"/>
-    </row>
-    <row r="786" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT786"/>
-      <c r="CJ786" s="5"/>
-    </row>
-    <row r="787" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS787" s="15"/>
-      <c r="BT787" s="16"/>
-      <c r="CJ787" s="5"/>
-    </row>
-    <row r="788" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CL763" s="15"/>
+    </row>
+    <row r="780" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV780"/>
+    </row>
+    <row r="781" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV781"/>
+      <c r="CL781" s="5"/>
+    </row>
+    <row r="782" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV782"/>
+      <c r="CL782" s="5"/>
+    </row>
+    <row r="783" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV783"/>
+      <c r="CL783" s="5"/>
+    </row>
+    <row r="784" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL784" s="5"/>
+    </row>
+    <row r="785" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV785"/>
+    </row>
+    <row r="786" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV786"/>
+      <c r="CL786" s="5"/>
+    </row>
+    <row r="787" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU787" s="15"/>
+      <c r="BV787" s="16"/>
+      <c r="CL787" s="5"/>
+    </row>
+    <row r="788" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H788" s="15"/>
-      <c r="CJ788" s="15"/>
-    </row>
-    <row r="791" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT791"/>
-    </row>
-    <row r="792" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT792"/>
-      <c r="CJ792" s="5"/>
-    </row>
-    <row r="793" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT793"/>
-      <c r="CJ793" s="5"/>
-    </row>
-    <row r="794" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT794"/>
-      <c r="CJ794" s="5"/>
-    </row>
-    <row r="795" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT795"/>
-      <c r="CJ795" s="5"/>
-    </row>
-    <row r="796" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT796"/>
-      <c r="CJ796" s="5"/>
-    </row>
-    <row r="797" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT797"/>
-      <c r="CJ797" s="5"/>
-    </row>
-    <row r="798" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT798"/>
-      <c r="CJ798" s="5"/>
-    </row>
-    <row r="799" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ799" s="5"/>
-    </row>
-    <row r="801" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT801"/>
-    </row>
-    <row r="802" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT802"/>
-      <c r="CJ802" s="5"/>
-    </row>
-    <row r="803" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT803"/>
-      <c r="CJ803" s="5"/>
-    </row>
-    <row r="804" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT804"/>
-      <c r="CJ804" s="5"/>
-    </row>
-    <row r="805" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT805"/>
-      <c r="CJ805" s="5"/>
-    </row>
-    <row r="806" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT806"/>
-      <c r="CJ806" s="5"/>
-    </row>
-    <row r="807" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ807" s="5"/>
-    </row>
-    <row r="808" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT808"/>
-    </row>
-    <row r="809" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT809"/>
-      <c r="CJ809" s="5"/>
-    </row>
-    <row r="810" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT810"/>
-      <c r="CJ810" s="5"/>
-    </row>
-    <row r="811" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT811"/>
-      <c r="CJ811" s="5"/>
-    </row>
-    <row r="812" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT812"/>
-      <c r="CJ812" s="5"/>
-    </row>
-    <row r="813" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT813"/>
-      <c r="CJ813" s="5"/>
-    </row>
-    <row r="814" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT814"/>
-      <c r="CJ814" s="5"/>
-    </row>
-    <row r="815" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT815"/>
-      <c r="CJ815" s="5"/>
-    </row>
-    <row r="816" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT816"/>
-      <c r="CJ816" s="5"/>
-    </row>
-    <row r="817" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT817"/>
-      <c r="CJ817" s="5"/>
-    </row>
-    <row r="818" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT818"/>
-      <c r="CJ818" s="5"/>
-    </row>
-    <row r="819" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT819"/>
-      <c r="CJ819" s="5"/>
-    </row>
-    <row r="820" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT820"/>
-      <c r="CJ820" s="5"/>
-    </row>
-    <row r="821" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT821"/>
-      <c r="CJ821" s="5"/>
-    </row>
-    <row r="822" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT822"/>
-      <c r="CJ822" s="5"/>
-    </row>
-    <row r="823" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT823"/>
-      <c r="CJ823" s="5"/>
-    </row>
-    <row r="824" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT824"/>
-      <c r="CJ824" s="5"/>
-    </row>
-    <row r="825" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT825"/>
-      <c r="CJ825" s="5"/>
-    </row>
-    <row r="826" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT826"/>
-      <c r="CJ826" s="5"/>
-    </row>
-    <row r="827" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT827"/>
-      <c r="CJ827" s="5"/>
-    </row>
-    <row r="828" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT828"/>
-      <c r="CJ828" s="5"/>
-    </row>
-    <row r="829" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT829"/>
-      <c r="CJ829" s="5"/>
-    </row>
-    <row r="830" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT830"/>
-      <c r="CJ830" s="5"/>
-    </row>
-    <row r="831" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT831"/>
-      <c r="CJ831" s="5"/>
-    </row>
-    <row r="832" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT832"/>
-      <c r="CJ832" s="5"/>
-    </row>
-    <row r="833" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT833"/>
-      <c r="CJ833" s="5"/>
-    </row>
-    <row r="834" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT834"/>
-      <c r="CJ834" s="5"/>
-    </row>
-    <row r="835" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT835"/>
-      <c r="CJ835" s="5"/>
-    </row>
-    <row r="836" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT836"/>
-      <c r="CJ836" s="5"/>
-    </row>
-    <row r="837" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT837"/>
-      <c r="CJ837" s="5"/>
-    </row>
-    <row r="838" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ838" s="5"/>
-    </row>
-    <row r="839" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT839"/>
-    </row>
-    <row r="840" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT840"/>
-      <c r="CJ840" s="5"/>
-    </row>
-    <row r="841" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT841"/>
-      <c r="CJ841" s="5"/>
-    </row>
-    <row r="842" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ842" s="5"/>
+      <c r="CL788" s="15"/>
+    </row>
+    <row r="791" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV791"/>
+    </row>
+    <row r="792" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV792"/>
+      <c r="CL792" s="5"/>
+    </row>
+    <row r="793" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV793"/>
+      <c r="CL793" s="5"/>
+    </row>
+    <row r="794" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV794"/>
+      <c r="CL794" s="5"/>
+    </row>
+    <row r="795" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV795"/>
+      <c r="CL795" s="5"/>
+    </row>
+    <row r="796" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV796"/>
+      <c r="CL796" s="5"/>
+    </row>
+    <row r="797" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV797"/>
+      <c r="CL797" s="5"/>
+    </row>
+    <row r="798" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV798"/>
+      <c r="CL798" s="5"/>
+    </row>
+    <row r="799" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL799" s="5"/>
+    </row>
+    <row r="801" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV801"/>
+    </row>
+    <row r="802" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV802"/>
+      <c r="CL802" s="5"/>
+    </row>
+    <row r="803" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV803"/>
+      <c r="CL803" s="5"/>
+    </row>
+    <row r="804" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV804"/>
+      <c r="CL804" s="5"/>
+    </row>
+    <row r="805" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV805"/>
+      <c r="CL805" s="5"/>
+    </row>
+    <row r="806" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV806"/>
+      <c r="CL806" s="5"/>
+    </row>
+    <row r="807" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL807" s="5"/>
+    </row>
+    <row r="808" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV808"/>
+    </row>
+    <row r="809" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV809"/>
+      <c r="CL809" s="5"/>
+    </row>
+    <row r="810" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV810"/>
+      <c r="CL810" s="5"/>
+    </row>
+    <row r="811" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV811"/>
+      <c r="CL811" s="5"/>
+    </row>
+    <row r="812" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV812"/>
+      <c r="CL812" s="5"/>
+    </row>
+    <row r="813" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV813"/>
+      <c r="CL813" s="5"/>
+    </row>
+    <row r="814" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV814"/>
+      <c r="CL814" s="5"/>
+    </row>
+    <row r="815" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV815"/>
+      <c r="CL815" s="5"/>
+    </row>
+    <row r="816" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV816"/>
+      <c r="CL816" s="5"/>
+    </row>
+    <row r="817" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV817"/>
+      <c r="CL817" s="5"/>
+    </row>
+    <row r="818" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV818"/>
+      <c r="CL818" s="5"/>
+    </row>
+    <row r="819" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV819"/>
+      <c r="CL819" s="5"/>
+    </row>
+    <row r="820" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV820"/>
+      <c r="CL820" s="5"/>
+    </row>
+    <row r="821" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV821"/>
+      <c r="CL821" s="5"/>
+    </row>
+    <row r="822" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV822"/>
+      <c r="CL822" s="5"/>
+    </row>
+    <row r="823" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV823"/>
+      <c r="CL823" s="5"/>
+    </row>
+    <row r="824" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV824"/>
+      <c r="CL824" s="5"/>
+    </row>
+    <row r="825" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV825"/>
+      <c r="CL825" s="5"/>
+    </row>
+    <row r="826" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV826"/>
+      <c r="CL826" s="5"/>
+    </row>
+    <row r="827" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV827"/>
+      <c r="CL827" s="5"/>
+    </row>
+    <row r="828" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV828"/>
+      <c r="CL828" s="5"/>
+    </row>
+    <row r="829" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV829"/>
+      <c r="CL829" s="5"/>
+    </row>
+    <row r="830" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV830"/>
+      <c r="CL830" s="5"/>
+    </row>
+    <row r="831" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV831"/>
+      <c r="CL831" s="5"/>
+    </row>
+    <row r="832" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV832"/>
+      <c r="CL832" s="5"/>
+    </row>
+    <row r="833" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV833"/>
+      <c r="CL833" s="5"/>
+    </row>
+    <row r="834" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV834"/>
+      <c r="CL834" s="5"/>
+    </row>
+    <row r="835" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV835"/>
+      <c r="CL835" s="5"/>
+    </row>
+    <row r="836" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV836"/>
+      <c r="CL836" s="5"/>
+    </row>
+    <row r="837" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV837"/>
+      <c r="CL837" s="5"/>
+    </row>
+    <row r="838" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL838" s="5"/>
+    </row>
+    <row r="839" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV839"/>
+    </row>
+    <row r="840" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV840"/>
+      <c r="CL840" s="5"/>
+    </row>
+    <row r="841" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV841"/>
+      <c r="CL841" s="5"/>
+    </row>
+    <row r="842" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL842" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -9140,37 +9188,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>383</v>
+      </c>
+      <c r="F1" t="s">
         <v>384</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>385</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>386</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>387</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>388</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>389</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>390</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>391</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>392</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -9184,43 +9232,43 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F2" t="s">
         <v>395</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>396</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>397</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>398</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>399</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>400</v>
-      </c>
-      <c r="K2" t="s">
-        <v>401</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
+        <v>401</v>
+      </c>
+      <c r="N2" t="s">
         <v>402</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>403</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>405</v>
-      </c>
       <c r="Q2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -9249,13 +9297,13 @@
         <v>116</v>
       </c>
       <c r="J3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K3" t="s">
         <v>117</v>
       </c>
       <c r="L3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M3" t="s">
         <v>116</v>
@@ -9264,13 +9312,27 @@
         <v>116</v>
       </c>
       <c r="O3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P3" t="s">
         <v>116</v>
       </c>
       <c r="Q3" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9326,7 +9388,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9337,10 +9399,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9351,7 +9413,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D3" t="s">
         <v>125</v>
@@ -9386,22 +9448,22 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G2" t="s">
         <v>409</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>410</v>
       </c>
-      <c r="H2" t="s">
-        <v>411</v>
-      </c>
       <c r="I2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9435,13 +9497,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C4" t="s">
         <v>412</v>
-      </c>
-      <c r="C4" t="s">
-        <v>413</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -9450,24 +9512,24 @@
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -9494,34 +9556,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C1" t="s">
         <v>415</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>416</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>417</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>418</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>419</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>420</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>421</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>422</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>423</v>
-      </c>
-      <c r="L1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9529,34 +9591,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C2" t="s">
         <v>425</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>426</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>427</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>428</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>429</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>430</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>431</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>432</v>
       </c>
-      <c r="J2" t="s">
-        <v>433</v>
-      </c>
       <c r="K2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L2" t="s">
         <v>97</v>
@@ -9573,7 +9635,7 @@
         <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -9633,22 +9695,22 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E2" t="s">
         <v>435</v>
-      </c>
-      <c r="E2" t="s">
-        <v>436</v>
       </c>
       <c r="F2" t="s">
         <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" t="s">
         <v>273</v>
       </c>
       <c r="I2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J2" t="s">
         <v>54</v>
@@ -9677,7 +9739,7 @@
         <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I3" t="s">
         <v>118</v>
@@ -9714,28 +9776,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -9743,28 +9805,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9804,22 +9866,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6A2BA8-9B2C-4E82-8B14-90F9E2F9C4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829D1042-51FB-4A55-8924-2878D2B26C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="482">
   <si>
     <t>Id</t>
   </si>
@@ -9428,16 +9428,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9463,10 +9468,13 @@
         <v>410</v>
       </c>
       <c r="I2" t="s">
+        <v>321</v>
+      </c>
+      <c r="J2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -9491,11 +9499,14 @@
       <c r="H3" t="s">
         <v>118</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
+        <v>361</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>371</v>
       </c>
@@ -9511,11 +9522,11 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>470</v>
       </c>
@@ -9528,7 +9539,7 @@
       <c r="E5">
         <v>10</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>471</v>
       </c>
     </row>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829D1042-51FB-4A55-8924-2878D2B26C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB41B549-14CE-4177-9EC7-1A4A1B646E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="483">
   <si>
     <t>Id</t>
   </si>
@@ -1765,6 +1765,9 @@
   <si>
     <t>string</t>
     <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>char_4182_oblvns_avemujica_1</t>
   </si>
 </sst>
 </file>
@@ -2961,7 +2964,7 @@
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="2" t="s">
-        <v>127</v>
+        <v>482</v>
       </c>
       <c r="G5">
         <v>1</v>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB41B549-14CE-4177-9EC7-1A4A1B646E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456BAB86-2A99-4C96-ABDE-0955D0DB1328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="483">
   <si>
     <t>Id</t>
   </si>
@@ -388,12 +388,6 @@
     <t>高度</t>
   </si>
   <si>
-    <t>高台单位？</t>
-  </si>
-  <si>
-    <t>地面</t>
-  </si>
-  <si>
     <t>阻挡个数</t>
   </si>
   <si>
@@ -548,12 +542,6 @@
   </si>
   <si>
     <t>Height</t>
-  </si>
-  <si>
-    <t>CanSetHigh</t>
-  </si>
-  <si>
-    <t>CanSetGround</t>
   </si>
   <si>
     <t>StopCount</t>
@@ -1768,6 +1756,22 @@
   </si>
   <si>
     <t>char_4182_oblvns_avemujica_1</t>
+  </si>
+  <si>
+    <t>可部署位</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanSetPos</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面位</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2361,7 +2365,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS598"/>
+  <dimension ref="A1:BR598"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2391,22 +2395,22 @@
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
     <col min="35" max="35" width="34.5" customWidth="1"/>
     <col min="36" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.5" customWidth="1"/>
+    <col min="49" max="49" width="24.33203125" customWidth="1"/>
+    <col min="51" max="51" width="17.75" customWidth="1"/>
+    <col min="52" max="52" width="7.83203125" customWidth="1"/>
+    <col min="55" max="55" width="24.25" customWidth="1"/>
+    <col min="56" max="56" width="13.25" customWidth="1"/>
+    <col min="57" max="57" width="16.08203125" customWidth="1"/>
+    <col min="58" max="58" width="8" customWidth="1"/>
+    <col min="63" max="63" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="14" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>5</v>
       </c>
@@ -2482,274 +2486,268 @@
       <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="AN1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>42</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="AN2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AO2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
         <v>84</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AR2" t="s">
         <v>85</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AS2" t="s">
         <v>86</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AT2" t="s">
         <v>87</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>88</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>89</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>90</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>91</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>93</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>94</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>95</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>96</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>97</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>98</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>99</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>100</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>101</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>105</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>107</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
         <v>108</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BP2" t="s">
         <v>109</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>110</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>111</v>
       </c>
-      <c r="BP2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2757,88 +2755,88 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="R3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="S3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="T3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="V3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="W3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Y3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Z3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AA3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AB3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AC3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AE3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AF3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
         <v>2</v>
@@ -2847,61 +2845,61 @@
         <v>2</v>
       </c>
       <c r="AI3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AJ3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU3" t="s">
         <v>116</v>
       </c>
-      <c r="AN3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>118</v>
-      </c>
       <c r="AV3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AW3" t="s">
         <v>117</v>
       </c>
       <c r="AX3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AZ3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BB3" t="s">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="BC3" t="s">
         <v>2</v>
@@ -2913,58 +2911,55 @@
         <v>2</v>
       </c>
       <c r="BF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>118</v>
-      </c>
       <c r="BI3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>124</v>
-      </c>
       <c r="BK3" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="BL3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BN3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BO3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BP3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BR3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3009,2498 +3004,2499 @@
         <v>4</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="AK5">
         <v>0</v>
       </c>
+      <c r="AM5" s="2" t="s">
+        <v>482</v>
+      </c>
       <c r="AN5">
+        <v>2</v>
+      </c>
+      <c r="AO5">
+        <v>0.5</v>
+      </c>
+      <c r="AV5">
+        <v>0.25</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BG5">
+        <v>6</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BJ5" s="19"/>
+      <c r="BL5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BR5">
         <v>1</v>
       </c>
-      <c r="AO5">
-        <v>2</v>
-      </c>
-      <c r="AP5">
-        <v>0.5</v>
-      </c>
-      <c r="AW5">
-        <v>0.25</v>
-      </c>
-      <c r="BB5" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="BD5" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BF5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG5" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="BH5">
-        <v>6</v>
-      </c>
-      <c r="BI5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="BJ5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BK5" s="19"/>
-      <c r="BM5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BN5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="BP5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="BQ5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="BR5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="BS5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E6" s="17"/>
-    </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="AM6" s="2"/>
+    </row>
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="E7" s="17"/>
       <c r="F7" s="2"/>
       <c r="N7" s="2"/>
       <c r="AG7" s="2"/>
       <c r="AI7" s="2"/>
-      <c r="BB7" s="2"/>
-    </row>
-    <row r="8" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BA7" s="2"/>
+    </row>
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="E8" s="17"/>
       <c r="F8" s="2"/>
       <c r="N8" s="2"/>
       <c r="AG8" s="2"/>
-      <c r="BB8" s="2"/>
-    </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BA8" s="2"/>
+    </row>
+    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="E9" s="17"/>
       <c r="F9" s="2"/>
       <c r="N9" s="2"/>
       <c r="AG9" s="2"/>
       <c r="AI9" s="2"/>
-      <c r="BB9" s="2"/>
-    </row>
-    <row r="10" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BA9" s="2"/>
+    </row>
+    <row r="10" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="E10" s="17"/>
       <c r="F10" s="2"/>
       <c r="N10" s="2"/>
       <c r="AG10" s="2"/>
       <c r="AI10" s="2"/>
-      <c r="BB10" s="2"/>
-    </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BA10" s="2"/>
+    </row>
+    <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="E11" s="17"/>
       <c r="F11" s="2"/>
       <c r="N11" s="2"/>
       <c r="AG11" s="2"/>
       <c r="AI11" s="2"/>
-      <c r="BB11" s="2"/>
-    </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BA11" s="2"/>
+    </row>
+    <row r="13" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E13" s="17"/>
     </row>
-    <row r="14" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E14" s="17"/>
     </row>
-    <row r="15" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E15" s="17"/>
       <c r="AG15" s="2"/>
-      <c r="BP15" s="20"/>
-    </row>
-    <row r="25" spans="35:63" x14ac:dyDescent="0.25">
+      <c r="BO15" s="20"/>
+    </row>
+    <row r="25" spans="35:62" x14ac:dyDescent="0.25">
       <c r="AI25" s="2"/>
     </row>
-    <row r="31" spans="35:63" x14ac:dyDescent="0.25">
+    <row r="31" spans="35:62" x14ac:dyDescent="0.25">
       <c r="AI31" s="2"/>
-      <c r="BK31" s="2"/>
-    </row>
-    <row r="33" spans="4:70" x14ac:dyDescent="0.25">
+      <c r="BJ31" s="2"/>
+    </row>
+    <row r="33" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI33" s="2"/>
     </row>
-    <row r="34" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI34" s="2"/>
     </row>
-    <row r="35" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI35" s="2"/>
-      <c r="BK35" s="2"/>
-    </row>
-    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BJ35" s="2"/>
+    </row>
+    <row r="36" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="18"/>
       <c r="E36" s="17"/>
-      <c r="BO36" s="21"/>
-      <c r="BR36" s="21"/>
-    </row>
-    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN36" s="21"/>
+      <c r="BQ36" s="21"/>
+    </row>
+    <row r="37" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="18"/>
       <c r="E37" s="17"/>
-      <c r="BO37" s="21"/>
-      <c r="BR37" s="21"/>
-    </row>
-    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN37" s="21"/>
+      <c r="BQ37" s="21"/>
+    </row>
+    <row r="38" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="18"/>
       <c r="E38" s="17"/>
-      <c r="BO38" s="21"/>
-      <c r="BR38" s="21"/>
-    </row>
-    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN38" s="21"/>
+      <c r="BQ38" s="21"/>
+    </row>
+    <row r="39" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="18"/>
       <c r="E39" s="17"/>
-      <c r="BO39" s="21"/>
-      <c r="BR39" s="21"/>
-    </row>
-    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN39" s="21"/>
+      <c r="BQ39" s="21"/>
+    </row>
+    <row r="40" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="18"/>
       <c r="E40" s="17"/>
-      <c r="BO40" s="21"/>
-      <c r="BR40" s="21"/>
-    </row>
-    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN40" s="21"/>
+      <c r="BQ40" s="21"/>
+    </row>
+    <row r="41" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="18"/>
       <c r="E41" s="17"/>
-      <c r="BO41" s="21"/>
-      <c r="BR41" s="21"/>
-    </row>
-    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN41" s="21"/>
+      <c r="BQ41" s="21"/>
+    </row>
+    <row r="42" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="18"/>
       <c r="E42" s="17"/>
-      <c r="BO42" s="21"/>
-      <c r="BR42" s="21"/>
-    </row>
-    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN42" s="21"/>
+      <c r="BQ42" s="21"/>
+    </row>
+    <row r="43" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="18"/>
       <c r="E43" s="17"/>
-      <c r="BR43" s="21"/>
-    </row>
-    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ43" s="21"/>
+    </row>
+    <row r="44" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="18"/>
       <c r="E44" s="17"/>
-      <c r="BR44" s="21"/>
-    </row>
-    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ44" s="21"/>
+    </row>
+    <row r="45" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="18"/>
       <c r="E45" s="17"/>
-      <c r="BR45" s="21"/>
-    </row>
-    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ45" s="21"/>
+    </row>
+    <row r="46" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="18"/>
       <c r="E46" s="17"/>
-      <c r="BO46" s="21"/>
-      <c r="BR46" s="21"/>
-    </row>
-    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN46" s="21"/>
+      <c r="BQ46" s="21"/>
+    </row>
+    <row r="47" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="18"/>
       <c r="E47" s="17"/>
-      <c r="BO47" s="21"/>
-      <c r="BR47" s="21"/>
-    </row>
-    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN47" s="21"/>
+      <c r="BQ47" s="21"/>
+    </row>
+    <row r="48" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="18"/>
       <c r="E48" s="17"/>
-      <c r="BO48" s="21"/>
-      <c r="BR48" s="21"/>
-    </row>
-    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN48" s="21"/>
+      <c r="BQ48" s="21"/>
+    </row>
+    <row r="49" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="18"/>
       <c r="E49" s="17"/>
-      <c r="BO49" s="21"/>
-      <c r="BR49" s="21"/>
-    </row>
-    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN49" s="21"/>
+      <c r="BQ49" s="21"/>
+    </row>
+    <row r="50" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="18"/>
       <c r="E50" s="17"/>
-      <c r="BO50" s="21"/>
-      <c r="BR50" s="21"/>
-    </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN50" s="21"/>
+      <c r="BQ50" s="21"/>
+    </row>
+    <row r="51" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="18"/>
       <c r="E51" s="17"/>
-      <c r="BO51" s="21"/>
-      <c r="BR51" s="21"/>
-    </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN51" s="21"/>
+      <c r="BQ51" s="21"/>
+    </row>
+    <row r="52" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="18"/>
       <c r="E52" s="17"/>
-      <c r="BO52" s="21"/>
-      <c r="BR52" s="21"/>
-    </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN52" s="21"/>
+      <c r="BQ52" s="21"/>
+    </row>
+    <row r="53" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="18"/>
       <c r="E53" s="17"/>
-      <c r="BO53" s="21"/>
-      <c r="BR53" s="21"/>
-    </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN53" s="21"/>
+      <c r="BQ53" s="21"/>
+    </row>
+    <row r="54" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="18"/>
       <c r="E54" s="17"/>
-      <c r="BO54" s="21"/>
-      <c r="BR54" s="21"/>
-    </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN54" s="21"/>
+      <c r="BQ54" s="21"/>
+    </row>
+    <row r="55" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="18"/>
       <c r="E55" s="17"/>
-      <c r="BO55" s="21"/>
-      <c r="BR55" s="21"/>
-    </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN55" s="21"/>
+      <c r="BQ55" s="21"/>
+    </row>
+    <row r="56" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="18"/>
       <c r="E56" s="17"/>
-      <c r="BO56" s="21"/>
-      <c r="BR56" s="21"/>
-    </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN56" s="21"/>
+      <c r="BQ56" s="21"/>
+    </row>
+    <row r="57" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="18"/>
       <c r="E57" s="17"/>
-      <c r="BO57" s="21"/>
-      <c r="BR57" s="21"/>
-    </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN57" s="21"/>
+      <c r="BQ57" s="21"/>
+    </row>
+    <row r="58" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="18"/>
       <c r="E58" s="17"/>
-      <c r="BO58" s="21"/>
-      <c r="BR58" s="21"/>
-    </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN58" s="21"/>
+      <c r="BQ58" s="21"/>
+    </row>
+    <row r="59" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="18"/>
       <c r="E59" s="17"/>
-      <c r="BO59" s="21"/>
-      <c r="BR59" s="21"/>
-    </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN59" s="21"/>
+      <c r="BQ59" s="21"/>
+    </row>
+    <row r="60" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="18"/>
       <c r="E60" s="17"/>
-      <c r="BO60" s="21"/>
-      <c r="BR60" s="21"/>
-    </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN60" s="21"/>
+      <c r="BQ60" s="21"/>
+    </row>
+    <row r="61" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="18"/>
       <c r="E61" s="17"/>
-      <c r="BO61" s="21"/>
-      <c r="BR61" s="21"/>
-    </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN61" s="21"/>
+      <c r="BQ61" s="21"/>
+    </row>
+    <row r="62" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="18"/>
       <c r="E62" s="17"/>
-      <c r="BO62" s="21"/>
-      <c r="BR62" s="21"/>
-    </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN62" s="21"/>
+      <c r="BQ62" s="21"/>
+    </row>
+    <row r="63" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="18"/>
       <c r="E63" s="17"/>
-      <c r="BO63" s="21"/>
-      <c r="BR63" s="21"/>
-    </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN63" s="21"/>
+      <c r="BQ63" s="21"/>
+    </row>
+    <row r="64" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="18"/>
       <c r="E64" s="17"/>
-      <c r="BO64" s="21"/>
-      <c r="BR64" s="21"/>
-    </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN64" s="21"/>
+      <c r="BQ64" s="21"/>
+    </row>
+    <row r="65" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="18"/>
       <c r="E65" s="17"/>
-      <c r="BO65" s="21"/>
-      <c r="BR65" s="21"/>
-    </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN65" s="21"/>
+      <c r="BQ65" s="21"/>
+    </row>
+    <row r="66" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="18"/>
       <c r="E66" s="17"/>
-      <c r="BO66" s="21"/>
-      <c r="BR66" s="21"/>
-    </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN66" s="21"/>
+      <c r="BQ66" s="21"/>
+    </row>
+    <row r="67" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="18"/>
       <c r="E67" s="17"/>
-      <c r="BO67" s="21"/>
-      <c r="BR67" s="21"/>
-    </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN67" s="21"/>
+      <c r="BQ67" s="21"/>
+    </row>
+    <row r="68" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="18"/>
       <c r="E68" s="17"/>
-      <c r="BO68" s="21"/>
-      <c r="BR68" s="21"/>
-    </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN68" s="21"/>
+      <c r="BQ68" s="21"/>
+    </row>
+    <row r="69" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="18"/>
       <c r="E69" s="17"/>
-      <c r="BO69" s="21"/>
-      <c r="BR69" s="21"/>
-    </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN69" s="21"/>
+      <c r="BQ69" s="21"/>
+    </row>
+    <row r="70" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="18"/>
       <c r="E70" s="17"/>
-      <c r="BO70" s="21"/>
-      <c r="BR70" s="21"/>
-    </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN70" s="21"/>
+      <c r="BQ70" s="21"/>
+    </row>
+    <row r="71" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="18"/>
       <c r="E71" s="17"/>
-      <c r="BO71" s="21"/>
-      <c r="BR71" s="21"/>
-    </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN71" s="21"/>
+      <c r="BQ71" s="21"/>
+    </row>
+    <row r="72" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="18"/>
       <c r="E72" s="17"/>
-      <c r="BO72" s="21"/>
-      <c r="BR72" s="21"/>
-    </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN72" s="21"/>
+      <c r="BQ72" s="21"/>
+    </row>
+    <row r="73" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="18"/>
       <c r="E73" s="17"/>
-      <c r="BO73" s="21"/>
-      <c r="BR73" s="21"/>
-    </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN73" s="21"/>
+      <c r="BQ73" s="21"/>
+    </row>
+    <row r="74" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="18"/>
       <c r="E74" s="17"/>
-      <c r="BO74" s="21"/>
-      <c r="BR74" s="21"/>
-    </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN74" s="21"/>
+      <c r="BQ74" s="21"/>
+    </row>
+    <row r="75" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="18"/>
       <c r="E75" s="17"/>
-      <c r="BO75" s="21"/>
-      <c r="BR75" s="21"/>
-    </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN75" s="21"/>
+      <c r="BQ75" s="21"/>
+    </row>
+    <row r="76" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="18"/>
       <c r="E76" s="17"/>
-      <c r="BO76" s="21"/>
-      <c r="BR76" s="21"/>
-    </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN76" s="21"/>
+      <c r="BQ76" s="21"/>
+    </row>
+    <row r="77" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="18"/>
       <c r="E77" s="17"/>
-      <c r="BO77" s="21"/>
-      <c r="BR77" s="21"/>
-    </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN77" s="21"/>
+      <c r="BQ77" s="21"/>
+    </row>
+    <row r="78" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="18"/>
       <c r="E78" s="17"/>
-      <c r="BO78" s="21"/>
-      <c r="BR78" s="21"/>
-    </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN78" s="21"/>
+      <c r="BQ78" s="21"/>
+    </row>
+    <row r="79" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="18"/>
       <c r="E79" s="17"/>
-      <c r="BO79" s="21"/>
-      <c r="BR79" s="21"/>
-    </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN79" s="21"/>
+      <c r="BQ79" s="21"/>
+    </row>
+    <row r="80" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="18"/>
       <c r="E80" s="17"/>
-      <c r="BO80" s="21"/>
-      <c r="BR80" s="21"/>
-    </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN80" s="21"/>
+      <c r="BQ80" s="21"/>
+    </row>
+    <row r="81" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="18"/>
       <c r="E81" s="17"/>
-      <c r="BO81" s="21"/>
-      <c r="BR81" s="21"/>
-    </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN81" s="21"/>
+      <c r="BQ81" s="21"/>
+    </row>
+    <row r="82" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="18"/>
       <c r="E82" s="17"/>
-      <c r="BO82" s="21"/>
-      <c r="BR82" s="21"/>
-    </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN82" s="21"/>
+      <c r="BQ82" s="21"/>
+    </row>
+    <row r="83" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="18"/>
       <c r="E83" s="17"/>
-      <c r="BO83" s="21"/>
-      <c r="BR83" s="21"/>
-    </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN83" s="21"/>
+      <c r="BQ83" s="21"/>
+    </row>
+    <row r="84" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="18"/>
       <c r="E84" s="17"/>
-      <c r="BO84" s="21"/>
-      <c r="BR84" s="21"/>
-    </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN84" s="21"/>
+      <c r="BQ84" s="21"/>
+    </row>
+    <row r="85" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="18"/>
       <c r="E85" s="17"/>
-      <c r="BO85" s="21"/>
-      <c r="BR85" s="21"/>
-    </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN85" s="21"/>
+      <c r="BQ85" s="21"/>
+    </row>
+    <row r="86" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="18"/>
       <c r="E86" s="17"/>
-      <c r="BO86" s="21"/>
-      <c r="BR86" s="21"/>
-    </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN86" s="21"/>
+      <c r="BQ86" s="21"/>
+    </row>
+    <row r="87" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="18"/>
       <c r="E87" s="17"/>
-      <c r="BO87" s="21"/>
-      <c r="BR87" s="21"/>
-    </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN87" s="21"/>
+      <c r="BQ87" s="21"/>
+    </row>
+    <row r="88" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="18"/>
       <c r="E88" s="17"/>
-      <c r="BO88" s="21"/>
-      <c r="BR88" s="21"/>
-    </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN88" s="21"/>
+      <c r="BQ88" s="21"/>
+    </row>
+    <row r="89" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="18"/>
       <c r="E89" s="17"/>
-      <c r="BO89" s="21"/>
-      <c r="BR89" s="21"/>
-    </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN89" s="21"/>
+      <c r="BQ89" s="21"/>
+    </row>
+    <row r="90" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="18"/>
       <c r="E90" s="17"/>
-      <c r="BO90" s="21"/>
-      <c r="BR90" s="21"/>
-    </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN90" s="21"/>
+      <c r="BQ90" s="21"/>
+    </row>
+    <row r="91" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="18"/>
       <c r="E91" s="17"/>
-      <c r="BO91" s="21"/>
-      <c r="BR91" s="21"/>
-    </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN91" s="21"/>
+      <c r="BQ91" s="21"/>
+    </row>
+    <row r="92" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="18"/>
       <c r="E92" s="17"/>
-      <c r="BO92" s="21"/>
-      <c r="BR92" s="21"/>
-    </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN92" s="21"/>
+      <c r="BQ92" s="21"/>
+    </row>
+    <row r="93" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="18"/>
       <c r="E93" s="17"/>
-      <c r="BO93" s="21"/>
-      <c r="BR93" s="21"/>
-    </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN93" s="21"/>
+      <c r="BQ93" s="21"/>
+    </row>
+    <row r="94" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="18"/>
       <c r="E94" s="17"/>
-      <c r="BO94" s="21"/>
-      <c r="BR94" s="21"/>
-    </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN94" s="21"/>
+      <c r="BQ94" s="21"/>
+    </row>
+    <row r="95" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="18"/>
       <c r="E95" s="17"/>
-      <c r="BO95" s="21"/>
-      <c r="BR95" s="21"/>
-    </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN95" s="21"/>
+      <c r="BQ95" s="21"/>
+    </row>
+    <row r="96" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="18"/>
       <c r="E96" s="17"/>
-      <c r="BO96" s="21"/>
-      <c r="BR96" s="21"/>
-    </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN96" s="21"/>
+      <c r="BQ96" s="21"/>
+    </row>
+    <row r="97" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="18"/>
       <c r="E97" s="17"/>
-      <c r="BO97" s="21"/>
-      <c r="BR97" s="21"/>
-    </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN97" s="21"/>
+      <c r="BQ97" s="21"/>
+    </row>
+    <row r="98" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="18"/>
       <c r="E98" s="17"/>
-      <c r="BO98" s="21"/>
-      <c r="BR98" s="21"/>
-    </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN98" s="21"/>
+      <c r="BQ98" s="21"/>
+    </row>
+    <row r="99" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="18"/>
       <c r="E99" s="17"/>
-      <c r="BO99" s="21"/>
-      <c r="BR99" s="21"/>
-    </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN99" s="21"/>
+      <c r="BQ99" s="21"/>
+    </row>
+    <row r="100" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="18"/>
       <c r="E100" s="17"/>
-      <c r="BO100" s="21"/>
-      <c r="BR100" s="21"/>
-    </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN100" s="21"/>
+      <c r="BQ100" s="21"/>
+    </row>
+    <row r="101" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="18"/>
       <c r="E101" s="17"/>
-      <c r="BO101" s="21"/>
-      <c r="BR101" s="21"/>
-    </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN101" s="21"/>
+      <c r="BQ101" s="21"/>
+    </row>
+    <row r="102" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="18"/>
       <c r="E102" s="17"/>
-      <c r="BO102" s="21"/>
-      <c r="BR102" s="21"/>
-    </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN102" s="21"/>
+      <c r="BQ102" s="21"/>
+    </row>
+    <row r="103" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="18"/>
       <c r="E103" s="17"/>
-      <c r="BO103" s="21"/>
-      <c r="BR103" s="21"/>
-    </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN103" s="21"/>
+      <c r="BQ103" s="21"/>
+    </row>
+    <row r="104" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="18"/>
       <c r="E104" s="17"/>
-      <c r="BO104" s="21"/>
-      <c r="BR104" s="21"/>
-    </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN104" s="21"/>
+      <c r="BQ104" s="21"/>
+    </row>
+    <row r="105" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="18"/>
       <c r="E105" s="17"/>
-      <c r="BO105" s="21"/>
-      <c r="BR105" s="21"/>
-    </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN105" s="21"/>
+      <c r="BQ105" s="21"/>
+    </row>
+    <row r="106" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="18"/>
       <c r="E106" s="17"/>
-      <c r="BO106" s="21"/>
-      <c r="BR106" s="21"/>
-    </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN106" s="21"/>
+      <c r="BQ106" s="21"/>
+    </row>
+    <row r="107" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="18"/>
       <c r="E107" s="17"/>
-      <c r="BO107" s="21"/>
-      <c r="BR107" s="21"/>
-    </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN107" s="21"/>
+      <c r="BQ107" s="21"/>
+    </row>
+    <row r="108" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="18"/>
       <c r="E108" s="17"/>
-      <c r="BO108" s="21"/>
-      <c r="BR108" s="21"/>
-    </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN108" s="21"/>
+      <c r="BQ108" s="21"/>
+    </row>
+    <row r="109" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="18"/>
       <c r="E109" s="17"/>
-      <c r="BO109" s="21"/>
-      <c r="BR109" s="21"/>
-    </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN109" s="21"/>
+      <c r="BQ109" s="21"/>
+    </row>
+    <row r="110" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="18"/>
       <c r="E110" s="17"/>
-      <c r="BO110" s="21"/>
-      <c r="BR110" s="21"/>
-    </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN110" s="21"/>
+      <c r="BQ110" s="21"/>
+    </row>
+    <row r="111" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="18"/>
       <c r="E111" s="17"/>
-      <c r="BO111" s="21"/>
-      <c r="BR111" s="21"/>
-    </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN111" s="21"/>
+      <c r="BQ111" s="21"/>
+    </row>
+    <row r="112" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="18"/>
       <c r="E112" s="17"/>
-      <c r="BO112" s="21"/>
-      <c r="BR112" s="21"/>
-    </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN112" s="21"/>
+      <c r="BQ112" s="21"/>
+    </row>
+    <row r="113" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="18"/>
       <c r="E113" s="17"/>
-      <c r="BO113" s="21"/>
-      <c r="BR113" s="21"/>
-    </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN113" s="21"/>
+      <c r="BQ113" s="21"/>
+    </row>
+    <row r="114" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="18"/>
       <c r="E114" s="17"/>
-      <c r="BO114" s="21"/>
-      <c r="BR114" s="21"/>
-    </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN114" s="21"/>
+      <c r="BQ114" s="21"/>
+    </row>
+    <row r="115" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="18"/>
       <c r="E115" s="17"/>
-      <c r="BO115" s="21"/>
-      <c r="BR115" s="21"/>
-    </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN115" s="21"/>
+      <c r="BQ115" s="21"/>
+    </row>
+    <row r="116" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="18"/>
       <c r="E116" s="17"/>
-      <c r="BO116" s="21"/>
-      <c r="BR116" s="21"/>
-    </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN116" s="21"/>
+      <c r="BQ116" s="21"/>
+    </row>
+    <row r="117" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="18"/>
       <c r="E117" s="17"/>
-      <c r="BO117" s="21"/>
-      <c r="BR117" s="21"/>
-    </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN117" s="21"/>
+      <c r="BQ117" s="21"/>
+    </row>
+    <row r="118" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="18"/>
       <c r="E118" s="17"/>
-      <c r="BO118" s="21"/>
-      <c r="BR118" s="21"/>
-    </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN118" s="21"/>
+      <c r="BQ118" s="21"/>
+    </row>
+    <row r="119" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="18"/>
       <c r="E119" s="17"/>
-      <c r="BO119" s="21"/>
-      <c r="BR119" s="21"/>
-    </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN119" s="21"/>
+      <c r="BQ119" s="21"/>
+    </row>
+    <row r="120" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="18"/>
       <c r="E120" s="17"/>
-      <c r="BO120" s="21"/>
-      <c r="BR120" s="21"/>
-    </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN120" s="21"/>
+      <c r="BQ120" s="21"/>
+    </row>
+    <row r="121" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="18"/>
       <c r="E121" s="17"/>
-      <c r="BO121" s="21"/>
-      <c r="BR121" s="21"/>
-    </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN121" s="21"/>
+      <c r="BQ121" s="21"/>
+    </row>
+    <row r="122" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="18"/>
       <c r="E122" s="17"/>
-      <c r="BO122" s="21"/>
-      <c r="BR122" s="21"/>
-    </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN122" s="21"/>
+      <c r="BQ122" s="21"/>
+    </row>
+    <row r="123" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="18"/>
       <c r="E123" s="17"/>
-      <c r="BO123" s="21"/>
-      <c r="BR123" s="21"/>
-    </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN123" s="21"/>
+      <c r="BQ123" s="21"/>
+    </row>
+    <row r="124" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="18"/>
       <c r="E124" s="17"/>
-      <c r="BO124" s="21"/>
-      <c r="BR124" s="21"/>
-    </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN124" s="21"/>
+      <c r="BQ124" s="21"/>
+    </row>
+    <row r="125" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="18"/>
       <c r="E125" s="17"/>
-      <c r="BO125" s="21"/>
-      <c r="BR125" s="21"/>
-    </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN125" s="21"/>
+      <c r="BQ125" s="21"/>
+    </row>
+    <row r="126" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="18"/>
       <c r="E126" s="17"/>
-      <c r="BO126" s="21"/>
-      <c r="BR126" s="21"/>
-    </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN126" s="21"/>
+      <c r="BQ126" s="21"/>
+    </row>
+    <row r="127" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="18"/>
       <c r="E127" s="17"/>
-      <c r="BO127" s="21"/>
-      <c r="BR127" s="21"/>
-    </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN127" s="21"/>
+      <c r="BQ127" s="21"/>
+    </row>
+    <row r="128" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="18"/>
       <c r="E128" s="17"/>
-      <c r="BO128" s="21"/>
-      <c r="BR128" s="21"/>
-    </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN128" s="21"/>
+      <c r="BQ128" s="21"/>
+    </row>
+    <row r="129" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="18"/>
       <c r="E129" s="17"/>
-      <c r="BO129" s="21"/>
-      <c r="BR129" s="21"/>
-    </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN129" s="21"/>
+      <c r="BQ129" s="21"/>
+    </row>
+    <row r="130" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="18"/>
       <c r="E130" s="17"/>
-      <c r="BO130" s="21"/>
-      <c r="BR130" s="21"/>
-    </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN130" s="21"/>
+      <c r="BQ130" s="21"/>
+    </row>
+    <row r="131" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="18"/>
       <c r="E131" s="17"/>
-      <c r="BO131" s="21"/>
-      <c r="BR131" s="21"/>
-    </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN131" s="21"/>
+      <c r="BQ131" s="21"/>
+    </row>
+    <row r="132" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="18"/>
       <c r="E132" s="17"/>
-      <c r="BO132" s="21"/>
-      <c r="BR132" s="21"/>
-    </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN132" s="21"/>
+      <c r="BQ132" s="21"/>
+    </row>
+    <row r="133" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="18"/>
       <c r="E133" s="17"/>
-      <c r="BO133" s="21"/>
-      <c r="BR133" s="21"/>
-    </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN133" s="21"/>
+      <c r="BQ133" s="21"/>
+    </row>
+    <row r="134" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="18"/>
       <c r="E134" s="17"/>
-      <c r="BO134" s="21"/>
-      <c r="BR134" s="21"/>
-    </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN134" s="21"/>
+      <c r="BQ134" s="21"/>
+    </row>
+    <row r="135" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="18"/>
       <c r="E135" s="17"/>
-      <c r="BO135" s="21"/>
-      <c r="BR135" s="21"/>
-    </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN135" s="21"/>
+      <c r="BQ135" s="21"/>
+    </row>
+    <row r="136" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="18"/>
       <c r="E136" s="17"/>
-      <c r="BO136" s="21"/>
-      <c r="BR136" s="21"/>
-    </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN136" s="21"/>
+      <c r="BQ136" s="21"/>
+    </row>
+    <row r="137" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="18"/>
       <c r="E137" s="17"/>
-      <c r="BO137" s="21"/>
-      <c r="BR137" s="21"/>
-    </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN137" s="21"/>
+      <c r="BQ137" s="21"/>
+    </row>
+    <row r="138" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="18"/>
       <c r="E138" s="17"/>
-      <c r="BO138" s="21"/>
-      <c r="BR138" s="21"/>
-    </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN138" s="21"/>
+      <c r="BQ138" s="21"/>
+    </row>
+    <row r="139" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="18"/>
       <c r="E139" s="17"/>
-      <c r="BO139" s="21"/>
-      <c r="BR139" s="21"/>
-    </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN139" s="21"/>
+      <c r="BQ139" s="21"/>
+    </row>
+    <row r="140" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="18"/>
       <c r="E140" s="17"/>
-      <c r="BO140" s="21"/>
-      <c r="BR140" s="21"/>
-    </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN140" s="21"/>
+      <c r="BQ140" s="21"/>
+    </row>
+    <row r="141" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="18"/>
       <c r="E141" s="17"/>
-      <c r="BO141" s="21"/>
-      <c r="BR141" s="21"/>
-    </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN141" s="21"/>
+      <c r="BQ141" s="21"/>
+    </row>
+    <row r="142" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="18"/>
       <c r="E142" s="17"/>
-      <c r="BO142" s="21"/>
-      <c r="BR142" s="21"/>
-    </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN142" s="21"/>
+      <c r="BQ142" s="21"/>
+    </row>
+    <row r="143" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="18"/>
       <c r="E143" s="17"/>
-      <c r="BO143" s="21"/>
-      <c r="BR143" s="21"/>
-    </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN143" s="21"/>
+      <c r="BQ143" s="21"/>
+    </row>
+    <row r="144" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="18"/>
       <c r="E144" s="17"/>
-      <c r="BO144" s="21"/>
-      <c r="BR144" s="21"/>
-    </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN144" s="21"/>
+      <c r="BQ144" s="21"/>
+    </row>
+    <row r="145" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="18"/>
       <c r="E145" s="17"/>
-      <c r="BO145" s="21"/>
-      <c r="BR145" s="21"/>
-    </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN145" s="21"/>
+      <c r="BQ145" s="21"/>
+    </row>
+    <row r="146" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="18"/>
       <c r="E146" s="17"/>
-      <c r="BO146" s="21"/>
-      <c r="BR146" s="21"/>
-    </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN146" s="21"/>
+      <c r="BQ146" s="21"/>
+    </row>
+    <row r="147" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="18"/>
       <c r="E147" s="17"/>
-      <c r="BO147" s="21"/>
-      <c r="BR147" s="21"/>
-    </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN147" s="21"/>
+      <c r="BQ147" s="21"/>
+    </row>
+    <row r="148" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="18"/>
       <c r="E148" s="17"/>
-      <c r="BO148" s="21"/>
-      <c r="BR148" s="21"/>
-    </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN148" s="21"/>
+      <c r="BQ148" s="21"/>
+    </row>
+    <row r="149" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="18"/>
       <c r="E149" s="17"/>
-      <c r="BO149" s="21"/>
-      <c r="BR149" s="21"/>
-    </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN149" s="21"/>
+      <c r="BQ149" s="21"/>
+    </row>
+    <row r="150" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="18"/>
       <c r="E150" s="17"/>
-      <c r="BO150" s="21"/>
-      <c r="BR150" s="21"/>
-    </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN150" s="21"/>
+      <c r="BQ150" s="21"/>
+    </row>
+    <row r="151" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="18"/>
       <c r="E151" s="17"/>
-      <c r="BO151" s="21"/>
-      <c r="BR151" s="21"/>
-    </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN151" s="21"/>
+      <c r="BQ151" s="21"/>
+    </row>
+    <row r="152" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="18"/>
       <c r="E152" s="17"/>
-      <c r="BO152" s="21"/>
-      <c r="BR152" s="21"/>
-    </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN152" s="21"/>
+      <c r="BQ152" s="21"/>
+    </row>
+    <row r="153" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="18"/>
       <c r="E153" s="17"/>
-      <c r="BO153" s="21"/>
-      <c r="BR153" s="21"/>
-    </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN153" s="21"/>
+      <c r="BQ153" s="21"/>
+    </row>
+    <row r="154" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="18"/>
       <c r="E154" s="17"/>
-      <c r="BO154" s="21"/>
-      <c r="BR154" s="21"/>
-    </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN154" s="21"/>
+      <c r="BQ154" s="21"/>
+    </row>
+    <row r="155" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="18"/>
       <c r="E155" s="17"/>
-      <c r="BO155" s="21"/>
-      <c r="BR155" s="21"/>
-    </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN155" s="21"/>
+      <c r="BQ155" s="21"/>
+    </row>
+    <row r="156" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="18"/>
       <c r="E156" s="17"/>
-      <c r="BO156" s="21"/>
-      <c r="BR156" s="21"/>
-    </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN156" s="21"/>
+      <c r="BQ156" s="21"/>
+    </row>
+    <row r="157" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="18"/>
       <c r="E157" s="17"/>
-      <c r="BO157" s="21"/>
-      <c r="BR157" s="21"/>
-    </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN157" s="21"/>
+      <c r="BQ157" s="21"/>
+    </row>
+    <row r="158" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="18"/>
       <c r="E158" s="17"/>
-      <c r="BO158" s="21"/>
-      <c r="BR158" s="21"/>
-    </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN158" s="21"/>
+      <c r="BQ158" s="21"/>
+    </row>
+    <row r="159" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="18"/>
       <c r="E159" s="17"/>
-      <c r="BO159" s="21"/>
-      <c r="BR159" s="21"/>
-    </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN159" s="21"/>
+      <c r="BQ159" s="21"/>
+    </row>
+    <row r="160" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="18"/>
       <c r="E160" s="17"/>
-      <c r="BO160" s="21"/>
-      <c r="BR160" s="21"/>
-    </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN160" s="21"/>
+      <c r="BQ160" s="21"/>
+    </row>
+    <row r="161" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="18"/>
       <c r="E161" s="17"/>
-      <c r="BO161" s="21"/>
-      <c r="BR161" s="21"/>
-    </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN161" s="21"/>
+      <c r="BQ161" s="21"/>
+    </row>
+    <row r="162" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="18"/>
       <c r="E162" s="17"/>
-      <c r="BO162" s="21"/>
-      <c r="BR162" s="21"/>
-    </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN162" s="21"/>
+      <c r="BQ162" s="21"/>
+    </row>
+    <row r="163" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="18"/>
       <c r="E163" s="17"/>
-      <c r="BO163" s="21"/>
-      <c r="BR163" s="21"/>
-    </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN163" s="21"/>
+      <c r="BQ163" s="21"/>
+    </row>
+    <row r="164" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="18"/>
       <c r="E164" s="17"/>
-      <c r="BO164" s="21"/>
-      <c r="BR164" s="21"/>
-    </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN164" s="21"/>
+      <c r="BQ164" s="21"/>
+    </row>
+    <row r="165" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="18"/>
       <c r="E165" s="17"/>
-      <c r="BO165" s="21"/>
-      <c r="BR165" s="21"/>
-    </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN165" s="21"/>
+      <c r="BQ165" s="21"/>
+    </row>
+    <row r="166" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="18"/>
       <c r="E166" s="17"/>
-      <c r="BO166" s="21"/>
-      <c r="BR166" s="21"/>
-    </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN166" s="21"/>
+      <c r="BQ166" s="21"/>
+    </row>
+    <row r="167" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="18"/>
       <c r="E167" s="17"/>
-      <c r="BO167" s="21"/>
-      <c r="BR167" s="21"/>
-    </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN167" s="21"/>
+      <c r="BQ167" s="21"/>
+    </row>
+    <row r="168" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="18"/>
       <c r="E168" s="17"/>
-      <c r="BO168" s="21"/>
-      <c r="BR168" s="21"/>
-    </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN168" s="21"/>
+      <c r="BQ168" s="21"/>
+    </row>
+    <row r="169" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="18"/>
       <c r="E169" s="17"/>
-      <c r="BO169" s="21"/>
-      <c r="BR169" s="21"/>
-    </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN169" s="21"/>
+      <c r="BQ169" s="21"/>
+    </row>
+    <row r="170" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="18"/>
       <c r="E170" s="17"/>
-      <c r="BO170" s="21"/>
-      <c r="BR170" s="21"/>
-    </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN170" s="21"/>
+      <c r="BQ170" s="21"/>
+    </row>
+    <row r="171" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="18"/>
       <c r="E171" s="17"/>
-      <c r="BO171" s="21"/>
-      <c r="BR171" s="21"/>
-    </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN171" s="21"/>
+      <c r="BQ171" s="21"/>
+    </row>
+    <row r="172" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="18"/>
       <c r="E172" s="17"/>
-      <c r="BO172" s="21"/>
-      <c r="BR172" s="21"/>
-    </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN172" s="21"/>
+      <c r="BQ172" s="21"/>
+    </row>
+    <row r="173" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="18"/>
       <c r="E173" s="17"/>
-      <c r="BO173" s="21"/>
-      <c r="BR173" s="21"/>
-    </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN173" s="21"/>
+      <c r="BQ173" s="21"/>
+    </row>
+    <row r="174" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="18"/>
       <c r="E174" s="17"/>
-      <c r="BO174" s="21"/>
-      <c r="BR174" s="21"/>
-    </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN174" s="21"/>
+      <c r="BQ174" s="21"/>
+    </row>
+    <row r="175" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="18"/>
       <c r="E175" s="17"/>
-      <c r="BO175" s="21"/>
-      <c r="BR175" s="21"/>
-    </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN175" s="21"/>
+      <c r="BQ175" s="21"/>
+    </row>
+    <row r="176" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="18"/>
       <c r="E176" s="17"/>
-      <c r="BO176" s="21"/>
-      <c r="BR176" s="21"/>
-    </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN176" s="21"/>
+      <c r="BQ176" s="21"/>
+    </row>
+    <row r="177" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="18"/>
       <c r="E177" s="17"/>
-      <c r="BO177" s="21"/>
-      <c r="BR177" s="21"/>
-    </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN177" s="21"/>
+      <c r="BQ177" s="21"/>
+    </row>
+    <row r="178" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="18"/>
       <c r="E178" s="17"/>
-      <c r="BO178" s="21"/>
-      <c r="BR178" s="21"/>
-    </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN178" s="21"/>
+      <c r="BQ178" s="21"/>
+    </row>
+    <row r="179" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="18"/>
       <c r="E179" s="17"/>
-      <c r="BO179" s="21"/>
-      <c r="BR179" s="21"/>
-    </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN179" s="21"/>
+      <c r="BQ179" s="21"/>
+    </row>
+    <row r="180" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="18"/>
       <c r="E180" s="17"/>
-      <c r="BO180" s="21"/>
-      <c r="BR180" s="21"/>
-    </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN180" s="21"/>
+      <c r="BQ180" s="21"/>
+    </row>
+    <row r="181" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="18"/>
       <c r="E181" s="17"/>
-      <c r="BO181" s="21"/>
-      <c r="BR181" s="21"/>
-    </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN181" s="21"/>
+      <c r="BQ181" s="21"/>
+    </row>
+    <row r="182" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="18"/>
       <c r="E182" s="17"/>
-      <c r="BO182" s="21"/>
-      <c r="BR182" s="21"/>
-    </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN182" s="21"/>
+      <c r="BQ182" s="21"/>
+    </row>
+    <row r="183" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="18"/>
       <c r="E183" s="17"/>
-      <c r="BO183" s="21"/>
-      <c r="BR183" s="21"/>
-    </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN183" s="21"/>
+      <c r="BQ183" s="21"/>
+    </row>
+    <row r="184" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="18"/>
       <c r="E184" s="17"/>
-      <c r="BO184" s="21"/>
-      <c r="BR184" s="21"/>
-    </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN184" s="21"/>
+      <c r="BQ184" s="21"/>
+    </row>
+    <row r="185" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="18"/>
       <c r="E185" s="17"/>
-      <c r="BO185" s="21"/>
-      <c r="BR185" s="21"/>
-    </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN185" s="21"/>
+      <c r="BQ185" s="21"/>
+    </row>
+    <row r="186" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="18"/>
       <c r="E186" s="17"/>
-      <c r="BO186" s="21"/>
-      <c r="BR186" s="21"/>
-    </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN186" s="21"/>
+      <c r="BQ186" s="21"/>
+    </row>
+    <row r="187" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="18"/>
       <c r="E187" s="17"/>
-      <c r="BO187" s="21"/>
-      <c r="BR187" s="21"/>
-    </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN187" s="21"/>
+      <c r="BQ187" s="21"/>
+    </row>
+    <row r="188" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="18"/>
       <c r="E188" s="17"/>
-      <c r="BO188" s="21"/>
-      <c r="BR188" s="21"/>
-    </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN188" s="21"/>
+      <c r="BQ188" s="21"/>
+    </row>
+    <row r="189" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="18"/>
       <c r="E189" s="17"/>
-      <c r="BO189" s="21"/>
-      <c r="BR189" s="21"/>
-    </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN189" s="21"/>
+      <c r="BQ189" s="21"/>
+    </row>
+    <row r="190" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="18"/>
       <c r="E190" s="17"/>
-      <c r="BO190" s="21"/>
-      <c r="BR190" s="21"/>
-    </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN190" s="21"/>
+      <c r="BQ190" s="21"/>
+    </row>
+    <row r="191" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="18"/>
       <c r="E191" s="17"/>
-      <c r="BO191" s="21"/>
-      <c r="BR191" s="21"/>
-    </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN191" s="21"/>
+      <c r="BQ191" s="21"/>
+    </row>
+    <row r="192" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="18"/>
       <c r="E192" s="17"/>
-      <c r="BO192" s="21"/>
-      <c r="BR192" s="21"/>
-    </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN192" s="21"/>
+      <c r="BQ192" s="21"/>
+    </row>
+    <row r="193" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="18"/>
       <c r="E193" s="17"/>
-      <c r="BO193" s="21"/>
-      <c r="BR193" s="21"/>
-    </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN193" s="21"/>
+      <c r="BQ193" s="21"/>
+    </row>
+    <row r="194" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="18"/>
       <c r="E194" s="17"/>
-      <c r="BO194" s="21"/>
-      <c r="BR194" s="21"/>
-    </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN194" s="21"/>
+      <c r="BQ194" s="21"/>
+    </row>
+    <row r="195" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="18"/>
       <c r="E195" s="17"/>
-      <c r="BO195" s="21"/>
-      <c r="BR195" s="21"/>
-    </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN195" s="21"/>
+      <c r="BQ195" s="21"/>
+    </row>
+    <row r="196" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="18"/>
       <c r="E196" s="17"/>
-      <c r="BO196" s="21"/>
-      <c r="BR196" s="21"/>
-    </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN196" s="21"/>
+      <c r="BQ196" s="21"/>
+    </row>
+    <row r="197" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="18"/>
       <c r="E197" s="17"/>
-      <c r="BO197" s="21"/>
-      <c r="BR197" s="21"/>
-    </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN197" s="21"/>
+      <c r="BQ197" s="21"/>
+    </row>
+    <row r="198" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="18"/>
       <c r="E198" s="17"/>
-      <c r="BO198" s="21"/>
-      <c r="BR198" s="21"/>
-    </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN198" s="21"/>
+      <c r="BQ198" s="21"/>
+    </row>
+    <row r="199" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="18"/>
       <c r="E199" s="17"/>
-      <c r="BO199" s="21"/>
-      <c r="BR199" s="21"/>
-    </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN199" s="21"/>
+      <c r="BQ199" s="21"/>
+    </row>
+    <row r="200" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="18"/>
       <c r="E200" s="17"/>
-      <c r="BO200" s="21"/>
-      <c r="BR200" s="21"/>
-    </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN200" s="21"/>
+      <c r="BQ200" s="21"/>
+    </row>
+    <row r="201" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="18"/>
       <c r="E201" s="17"/>
-      <c r="BO201" s="21"/>
-      <c r="BR201" s="21"/>
-    </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN201" s="21"/>
+      <c r="BQ201" s="21"/>
+    </row>
+    <row r="202" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="18"/>
       <c r="E202" s="17"/>
-      <c r="BO202" s="21"/>
-      <c r="BR202" s="21"/>
-    </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN202" s="21"/>
+      <c r="BQ202" s="21"/>
+    </row>
+    <row r="203" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="18"/>
       <c r="E203" s="17"/>
-      <c r="BO203" s="21"/>
-      <c r="BR203" s="21"/>
-    </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN203" s="21"/>
+      <c r="BQ203" s="21"/>
+    </row>
+    <row r="204" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="18"/>
       <c r="E204" s="17"/>
-      <c r="BO204" s="21"/>
-      <c r="BR204" s="21"/>
-    </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN204" s="21"/>
+      <c r="BQ204" s="21"/>
+    </row>
+    <row r="205" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="18"/>
       <c r="E205" s="17"/>
-      <c r="BO205" s="21"/>
-      <c r="BR205" s="21"/>
-    </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN205" s="21"/>
+      <c r="BQ205" s="21"/>
+    </row>
+    <row r="206" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="18"/>
       <c r="E206" s="17"/>
-      <c r="BO206" s="21"/>
-      <c r="BR206" s="21"/>
-    </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN206" s="21"/>
+      <c r="BQ206" s="21"/>
+    </row>
+    <row r="207" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="18"/>
       <c r="E207" s="17"/>
-      <c r="BO207" s="21"/>
-      <c r="BR207" s="21"/>
-    </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN207" s="21"/>
+      <c r="BQ207" s="21"/>
+    </row>
+    <row r="208" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="18"/>
       <c r="E208" s="17"/>
-      <c r="BO208" s="21"/>
-      <c r="BR208" s="21"/>
-    </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN208" s="21"/>
+      <c r="BQ208" s="21"/>
+    </row>
+    <row r="209" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="18"/>
       <c r="E209" s="17"/>
-      <c r="BO209" s="21"/>
-      <c r="BR209" s="21"/>
-    </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN209" s="21"/>
+      <c r="BQ209" s="21"/>
+    </row>
+    <row r="210" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="18"/>
       <c r="E210" s="17"/>
-      <c r="BO210" s="21"/>
-      <c r="BR210" s="21"/>
-    </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN210" s="21"/>
+      <c r="BQ210" s="21"/>
+    </row>
+    <row r="211" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="18"/>
       <c r="E211" s="17"/>
-      <c r="BO211" s="21"/>
-      <c r="BR211" s="21"/>
-    </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN211" s="21"/>
+      <c r="BQ211" s="21"/>
+    </row>
+    <row r="212" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="18"/>
       <c r="E212" s="17"/>
-      <c r="BO212" s="21"/>
-      <c r="BR212" s="21"/>
-    </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN212" s="21"/>
+      <c r="BQ212" s="21"/>
+    </row>
+    <row r="213" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="18"/>
       <c r="E213" s="17"/>
-      <c r="BO213" s="21"/>
-      <c r="BR213" s="21"/>
-    </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN213" s="21"/>
+      <c r="BQ213" s="21"/>
+    </row>
+    <row r="214" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="18"/>
       <c r="E214" s="17"/>
-      <c r="BO214" s="21"/>
-      <c r="BR214" s="21"/>
-    </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN214" s="21"/>
+      <c r="BQ214" s="21"/>
+    </row>
+    <row r="215" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="18"/>
       <c r="E215" s="17"/>
-      <c r="BO215" s="21"/>
-      <c r="BR215" s="21"/>
-    </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN215" s="21"/>
+      <c r="BQ215" s="21"/>
+    </row>
+    <row r="216" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="18"/>
       <c r="E216" s="17"/>
-      <c r="BO216" s="21"/>
-      <c r="BR216" s="21"/>
-    </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN216" s="21"/>
+      <c r="BQ216" s="21"/>
+    </row>
+    <row r="217" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="18"/>
       <c r="E217" s="17"/>
-      <c r="BO217" s="21"/>
-      <c r="BR217" s="21"/>
-    </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN217" s="21"/>
+      <c r="BQ217" s="21"/>
+    </row>
+    <row r="218" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="18"/>
       <c r="E218" s="17"/>
-      <c r="BO218" s="21"/>
-      <c r="BR218" s="21"/>
-    </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN218" s="21"/>
+      <c r="BQ218" s="21"/>
+    </row>
+    <row r="219" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="18"/>
       <c r="E219" s="17"/>
-      <c r="BO219" s="21"/>
-      <c r="BR219" s="21"/>
-    </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN219" s="21"/>
+      <c r="BQ219" s="21"/>
+    </row>
+    <row r="220" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="18"/>
       <c r="E220" s="17"/>
-      <c r="BO220" s="21"/>
-      <c r="BR220" s="21"/>
-    </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN220" s="21"/>
+      <c r="BQ220" s="21"/>
+    </row>
+    <row r="221" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="18"/>
       <c r="E221" s="17"/>
-      <c r="BO221" s="21"/>
-      <c r="BR221" s="21"/>
-    </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN221" s="21"/>
+      <c r="BQ221" s="21"/>
+    </row>
+    <row r="222" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="18"/>
       <c r="E222" s="17"/>
-      <c r="BO222" s="21"/>
-      <c r="BR222" s="21"/>
-    </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN222" s="21"/>
+      <c r="BQ222" s="21"/>
+    </row>
+    <row r="223" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="18"/>
       <c r="E223" s="17"/>
-      <c r="BO223" s="21"/>
-      <c r="BR223" s="21"/>
-    </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN223" s="21"/>
+      <c r="BQ223" s="21"/>
+    </row>
+    <row r="224" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="18"/>
       <c r="E224" s="17"/>
-      <c r="BO224" s="21"/>
-      <c r="BR224" s="21"/>
-    </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN224" s="21"/>
+      <c r="BQ224" s="21"/>
+    </row>
+    <row r="225" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="18"/>
       <c r="E225" s="17"/>
-      <c r="BO225" s="21"/>
-      <c r="BR225" s="21"/>
-    </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN225" s="21"/>
+      <c r="BQ225" s="21"/>
+    </row>
+    <row r="226" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="18"/>
       <c r="E226" s="17"/>
-      <c r="BO226" s="21"/>
-      <c r="BR226" s="21"/>
-    </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN226" s="21"/>
+      <c r="BQ226" s="21"/>
+    </row>
+    <row r="227" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="18"/>
       <c r="E227" s="17"/>
-      <c r="BO227" s="21"/>
-      <c r="BR227" s="21"/>
-    </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN227" s="21"/>
+      <c r="BQ227" s="21"/>
+    </row>
+    <row r="228" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="18"/>
       <c r="E228" s="17"/>
-      <c r="BO228" s="21"/>
-      <c r="BR228" s="21"/>
-    </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN228" s="21"/>
+      <c r="BQ228" s="21"/>
+    </row>
+    <row r="229" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="18"/>
       <c r="E229" s="17"/>
-      <c r="BO229" s="21"/>
-      <c r="BR229" s="21"/>
-    </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN229" s="21"/>
+      <c r="BQ229" s="21"/>
+    </row>
+    <row r="230" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="18"/>
       <c r="E230" s="17"/>
-      <c r="BO230" s="21"/>
-      <c r="BR230" s="21"/>
-    </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN230" s="21"/>
+      <c r="BQ230" s="21"/>
+    </row>
+    <row r="231" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="18"/>
       <c r="E231" s="17"/>
-      <c r="BO231" s="21"/>
-      <c r="BR231" s="21"/>
-    </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN231" s="21"/>
+      <c r="BQ231" s="21"/>
+    </row>
+    <row r="232" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="18"/>
       <c r="E232" s="17"/>
-      <c r="BO232" s="21"/>
-      <c r="BR232" s="21"/>
-    </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN232" s="21"/>
+      <c r="BQ232" s="21"/>
+    </row>
+    <row r="233" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="18"/>
       <c r="E233" s="17"/>
-      <c r="BO233" s="21"/>
-      <c r="BR233" s="21"/>
-    </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN233" s="21"/>
+      <c r="BQ233" s="21"/>
+    </row>
+    <row r="234" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="18"/>
       <c r="E234" s="17"/>
-      <c r="BO234" s="21"/>
-      <c r="BR234" s="21"/>
-    </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN234" s="21"/>
+      <c r="BQ234" s="21"/>
+    </row>
+    <row r="235" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="18"/>
       <c r="E235" s="17"/>
-      <c r="BO235" s="21"/>
-      <c r="BR235" s="21"/>
-    </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN235" s="21"/>
+      <c r="BQ235" s="21"/>
+    </row>
+    <row r="236" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="18"/>
       <c r="E236" s="17"/>
-      <c r="BO236" s="21"/>
-      <c r="BR236" s="21"/>
-    </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN236" s="21"/>
+      <c r="BQ236" s="21"/>
+    </row>
+    <row r="237" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="18"/>
       <c r="E237" s="17"/>
-      <c r="BO237" s="21"/>
-      <c r="BR237" s="21"/>
-    </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN237" s="21"/>
+      <c r="BQ237" s="21"/>
+    </row>
+    <row r="238" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="18"/>
       <c r="E238" s="17"/>
-      <c r="BO238" s="21"/>
-      <c r="BR238" s="21"/>
-    </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN238" s="21"/>
+      <c r="BQ238" s="21"/>
+    </row>
+    <row r="239" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="18"/>
       <c r="E239" s="17"/>
-      <c r="BO239" s="21"/>
-      <c r="BR239" s="21"/>
-    </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN239" s="21"/>
+      <c r="BQ239" s="21"/>
+    </row>
+    <row r="240" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="18"/>
       <c r="E240" s="17"/>
-      <c r="BO240" s="21"/>
-      <c r="BR240" s="21"/>
-    </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN240" s="21"/>
+      <c r="BQ240" s="21"/>
+    </row>
+    <row r="241" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="18"/>
       <c r="E241" s="17"/>
-      <c r="BO241" s="21"/>
-      <c r="BR241" s="21"/>
-    </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN241" s="21"/>
+      <c r="BQ241" s="21"/>
+    </row>
+    <row r="242" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="18"/>
       <c r="E242" s="17"/>
-      <c r="BO242" s="21"/>
-      <c r="BR242" s="21"/>
-    </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN242" s="21"/>
+      <c r="BQ242" s="21"/>
+    </row>
+    <row r="243" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="18"/>
       <c r="E243" s="17"/>
-      <c r="BR243" s="21"/>
-    </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ243" s="21"/>
+    </row>
+    <row r="244" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="18"/>
       <c r="E244" s="17"/>
-      <c r="BO244" s="21"/>
-      <c r="BR244" s="21"/>
-    </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN244" s="21"/>
+      <c r="BQ244" s="21"/>
+    </row>
+    <row r="245" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="18"/>
       <c r="E245" s="17"/>
-      <c r="BO245" s="21"/>
-      <c r="BR245" s="21"/>
-    </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN245" s="21"/>
+      <c r="BQ245" s="21"/>
+    </row>
+    <row r="246" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="18"/>
       <c r="E246" s="17"/>
-      <c r="BO246" s="21"/>
-      <c r="BR246" s="21"/>
-    </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN246" s="21"/>
+      <c r="BQ246" s="21"/>
+    </row>
+    <row r="247" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="18"/>
       <c r="E247" s="17"/>
-      <c r="BO247" s="21"/>
-      <c r="BR247" s="21"/>
-    </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN247" s="21"/>
+      <c r="BQ247" s="21"/>
+    </row>
+    <row r="248" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="18"/>
       <c r="E248" s="17"/>
-      <c r="BO248" s="21"/>
-      <c r="BR248" s="21"/>
-    </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN248" s="21"/>
+      <c r="BQ248" s="21"/>
+    </row>
+    <row r="249" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="18"/>
       <c r="E249" s="17"/>
-      <c r="BO249" s="21"/>
-      <c r="BR249" s="21"/>
-    </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN249" s="21"/>
+      <c r="BQ249" s="21"/>
+    </row>
+    <row r="250" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="18"/>
       <c r="E250" s="17"/>
-      <c r="BO250" s="21"/>
-      <c r="BR250" s="21"/>
-    </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN250" s="21"/>
+      <c r="BQ250" s="21"/>
+    </row>
+    <row r="251" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="18"/>
       <c r="E251" s="17"/>
-      <c r="BO251" s="21"/>
-      <c r="BR251" s="21"/>
-    </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN251" s="21"/>
+      <c r="BQ251" s="21"/>
+    </row>
+    <row r="252" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="18"/>
       <c r="E252" s="17"/>
-      <c r="BO252" s="21"/>
-      <c r="BR252" s="21"/>
-    </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN252" s="21"/>
+      <c r="BQ252" s="21"/>
+    </row>
+    <row r="253" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="18"/>
       <c r="E253" s="17"/>
-      <c r="BO253" s="21"/>
-      <c r="BR253" s="21"/>
-    </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN253" s="21"/>
+      <c r="BQ253" s="21"/>
+    </row>
+    <row r="254" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="18"/>
       <c r="E254" s="17"/>
-      <c r="BO254" s="21"/>
-      <c r="BR254" s="21"/>
-    </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN254" s="21"/>
+      <c r="BQ254" s="21"/>
+    </row>
+    <row r="255" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="18"/>
       <c r="E255" s="17"/>
-      <c r="BO255" s="21"/>
-      <c r="BR255" s="21"/>
-    </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN255" s="21"/>
+      <c r="BQ255" s="21"/>
+    </row>
+    <row r="256" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="18"/>
       <c r="E256" s="17"/>
-      <c r="BO256" s="21"/>
-      <c r="BR256" s="21"/>
-    </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN256" s="21"/>
+      <c r="BQ256" s="21"/>
+    </row>
+    <row r="257" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="18"/>
       <c r="E257" s="17"/>
-      <c r="BO257" s="21"/>
-      <c r="BR257" s="21"/>
-    </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN257" s="21"/>
+      <c r="BQ257" s="21"/>
+    </row>
+    <row r="258" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="18"/>
       <c r="E258" s="17"/>
-      <c r="BO258" s="21"/>
-      <c r="BR258" s="21"/>
-    </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN258" s="21"/>
+      <c r="BQ258" s="21"/>
+    </row>
+    <row r="259" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="18"/>
       <c r="E259" s="17"/>
-      <c r="BO259" s="21"/>
-      <c r="BR259" s="21"/>
-    </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN259" s="21"/>
+      <c r="BQ259" s="21"/>
+    </row>
+    <row r="260" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="18"/>
       <c r="E260" s="17"/>
-      <c r="BO260" s="21"/>
-      <c r="BR260" s="21"/>
-    </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN260" s="21"/>
+      <c r="BQ260" s="21"/>
+    </row>
+    <row r="261" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="18"/>
       <c r="E261" s="17"/>
-      <c r="BO261" s="21"/>
-      <c r="BR261" s="21"/>
-    </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN261" s="21"/>
+      <c r="BQ261" s="21"/>
+    </row>
+    <row r="262" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="18"/>
       <c r="E262" s="17"/>
-      <c r="BO262" s="21"/>
-      <c r="BR262" s="21"/>
-    </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN262" s="21"/>
+      <c r="BQ262" s="21"/>
+    </row>
+    <row r="263" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="18"/>
       <c r="E263" s="17"/>
-      <c r="BO263" s="21"/>
-      <c r="BR263" s="21"/>
-    </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN263" s="21"/>
+      <c r="BQ263" s="21"/>
+    </row>
+    <row r="264" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="18"/>
       <c r="E264" s="17"/>
-      <c r="BO264" s="21"/>
-      <c r="BR264" s="21"/>
-    </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN264" s="21"/>
+      <c r="BQ264" s="21"/>
+    </row>
+    <row r="265" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="18"/>
       <c r="E265" s="17"/>
-      <c r="BO265" s="21"/>
-      <c r="BR265" s="21"/>
-    </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN265" s="21"/>
+      <c r="BQ265" s="21"/>
+    </row>
+    <row r="266" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="18"/>
       <c r="E266" s="17"/>
-      <c r="BO266" s="21"/>
-      <c r="BR266" s="21"/>
-    </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN266" s="21"/>
+      <c r="BQ266" s="21"/>
+    </row>
+    <row r="267" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="18"/>
       <c r="E267" s="17"/>
-      <c r="BO267" s="21"/>
-      <c r="BR267" s="21"/>
-    </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN267" s="21"/>
+      <c r="BQ267" s="21"/>
+    </row>
+    <row r="268" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="18"/>
       <c r="E268" s="17"/>
-      <c r="BO268" s="21"/>
-      <c r="BR268" s="21"/>
-    </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN268" s="21"/>
+      <c r="BQ268" s="21"/>
+    </row>
+    <row r="269" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="18"/>
       <c r="E269" s="17"/>
-      <c r="BO269" s="21"/>
-      <c r="BR269" s="21"/>
-    </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN269" s="21"/>
+      <c r="BQ269" s="21"/>
+    </row>
+    <row r="270" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="18"/>
       <c r="E270" s="17"/>
-      <c r="BO270" s="21"/>
-      <c r="BR270" s="21"/>
-    </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN270" s="21"/>
+      <c r="BQ270" s="21"/>
+    </row>
+    <row r="271" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="18"/>
       <c r="E271" s="17"/>
-      <c r="BO271" s="21"/>
-      <c r="BR271" s="21"/>
-    </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN271" s="21"/>
+      <c r="BQ271" s="21"/>
+    </row>
+    <row r="272" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="18"/>
       <c r="E272" s="17"/>
-      <c r="BO272" s="21"/>
-      <c r="BR272" s="21"/>
-    </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN272" s="21"/>
+      <c r="BQ272" s="21"/>
+    </row>
+    <row r="273" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="18"/>
       <c r="E273" s="17"/>
-      <c r="BO273" s="21"/>
-      <c r="BR273" s="21"/>
-    </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN273" s="21"/>
+      <c r="BQ273" s="21"/>
+    </row>
+    <row r="274" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="18"/>
       <c r="E274" s="17"/>
-      <c r="BO274" s="21"/>
-      <c r="BR274" s="21"/>
-    </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN274" s="21"/>
+      <c r="BQ274" s="21"/>
+    </row>
+    <row r="275" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="18"/>
       <c r="E275" s="17"/>
-      <c r="BO275" s="21"/>
-      <c r="BR275" s="21"/>
-    </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN275" s="21"/>
+      <c r="BQ275" s="21"/>
+    </row>
+    <row r="276" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="18"/>
       <c r="E276" s="17"/>
-      <c r="BO276" s="21"/>
-      <c r="BR276" s="21"/>
-    </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN276" s="21"/>
+      <c r="BQ276" s="21"/>
+    </row>
+    <row r="277" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="18"/>
       <c r="E277" s="17"/>
-      <c r="BO277" s="21"/>
-      <c r="BR277" s="21"/>
-    </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN277" s="21"/>
+      <c r="BQ277" s="21"/>
+    </row>
+    <row r="278" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="18"/>
       <c r="E278" s="17"/>
-      <c r="BO278" s="21"/>
-      <c r="BR278" s="21"/>
-    </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN278" s="21"/>
+      <c r="BQ278" s="21"/>
+    </row>
+    <row r="279" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="18"/>
       <c r="E279" s="17"/>
-      <c r="BO279" s="21"/>
-      <c r="BR279" s="21"/>
-    </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN279" s="21"/>
+      <c r="BQ279" s="21"/>
+    </row>
+    <row r="280" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="18"/>
       <c r="E280" s="17"/>
-      <c r="BO280" s="21"/>
-      <c r="BR280" s="21"/>
-    </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN280" s="21"/>
+      <c r="BQ280" s="21"/>
+    </row>
+    <row r="281" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="18"/>
       <c r="E281" s="17"/>
-      <c r="BO281" s="21"/>
-      <c r="BR281" s="21"/>
-    </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN281" s="21"/>
+      <c r="BQ281" s="21"/>
+    </row>
+    <row r="282" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="18"/>
       <c r="E282" s="17"/>
-      <c r="BO282" s="21"/>
-      <c r="BR282" s="21"/>
-    </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN282" s="21"/>
+      <c r="BQ282" s="21"/>
+    </row>
+    <row r="283" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="18"/>
       <c r="E283" s="17"/>
-      <c r="BO283" s="21"/>
-      <c r="BR283" s="21"/>
-    </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN283" s="21"/>
+      <c r="BQ283" s="21"/>
+    </row>
+    <row r="284" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="18"/>
       <c r="E284" s="17"/>
-      <c r="BO284" s="21"/>
-      <c r="BR284" s="21"/>
-    </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN284" s="21"/>
+      <c r="BQ284" s="21"/>
+    </row>
+    <row r="285" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="18"/>
       <c r="E285" s="17"/>
-      <c r="BO285" s="21"/>
-      <c r="BR285" s="21"/>
-    </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN285" s="21"/>
+      <c r="BQ285" s="21"/>
+    </row>
+    <row r="286" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="18"/>
       <c r="E286" s="17"/>
-      <c r="BR286" s="21"/>
-    </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ286" s="21"/>
+    </row>
+    <row r="287" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="18"/>
       <c r="E287" s="17"/>
-      <c r="BO287" s="21"/>
-      <c r="BR287" s="21"/>
-    </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN287" s="21"/>
+      <c r="BQ287" s="21"/>
+    </row>
+    <row r="288" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="18"/>
       <c r="E288" s="17"/>
-      <c r="BO288" s="21"/>
-      <c r="BR288" s="21"/>
-    </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN288" s="21"/>
+      <c r="BQ288" s="21"/>
+    </row>
+    <row r="289" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="18"/>
       <c r="E289" s="17"/>
-      <c r="BO289" s="21"/>
-      <c r="BR289" s="21"/>
-    </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN289" s="21"/>
+      <c r="BQ289" s="21"/>
+    </row>
+    <row r="290" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="18"/>
       <c r="E290" s="17"/>
-      <c r="BO290" s="21"/>
-      <c r="BR290" s="21"/>
-    </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN290" s="21"/>
+      <c r="BQ290" s="21"/>
+    </row>
+    <row r="291" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="18"/>
       <c r="E291" s="17"/>
-      <c r="BO291" s="21"/>
-      <c r="BR291" s="21"/>
-    </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN291" s="21"/>
+      <c r="BQ291" s="21"/>
+    </row>
+    <row r="292" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="18"/>
       <c r="E292" s="17"/>
-      <c r="BO292" s="21"/>
-      <c r="BR292" s="21"/>
-    </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN292" s="21"/>
+      <c r="BQ292" s="21"/>
+    </row>
+    <row r="293" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="18"/>
       <c r="E293" s="17"/>
-      <c r="BO293" s="21"/>
-      <c r="BR293" s="21"/>
-    </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN293" s="21"/>
+      <c r="BQ293" s="21"/>
+    </row>
+    <row r="294" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="18"/>
       <c r="E294" s="17"/>
-      <c r="BO294" s="21"/>
-      <c r="BR294" s="21"/>
-    </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN294" s="21"/>
+      <c r="BQ294" s="21"/>
+    </row>
+    <row r="295" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="18"/>
       <c r="E295" s="17"/>
-      <c r="BO295" s="21"/>
-      <c r="BR295" s="21"/>
-    </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN295" s="21"/>
+      <c r="BQ295" s="21"/>
+    </row>
+    <row r="296" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="18"/>
       <c r="E296" s="17"/>
-      <c r="BO296" s="21"/>
-      <c r="BR296" s="21"/>
-    </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN296" s="21"/>
+      <c r="BQ296" s="21"/>
+    </row>
+    <row r="297" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="18"/>
       <c r="E297" s="17"/>
-      <c r="BO297" s="21"/>
-      <c r="BR297" s="21"/>
-    </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN297" s="21"/>
+      <c r="BQ297" s="21"/>
+    </row>
+    <row r="298" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="18"/>
       <c r="E298" s="17"/>
-      <c r="BO298" s="21"/>
-      <c r="BR298" s="21"/>
-    </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN298" s="21"/>
+      <c r="BQ298" s="21"/>
+    </row>
+    <row r="299" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="18"/>
       <c r="E299" s="17"/>
-      <c r="BO299" s="21"/>
-      <c r="BR299" s="21"/>
-    </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN299" s="21"/>
+      <c r="BQ299" s="21"/>
+    </row>
+    <row r="300" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="18"/>
       <c r="E300" s="17"/>
-      <c r="BO300" s="21"/>
-      <c r="BR300" s="21"/>
-    </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN300" s="21"/>
+      <c r="BQ300" s="21"/>
+    </row>
+    <row r="301" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="18"/>
       <c r="E301" s="17"/>
-      <c r="BO301" s="21"/>
-      <c r="BR301" s="21"/>
-    </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN301" s="21"/>
+      <c r="BQ301" s="21"/>
+    </row>
+    <row r="302" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="18"/>
       <c r="E302" s="17"/>
-      <c r="BO302" s="21"/>
-      <c r="BR302" s="21"/>
-    </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN302" s="21"/>
+      <c r="BQ302" s="21"/>
+    </row>
+    <row r="303" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="18"/>
       <c r="E303" s="17"/>
-      <c r="BO303" s="21"/>
-      <c r="BR303" s="21"/>
-    </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN303" s="21"/>
+      <c r="BQ303" s="21"/>
+    </row>
+    <row r="304" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="18"/>
       <c r="E304" s="17"/>
-      <c r="BO304" s="21"/>
-      <c r="BR304" s="21"/>
-    </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN304" s="21"/>
+      <c r="BQ304" s="21"/>
+    </row>
+    <row r="305" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="18"/>
       <c r="E305" s="17"/>
-      <c r="BO305" s="21"/>
-      <c r="BR305" s="21"/>
-    </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN305" s="21"/>
+      <c r="BQ305" s="21"/>
+    </row>
+    <row r="306" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="18"/>
       <c r="E306" s="17"/>
-      <c r="BO306" s="21"/>
-      <c r="BR306" s="21"/>
-    </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN306" s="21"/>
+      <c r="BQ306" s="21"/>
+    </row>
+    <row r="307" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="18"/>
       <c r="E307" s="17"/>
-      <c r="BO307" s="21"/>
-      <c r="BR307" s="21"/>
-    </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN307" s="21"/>
+      <c r="BQ307" s="21"/>
+    </row>
+    <row r="308" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="18"/>
       <c r="E308" s="17"/>
-      <c r="BO308" s="21"/>
-      <c r="BR308" s="21"/>
-    </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN308" s="21"/>
+      <c r="BQ308" s="21"/>
+    </row>
+    <row r="309" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="18"/>
       <c r="E309" s="17"/>
-      <c r="BO309" s="21"/>
-      <c r="BR309" s="21"/>
-    </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN309" s="21"/>
+      <c r="BQ309" s="21"/>
+    </row>
+    <row r="310" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="18"/>
       <c r="E310" s="17"/>
-      <c r="BO310" s="21"/>
-      <c r="BR310" s="21"/>
-    </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN310" s="21"/>
+      <c r="BQ310" s="21"/>
+    </row>
+    <row r="311" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="18"/>
       <c r="E311" s="17"/>
-      <c r="BO311" s="21"/>
-      <c r="BR311" s="21"/>
-    </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN311" s="21"/>
+      <c r="BQ311" s="21"/>
+    </row>
+    <row r="312" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="18"/>
       <c r="E312" s="17"/>
-      <c r="BO312" s="21"/>
-      <c r="BR312" s="21"/>
-    </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN312" s="21"/>
+      <c r="BQ312" s="21"/>
+    </row>
+    <row r="313" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="18"/>
       <c r="E313" s="17"/>
-      <c r="BO313" s="21"/>
-      <c r="BR313" s="21"/>
-    </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN313" s="21"/>
+      <c r="BQ313" s="21"/>
+    </row>
+    <row r="314" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="18"/>
       <c r="E314" s="17"/>
-      <c r="BO314" s="21"/>
-      <c r="BR314" s="21"/>
-    </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN314" s="21"/>
+      <c r="BQ314" s="21"/>
+    </row>
+    <row r="315" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="18"/>
       <c r="E315" s="17"/>
-      <c r="BO315" s="21"/>
-      <c r="BR315" s="21"/>
-    </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN315" s="21"/>
+      <c r="BQ315" s="21"/>
+    </row>
+    <row r="316" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="18"/>
       <c r="E316" s="17"/>
-      <c r="BO316" s="21"/>
-      <c r="BR316" s="21"/>
-    </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN316" s="21"/>
+      <c r="BQ316" s="21"/>
+    </row>
+    <row r="317" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="18"/>
       <c r="E317" s="17"/>
-      <c r="BO317" s="21"/>
-      <c r="BR317" s="21"/>
-    </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN317" s="21"/>
+      <c r="BQ317" s="21"/>
+    </row>
+    <row r="318" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="18"/>
       <c r="E318" s="17"/>
-      <c r="BO318" s="21"/>
-      <c r="BR318" s="21"/>
-    </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN318" s="21"/>
+      <c r="BQ318" s="21"/>
+    </row>
+    <row r="319" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="18"/>
       <c r="E319" s="17"/>
-      <c r="BO319" s="21"/>
-      <c r="BR319" s="21"/>
-    </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN319" s="21"/>
+      <c r="BQ319" s="21"/>
+    </row>
+    <row r="320" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="18"/>
       <c r="E320" s="17"/>
-      <c r="BO320" s="21"/>
-      <c r="BR320" s="21"/>
-    </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN320" s="21"/>
+      <c r="BQ320" s="21"/>
+    </row>
+    <row r="321" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="18"/>
       <c r="E321" s="17"/>
-      <c r="BO321" s="21"/>
-      <c r="BR321" s="21"/>
-    </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN321" s="21"/>
+      <c r="BQ321" s="21"/>
+    </row>
+    <row r="322" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="18"/>
       <c r="E322" s="17"/>
-      <c r="BO322" s="21"/>
-      <c r="BR322" s="21"/>
-    </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN322" s="21"/>
+      <c r="BQ322" s="21"/>
+    </row>
+    <row r="323" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="18"/>
       <c r="E323" s="17"/>
-      <c r="BO323" s="21"/>
-      <c r="BR323" s="21"/>
-    </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN323" s="21"/>
+      <c r="BQ323" s="21"/>
+    </row>
+    <row r="324" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="18"/>
       <c r="E324" s="17"/>
-      <c r="BO324" s="21"/>
-      <c r="BR324" s="21"/>
-    </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN324" s="21"/>
+      <c r="BQ324" s="21"/>
+    </row>
+    <row r="325" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="18"/>
       <c r="E325" s="17"/>
-      <c r="BO325" s="21"/>
-      <c r="BR325" s="21"/>
-    </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN325" s="21"/>
+      <c r="BQ325" s="21"/>
+    </row>
+    <row r="326" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="18"/>
       <c r="E326" s="17"/>
-      <c r="BO326" s="21"/>
-      <c r="BR326" s="21"/>
-    </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN326" s="21"/>
+      <c r="BQ326" s="21"/>
+    </row>
+    <row r="327" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="18"/>
       <c r="E327" s="17"/>
-      <c r="BO327" s="21"/>
-      <c r="BR327" s="21"/>
-    </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN327" s="21"/>
+      <c r="BQ327" s="21"/>
+    </row>
+    <row r="328" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="18"/>
       <c r="E328" s="17"/>
-      <c r="BO328" s="21"/>
-      <c r="BR328" s="21"/>
-    </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN328" s="21"/>
+      <c r="BQ328" s="21"/>
+    </row>
+    <row r="329" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="18"/>
       <c r="E329" s="17"/>
-      <c r="BO329" s="21"/>
-      <c r="BR329" s="21"/>
-    </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN329" s="21"/>
+      <c r="BQ329" s="21"/>
+    </row>
+    <row r="330" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="18"/>
       <c r="E330" s="17"/>
-      <c r="BO330" s="21"/>
-      <c r="BR330" s="21"/>
-    </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN330" s="21"/>
+      <c r="BQ330" s="21"/>
+    </row>
+    <row r="331" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="18"/>
       <c r="E331" s="17"/>
-      <c r="BO331" s="21"/>
-      <c r="BR331" s="21"/>
-    </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN331" s="21"/>
+      <c r="BQ331" s="21"/>
+    </row>
+    <row r="332" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="18"/>
       <c r="E332" s="17"/>
-      <c r="BO332" s="21"/>
-      <c r="BR332" s="21"/>
-    </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN332" s="21"/>
+      <c r="BQ332" s="21"/>
+    </row>
+    <row r="333" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="18"/>
       <c r="E333" s="17"/>
-      <c r="BO333" s="21"/>
-      <c r="BR333" s="21"/>
-    </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN333" s="21"/>
+      <c r="BQ333" s="21"/>
+    </row>
+    <row r="334" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="18"/>
       <c r="E334" s="17"/>
-      <c r="BO334" s="21"/>
-      <c r="BR334" s="21"/>
-    </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN334" s="21"/>
+      <c r="BQ334" s="21"/>
+    </row>
+    <row r="335" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="18"/>
       <c r="E335" s="17"/>
-      <c r="BO335" s="21"/>
-      <c r="BR335" s="21"/>
-    </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN335" s="21"/>
+      <c r="BQ335" s="21"/>
+    </row>
+    <row r="336" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="18"/>
       <c r="E336" s="17"/>
-      <c r="BO336" s="21"/>
-      <c r="BR336" s="21"/>
-    </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN336" s="21"/>
+      <c r="BQ336" s="21"/>
+    </row>
+    <row r="337" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="18"/>
       <c r="E337" s="17"/>
-      <c r="BO337" s="21"/>
-      <c r="BR337" s="21"/>
-    </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN337" s="21"/>
+      <c r="BQ337" s="21"/>
+    </row>
+    <row r="338" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="18"/>
       <c r="E338" s="17"/>
-      <c r="BO338" s="21"/>
-      <c r="BR338" s="21"/>
-    </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN338" s="21"/>
+      <c r="BQ338" s="21"/>
+    </row>
+    <row r="339" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="18"/>
       <c r="E339" s="17"/>
-      <c r="BO339" s="21"/>
-      <c r="BR339" s="21"/>
-    </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN339" s="21"/>
+      <c r="BQ339" s="21"/>
+    </row>
+    <row r="340" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="18"/>
       <c r="E340" s="17"/>
-      <c r="BO340" s="21"/>
-      <c r="BR340" s="21"/>
-    </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN340" s="21"/>
+      <c r="BQ340" s="21"/>
+    </row>
+    <row r="341" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="18"/>
       <c r="E341" s="17"/>
-      <c r="BO341" s="21"/>
-      <c r="BR341" s="21"/>
-    </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN341" s="21"/>
+      <c r="BQ341" s="21"/>
+    </row>
+    <row r="342" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="18"/>
       <c r="E342" s="17"/>
-      <c r="BR342" s="21"/>
-    </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ342" s="21"/>
+    </row>
+    <row r="343" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="18"/>
       <c r="E343" s="17"/>
-      <c r="BR343" s="21"/>
-    </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ343" s="21"/>
+    </row>
+    <row r="344" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="18"/>
       <c r="E344" s="17"/>
-      <c r="BR344" s="21"/>
-    </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ344" s="21"/>
+    </row>
+    <row r="345" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="18"/>
       <c r="E345" s="17"/>
-      <c r="BO345" s="21"/>
-      <c r="BR345" s="21"/>
-    </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN345" s="21"/>
+      <c r="BQ345" s="21"/>
+    </row>
+    <row r="346" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="18"/>
       <c r="E346" s="17"/>
-      <c r="BO346" s="21"/>
-      <c r="BR346" s="21"/>
-    </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN346" s="21"/>
+      <c r="BQ346" s="21"/>
+    </row>
+    <row r="347" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="18"/>
       <c r="E347" s="17"/>
-      <c r="BO347" s="21"/>
-      <c r="BR347" s="21"/>
-    </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN347" s="21"/>
+      <c r="BQ347" s="21"/>
+    </row>
+    <row r="348" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="18"/>
       <c r="E348" s="17"/>
-      <c r="BO348" s="21"/>
-      <c r="BR348" s="21"/>
-    </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN348" s="21"/>
+      <c r="BQ348" s="21"/>
+    </row>
+    <row r="349" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="18"/>
       <c r="E349" s="17"/>
-      <c r="BO349" s="21"/>
-      <c r="BR349" s="21"/>
-    </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN349" s="21"/>
+      <c r="BQ349" s="21"/>
+    </row>
+    <row r="350" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="18"/>
       <c r="E350" s="17"/>
-      <c r="BO350" s="21"/>
-      <c r="BR350" s="21"/>
-    </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN350" s="21"/>
+      <c r="BQ350" s="21"/>
+    </row>
+    <row r="351" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="18"/>
       <c r="E351" s="17"/>
-      <c r="BO351" s="21"/>
-      <c r="BR351" s="21"/>
-    </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN351" s="21"/>
+      <c r="BQ351" s="21"/>
+    </row>
+    <row r="352" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="18"/>
       <c r="E352" s="17"/>
-      <c r="BO352" s="21"/>
-      <c r="BR352" s="21"/>
-    </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN352" s="21"/>
+      <c r="BQ352" s="21"/>
+    </row>
+    <row r="353" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="18"/>
       <c r="E353" s="17"/>
-      <c r="BO353" s="21"/>
-      <c r="BR353" s="21"/>
-    </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN353" s="21"/>
+      <c r="BQ353" s="21"/>
+    </row>
+    <row r="354" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="18"/>
       <c r="E354" s="17"/>
-      <c r="BO354" s="21"/>
-      <c r="BR354" s="21"/>
-    </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN354" s="21"/>
+      <c r="BQ354" s="21"/>
+    </row>
+    <row r="355" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="18"/>
       <c r="E355" s="17"/>
-      <c r="BO355" s="21"/>
-      <c r="BR355" s="21"/>
-    </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN355" s="21"/>
+      <c r="BQ355" s="21"/>
+    </row>
+    <row r="356" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="18"/>
       <c r="E356" s="17"/>
-      <c r="BO356" s="21"/>
-      <c r="BR356" s="21"/>
-    </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN356" s="21"/>
+      <c r="BQ356" s="21"/>
+    </row>
+    <row r="357" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="18"/>
       <c r="E357" s="17"/>
-      <c r="BO357" s="21"/>
-      <c r="BR357" s="21"/>
-    </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN357" s="21"/>
+      <c r="BQ357" s="21"/>
+    </row>
+    <row r="358" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="18"/>
       <c r="E358" s="17"/>
-      <c r="BO358" s="21"/>
-      <c r="BR358" s="21"/>
-    </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN358" s="21"/>
+      <c r="BQ358" s="21"/>
+    </row>
+    <row r="359" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="18"/>
       <c r="E359" s="17"/>
-      <c r="BO359" s="21"/>
-      <c r="BR359" s="21"/>
-    </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN359" s="21"/>
+      <c r="BQ359" s="21"/>
+    </row>
+    <row r="360" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="18"/>
       <c r="E360" s="17"/>
-      <c r="BO360" s="21"/>
-      <c r="BR360" s="21"/>
-    </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN360" s="21"/>
+      <c r="BQ360" s="21"/>
+    </row>
+    <row r="361" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="18"/>
       <c r="E361" s="17"/>
-      <c r="BO361" s="21"/>
-      <c r="BR361" s="21"/>
-    </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN361" s="21"/>
+      <c r="BQ361" s="21"/>
+    </row>
+    <row r="362" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="18"/>
       <c r="E362" s="17"/>
-      <c r="BO362" s="21"/>
-      <c r="BR362" s="21"/>
-    </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN362" s="21"/>
+      <c r="BQ362" s="21"/>
+    </row>
+    <row r="363" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="18"/>
       <c r="E363" s="17"/>
-      <c r="BO363" s="21"/>
-      <c r="BR363" s="21"/>
-    </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN363" s="21"/>
+      <c r="BQ363" s="21"/>
+    </row>
+    <row r="364" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="18"/>
       <c r="E364" s="17"/>
-      <c r="BO364" s="21"/>
-      <c r="BR364" s="21"/>
-    </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN364" s="21"/>
+      <c r="BQ364" s="21"/>
+    </row>
+    <row r="365" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="18"/>
       <c r="E365" s="17"/>
-      <c r="BO365" s="21"/>
-      <c r="BR365" s="21"/>
-    </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN365" s="21"/>
+      <c r="BQ365" s="21"/>
+    </row>
+    <row r="366" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="18"/>
       <c r="E366" s="17"/>
-      <c r="BO366" s="21"/>
-      <c r="BR366" s="21"/>
-    </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN366" s="21"/>
+      <c r="BQ366" s="21"/>
+    </row>
+    <row r="367" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="18"/>
       <c r="E367" s="17"/>
-      <c r="BO367" s="21"/>
-      <c r="BR367" s="21"/>
-    </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN367" s="21"/>
+      <c r="BQ367" s="21"/>
+    </row>
+    <row r="368" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="18"/>
       <c r="E368" s="17"/>
-      <c r="BO368" s="21"/>
-      <c r="BR368" s="21"/>
-    </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN368" s="21"/>
+      <c r="BQ368" s="21"/>
+    </row>
+    <row r="369" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="18"/>
       <c r="E369" s="17"/>
-      <c r="BO369" s="21"/>
-      <c r="BR369" s="21"/>
-    </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN369" s="21"/>
+      <c r="BQ369" s="21"/>
+    </row>
+    <row r="370" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="18"/>
       <c r="E370" s="17"/>
-      <c r="BO370" s="21"/>
-      <c r="BR370" s="21"/>
-    </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN370" s="21"/>
+      <c r="BQ370" s="21"/>
+    </row>
+    <row r="371" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="18"/>
       <c r="E371" s="17"/>
-      <c r="BO371" s="21"/>
-      <c r="BR371" s="21"/>
-    </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN371" s="21"/>
+      <c r="BQ371" s="21"/>
+    </row>
+    <row r="372" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="18"/>
       <c r="E372" s="17"/>
-      <c r="BO372" s="21"/>
-      <c r="BR372" s="21"/>
-    </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN372" s="21"/>
+      <c r="BQ372" s="21"/>
+    </row>
+    <row r="373" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="18"/>
       <c r="E373" s="17"/>
-      <c r="BO373" s="21"/>
-      <c r="BR373" s="21"/>
-    </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN373" s="21"/>
+      <c r="BQ373" s="21"/>
+    </row>
+    <row r="374" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="18"/>
       <c r="E374" s="17"/>
-      <c r="BO374" s="21"/>
-      <c r="BR374" s="21"/>
-    </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN374" s="21"/>
+      <c r="BQ374" s="21"/>
+    </row>
+    <row r="375" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="18"/>
       <c r="E375" s="17"/>
-      <c r="BO375" s="21"/>
-      <c r="BR375" s="21"/>
-    </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN375" s="21"/>
+      <c r="BQ375" s="21"/>
+    </row>
+    <row r="376" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="18"/>
       <c r="E376" s="17"/>
-      <c r="BO376" s="21"/>
-      <c r="BR376" s="21"/>
-    </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN376" s="21"/>
+      <c r="BQ376" s="21"/>
+    </row>
+    <row r="377" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="18"/>
       <c r="E377" s="17"/>
-      <c r="BO377" s="21"/>
-      <c r="BR377" s="21"/>
-    </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN377" s="21"/>
+      <c r="BQ377" s="21"/>
+    </row>
+    <row r="378" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="18"/>
       <c r="E378" s="17"/>
-      <c r="BO378" s="21"/>
-      <c r="BR378" s="21"/>
-    </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN378" s="21"/>
+      <c r="BQ378" s="21"/>
+    </row>
+    <row r="379" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="18"/>
       <c r="E379" s="17"/>
-      <c r="BR379" s="21"/>
-    </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ379" s="21"/>
+    </row>
+    <row r="380" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="18"/>
       <c r="E380" s="17"/>
-      <c r="BR380" s="21"/>
-    </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ380" s="21"/>
+    </row>
+    <row r="381" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="18"/>
       <c r="E381" s="17"/>
-      <c r="BO381" s="21"/>
-      <c r="BR381" s="21"/>
-    </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN381" s="21"/>
+      <c r="BQ381" s="21"/>
+    </row>
+    <row r="382" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="18"/>
       <c r="E382" s="17"/>
-      <c r="BO382" s="21"/>
-      <c r="BR382" s="21"/>
-    </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN382" s="21"/>
+      <c r="BQ382" s="21"/>
+    </row>
+    <row r="383" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="18"/>
       <c r="E383" s="17"/>
-      <c r="BO383" s="21"/>
-      <c r="BR383" s="21"/>
-    </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN383" s="21"/>
+      <c r="BQ383" s="21"/>
+    </row>
+    <row r="384" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="18"/>
       <c r="E384" s="17"/>
-      <c r="BO384" s="21"/>
-      <c r="BR384" s="21"/>
-    </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN384" s="21"/>
+      <c r="BQ384" s="21"/>
+    </row>
+    <row r="385" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="18"/>
       <c r="E385" s="17"/>
-      <c r="BO385" s="21"/>
-      <c r="BR385" s="21"/>
-    </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN385" s="21"/>
+      <c r="BQ385" s="21"/>
+    </row>
+    <row r="386" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="18"/>
       <c r="E386" s="17"/>
-      <c r="BO386" s="21"/>
-      <c r="BR386" s="21"/>
-    </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN386" s="21"/>
+      <c r="BQ386" s="21"/>
+    </row>
+    <row r="387" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="18"/>
       <c r="E387" s="17"/>
-      <c r="BO387" s="21"/>
-      <c r="BR387" s="21"/>
-    </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN387" s="21"/>
+      <c r="BQ387" s="21"/>
+    </row>
+    <row r="388" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="18"/>
       <c r="E388" s="17"/>
-      <c r="BO388" s="21"/>
-      <c r="BR388" s="21"/>
-    </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN388" s="21"/>
+      <c r="BQ388" s="21"/>
+    </row>
+    <row r="389" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="18"/>
       <c r="E389" s="17"/>
-      <c r="BO389" s="21"/>
-      <c r="BR389" s="21"/>
-    </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN389" s="21"/>
+      <c r="BQ389" s="21"/>
+    </row>
+    <row r="390" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="18"/>
       <c r="E390" s="17"/>
-      <c r="BO390" s="21"/>
-      <c r="BR390" s="21"/>
-    </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN390" s="21"/>
+      <c r="BQ390" s="21"/>
+    </row>
+    <row r="391" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="18"/>
       <c r="E391" s="17"/>
-      <c r="BO391" s="21"/>
-      <c r="BR391" s="21"/>
-    </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN391" s="21"/>
+      <c r="BQ391" s="21"/>
+    </row>
+    <row r="392" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="18"/>
       <c r="E392" s="17"/>
-      <c r="BO392" s="21"/>
-      <c r="BR392" s="21"/>
-    </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN392" s="21"/>
+      <c r="BQ392" s="21"/>
+    </row>
+    <row r="393" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="18"/>
       <c r="E393" s="17"/>
-      <c r="BO393" s="21"/>
-      <c r="BR393" s="21"/>
-    </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN393" s="21"/>
+      <c r="BQ393" s="21"/>
+    </row>
+    <row r="394" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="18"/>
       <c r="E394" s="17"/>
-      <c r="BO394" s="21"/>
-      <c r="BR394" s="21"/>
-    </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN394" s="21"/>
+      <c r="BQ394" s="21"/>
+    </row>
+    <row r="395" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="18"/>
       <c r="E395" s="17"/>
-      <c r="BO395" s="21"/>
-      <c r="BR395" s="21"/>
-    </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN395" s="21"/>
+      <c r="BQ395" s="21"/>
+    </row>
+    <row r="396" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="18"/>
       <c r="E396" s="17"/>
-      <c r="BO396" s="21"/>
-      <c r="BR396" s="21"/>
-    </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN396" s="21"/>
+      <c r="BQ396" s="21"/>
+    </row>
+    <row r="397" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="18"/>
       <c r="E397" s="17"/>
-      <c r="BO397" s="21"/>
-      <c r="BR397" s="21"/>
-    </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN397" s="21"/>
+      <c r="BQ397" s="21"/>
+    </row>
+    <row r="398" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="18"/>
       <c r="E398" s="17"/>
-      <c r="BO398" s="21"/>
-      <c r="BR398" s="21"/>
-    </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN398" s="21"/>
+      <c r="BQ398" s="21"/>
+    </row>
+    <row r="399" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="18"/>
       <c r="E399" s="17"/>
-      <c r="BO399" s="21"/>
-      <c r="BR399" s="21"/>
-    </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN399" s="21"/>
+      <c r="BQ399" s="21"/>
+    </row>
+    <row r="400" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="18"/>
       <c r="E400" s="17"/>
-      <c r="BO400" s="21"/>
-      <c r="BR400" s="21"/>
-    </row>
-    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN400" s="21"/>
+      <c r="BQ400" s="21"/>
+    </row>
+    <row r="401" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="18"/>
       <c r="E401" s="17"/>
-      <c r="BO401" s="21"/>
-      <c r="BR401" s="21"/>
-    </row>
-    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN401" s="21"/>
+      <c r="BQ401" s="21"/>
+    </row>
+    <row r="402" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="18"/>
       <c r="E402" s="17"/>
-      <c r="BO402" s="21"/>
-      <c r="BR402" s="21"/>
-    </row>
-    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN402" s="21"/>
+      <c r="BQ402" s="21"/>
+    </row>
+    <row r="403" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="18"/>
       <c r="E403" s="17"/>
-      <c r="BO403" s="21"/>
-      <c r="BR403" s="21"/>
-    </row>
-    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN403" s="21"/>
+      <c r="BQ403" s="21"/>
+    </row>
+    <row r="404" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="18"/>
       <c r="E404" s="17"/>
-      <c r="BR404" s="21"/>
-    </row>
-    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ404" s="21"/>
+    </row>
+    <row r="405" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="18"/>
       <c r="E405" s="17"/>
-      <c r="BR405" s="21"/>
-    </row>
-    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ405" s="21"/>
+    </row>
+    <row r="406" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="18"/>
       <c r="E406" s="17"/>
-      <c r="BO406" s="21"/>
-      <c r="BR406" s="21"/>
-    </row>
-    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN406" s="21"/>
+      <c r="BQ406" s="21"/>
+    </row>
+    <row r="407" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="18"/>
       <c r="E407" s="17"/>
-      <c r="BO407" s="21"/>
-      <c r="BR407" s="21"/>
-    </row>
-    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN407" s="21"/>
+      <c r="BQ407" s="21"/>
+    </row>
+    <row r="408" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="18"/>
       <c r="E408" s="17"/>
-      <c r="BR408" s="21"/>
-    </row>
-    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ408" s="21"/>
+    </row>
+    <row r="409" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="18"/>
       <c r="E409" s="17"/>
-      <c r="BR409" s="21"/>
-    </row>
-    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ409" s="21"/>
+    </row>
+    <row r="410" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D410" s="18"/>
       <c r="E410" s="17"/>
-      <c r="BO410" s="21"/>
-      <c r="BR410" s="21"/>
-    </row>
-    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN410" s="21"/>
+      <c r="BQ410" s="21"/>
+    </row>
+    <row r="411" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D411" s="18"/>
       <c r="E411" s="17"/>
-      <c r="BO411" s="21"/>
-      <c r="BR411" s="21"/>
-    </row>
-    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN411" s="21"/>
+      <c r="BQ411" s="21"/>
+    </row>
+    <row r="412" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D412" s="18"/>
       <c r="E412" s="17"/>
-      <c r="BO412" s="21"/>
-      <c r="BR412" s="21"/>
-    </row>
-    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN412" s="21"/>
+      <c r="BQ412" s="21"/>
+    </row>
+    <row r="413" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D413" s="18"/>
       <c r="E413" s="17"/>
-      <c r="BO413" s="21"/>
-      <c r="BR413" s="21"/>
-    </row>
-    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN413" s="21"/>
+      <c r="BQ413" s="21"/>
+    </row>
+    <row r="414" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D414" s="18"/>
       <c r="E414" s="17"/>
-      <c r="BO414" s="21"/>
-      <c r="BR414" s="21"/>
-    </row>
-    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN414" s="21"/>
+      <c r="BQ414" s="21"/>
+    </row>
+    <row r="415" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D415" s="18"/>
       <c r="E415" s="17"/>
-      <c r="BO415" s="21"/>
-      <c r="BR415" s="21"/>
-    </row>
-    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN415" s="21"/>
+      <c r="BQ415" s="21"/>
+    </row>
+    <row r="416" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D416" s="18"/>
       <c r="E416" s="17"/>
-      <c r="BO416" s="21"/>
-      <c r="BR416" s="21"/>
-    </row>
-    <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN416" s="21"/>
+      <c r="BQ416" s="21"/>
+    </row>
+    <row r="417" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D417" s="18"/>
       <c r="E417" s="17"/>
-      <c r="BO417" s="21"/>
-      <c r="BR417" s="21"/>
-    </row>
-    <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN417" s="21"/>
+      <c r="BQ417" s="21"/>
+    </row>
+    <row r="418" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D418" s="18"/>
       <c r="E418" s="17"/>
-      <c r="BO418" s="21"/>
-      <c r="BR418" s="21"/>
-    </row>
-    <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN418" s="21"/>
+      <c r="BQ418" s="21"/>
+    </row>
+    <row r="419" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D419" s="18"/>
       <c r="E419" s="17"/>
-      <c r="BO419" s="21"/>
-      <c r="BR419" s="21"/>
-    </row>
-    <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN419" s="21"/>
+      <c r="BQ419" s="21"/>
+    </row>
+    <row r="420" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D420" s="18"/>
       <c r="E420" s="17"/>
-      <c r="BO420" s="21"/>
-      <c r="BR420" s="21"/>
-    </row>
-    <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN420" s="21"/>
+      <c r="BQ420" s="21"/>
+    </row>
+    <row r="421" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D421" s="18"/>
       <c r="E421" s="17"/>
-      <c r="BO421" s="21"/>
-      <c r="BR421" s="21"/>
-    </row>
-    <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN421" s="21"/>
+      <c r="BQ421" s="21"/>
+    </row>
+    <row r="422" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D422" s="18"/>
       <c r="E422" s="17"/>
-      <c r="BO422" s="21"/>
-      <c r="BR422" s="21"/>
-    </row>
-    <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN422" s="21"/>
+      <c r="BQ422" s="21"/>
+    </row>
+    <row r="423" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D423" s="18"/>
       <c r="E423" s="17"/>
-      <c r="BO423" s="21"/>
-      <c r="BR423" s="21"/>
-    </row>
-    <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN423" s="21"/>
+      <c r="BQ423" s="21"/>
+    </row>
+    <row r="424" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D424" s="18"/>
       <c r="E424" s="17"/>
-      <c r="BO424" s="21"/>
-      <c r="BR424" s="21"/>
-    </row>
-    <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN424" s="21"/>
+      <c r="BQ424" s="21"/>
+    </row>
+    <row r="425" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D425" s="18"/>
       <c r="E425" s="17"/>
-      <c r="BO425" s="21"/>
-      <c r="BR425" s="21"/>
-    </row>
-    <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN425" s="21"/>
+      <c r="BQ425" s="21"/>
+    </row>
+    <row r="426" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D426" s="18"/>
       <c r="E426" s="17"/>
-      <c r="BO426" s="21"/>
-      <c r="BR426" s="21"/>
-    </row>
-    <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN426" s="21"/>
+      <c r="BQ426" s="21"/>
+    </row>
+    <row r="427" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D427" s="18"/>
       <c r="E427" s="17"/>
     </row>
-    <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D428" s="18"/>
       <c r="E428" s="17"/>
     </row>
-    <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D429" s="18"/>
       <c r="E429" s="17"/>
     </row>
-    <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D430" s="18"/>
       <c r="E430" s="17"/>
     </row>
-    <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D431" s="18"/>
       <c r="E431" s="17"/>
     </row>
-    <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D432" s="18"/>
       <c r="E432" s="17"/>
     </row>
@@ -5994,334 +5990,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" t="s">
         <v>140</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>142</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>143</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="U1" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="V1" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="Y1" t="s">
         <v>157</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="V1" s="5" t="s">
+      <c r="Z1" t="s">
         <v>158</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="AB1" t="s">
         <v>160</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>161</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>162</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AE1" t="s">
         <v>163</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>164</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>165</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>166</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AI1" t="s">
         <v>167</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>168</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>169</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AL1" t="s">
         <v>170</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AM1" t="s">
         <v>171</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AN1" t="s">
         <v>172</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AO1" t="s">
         <v>173</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AP1" t="s">
         <v>174</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AQ1" t="s">
         <v>175</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AR1" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="AT1" t="s">
         <v>176</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AU1" t="s">
         <v>177</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AV1" t="s">
         <v>178</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AW1" t="s">
         <v>179</v>
       </c>
-      <c r="AR1" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="AS1" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AX1" t="s">
         <v>180</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AY1" t="s">
         <v>181</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AZ1" t="s">
         <v>182</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BA1" t="s">
         <v>183</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BC1" t="s">
         <v>185</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BD1" t="s">
         <v>186</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BE1" t="s">
         <v>187</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>188</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BG1" t="s">
         <v>189</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BH1" t="s">
         <v>190</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BJ1" t="s">
+        <v>190</v>
+      </c>
+      <c r="BK1" t="s">
         <v>191</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BL1" t="s">
         <v>192</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BM1" t="s">
         <v>193</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BN1" t="s">
         <v>194</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>194</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BO1" t="s">
         <v>195</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BP1" t="s">
         <v>196</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BQ1" t="s">
         <v>197</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BR1" t="s">
         <v>198</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BS1" t="s">
         <v>199</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BT1" t="s">
         <v>200</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BV1" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BW1" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BX1" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BY1" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="CA1" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="CB1" t="s">
         <v>208</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="CC1" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="BZ1" s="6" t="s">
+      <c r="CD1" t="s">
         <v>210</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CE1" t="s">
         <v>211</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CF1" t="s">
         <v>212</v>
       </c>
-      <c r="CC1" s="6" t="s">
+      <c r="CG1" t="s">
         <v>213</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CH1" t="s">
         <v>214</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CI1" t="s">
         <v>215</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CJ1" t="s">
         <v>216</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CK1" t="s">
         <v>217</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CM1" t="s">
         <v>219</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CN1" t="s">
         <v>220</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CO1" t="s">
         <v>221</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CP1" t="s">
         <v>222</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CQ1" t="s">
         <v>223</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CR1" t="s">
+        <v>200</v>
+      </c>
+      <c r="CS1" t="s">
         <v>224</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CT1" t="s">
         <v>225</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CU1" t="s">
         <v>226</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CV1" t="s">
         <v>227</v>
       </c>
-      <c r="CR1" t="s">
-        <v>204</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CW1" t="s">
         <v>228</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CX1" t="s">
         <v>229</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CY1" t="s">
         <v>230</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CZ1" t="s">
+        <v>229</v>
+      </c>
+      <c r="DA1" t="s">
         <v>231</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DB1" t="s">
         <v>232</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DC1" t="s">
         <v>233</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DD1" t="s">
         <v>234</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>233</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DE1" t="s">
         <v>235</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DF1" t="s">
         <v>236</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DG1" t="s">
         <v>237</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DH1" t="s">
         <v>238</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DI1" t="s">
         <v>239</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>240</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>241</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>242</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6329,337 +6325,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>259</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>260</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>264</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>268</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>285</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>286</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>287</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>289</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>292</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>293</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>294</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>295</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>296</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BO2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="I2" t="s">
-        <v>247</v>
-      </c>
-      <c r="J2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>263</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>268</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>269</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>270</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>274</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>288</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>289</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>292</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>293</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>294</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>295</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>296</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>297</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BP2" t="s">
         <v>298</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BQ2" t="s">
         <v>299</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BR2" t="s">
         <v>300</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BS2" t="s">
         <v>301</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BT2" t="s">
         <v>302</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV2" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BW2" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BX2" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BY2" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="BU2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="CB2" t="s">
         <v>309</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="CC2" t="s">
         <v>310</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CD2" t="s">
         <v>311</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CE2" t="s">
         <v>312</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CF2" t="s">
         <v>313</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CG2" t="s">
         <v>314</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CH2" t="s">
         <v>315</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CI2" t="s">
         <v>316</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CJ2" t="s">
         <v>317</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CK2" t="s">
         <v>318</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CM2" t="s">
         <v>320</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CN2" t="s">
         <v>321</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CO2" t="s">
         <v>322</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CP2" t="s">
         <v>323</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CQ2" t="s">
         <v>324</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CR2" t="s">
         <v>325</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CS2" t="s">
         <v>326</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CT2" t="s">
         <v>327</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CU2" t="s">
         <v>328</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CV2" t="s">
         <v>329</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CW2" t="s">
         <v>330</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CX2" t="s">
         <v>331</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CY2" t="s">
         <v>332</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CZ2" t="s">
         <v>333</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="DA2" t="s">
         <v>334</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DB2" t="s">
         <v>335</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DC2" t="s">
         <v>336</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DD2" t="s">
         <v>337</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DE2" t="s">
         <v>338</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DF2" t="s">
         <v>339</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DG2" t="s">
         <v>340</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DH2" t="s">
         <v>341</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DI2" t="s">
         <v>342</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>343</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>344</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>345</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -6679,330 +6675,330 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>343</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="J3" t="s">
-        <v>347</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="M3" s="5" t="s">
+      <c r="P3" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>346</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI3" t="s">
         <v>118</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>350</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>122</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AM3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AN3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AO3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AP3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="AT3" t="s">
+        <v>349</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>350</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>349</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>351</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>352</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="BX3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="BY3" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="AU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
+      <c r="BZ3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA3" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CC3" t="s">
         <v>354</v>
       </c>
-      <c r="AY3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>353</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
+      <c r="CD3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG3" t="s">
         <v>355</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="CH3" t="s">
         <v>356</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="BX3" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY3" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="BZ3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA3" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>358</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>359</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>360</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="CK3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="CL3" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="CM3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CN3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CO3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CP3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CQ3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CR3" t="s">
+        <v>354</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CV3" t="s">
         <v>358</v>
       </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>362</v>
-      </c>
       <c r="CW3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="CX3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="CY3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="CZ3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="DA3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="DB3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="DC3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="DD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DE3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DF3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DG3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DH3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DI3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
@@ -7013,33 +7009,33 @@
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="H6" s="2"/>
       <c r="K6" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="P6"/>
       <c r="AC6">
         <v>4</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="AN6">
         <v>1</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AV6">
         <v>15</v>
       </c>
       <c r="AX6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -7051,38 +7047,38 @@
         <v>1</v>
       </c>
       <c r="CB6" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="CG6" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="CH6" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="CI6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="CL6" s="2"/>
       <c r="CM6" s="2"/>
       <c r="CN6" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="CY6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="O7"/>
       <c r="AC7">
@@ -7092,7 +7088,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AV7">
         <v>2.5</v>
@@ -7102,26 +7098,26 @@
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K8" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>376</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>380</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AG8" s="2"/>
       <c r="AO8" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AX8" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -7134,12 +7130,12 @@
       </c>
       <c r="CG8" s="2"/>
       <c r="CL8" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="CN8" s="2"/>
       <c r="CO8" s="2"/>
       <c r="CY8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
@@ -7155,22 +7151,22 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>462</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>466</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AO10" s="2"/>
       <c r="AX10" s="2"/>
@@ -7183,7 +7179,7 @@
       <c r="CG10" s="2"/>
       <c r="CL10" s="2"/>
       <c r="CN10" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="CO10" s="2"/>
     </row>
@@ -9191,37 +9187,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G1" t="s">
+        <v>381</v>
+      </c>
+      <c r="H1" t="s">
+        <v>382</v>
+      </c>
+      <c r="I1" t="s">
         <v>383</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>384</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>385</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>386</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>387</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>388</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="M1" t="s">
-        <v>390</v>
-      </c>
-      <c r="N1" t="s">
-        <v>391</v>
-      </c>
-      <c r="O1" t="s">
-        <v>392</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -9229,49 +9225,49 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H2" t="s">
+        <v>393</v>
+      </c>
+      <c r="I2" t="s">
         <v>394</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>395</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>396</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
         <v>397</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>398</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>399</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>401</v>
-      </c>
-      <c r="N2" t="s">
-        <v>402</v>
-      </c>
-      <c r="O2" t="s">
-        <v>403</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="Q2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -9285,57 +9281,57 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="P3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9391,7 +9387,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9399,13 +9395,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9416,10 +9412,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -9442,7 +9438,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -9450,31 +9446,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
       <c r="D2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="H2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="I2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9491,33 +9487,33 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -9526,24 +9522,24 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C5" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -9570,34 +9566,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F1" t="s">
         <v>414</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>415</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>416</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>417</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>418</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>419</v>
-      </c>
-      <c r="I1" t="s">
-        <v>420</v>
-      </c>
-      <c r="J1" t="s">
-        <v>421</v>
-      </c>
-      <c r="K1" t="s">
-        <v>422</v>
-      </c>
-      <c r="L1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9605,37 +9601,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F2" t="s">
         <v>424</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>425</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>426</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>427</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>428</v>
       </c>
-      <c r="G2" t="s">
-        <v>429</v>
-      </c>
-      <c r="H2" t="s">
-        <v>430</v>
-      </c>
-      <c r="I2" t="s">
-        <v>431</v>
-      </c>
-      <c r="J2" t="s">
-        <v>432</v>
-      </c>
       <c r="K2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -9646,34 +9642,34 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -9703,31 +9699,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
       <c r="G2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="H2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9744,22 +9740,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -9790,28 +9786,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -9819,28 +9815,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9848,10 +9844,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -9874,28 +9870,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
   <si>
     <t>Id</t>
   </si>
@@ -313,6 +313,9 @@
     <t>UnitData[]</t>
   </si>
   <si>
+    <t>CCB</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
@@ -370,6 +373,9 @@
     <t>部署策略</t>
   </si>
   <si>
+    <t>可部署上限</t>
+  </si>
+  <si>
     <t>仇恨等级</t>
   </si>
   <si>
@@ -526,6 +532,9 @@
     <t>RedeployPolicy</t>
   </si>
   <si>
+    <t>BuildCountLimit</t>
+  </si>
+  <si>
     <t>Hatred</t>
   </si>
   <si>
@@ -676,9 +685,6 @@
     <t>System.Collections.Generic.Dictionary&lt;string,object&gt;</t>
   </si>
   <si>
-    <t>CCB</t>
-  </si>
-  <si>
     <t>干员</t>
   </si>
   <si>
@@ -1669,6 +1675,9 @@
     <t>MapHp</t>
   </si>
   <si>
+    <t>UnitTypeEnum[]</t>
+  </si>
+  <si>
     <t>仅单面</t>
   </si>
   <si>
@@ -1736,20 +1745,14 @@
   </si>
   <si>
     <t>/Spine/丰川祥子/back/char_4182_oblvns_avemujica_1.skel.bytes</t>
-  </si>
-  <si>
-    <t>UnitTypeEnum[]</t>
-  </si>
-  <si>
-    <t>CCB</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1761,27 +1764,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1811,19 +1793,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2128,756 +2110,930 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1"/>
+    <col min="1" max="2" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BT5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
-    <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1"/>
-    <col min="7" max="7" width="8.25" customWidth="1"/>
-    <col min="8" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="4.08203125" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1"/>
-    <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.75" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="10.25" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1"/>
-    <col min="23" max="23" width="10.75" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1"/>
-    <col min="26" max="26" width="10.75" customWidth="1"/>
-    <col min="27" max="28" width="9" customWidth="1"/>
-    <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1"/>
-    <col min="31" max="31" width="9" customWidth="1"/>
-    <col min="32" max="32" width="9.75" customWidth="1"/>
-    <col min="33" max="33" width="7.83203125" customWidth="1"/>
-    <col min="34" max="34" width="15.83203125" customWidth="1"/>
-    <col min="35" max="35" width="13.83203125" customWidth="1"/>
-    <col min="36" max="36" width="34.5" customWidth="1"/>
-    <col min="37" max="38" width="9.83203125" customWidth="1"/>
-    <col min="39" max="42" width="9" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="44" max="49" width="9" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="51" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="54" max="55" width="9" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="60" max="63" width="9" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
+    <col min="8" max="8" width="9" customWidth="1" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="9" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6" customWidth="1" style="2"/>
+    <col min="12" max="12" width="4.08203125" customWidth="1" style="2"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="4" customWidth="1" style="2"/>
+    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
+    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
+    <col min="27" max="27" width="9" customWidth="1" style="2"/>
+    <col min="28" max="28" width="9" customWidth="1" style="2"/>
+    <col min="29" max="29" width="8" customWidth="1" style="2"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="9" customWidth="1" style="2"/>
+    <col min="32" max="32" width="9" customWidth="1" style="2"/>
+    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
+    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
+    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
+    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="9" customWidth="1" style="2"/>
+    <col min="41" max="41" width="9" customWidth="1" style="2"/>
+    <col min="42" max="42" width="9" customWidth="1" style="2"/>
+    <col min="43" max="43" width="9" customWidth="1" style="2"/>
+    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
+    <col min="45" max="45" width="9" customWidth="1" style="2"/>
+    <col min="46" max="46" width="9" customWidth="1" style="2"/>
+    <col min="47" max="47" width="9" customWidth="1" style="2"/>
+    <col min="48" max="48" width="9" customWidth="1" style="2"/>
+    <col min="49" max="49" width="9" customWidth="1" style="2"/>
+    <col min="50" max="50" width="9" customWidth="1" style="2"/>
+    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
+    <col min="52" max="52" width="9" customWidth="1" style="2"/>
+    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
+    <col min="55" max="55" width="9" customWidth="1" style="2"/>
+    <col min="56" max="56" width="9" customWidth="1" style="2"/>
+    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
+    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
+    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8" customWidth="1" style="2"/>
+    <col min="61" max="61" width="9" customWidth="1" style="2"/>
+    <col min="62" max="62" width="9" customWidth="1" style="2"/>
+    <col min="63" max="63" width="9" customWidth="1" style="2"/>
+    <col min="64" max="64" width="9" customWidth="1" style="2"/>
+    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
+    <col min="66" max="66" width="14" customWidth="1" style="2"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
+    <col min="68" max="68" width="14" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="71" max="71" width="14" customWidth="1" style="2"/>
+    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BG1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="BH1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="BI1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BJ1" s="2"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2"/>
+      <c r="BD4" s="2"/>
+      <c r="BE4" s="2"/>
+      <c r="BF4" s="2"/>
+      <c r="BG4" s="2"/>
+      <c r="BH4" s="2"/>
+      <c r="BI4" s="2"/>
+      <c r="BJ4" s="2"/>
+      <c r="BK4" s="2"/>
+      <c r="BL4" s="2"/>
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2"/>
+      <c r="BO4" s="2"/>
+      <c r="BP4" s="2"/>
+      <c r="BQ4" s="2"/>
+      <c r="BR4" s="2"/>
+      <c r="BS4" s="2"/>
+      <c r="BT4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>90</v>
+      </c>
+      <c r="K5" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2">
+        <v>500</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2">
+        <v>500</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2">
+        <v>20</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2">
+        <v>10</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V5" s="2">
+        <v>70</v>
+      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="AJ5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AL5" s="2"/>
+      <c r="AM5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP5" s="2">
+        <v>2</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="2"/>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2"/>
+      <c r="BA5" s="2"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BD5" s="2"/>
+      <c r="BE5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BI5" s="2">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>11</v>
-      </c>
-      <c r="S1" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" t="s">
-        <v>13</v>
-      </c>
-      <c r="V1" t="s">
-        <v>14</v>
-      </c>
-      <c r="X1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>40</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>41</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>42</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>44</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>45</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" t="s">
-        <v>58</v>
-      </c>
-      <c r="P2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>60</v>
-      </c>
-      <c r="R2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S2" t="s">
-        <v>62</v>
-      </c>
-      <c r="T2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U2" t="s">
-        <v>64</v>
-      </c>
-      <c r="V2" t="s">
-        <v>65</v>
-      </c>
-      <c r="W2" t="s">
-        <v>66</v>
-      </c>
-      <c r="X2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L3" t="s">
-        <v>117</v>
-      </c>
-      <c r="M3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" t="s">
-        <v>117</v>
-      </c>
-      <c r="P3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>117</v>
-      </c>
-      <c r="R3" t="s">
-        <v>117</v>
-      </c>
-      <c r="S3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" t="s">
-        <v>117</v>
-      </c>
-      <c r="X3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="B5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>90</v>
-      </c>
-      <c r="K5">
-        <v>10000</v>
-      </c>
-      <c r="M5">
-        <v>500</v>
-      </c>
-      <c r="O5">
-        <v>500</v>
-      </c>
-      <c r="Q5">
-        <v>20</v>
-      </c>
-      <c r="S5">
-        <v>10</v>
-      </c>
-      <c r="U5">
-        <v>0.5</v>
-      </c>
-      <c r="V5">
-        <v>70</v>
-      </c>
-      <c r="Y5">
-        <v>0.05</v>
-      </c>
-      <c r="Z5">
-        <v>2</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>128</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>129</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>130</v>
-      </c>
-      <c r="AO5">
-        <v>2</v>
-      </c>
-      <c r="AP5">
-        <v>0.5</v>
-      </c>
-      <c r="AW5">
-        <v>0.25</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>131</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>132</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>133</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>134</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>135</v>
-      </c>
-      <c r="BH5">
-        <v>6</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>136</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>137</v>
-      </c>
-      <c r="BM5" t="s">
+      <c r="BJ5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BK5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="BP5" t="s">
+      <c r="BL5" s="2"/>
+      <c r="BM5" s="2"/>
+      <c r="BN5" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="BQ5" t="s">
-        <v>140</v>
-      </c>
-      <c r="BR5" t="s">
+      <c r="BO5" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="BS5">
+      <c r="BP5" s="2"/>
+      <c r="BQ5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BT5" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2885,6 +3041,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2894,1299 +3051,1299 @@
   <dimension ref="A1:DI704"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="20.58203125" customWidth="1"/>
-    <col min="9" max="9" width="10.75" customWidth="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1"/>
-    <col min="17" max="17" width="21.5" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1"/>
-    <col min="22" max="22" width="17.75" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1"/>
-    <col min="24" max="24" width="18.5" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1"/>
-    <col min="32" max="32" width="13.75" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1"/>
-    <col min="36" max="36" width="12.5" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1"/>
-    <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1"/>
-    <col min="47" max="47" width="12.25" customWidth="1"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1"/>
-    <col min="51" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="7" customWidth="1"/>
-    <col min="53" max="53" width="11.75" customWidth="1"/>
-    <col min="54" max="54" width="19.75" customWidth="1"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1"/>
-    <col min="56" max="56" width="8.5" customWidth="1"/>
-    <col min="57" max="57" width="13.5" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1"/>
-    <col min="60" max="60" width="8.25" customWidth="1"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1"/>
-    <col min="68" max="70" width="11.25" customWidth="1"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1"/>
-    <col min="72" max="73" width="8" customWidth="1"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1"/>
-    <col min="75" max="76" width="8.5" customWidth="1"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1"/>
-    <col min="80" max="80" width="13.5" customWidth="1"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1"/>
-    <col min="82" max="82" width="15.75" customWidth="1"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1"/>
-    <col min="86" max="86" width="9" customWidth="1"/>
-    <col min="87" max="87" width="16" customWidth="1"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1"/>
-    <col min="93" max="98" width="9" customWidth="1"/>
-    <col min="99" max="99" width="14" customWidth="1"/>
-    <col min="100" max="100" width="8" customWidth="1"/>
-    <col min="101" max="101" width="9" customWidth="1"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1"/>
-    <col min="103" max="103" width="13.75" customWidth="1"/>
-    <col min="104" max="109" width="9" customWidth="1"/>
-    <col min="110" max="110" width="15.5" customWidth="1"/>
-    <col min="111" max="113" width="9" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1" style="2"/>
+    <col min="9" max="9" width="10.75" customWidth="1" style="2"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="15" customWidth="1" style="2"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
+    <col min="51" max="51" width="9" customWidth="1" style="2"/>
+    <col min="52" max="52" width="7" customWidth="1" style="2"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
+    <col min="72" max="73" width="8" customWidth="1" style="2"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
+    <col min="86" max="86" width="9" customWidth="1" style="2"/>
+    <col min="87" max="87" width="16" customWidth="1" style="2"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
+    <col min="93" max="98" width="9" customWidth="1" style="2"/>
+    <col min="99" max="99" width="14" customWidth="1" style="2"/>
+    <col min="100" max="100" width="8" customWidth="1" style="2"/>
+    <col min="101" max="101" width="9" customWidth="1" style="2"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
+    <col min="104" max="109" width="9" customWidth="1" style="2"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
+    <col min="111" max="113" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E1" t="s">
+    <row r="1">
+      <c r="B1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G1" t="s">
+      <c r="E1" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H1" t="s">
+      <c r="F1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I1" t="s">
+      <c r="G1" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="J1" t="s">
+      <c r="H1" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="K1" t="s">
+      <c r="I1" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="L1" t="s">
+      <c r="J1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="M1" t="s">
+      <c r="K1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="N1" t="s">
+      <c r="L1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="O1" t="s">
+      <c r="M1" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="P1" t="s">
+      <c r="N1" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="O1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="R1" t="s">
+      <c r="P1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="T1" t="s">
+      <c r="R1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="U1" t="s">
-        <v>159</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="S1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="W1" t="s">
+      <c r="T1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="X1" t="s">
+      <c r="U1" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="W1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="X1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>198</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BJ1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="BK1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BR1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BT1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BV1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BW1" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="BX1" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="BY1" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CA1" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CB1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CC1" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CD1" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CE1" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CF1" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CG1" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CH1" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CI1" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CK1" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CM1" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CN1" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CO1" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="CR1" t="s">
-        <v>208</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CP1" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CQ1" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CR1" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CT1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CU1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CV1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CW1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>237</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="CX1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="CY1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="CZ1" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DA1" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DB1" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DC1" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DD1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DE1" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DF1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DG1" s="2" t="s">
         <v>247</v>
       </c>
+      <c r="DH1" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="DI1" s="2" t="s">
+        <v>249</v>
+      </c>
     </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F2" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="J2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I2" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="L2" t="s">
+      <c r="J2" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="M2" t="s">
+      <c r="K2" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="N2" t="s">
+      <c r="L2" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="O2" t="s">
+      <c r="M2" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="P2" t="s">
+      <c r="N2" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="O2" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="R2" t="s">
+      <c r="P2" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="S2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="T2" t="s">
+      <c r="R2" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="U2" t="s">
+      <c r="S2" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="V2" t="s">
+      <c r="T2" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="W2" t="s">
+      <c r="U2" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="X2" t="s">
+      <c r="V2" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="W2" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="X2" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AW2" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BE2" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BG2" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BI2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BN2" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BO2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="BP2" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BR2" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="BU2" t="s">
-        <v>94</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="BS2" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BT2" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BV2" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BW2" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="BX2" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="BY2" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="BZ2" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CA2" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CB2" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CC2" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CD2" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CE2" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CF2" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CG2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CH2" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CI2" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CJ2" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CK2" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CM2" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CN2" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CO2" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CP2" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CQ2" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CR2" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CS2" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CT2" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CU2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CV2" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CW2" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="CX2" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="CY2" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="CZ2" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DA2" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DB2" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DC2" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DD2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DE2" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DF2" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="DI2" t="s">
+      <c r="DG2" s="2" t="s">
         <v>353</v>
       </c>
+      <c r="DH2" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="DI2" s="2" t="s">
+        <v>355</v>
+      </c>
     </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J3" t="s">
-        <v>354</v>
-      </c>
-      <c r="K3" t="s">
-        <v>355</v>
-      </c>
-      <c r="L3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="M3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="K3" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="P3" t="s">
+      <c r="N3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="O3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="R3" t="s">
+      <c r="AD3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="S3" t="s">
-        <v>115</v>
-      </c>
-      <c r="T3" t="s">
-        <v>116</v>
-      </c>
-      <c r="U3" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" t="s">
-        <v>116</v>
-      </c>
-      <c r="W3" t="s">
-        <v>115</v>
-      </c>
-      <c r="X3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>357</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI3" t="s">
+      <c r="AL3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="CB3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>358</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>359</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>360</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>361</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>360</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BO3" t="s">
+      <c r="CC3" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="CI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR3" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="CS3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CT3" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="CU3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CV3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="CW3" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="CX3" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="CY3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="CZ3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="DA3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="DB3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="DC3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="DD3" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="BQ3" t="s">
-        <v>362</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>363</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>364</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>364</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>365</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>366</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>367</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>368</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>368</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>120</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>120</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>365</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>369</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>370</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>370</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>369</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>369</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>369</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>369</v>
-      </c>
-      <c r="DC3" t="s">
-        <v>369</v>
-      </c>
-      <c r="DD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DE3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DF3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DG3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DH3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DI3" t="s">
-        <v>115</v>
+      <c r="DE3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DF3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DG3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DH3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DI3" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>371</v>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>373</v>
       </c>
     </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>372</v>
-      </c>
-      <c r="C6" t="s">
-        <v>373</v>
-      </c>
-      <c r="K6" t="s">
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="AC6">
+      <c r="C6" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="AC6" s="2">
         <v>4</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AJ6" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AN6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AV6" s="2">
+        <v>15</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AZ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="2">
+        <v>2</v>
+      </c>
+      <c r="BD6" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="CG6" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="CH6" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="CI6" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="CY6" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="AN6">
+      <c r="J7" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="2">
         <v>1</v>
       </c>
-      <c r="AO6" t="s">
-        <v>376</v>
-      </c>
-      <c r="AV6">
-        <v>15</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>377</v>
-      </c>
-      <c r="AZ6">
+      <c r="AO7" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AV7" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AX8" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AZ8" s="2">
         <v>0</v>
       </c>
-      <c r="BB6">
-        <v>2</v>
-      </c>
-      <c r="BD6">
+      <c r="BB8" s="2">
+        <v>2</v>
+      </c>
+      <c r="BD8" s="2">
         <v>1</v>
       </c>
-      <c r="CB6" t="s">
-        <v>56</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>378</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>379</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>380</v>
-      </c>
-      <c r="CN6" t="s">
-        <v>381</v>
-      </c>
-      <c r="CY6" t="s">
-        <v>382</v>
+      <c r="CL8" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="CY8" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>383</v>
-      </c>
-      <c r="C7" t="s">
-        <v>373</v>
-      </c>
-      <c r="J7" t="s">
-        <v>384</v>
-      </c>
-      <c r="K7" t="s">
-        <v>385</v>
-      </c>
-      <c r="AC7">
-        <v>2</v>
-      </c>
-      <c r="AD7">
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC10" s="2">
         <v>1</v>
       </c>
-      <c r="AO7" t="s">
-        <v>376</v>
-      </c>
-      <c r="AV7">
-        <v>2.5</v>
+      <c r="AG10" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="BD10" s="2">
+        <v>1</v>
+      </c>
+      <c r="BT10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="CN10" s="2" t="s">
+        <v>397</v>
       </c>
     </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>386</v>
-      </c>
-      <c r="C8" t="s">
-        <v>387</v>
-      </c>
-      <c r="K8" t="s">
-        <v>385</v>
-      </c>
-      <c r="L8" t="s">
-        <v>388</v>
-      </c>
-      <c r="AC8">
-        <v>2</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>389</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>377</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>2</v>
-      </c>
-      <c r="BD8">
+    <row r="684">
+      <c r="CL684" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="CL686" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="CL687" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="CL689" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="CL696" s="2">
         <v>1</v>
       </c>
-      <c r="CL8" t="s">
-        <v>390</v>
-      </c>
-      <c r="CY8" t="s">
-        <v>391</v>
-      </c>
     </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>392</v>
-      </c>
-      <c r="C10" t="s">
-        <v>373</v>
-      </c>
-      <c r="K10" t="s">
-        <v>385</v>
-      </c>
-      <c r="L10" t="s">
-        <v>393</v>
-      </c>
-      <c r="AC10">
-        <v>1</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>394</v>
-      </c>
-      <c r="BD10">
-        <v>1</v>
-      </c>
-      <c r="BT10">
-        <v>0.1</v>
-      </c>
-      <c r="CN10" t="s">
-        <v>395</v>
+    <row r="698">
+      <c r="CL698" s="2">
+        <v>0.4</v>
       </c>
     </row>
-    <row r="684" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL684">
-        <v>0.15</v>
+    <row r="699">
+      <c r="CL699" s="2">
+        <v>0.6</v>
       </c>
     </row>
-    <row r="686" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL686">
-        <v>0.2</v>
+    <row r="702">
+      <c r="CL702" s="2">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="687" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL687">
-        <v>0.1</v>
+    <row r="703">
+      <c r="CL703" s="2">
+        <v>0.667</v>
       </c>
     </row>
-    <row r="689" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL689">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="696" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL696">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="698" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL698">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="699" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL699">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="702" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL702">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="703" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL703">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="704" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL704">
+    <row r="704">
+      <c r="CL704" s="2">
         <v>0.2</v>
       </c>
     </row>
@@ -4194,6 +4351,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4203,177 +4361,178 @@
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1" style="2"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
+    <col min="3" max="6" width="9" customWidth="1" style="2"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
+    <col min="8" max="8" width="15" customWidth="1" style="2"/>
+    <col min="9" max="13" width="9" customWidth="1" style="2"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>396</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="G1" t="s">
-        <v>398</v>
-      </c>
-      <c r="H1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I1" t="s">
-        <v>400</v>
-      </c>
-      <c r="J1" t="s">
-        <v>401</v>
-      </c>
-      <c r="L1" t="s">
-        <v>402</v>
-      </c>
-      <c r="M1" t="s">
-        <v>403</v>
-      </c>
-      <c r="N1" t="s">
-        <v>404</v>
-      </c>
-      <c r="O1" t="s">
-        <v>405</v>
-      </c>
-      <c r="P1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F2" t="s">
-        <v>408</v>
-      </c>
-      <c r="G2" t="s">
-        <v>409</v>
-      </c>
-      <c r="H2" t="s">
-        <v>410</v>
-      </c>
-      <c r="I2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J2" t="s">
-        <v>412</v>
-      </c>
-      <c r="K2" t="s">
-        <v>413</v>
-      </c>
-      <c r="L2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" t="s">
-        <v>414</v>
-      </c>
-      <c r="N2" t="s">
-        <v>415</v>
-      </c>
-      <c r="O2" t="s">
-        <v>416</v>
-      </c>
-      <c r="P2" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J3" t="s">
-        <v>369</v>
-      </c>
-      <c r="K3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>333</v>
-      </c>
-      <c r="M3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N3" t="s">
-        <v>115</v>
-      </c>
-      <c r="O3" t="s">
-        <v>333</v>
-      </c>
-      <c r="P3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>395</v>
-      </c>
-      <c r="C4" t="s">
-        <v>418</v>
-      </c>
-      <c r="K4">
+      <c r="C4" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="K4" s="2">
         <v>5</v>
       </c>
-      <c r="Q4" t="s">
-        <v>419</v>
+      <c r="Q4" s="2" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4382,52 +4541,53 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>420</v>
+      <c r="C1" s="2" t="s">
+        <v>422</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D2" t="s">
-        <v>339</v>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4436,123 +4596,124 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="10" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I1" t="s">
-        <v>224</v>
+    <row r="1">
+      <c r="I1" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" t="s">
-        <v>423</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="I2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J2" t="s">
-        <v>339</v>
+      <c r="G2" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>368</v>
-      </c>
-      <c r="J3" t="s">
-        <v>124</v>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>426</v>
-      </c>
-      <c r="B4" t="s">
-        <v>427</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="E4">
+      <c r="B4" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E4" s="2">
         <v>10</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>429</v>
+      <c r="J4" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>379</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C5" t="s">
-        <v>428</v>
-      </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>10</v>
       </c>
-      <c r="J5" t="s">
-        <v>431</v>
+      <c r="J5" s="2" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4561,129 +4722,130 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1"/>
-    <col min="5" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28" customWidth="1" style="2"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
+    <col min="12" max="12" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C1" t="s">
-        <v>433</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C1" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E1" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="J1" t="s">
+      <c r="H1" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="K1" t="s">
+      <c r="I1" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="L1" t="s">
+      <c r="J1" s="2" t="s">
         <v>441</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>443</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E2" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F2" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G2" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="J2" t="s">
+      <c r="H2" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="K2" t="s">
-        <v>423</v>
-      </c>
-      <c r="L2" t="s">
-        <v>96</v>
+      <c r="I2" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" t="s">
-        <v>451</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>116</v>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4693,49 +4855,49 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1"/>
-    <col min="2" max="2" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
+    <col min="7" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="H2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="E2" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="J2" t="s">
-        <v>53</v>
+      <c r="F2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4749,27 +4911,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4778,133 +4941,134 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1"/>
-    <col min="6" max="6" width="39.5" customWidth="1"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1"/>
-    <col min="8" max="8" width="32.25" customWidth="1"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C1" t="s">
-        <v>457</v>
-      </c>
-      <c r="D1" t="s">
-        <v>458</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="B1" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C1" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="G1" t="s">
+      <c r="D1" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E1" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" s="2" t="s">
         <v>463</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>466</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B2" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C2" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D2" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E2" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F2" s="2" t="s">
         <v>471</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>474</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>472</v>
-      </c>
-      <c r="C4">
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>473</v>
-      </c>
-      <c r="E4" t="s">
-        <v>474</v>
-      </c>
-      <c r="F4" t="s">
-        <v>475</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="D4" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="H4" t="s">
+      <c r="E4" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="I4" t="s">
+      <c r="F4" s="2" t="s">
         <v>478</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>481</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65736149-DD00-4944-BA9C-54A965402427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756F9752-8540-4EF7-9302-48068E1395A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -47,6 +47,30 @@
   </authors>
   <commentList>
     <comment ref="AK1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>PC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0:干员 1:敌人 2:仅技能条 3:技能+血条</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AM1" authorId="0" shapeId="0" xr:uid="{E98F2C31-5FE6-49FE-8F71-0FCD7A097384}">
       <text>
         <r>
           <rPr>
@@ -299,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="487">
   <si>
     <t>Id</t>
   </si>
@@ -388,9 +412,6 @@
     <t>可选技能</t>
   </si>
   <si>
-    <t>血条类型</t>
-  </si>
-  <si>
     <t>高度</t>
   </si>
   <si>
@@ -1745,14 +1766,37 @@
   </si>
   <si>
     <t>/Spine/丰川祥子/back/char_4182_oblvns_avemujica_1.skel.bytes</t>
+  </si>
+  <si>
+    <t>血条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技力条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpBarType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:蓝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:绿</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1764,6 +1808,34 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1793,19 +1865,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2110,930 +2182,777 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BT5"/>
+  <dimension ref="A1:BU5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
-    <col min="8" max="8" width="9" customWidth="1" style="2"/>
-    <col min="9" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="9" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6" customWidth="1" style="2"/>
-    <col min="12" max="12" width="4.08203125" customWidth="1" style="2"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="4" customWidth="1" style="2"/>
-    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
-    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
-    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
-    <col min="27" max="27" width="9" customWidth="1" style="2"/>
-    <col min="28" max="28" width="9" customWidth="1" style="2"/>
-    <col min="29" max="29" width="8" customWidth="1" style="2"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="9" customWidth="1" style="2"/>
-    <col min="32" max="32" width="9" customWidth="1" style="2"/>
-    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
-    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
-    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
-    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
-    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="9" customWidth="1" style="2"/>
-    <col min="41" max="41" width="9" customWidth="1" style="2"/>
-    <col min="42" max="42" width="9" customWidth="1" style="2"/>
-    <col min="43" max="43" width="9" customWidth="1" style="2"/>
-    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
-    <col min="45" max="45" width="9" customWidth="1" style="2"/>
-    <col min="46" max="46" width="9" customWidth="1" style="2"/>
-    <col min="47" max="47" width="9" customWidth="1" style="2"/>
-    <col min="48" max="48" width="9" customWidth="1" style="2"/>
-    <col min="49" max="49" width="9" customWidth="1" style="2"/>
-    <col min="50" max="50" width="9" customWidth="1" style="2"/>
-    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
-    <col min="52" max="52" width="9" customWidth="1" style="2"/>
-    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
-    <col min="55" max="55" width="9" customWidth="1" style="2"/>
-    <col min="56" max="56" width="9" customWidth="1" style="2"/>
-    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
-    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
-    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8" customWidth="1" style="2"/>
-    <col min="61" max="61" width="9" customWidth="1" style="2"/>
-    <col min="62" max="62" width="9" customWidth="1" style="2"/>
-    <col min="63" max="63" width="9" customWidth="1" style="2"/>
-    <col min="64" max="64" width="9" customWidth="1" style="2"/>
-    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
-    <col min="66" max="66" width="14" customWidth="1" style="2"/>
-    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
-    <col min="71" max="71" width="14" customWidth="1" style="2"/>
-    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="8" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="4.08203125" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1"/>
+    <col min="14" max="14" width="4" customWidth="1"/>
+    <col min="15" max="15" width="7.75" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1"/>
+    <col min="23" max="23" width="10.75" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1"/>
+    <col min="26" max="26" width="10.75" customWidth="1"/>
+    <col min="27" max="28" width="9" customWidth="1"/>
+    <col min="29" max="29" width="8" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1"/>
+    <col min="31" max="32" width="9" customWidth="1"/>
+    <col min="33" max="33" width="9.75" customWidth="1"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1"/>
+    <col min="37" max="37" width="34.5" customWidth="1"/>
+    <col min="38" max="40" width="9.83203125" customWidth="1"/>
+    <col min="41" max="44" width="9" customWidth="1"/>
+    <col min="45" max="45" width="12.5" customWidth="1"/>
+    <col min="46" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="24.33203125" customWidth="1"/>
+    <col min="53" max="53" width="9" customWidth="1"/>
+    <col min="54" max="54" width="17.75" customWidth="1"/>
+    <col min="55" max="55" width="7.83203125" customWidth="1"/>
+    <col min="56" max="57" width="9" customWidth="1"/>
+    <col min="58" max="58" width="24.25" customWidth="1"/>
+    <col min="59" max="59" width="13.25" customWidth="1"/>
+    <col min="60" max="60" width="16.08203125" customWidth="1"/>
+    <col min="61" max="61" width="8" customWidth="1"/>
+    <col min="62" max="65" width="9" customWidth="1"/>
+    <col min="66" max="66" width="39.58203125" customWidth="1"/>
+    <col min="67" max="67" width="14" customWidth="1"/>
+    <col min="68" max="68" width="14.83203125" customWidth="1"/>
+    <col min="69" max="72" width="14" customWidth="1"/>
+    <col min="73" max="73" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2" t="s">
+      <c r="U1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2" t="s">
+      <c r="X1" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>25</v>
       </c>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>28</v>
       </c>
       <c r="AM1" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="AO1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AU1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>43</v>
       </c>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BI1" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BJ1" t="s">
         <v>47</v>
       </c>
-      <c r="BI1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>48</v>
       </c>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>61</v>
+      </c>
+      <c r="R2" t="s">
+        <v>62</v>
+      </c>
+      <c r="S2" t="s">
+        <v>63</v>
+      </c>
+      <c r="T2" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" t="s">
+        <v>65</v>
+      </c>
+      <c r="V2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X2" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>95</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y2" s="2" t="s">
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" t="s">
+        <v>119</v>
+      </c>
+      <c r="P3" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>119</v>
+      </c>
+      <c r="R3" t="s">
+        <v>119</v>
+      </c>
+      <c r="S3" t="s">
+        <v>119</v>
+      </c>
+      <c r="T3" t="s">
+        <v>119</v>
+      </c>
+      <c r="U3" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" t="s">
+        <v>119</v>
+      </c>
+      <c r="X3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>90</v>
+      </c>
+      <c r="K5">
+        <v>10000</v>
+      </c>
+      <c r="M5">
+        <v>500</v>
+      </c>
+      <c r="O5">
+        <v>500</v>
+      </c>
+      <c r="Q5">
+        <v>20</v>
+      </c>
+      <c r="S5">
+        <v>10</v>
+      </c>
+      <c r="U5">
+        <v>0.5</v>
+      </c>
+      <c r="V5">
         <v>70</v>
       </c>
-      <c r="Z2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BI2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BK2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
-      <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2"/>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BB4" s="2"/>
-      <c r="BC4" s="2"/>
-      <c r="BD4" s="2"/>
-      <c r="BE4" s="2"/>
-      <c r="BF4" s="2"/>
-      <c r="BG4" s="2"/>
-      <c r="BH4" s="2"/>
-      <c r="BI4" s="2"/>
-      <c r="BJ4" s="2"/>
-      <c r="BK4" s="2"/>
-      <c r="BL4" s="2"/>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2"/>
-      <c r="BO4" s="2"/>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2"/>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="Y5">
+        <v>0.05</v>
+      </c>
+      <c r="Z5">
+        <v>2</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="AJ5" t="s">
         <v>129</v>
       </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2">
-        <v>90</v>
-      </c>
-      <c r="K5" s="2">
-        <v>10000</v>
-      </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2">
-        <v>500</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2">
-        <v>500</v>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2">
-        <v>20</v>
-      </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2">
-        <v>10</v>
-      </c>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2">
+      <c r="AK5" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ5">
+        <v>2</v>
+      </c>
+      <c r="AR5">
         <v>0.5</v>
       </c>
-      <c r="V5" s="2">
-        <v>70</v>
-      </c>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>2</v>
-      </c>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ5" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AL5" s="2"/>
-      <c r="AM5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2" t="s">
+      <c r="AY5">
+        <v>0.25</v>
+      </c>
+      <c r="BD5" t="s">
         <v>132</v>
       </c>
-      <c r="AP5" s="2">
-        <v>2</v>
-      </c>
-      <c r="AQ5" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AR5" s="2"/>
-      <c r="AS5" s="2"/>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2"/>
-      <c r="BA5" s="2"/>
-      <c r="BB5" s="2"/>
-      <c r="BC5" s="2" t="s">
+      <c r="BF5" t="s">
         <v>133</v>
       </c>
-      <c r="BD5" s="2"/>
-      <c r="BE5" s="2" t="s">
+      <c r="BG5" t="s">
         <v>134</v>
       </c>
-      <c r="BF5" s="2" t="s">
+      <c r="BH5" t="s">
         <v>135</v>
       </c>
-      <c r="BG5" s="2" t="s">
+      <c r="BI5" t="s">
         <v>136</v>
       </c>
-      <c r="BH5" s="2" t="s">
+      <c r="BJ5">
+        <v>6</v>
+      </c>
+      <c r="BK5" t="s">
         <v>137</v>
       </c>
-      <c r="BI5" s="2">
-        <v>6</v>
-      </c>
-      <c r="BJ5" s="2" t="s">
+      <c r="BL5" t="s">
         <v>138</v>
       </c>
-      <c r="BK5" s="2" t="s">
+      <c r="BO5" t="s">
         <v>139</v>
       </c>
-      <c r="BL5" s="2"/>
-      <c r="BM5" s="2"/>
-      <c r="BN5" s="2" t="s">
+      <c r="BP5" t="s">
         <v>140</v>
       </c>
-      <c r="BO5" s="2" t="s">
+      <c r="BR5" t="s">
         <v>141</v>
       </c>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2" t="s">
+      <c r="BS5" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT5" t="s">
         <v>142</v>
       </c>
-      <c r="BR5" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="BS5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="BT5" s="2">
+      <c r="BU5">
         <v>1</v>
       </c>
     </row>
@@ -3041,7 +2960,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3051,1299 +2969,1299 @@
   <dimension ref="A1:DI704"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="20.58203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="10.75" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="113" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1"/>
+    <col min="9" max="9" width="10.75" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1"/>
+    <col min="40" max="40" width="15" customWidth="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="51" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="86" max="86" width="9" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="93" max="98" width="9" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="101" max="101" width="9" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="104" max="109" width="9" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="111" max="113" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" t="s">
         <v>144</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>145</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" t="s">
         <v>146</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" t="s">
         <v>147</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" t="s">
         <v>148</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>149</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" t="s">
         <v>150</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" t="s">
         <v>151</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
         <v>152</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" t="s">
         <v>153</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" t="s">
         <v>154</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" t="s">
         <v>155</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" t="s">
         <v>156</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>157</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" t="s">
         <v>158</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" t="s">
         <v>159</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" t="s">
         <v>160</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" t="s">
+        <v>160</v>
+      </c>
+      <c r="V1" t="s">
         <v>161</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" t="s">
         <v>162</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" t="s">
         <v>163</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>164</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>165</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>166</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>167</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>168</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>169</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>170</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>171</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>172</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" t="s">
         <v>173</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" t="s">
         <v>174</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" t="s">
         <v>175</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>176</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>177</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" t="s">
         <v>178</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" t="s">
         <v>179</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" t="s">
         <v>180</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>181</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>182</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>183</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" t="s">
         <v>184</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AT1" t="s">
         <v>185</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AU1" t="s">
         <v>186</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>187</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>188</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>189</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>190</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>191</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>192</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>193</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>194</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BD1" t="s">
         <v>195</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BE1" t="s">
         <v>196</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>197</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>198</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>199</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BJ1" t="s">
+        <v>199</v>
+      </c>
+      <c r="BK1" t="s">
         <v>200</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BL1" t="s">
         <v>201</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BM1" t="s">
         <v>202</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BN1" t="s">
         <v>203</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BO1" t="s">
         <v>204</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BP1" t="s">
         <v>205</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BQ1" t="s">
         <v>206</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BR1" t="s">
         <v>207</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BS1" t="s">
         <v>208</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BT1" t="s">
         <v>209</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BU1" t="s">
         <v>210</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BV1" t="s">
         <v>211</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BW1" t="s">
         <v>212</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BX1" t="s">
         <v>213</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BY1" t="s">
         <v>214</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BZ1" t="s">
         <v>215</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="CA1" t="s">
         <v>216</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="CB1" t="s">
         <v>217</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="CC1" t="s">
         <v>218</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CD1" t="s">
         <v>219</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CE1" t="s">
         <v>220</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CF1" t="s">
         <v>221</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CG1" t="s">
         <v>222</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CH1" t="s">
         <v>223</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CI1" t="s">
         <v>224</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CJ1" t="s">
         <v>225</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CK1" t="s">
         <v>226</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CL1" t="s">
         <v>227</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CM1" t="s">
         <v>228</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CN1" t="s">
         <v>229</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CO1" t="s">
         <v>230</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CP1" t="s">
         <v>231</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CQ1" t="s">
         <v>232</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CR1" t="s">
+        <v>209</v>
+      </c>
+      <c r="CS1" t="s">
         <v>233</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CT1" t="s">
         <v>234</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CU1" t="s">
         <v>235</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CV1" t="s">
         <v>236</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CW1" t="s">
         <v>237</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CX1" t="s">
         <v>238</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CY1" t="s">
         <v>239</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CZ1" t="s">
+        <v>238</v>
+      </c>
+      <c r="DA1" t="s">
         <v>240</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="DB1" t="s">
         <v>241</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="DC1" t="s">
         <v>242</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="DD1" t="s">
         <v>243</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DE1" t="s">
         <v>244</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DF1" t="s">
         <v>245</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DG1" t="s">
         <v>246</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DH1" t="s">
         <v>247</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DI1" t="s">
         <v>248</v>
       </c>
-      <c r="DI1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
         <v>249</v>
       </c>
+      <c r="F2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K2" t="s">
+        <v>254</v>
+      </c>
+      <c r="L2" t="s">
+        <v>255</v>
+      </c>
+      <c r="M2" t="s">
+        <v>256</v>
+      </c>
+      <c r="N2" t="s">
+        <v>257</v>
+      </c>
+      <c r="O2" t="s">
+        <v>258</v>
+      </c>
+      <c r="P2" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>260</v>
+      </c>
+      <c r="R2" t="s">
+        <v>261</v>
+      </c>
+      <c r="S2" t="s">
+        <v>262</v>
+      </c>
+      <c r="T2" t="s">
+        <v>263</v>
+      </c>
+      <c r="U2" t="s">
+        <v>264</v>
+      </c>
+      <c r="V2" t="s">
+        <v>265</v>
+      </c>
+      <c r="W2" t="s">
+        <v>266</v>
+      </c>
+      <c r="X2" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>268</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>285</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>286</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>287</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>288</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>289</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>290</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>291</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>292</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>294</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>295</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>296</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>300</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>301</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>302</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>303</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>304</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>305</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>309</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>81</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>310</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>311</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>312</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>313</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>314</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>315</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>316</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>317</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>318</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>319</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>320</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>321</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>322</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>323</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>324</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>325</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>326</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>327</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>328</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>329</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>331</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>333</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>334</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>335</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>336</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>337</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>338</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>339</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>340</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>341</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>342</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>343</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>344</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>345</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>346</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>347</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>348</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>349</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>350</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>351</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>352</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>353</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>354</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K3" t="s">
+        <v>356</v>
+      </c>
+      <c r="L3" t="s">
+        <v>357</v>
+      </c>
+      <c r="M3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" t="s">
+        <v>122</v>
+      </c>
+      <c r="P3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>122</v>
+      </c>
+      <c r="R3" t="s">
+        <v>122</v>
+      </c>
+      <c r="S3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T3" t="s">
+        <v>118</v>
+      </c>
+      <c r="U3" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" t="s">
+        <v>118</v>
+      </c>
+      <c r="W3" t="s">
+        <v>117</v>
+      </c>
+      <c r="X3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>358</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>359</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>360</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>361</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>362</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>361</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>363</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>364</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>365</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>365</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CC3" t="s">
+        <v>366</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>367</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>368</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>369</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>369</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>366</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CV3" t="s">
+        <v>370</v>
+      </c>
+      <c r="CW3" t="s">
+        <v>371</v>
+      </c>
+      <c r="CX3" t="s">
+        <v>371</v>
+      </c>
+      <c r="CY3" t="s">
+        <v>370</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>370</v>
+      </c>
+      <c r="DA3" t="s">
+        <v>370</v>
+      </c>
+      <c r="DB3" t="s">
+        <v>370</v>
+      </c>
+      <c r="DC3" t="s">
+        <v>370</v>
+      </c>
+      <c r="DD3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DG3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C6" t="s">
+        <v>374</v>
+      </c>
+      <c r="K6" t="s">
+        <v>375</v>
+      </c>
+      <c r="AC6">
+        <v>4</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>376</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>377</v>
+      </c>
+      <c r="AV6">
+        <v>15</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>378</v>
+      </c>
+      <c r="AZ6">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="BI2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BK2" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="BU2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BV2" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="BX2" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="BY2" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="CA2" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="CB2" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="CC2" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="CD2" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="CE2" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="CF2" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="CG2" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="CH2" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="CJ2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CK2" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="CL2" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CM2" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="CN2" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="CO2" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="CP2" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="CQ2" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="CR2" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="CS2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="CT2" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="CU2" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="CV2" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="CW2" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="CX2" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="CY2" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="CZ2" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="DA2" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="DB2" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="DC2" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="DD2" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="DE2" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="DF2" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="DG2" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="DH2" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="DI2" s="2" t="s">
-        <v>355</v>
+      <c r="BB6">
+        <v>2</v>
+      </c>
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>57</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>379</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>380</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>381</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>382</v>
+      </c>
+      <c r="CY6" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="CI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>118</v>
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" t="s">
+        <v>374</v>
+      </c>
+      <c r="J7" t="s">
+        <v>385</v>
+      </c>
+      <c r="K7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AC7">
+        <v>2</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>377</v>
+      </c>
+      <c r="AV7">
+        <v>2.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>373</v>
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>387</v>
+      </c>
+      <c r="C8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L8" t="s">
+        <v>389</v>
+      </c>
+      <c r="AC8">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>390</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>378</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>2</v>
+      </c>
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="CL8" t="s">
+        <v>391</v>
+      </c>
+      <c r="CY8" t="s">
+        <v>392</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C10" t="s">
         <v>374</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="AC6" s="2">
-        <v>4</v>
-      </c>
-      <c r="AJ6" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AN6" s="2">
+      <c r="K10" t="s">
+        <v>386</v>
+      </c>
+      <c r="L10" t="s">
+        <v>394</v>
+      </c>
+      <c r="AC10">
         <v>1</v>
       </c>
-      <c r="AO6" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AV6" s="2">
-        <v>15</v>
-      </c>
-      <c r="AX6" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AZ6" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB6" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD6" s="2">
+      <c r="AG10" t="s">
+        <v>395</v>
+      </c>
+      <c r="BD10">
         <v>1</v>
       </c>
-      <c r="CB6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="CG6" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CH6" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="CI6" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="CN6" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="CY6" s="2" t="s">
-        <v>384</v>
+      <c r="BT10">
+        <v>0.1</v>
+      </c>
+      <c r="CN10" t="s">
+        <v>396</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="2">
+    <row r="684" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL684">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="686" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL686">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="687" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL687">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="689" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL689">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="696" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL696">
         <v>1</v>
       </c>
-      <c r="AO7" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AV7" s="2">
-        <v>2.5</v>
-      </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AX8" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AZ8" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB8" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL8" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CY8" s="2" t="s">
-        <v>393</v>
+    <row r="698" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL698">
+        <v>0.4</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="BD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BT10" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN10" s="2" t="s">
-        <v>397</v>
+    <row r="699" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL699">
+        <v>0.6</v>
       </c>
     </row>
-    <row r="684">
-      <c r="CL684" s="2">
-        <v>0.15</v>
+    <row r="702" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL702">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="686">
-      <c r="CL686" s="2">
-        <v>0.2</v>
+    <row r="703" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL703">
+        <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="687">
-      <c r="CL687" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="CL689" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="CL696" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="CL698" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="CL699" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="CL702" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="CL703" s="2">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="CL704" s="2">
+    <row r="704" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL704">
         <v>0.2</v>
       </c>
     </row>
@@ -4351,7 +4269,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4361,178 +4278,177 @@
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="3" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F1" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" t="s">
         <v>399</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" t="s">
         <v>400</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>401</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" t="s">
         <v>402</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" t="s">
         <v>403</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" t="s">
         <v>404</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" t="s">
         <v>405</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" t="s">
         <v>406</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" t="s">
         <v>407</v>
       </c>
-      <c r="P1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
         <v>408</v>
       </c>
+      <c r="F2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G2" t="s">
+        <v>410</v>
+      </c>
+      <c r="H2" t="s">
+        <v>411</v>
+      </c>
+      <c r="I2" t="s">
+        <v>412</v>
+      </c>
+      <c r="J2" t="s">
+        <v>413</v>
+      </c>
+      <c r="K2" t="s">
+        <v>414</v>
+      </c>
+      <c r="L2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" t="s">
+        <v>415</v>
+      </c>
+      <c r="N2" t="s">
+        <v>416</v>
+      </c>
+      <c r="O2" t="s">
+        <v>417</v>
+      </c>
+      <c r="P2" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>340</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="P2" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" t="s">
+        <v>370</v>
+      </c>
+      <c r="K3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L3" t="s">
+        <v>334</v>
+      </c>
+      <c r="M3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" t="s">
+        <v>117</v>
+      </c>
+      <c r="O3" t="s">
+        <v>334</v>
+      </c>
+      <c r="P3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" t="s">
         <v>419</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="s">
         <v>420</v>
-      </c>
-      <c r="K4" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>421</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4541,53 +4457,52 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>422</v>
       </c>
+      <c r="D2" t="s">
+        <v>340</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>127</v>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D3" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4596,124 +4511,123 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="I1" s="2" t="s">
-        <v>226</v>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>225</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
         <v>424</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" t="s">
         <v>425</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
         <v>426</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" t="s">
+        <v>369</v>
+      </c>
+      <c r="J3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>427</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>341</v>
+      <c r="B4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>430</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C5" t="s">
         <v>429</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="E5">
         <v>10</v>
       </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="J5" t="s">
         <v>432</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E5" s="2">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>433</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4722,130 +4636,129 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C1" t="s">
         <v>434</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
         <v>435</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>436</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" t="s">
         <v>437</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" t="s">
         <v>438</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>439</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" t="s">
         <v>440</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" t="s">
         <v>441</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
         <v>442</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>443</v>
       </c>
+      <c r="C2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H2" t="s">
+        <v>449</v>
+      </c>
+      <c r="I2" t="s">
+        <v>450</v>
+      </c>
+      <c r="J2" t="s">
+        <v>451</v>
+      </c>
+      <c r="K2" t="s">
+        <v>424</v>
+      </c>
+      <c r="L2" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="J2" s="2" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" t="s">
         <v>452</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="L3" t="s">
         <v>118</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4855,84 +4768,83 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E2" t="s">
         <v>454</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s">
         <v>455</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I2" t="s">
         <v>456</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4941,134 +4853,133 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1"/>
+    <col min="6" max="6" width="39.5" customWidth="1"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1"/>
+    <col min="8" max="8" width="32.25" customWidth="1"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1" t="s">
         <v>459</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
         <v>460</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>461</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" t="s">
         <v>462</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" t="s">
         <v>463</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" t="s">
         <v>464</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>465</v>
       </c>
-      <c r="I1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>466</v>
       </c>
+      <c r="C2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F2" t="s">
+        <v>470</v>
+      </c>
+      <c r="G2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I2" t="s">
+        <v>473</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I2" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>475</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" t="s">
         <v>476</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" t="s">
         <v>477</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" t="s">
         <v>478</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" t="s">
         <v>479</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" t="s">
         <v>480</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>481</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
   <si>
     <t>Id</t>
   </si>
@@ -346,6 +346,9 @@
     <t>模型大小倍率</t>
   </si>
   <si>
+    <t>模型偏移</t>
+  </si>
+  <si>
     <t>精英化</t>
   </si>
   <si>
@@ -412,6 +415,12 @@
     <t>可选技能</t>
   </si>
   <si>
+    <t>血条</t>
+  </si>
+  <si>
+    <t>技力条</t>
+  </si>
+  <si>
     <t>高度</t>
   </si>
   <si>
@@ -481,6 +490,9 @@
     <t>ModelScale</t>
   </si>
   <si>
+    <t>ModelOffset</t>
+  </si>
+  <si>
     <t>engName</t>
   </si>
   <si>
@@ -577,6 +589,9 @@
     <t>HpBarType</t>
   </si>
   <si>
+    <t>SpBarType</t>
+  </si>
+  <si>
     <t>Height</t>
   </si>
   <si>
@@ -682,6 +697,9 @@
     <t>float</t>
   </si>
   <si>
+    <t>UnityEngine.Vector3</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -718,6 +736,12 @@
     <t>CCB普攻,起飞</t>
   </si>
   <si>
+    <t>小型:蓝</t>
+  </si>
+  <si>
+    <t>小型:绿</t>
+  </si>
+  <si>
     <t>地面位</t>
   </si>
   <si>
@@ -1681,9 +1705,6 @@
     <t>ForwordDirection</t>
   </si>
   <si>
-    <t>UnityEngine.Vector3</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -1766,37 +1787,14 @@
   </si>
   <si>
     <t>/Spine/丰川祥子/back/char_4182_oblvns_avemujica_1.skel.bytes</t>
-  </si>
-  <si>
-    <t>血条</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>技力条</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpBarType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型:蓝</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型:绿</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1808,34 +1806,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1865,19 +1835,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2182,777 +2152,956 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1"/>
+    <col min="1" max="2" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BU5"/>
+  <dimension ref="A1:BV5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
-    <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1"/>
-    <col min="7" max="7" width="8.25" customWidth="1"/>
-    <col min="8" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="4.08203125" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1"/>
-    <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.75" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="10.25" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1"/>
-    <col min="23" max="23" width="10.75" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1"/>
-    <col min="26" max="26" width="10.75" customWidth="1"/>
-    <col min="27" max="28" width="9" customWidth="1"/>
-    <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1"/>
-    <col min="31" max="32" width="9" customWidth="1"/>
-    <col min="33" max="33" width="9.75" customWidth="1"/>
-    <col min="34" max="34" width="7.83203125" customWidth="1"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1"/>
-    <col min="36" max="36" width="13.83203125" customWidth="1"/>
-    <col min="37" max="37" width="34.5" customWidth="1"/>
-    <col min="38" max="40" width="9.83203125" customWidth="1"/>
-    <col min="41" max="44" width="9" customWidth="1"/>
-    <col min="45" max="45" width="12.5" customWidth="1"/>
-    <col min="46" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="24.33203125" customWidth="1"/>
-    <col min="53" max="53" width="9" customWidth="1"/>
-    <col min="54" max="54" width="17.75" customWidth="1"/>
-    <col min="55" max="55" width="7.83203125" customWidth="1"/>
-    <col min="56" max="57" width="9" customWidth="1"/>
-    <col min="58" max="58" width="24.25" customWidth="1"/>
-    <col min="59" max="59" width="13.25" customWidth="1"/>
-    <col min="60" max="60" width="16.08203125" customWidth="1"/>
-    <col min="61" max="61" width="8" customWidth="1"/>
-    <col min="62" max="65" width="9" customWidth="1"/>
-    <col min="66" max="66" width="39.58203125" customWidth="1"/>
-    <col min="67" max="67" width="14" customWidth="1"/>
-    <col min="68" max="68" width="14.83203125" customWidth="1"/>
-    <col min="69" max="72" width="14" customWidth="1"/>
-    <col min="73" max="73" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
+    <col min="8" max="8" width="9" customWidth="1" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="9" customWidth="1" style="2"/>
+    <col min="11" max="11" width="9" customWidth="1" style="2"/>
+    <col min="12" max="12" width="6" customWidth="1" style="2"/>
+    <col min="13" max="13" width="4.08203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="5.58203125" customWidth="1" style="2"/>
+    <col min="15" max="15" width="4" customWidth="1" style="2"/>
+    <col min="16" max="16" width="7.75" customWidth="1" style="2"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1" style="2"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="3.83203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="3.58203125" customWidth="1" style="2"/>
+    <col min="22" max="22" width="10.25" customWidth="1" style="2"/>
+    <col min="23" max="23" width="9.58203125" customWidth="1" style="2"/>
+    <col min="24" max="24" width="10.75" customWidth="1" style="2"/>
+    <col min="25" max="25" width="12.83203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="13.08203125" customWidth="1" style="2"/>
+    <col min="27" max="27" width="10.75" customWidth="1" style="2"/>
+    <col min="28" max="28" width="9" customWidth="1" style="2"/>
+    <col min="29" max="29" width="9" customWidth="1" style="2"/>
+    <col min="30" max="30" width="8" customWidth="1" style="2"/>
+    <col min="31" max="31" width="17.08203125" customWidth="1" style="2"/>
+    <col min="32" max="32" width="9" customWidth="1" style="2"/>
+    <col min="33" max="33" width="9" customWidth="1" style="2"/>
+    <col min="34" max="34" width="9.75" customWidth="1" style="2"/>
+    <col min="35" max="35" width="7.83203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="15.83203125" customWidth="1" style="2"/>
+    <col min="37" max="37" width="13.83203125" customWidth="1" style="2"/>
+    <col min="38" max="38" width="34.5" customWidth="1" style="2"/>
+    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="9.83203125" customWidth="1" style="2"/>
+    <col min="41" max="41" width="9.83203125" customWidth="1" style="2"/>
+    <col min="42" max="42" width="9" customWidth="1" style="2"/>
+    <col min="43" max="43" width="9" customWidth="1" style="2"/>
+    <col min="44" max="44" width="9" customWidth="1" style="2"/>
+    <col min="45" max="45" width="9" customWidth="1" style="2"/>
+    <col min="46" max="46" width="12.5" customWidth="1" style="2"/>
+    <col min="47" max="47" width="9" customWidth="1" style="2"/>
+    <col min="48" max="48" width="9" customWidth="1" style="2"/>
+    <col min="49" max="49" width="9" customWidth="1" style="2"/>
+    <col min="50" max="50" width="9" customWidth="1" style="2"/>
+    <col min="51" max="51" width="9" customWidth="1" style="2"/>
+    <col min="52" max="52" width="9" customWidth="1" style="2"/>
+    <col min="53" max="53" width="24.33203125" customWidth="1" style="2"/>
+    <col min="54" max="54" width="9" customWidth="1" style="2"/>
+    <col min="55" max="55" width="17.75" customWidth="1" style="2"/>
+    <col min="56" max="56" width="7.83203125" customWidth="1" style="2"/>
+    <col min="57" max="57" width="9" customWidth="1" style="2"/>
+    <col min="58" max="58" width="9" customWidth="1" style="2"/>
+    <col min="59" max="59" width="24.25" customWidth="1" style="2"/>
+    <col min="60" max="60" width="13.25" customWidth="1" style="2"/>
+    <col min="61" max="61" width="16.08203125" customWidth="1" style="2"/>
+    <col min="62" max="62" width="8" customWidth="1" style="2"/>
+    <col min="63" max="63" width="9" customWidth="1" style="2"/>
+    <col min="64" max="64" width="9" customWidth="1" style="2"/>
+    <col min="65" max="65" width="9" customWidth="1" style="2"/>
+    <col min="66" max="66" width="9" customWidth="1" style="2"/>
+    <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
+    <col min="68" max="68" width="14" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="71" max="71" width="14" customWidth="1" style="2"/>
+    <col min="72" max="72" width="14" customWidth="1" style="2"/>
+    <col min="73" max="73" width="14" customWidth="1" style="2"/>
+    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O1" t="s">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="O1" s="2"/>
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="U1" t="s">
+      <c r="S1" s="2"/>
+      <c r="T1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="V1" t="s">
+      <c r="U1" s="2"/>
+      <c r="V1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="X1" t="s">
+      <c r="W1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>481</v>
+        <v>29</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AP1" t="s">
         <v>30</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BE1" s="2"/>
+      <c r="BF1" s="2"/>
+      <c r="BG1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="BI1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BJ1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="BK1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+      <c r="BU1" s="2"/>
+      <c r="BV1" s="2"/>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="C2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" t="s">
+      <c r="G2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" t="s">
+      <c r="H2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
+      <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="J2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" t="s">
+      <c r="K2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" t="s">
+      <c r="L2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" t="s">
+      <c r="M2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="N2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
+      <c r="O2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" t="s">
+      <c r="P2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="R2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="S2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="T2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="U2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="V2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="W2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="X2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="AK2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="AN2" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" t="s">
         <v>87</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="AW2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BE2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BG2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BI2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BN2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BO2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BP2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="BU2" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>116</v>
       </c>
+      <c r="BR2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" t="s">
-        <v>119</v>
-      </c>
-      <c r="M3" t="s">
-        <v>119</v>
-      </c>
-      <c r="N3" t="s">
-        <v>119</v>
-      </c>
-      <c r="O3" t="s">
-        <v>119</v>
-      </c>
-      <c r="P3" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>119</v>
-      </c>
-      <c r="R3" t="s">
-        <v>119</v>
-      </c>
-      <c r="S3" t="s">
-        <v>119</v>
-      </c>
-      <c r="T3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U3" t="s">
-        <v>118</v>
-      </c>
-      <c r="V3" t="s">
-        <v>119</v>
-      </c>
-      <c r="W3" t="s">
-        <v>119</v>
-      </c>
-      <c r="X3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>120</v>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>484</v>
+        <v>126</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AX3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AT3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AY3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ3" t="s">
+      <c r="AU3" s="2"/>
+      <c r="AV3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="BA3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BI3" t="s">
+      <c r="AW3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>126</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>118</v>
+      <c r="AY3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2"/>
+      <c r="BD4" s="2"/>
+      <c r="BE4" s="2"/>
+      <c r="BF4" s="2"/>
+      <c r="BG4" s="2"/>
+      <c r="BH4" s="2"/>
+      <c r="BI4" s="2"/>
+      <c r="BJ4" s="2"/>
+      <c r="BK4" s="2"/>
+      <c r="BL4" s="2"/>
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2"/>
+      <c r="BO4" s="2"/>
+      <c r="BP4" s="2"/>
+      <c r="BQ4" s="2"/>
+      <c r="BR4" s="2"/>
+      <c r="BS4" s="2"/>
+      <c r="BT4" s="2"/>
+      <c r="BU4" s="2"/>
+      <c r="BV4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5">
+      <c r="B5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
+        <v>2</v>
+      </c>
+      <c r="K5" s="2">
         <v>90</v>
       </c>
-      <c r="K5">
+      <c r="L5" s="2">
         <v>10000</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2"/>
+      <c r="N5" s="2">
         <v>500</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="2"/>
+      <c r="P5" s="2">
         <v>500</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2">
         <v>20</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="2"/>
+      <c r="T5" s="2">
         <v>10</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="2"/>
+      <c r="V5" s="2">
         <v>0.5</v>
       </c>
-      <c r="V5">
+      <c r="W5" s="2">
         <v>70</v>
       </c>
-      <c r="Y5">
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2">
         <v>0.05</v>
       </c>
-      <c r="Z5">
-        <v>2</v>
-      </c>
-      <c r="AC5">
+      <c r="AA5" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2">
         <v>1</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>129</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>130</v>
-      </c>
-      <c r="AM5" s="2" t="s">
-        <v>485</v>
-      </c>
+      <c r="AK5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM5" s="2"/>
       <c r="AN5" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ5">
-        <v>2</v>
-      </c>
-      <c r="AR5">
+        <v>137</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AR5" s="2">
+        <v>2</v>
+      </c>
+      <c r="AS5" s="2">
         <v>0.5</v>
       </c>
-      <c r="AY5">
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2"/>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2">
         <v>0.25</v>
       </c>
-      <c r="BD5" t="s">
-        <v>132</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>133</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>134</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>135</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>136</v>
-      </c>
-      <c r="BJ5">
+      <c r="BA5" s="2"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2"/>
+      <c r="BD5" s="2"/>
+      <c r="BE5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BF5" s="2"/>
+      <c r="BG5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BK5" s="2">
         <v>6</v>
       </c>
-      <c r="BK5" t="s">
-        <v>137</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>139</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>140</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>141</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>141</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>142</v>
-      </c>
-      <c r="BU5">
+      <c r="BL5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="BN5" s="2"/>
+      <c r="BO5" s="2"/>
+      <c r="BP5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BR5" s="2"/>
+      <c r="BS5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BV5" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2960,6 +3109,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2969,1299 +3119,1299 @@
   <dimension ref="A1:DI704"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="20.58203125" customWidth="1"/>
-    <col min="9" max="9" width="10.75" customWidth="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1"/>
-    <col min="17" max="17" width="21.5" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1"/>
-    <col min="22" max="22" width="17.75" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1"/>
-    <col min="24" max="24" width="18.5" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1"/>
-    <col min="32" max="32" width="13.75" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1"/>
-    <col min="36" max="36" width="12.5" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1"/>
-    <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1"/>
-    <col min="47" max="47" width="12.25" customWidth="1"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1"/>
-    <col min="51" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="7" customWidth="1"/>
-    <col min="53" max="53" width="11.75" customWidth="1"/>
-    <col min="54" max="54" width="19.75" customWidth="1"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1"/>
-    <col min="56" max="56" width="8.5" customWidth="1"/>
-    <col min="57" max="57" width="13.5" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1"/>
-    <col min="60" max="60" width="8.25" customWidth="1"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1"/>
-    <col min="68" max="70" width="11.25" customWidth="1"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1"/>
-    <col min="72" max="73" width="8" customWidth="1"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1"/>
-    <col min="75" max="76" width="8.5" customWidth="1"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1"/>
-    <col min="80" max="80" width="13.5" customWidth="1"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1"/>
-    <col min="82" max="82" width="15.75" customWidth="1"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1"/>
-    <col min="86" max="86" width="9" customWidth="1"/>
-    <col min="87" max="87" width="16" customWidth="1"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1"/>
-    <col min="93" max="98" width="9" customWidth="1"/>
-    <col min="99" max="99" width="14" customWidth="1"/>
-    <col min="100" max="100" width="8" customWidth="1"/>
-    <col min="101" max="101" width="9" customWidth="1"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1"/>
-    <col min="103" max="103" width="13.75" customWidth="1"/>
-    <col min="104" max="109" width="9" customWidth="1"/>
-    <col min="110" max="110" width="15.5" customWidth="1"/>
-    <col min="111" max="113" width="9" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1" style="2"/>
+    <col min="9" max="9" width="10.75" customWidth="1" style="2"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="15" customWidth="1" style="2"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
+    <col min="51" max="51" width="9" customWidth="1" style="2"/>
+    <col min="52" max="52" width="7" customWidth="1" style="2"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
+    <col min="72" max="73" width="8" customWidth="1" style="2"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
+    <col min="86" max="86" width="9" customWidth="1" style="2"/>
+    <col min="87" max="87" width="16" customWidth="1" style="2"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
+    <col min="93" max="98" width="9" customWidth="1" style="2"/>
+    <col min="99" max="99" width="14" customWidth="1" style="2"/>
+    <col min="100" max="100" width="8" customWidth="1" style="2"/>
+    <col min="101" max="101" width="9" customWidth="1" style="2"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
+    <col min="104" max="109" width="9" customWidth="1" style="2"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
+    <col min="111" max="113" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G1" t="s">
-        <v>147</v>
-      </c>
-      <c r="H1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J1" t="s">
-        <v>150</v>
-      </c>
-      <c r="K1" t="s">
+    <row r="1">
+      <c r="B1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="L1" t="s">
+      <c r="D1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M1" t="s">
+      <c r="E1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="N1" t="s">
+      <c r="F1" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="O1" t="s">
+      <c r="G1" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="P1" t="s">
+      <c r="H1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="I1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="R1" t="s">
+      <c r="J1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="S1" t="s">
+      <c r="K1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T1" t="s">
+      <c r="L1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="U1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="M1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="W1" t="s">
+      <c r="N1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="X1" t="s">
+      <c r="O1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="P1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="R1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="S1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="T1" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="U1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="W1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="X1" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>199</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BJ1" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="BK1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="BR1" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="BT1" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="BV1" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="BW1" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="BX1" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="BY1" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CA1" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CB1" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CC1" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CD1" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CE1" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CF1" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CG1" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CH1" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CI1" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="CR1" t="s">
-        <v>209</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CK1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CM1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CN1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CO1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CP1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>238</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="CQ1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="CR1" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="CS1" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="CT1" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="CU1" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="CV1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="CW1" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="CX1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="CY1" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="CZ1" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="DA1" s="2" t="s">
         <v>248</v>
       </c>
+      <c r="DB1" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="DC1" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="DD1" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="DE1" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="DF1" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="DG1" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="DH1" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="DI1" s="2" t="s">
+        <v>256</v>
+      </c>
     </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>251</v>
-      </c>
-      <c r="I2" t="s">
-        <v>252</v>
-      </c>
-      <c r="J2" t="s">
-        <v>253</v>
-      </c>
-      <c r="K2" t="s">
-        <v>254</v>
-      </c>
-      <c r="L2" t="s">
-        <v>255</v>
-      </c>
-      <c r="M2" t="s">
-        <v>256</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="O2" t="s">
+      <c r="F2" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="P2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="I2" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="R2" t="s">
+      <c r="J2" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="S2" t="s">
+      <c r="K2" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="T2" t="s">
+      <c r="L2" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="U2" t="s">
+      <c r="M2" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="V2" t="s">
+      <c r="N2" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="W2" t="s">
+      <c r="O2" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="X2" t="s">
+      <c r="P2" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="R2" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="S2" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="T2" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="U2" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="V2" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="W2" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="X2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="AW2" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BE2" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="BO2" t="s">
-        <v>81</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BG2" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BI2" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="BU2" t="s">
-        <v>96</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BN2" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BO2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="BP2" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="BR2" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="BS2" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="BT2" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BV2" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="BW2" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="BX2" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="BY2" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="BZ2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CA2" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CB2" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CC2" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CD2" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CE2" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CF2" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CG2" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CH2" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CI2" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CJ2" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CK2" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CM2" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CN2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CO2" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CP2" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CQ2" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="CR2" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="CS2" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="CT2" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="CU2" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="CV2" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="CW2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="CX2" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="CY2" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="CZ2" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="DI2" t="s">
+      <c r="DA2" s="2" t="s">
         <v>354</v>
       </c>
+      <c r="DB2" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="DC2" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="DD2" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="DE2" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="DF2" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="DG2" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="DH2" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="DI2" s="2" t="s">
+        <v>362</v>
+      </c>
     </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>355</v>
-      </c>
-      <c r="K3" t="s">
-        <v>356</v>
-      </c>
-      <c r="L3" t="s">
-        <v>357</v>
-      </c>
-      <c r="M3" t="s">
-        <v>119</v>
-      </c>
-      <c r="N3" t="s">
-        <v>119</v>
-      </c>
-      <c r="O3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="P3" t="s">
+      <c r="J3" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="T3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="R3" t="s">
+      <c r="X3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="S3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" t="s">
-        <v>118</v>
-      </c>
-      <c r="U3" t="s">
-        <v>118</v>
-      </c>
-      <c r="V3" t="s">
-        <v>118</v>
-      </c>
-      <c r="W3" t="s">
-        <v>117</v>
-      </c>
-      <c r="X3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>358</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="Y3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AK3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>359</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>360</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>361</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>362</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>361</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>363</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>364</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>365</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>365</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>366</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CG3" t="s">
+      <c r="AK3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO3" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="CH3" t="s">
+      <c r="AP3" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="CI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" t="s">
+      <c r="AQ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="AU3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BH3" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="CL3" t="s">
+      <c r="BI3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BO3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="CM3" t="s">
+      <c r="BP3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BU3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="CN3" t="s">
+      <c r="BV3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="CO3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>366</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>117</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>370</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>371</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>371</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>370</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>370</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>370</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>370</v>
-      </c>
-      <c r="DC3" t="s">
-        <v>370</v>
-      </c>
-      <c r="DD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DE3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DG3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DH3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DI3" t="s">
-        <v>117</v>
+      <c r="CA3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="CB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CC3" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="CI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CQ3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CR3" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="CS3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CT3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CU3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="CV3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="CW3" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="CX3" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="CY3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="CZ3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="DA3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="DB3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="DC3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="DD3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DF3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DG3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DH3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DI3" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>372</v>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>380</v>
       </c>
     </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>373</v>
-      </c>
-      <c r="C6" t="s">
-        <v>374</v>
-      </c>
-      <c r="K6" t="s">
-        <v>375</v>
-      </c>
-      <c r="AC6">
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC6" s="2">
         <v>4</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>376</v>
-      </c>
-      <c r="AN6">
+      <c r="AJ6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="AN6" s="2">
         <v>1</v>
       </c>
-      <c r="AO6" t="s">
-        <v>377</v>
-      </c>
-      <c r="AV6">
+      <c r="AO6" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="AV6" s="2">
         <v>15</v>
       </c>
-      <c r="AX6" t="s">
-        <v>378</v>
-      </c>
-      <c r="AZ6">
+      <c r="AX6" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="AZ6" s="2">
         <v>0</v>
       </c>
-      <c r="BB6">
-        <v>2</v>
-      </c>
-      <c r="BD6">
+      <c r="BB6" s="2">
+        <v>2</v>
+      </c>
+      <c r="BD6" s="2">
         <v>1</v>
       </c>
-      <c r="CB6" t="s">
-        <v>57</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>379</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>380</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>381</v>
-      </c>
-      <c r="CN6" t="s">
+      <c r="CB6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG6" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="CH6" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="CI6" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="CY6" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="CY6" t="s">
-        <v>383</v>
+      <c r="J7" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="AV7" s="2">
+        <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>384</v>
-      </c>
-      <c r="C7" t="s">
-        <v>374</v>
-      </c>
-      <c r="J7" t="s">
-        <v>385</v>
-      </c>
-      <c r="K7" t="s">
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="AX8" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="AC7">
-        <v>2</v>
-      </c>
-      <c r="AD7">
+      <c r="AZ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="2">
+        <v>2</v>
+      </c>
+      <c r="BD8" s="2">
         <v>1</v>
       </c>
-      <c r="AO7" t="s">
-        <v>377</v>
-      </c>
-      <c r="AV7">
-        <v>2.5</v>
+      <c r="CL8" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="CY8" s="2" t="s">
+        <v>400</v>
       </c>
     </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>387</v>
-      </c>
-      <c r="C8" t="s">
-        <v>388</v>
-      </c>
-      <c r="K8" t="s">
-        <v>386</v>
-      </c>
-      <c r="L8" t="s">
-        <v>389</v>
-      </c>
-      <c r="AC8">
-        <v>2</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>390</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>378</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>2</v>
-      </c>
-      <c r="BD8">
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="AC10" s="2">
         <v>1</v>
       </c>
-      <c r="CL8" t="s">
-        <v>391</v>
-      </c>
-      <c r="CY8" t="s">
-        <v>392</v>
+      <c r="AG10" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="BD10" s="2">
+        <v>1</v>
+      </c>
+      <c r="BT10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="CN10" s="2" t="s">
+        <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>393</v>
-      </c>
-      <c r="C10" t="s">
-        <v>374</v>
-      </c>
-      <c r="K10" t="s">
-        <v>386</v>
-      </c>
-      <c r="L10" t="s">
-        <v>394</v>
-      </c>
-      <c r="AC10">
+    <row r="684">
+      <c r="CL684" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="CL686" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="CL687" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="CL689" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="CL696" s="2">
         <v>1</v>
       </c>
-      <c r="AG10" t="s">
-        <v>395</v>
-      </c>
-      <c r="BD10">
-        <v>1</v>
-      </c>
-      <c r="BT10">
-        <v>0.1</v>
-      </c>
-      <c r="CN10" t="s">
-        <v>396</v>
-      </c>
     </row>
-    <row r="684" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL684">
-        <v>0.15</v>
+    <row r="698">
+      <c r="CL698" s="2">
+        <v>0.4</v>
       </c>
     </row>
-    <row r="686" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL686">
-        <v>0.2</v>
+    <row r="699">
+      <c r="CL699" s="2">
+        <v>0.6</v>
       </c>
     </row>
-    <row r="687" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL687">
-        <v>0.1</v>
+    <row r="702">
+      <c r="CL702" s="2">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="689" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL689">
-        <v>0.2</v>
+    <row r="703">
+      <c r="CL703" s="2">
+        <v>0.667</v>
       </c>
     </row>
-    <row r="696" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL696">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="698" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL698">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="699" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL699">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="702" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL702">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="703" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL703">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="704" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL704">
+    <row r="704">
+      <c r="CL704" s="2">
         <v>0.2</v>
       </c>
     </row>
@@ -4269,6 +4419,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4278,177 +4429,178 @@
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1" style="2"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
+    <col min="3" max="6" width="9" customWidth="1" style="2"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
+    <col min="8" max="8" width="15" customWidth="1" style="2"/>
+    <col min="9" max="13" width="9" customWidth="1" style="2"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
-        <v>397</v>
-      </c>
-      <c r="F1" t="s">
-        <v>398</v>
-      </c>
-      <c r="G1" t="s">
-        <v>399</v>
-      </c>
-      <c r="H1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I1" t="s">
-        <v>401</v>
-      </c>
-      <c r="J1" t="s">
-        <v>402</v>
-      </c>
-      <c r="L1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="N1" t="s">
-        <v>405</v>
-      </c>
-      <c r="O1" t="s">
-        <v>406</v>
-      </c>
-      <c r="P1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F2" t="s">
-        <v>409</v>
-      </c>
-      <c r="G2" t="s">
-        <v>410</v>
-      </c>
-      <c r="H2" t="s">
-        <v>411</v>
-      </c>
-      <c r="I2" t="s">
-        <v>412</v>
-      </c>
-      <c r="J2" t="s">
-        <v>413</v>
-      </c>
-      <c r="K2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>415</v>
-      </c>
-      <c r="N2" t="s">
-        <v>416</v>
-      </c>
-      <c r="O2" t="s">
-        <v>417</v>
-      </c>
-      <c r="P2" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>370</v>
-      </c>
-      <c r="K3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L3" t="s">
-        <v>334</v>
-      </c>
-      <c r="M3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" t="s">
-        <v>334</v>
-      </c>
-      <c r="P3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>396</v>
-      </c>
-      <c r="C4" t="s">
-        <v>419</v>
-      </c>
-      <c r="K4">
+      <c r="C4" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="K4" s="2">
         <v>5</v>
       </c>
-      <c r="Q4" t="s">
-        <v>420</v>
+      <c r="Q4" s="2" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4457,52 +4609,53 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>421</v>
+      <c r="C1" s="2" t="s">
+        <v>429</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D2" t="s">
-        <v>340</v>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D3" t="s">
-        <v>126</v>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4511,123 +4664,124 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="10" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I1" t="s">
-        <v>225</v>
+    <row r="1">
+      <c r="I1" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" t="s">
-        <v>424</v>
-      </c>
-      <c r="G2" t="s">
-        <v>425</v>
-      </c>
-      <c r="H2" t="s">
-        <v>426</v>
-      </c>
-      <c r="I2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J2" t="s">
-        <v>340</v>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I3" t="s">
-        <v>369</v>
-      </c>
-      <c r="J3" t="s">
-        <v>126</v>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>427</v>
-      </c>
-      <c r="B4" t="s">
-        <v>428</v>
-      </c>
-      <c r="C4" t="s">
-        <v>429</v>
-      </c>
-      <c r="E4">
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E4" s="2">
         <v>10</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>430</v>
+      <c r="J4" s="2" t="s">
+        <v>438</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>380</v>
-      </c>
-      <c r="B5" t="s">
-        <v>431</v>
-      </c>
-      <c r="C5" t="s">
-        <v>429</v>
-      </c>
-      <c r="E5">
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E5" s="2">
         <v>10</v>
       </c>
-      <c r="J5" t="s">
-        <v>432</v>
+      <c r="J5" s="2" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4636,129 +4790,130 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1"/>
-    <col min="5" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28" customWidth="1" style="2"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
+    <col min="12" max="12" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D1" t="s">
-        <v>435</v>
-      </c>
-      <c r="E1" t="s">
-        <v>436</v>
-      </c>
-      <c r="F1" t="s">
-        <v>437</v>
-      </c>
-      <c r="H1" t="s">
-        <v>438</v>
-      </c>
-      <c r="I1" t="s">
-        <v>439</v>
-      </c>
-      <c r="J1" t="s">
-        <v>440</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="B1" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="L1" t="s">
+      <c r="C1" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>450</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D2" t="s">
-        <v>445</v>
-      </c>
-      <c r="E2" t="s">
-        <v>446</v>
-      </c>
-      <c r="F2" t="s">
-        <v>447</v>
-      </c>
-      <c r="G2" t="s">
-        <v>448</v>
-      </c>
-      <c r="H2" t="s">
-        <v>449</v>
-      </c>
-      <c r="I2" t="s">
-        <v>450</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="B2" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="K2" t="s">
-        <v>424</v>
-      </c>
-      <c r="L2" t="s">
-        <v>98</v>
+      <c r="C2" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" t="s">
-        <v>452</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L3" t="s">
-        <v>118</v>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4768,49 +4923,49 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1"/>
-    <col min="2" max="2" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
+    <col min="7" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" t="s">
-        <v>455</v>
-      </c>
-      <c r="H2" t="s">
-        <v>278</v>
-      </c>
-      <c r="I2" t="s">
-        <v>456</v>
-      </c>
-      <c r="J2" t="s">
-        <v>54</v>
+      <c r="B2" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4824,27 +4979,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4853,133 +5009,134 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1"/>
-    <col min="6" max="6" width="39.5" customWidth="1"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1"/>
-    <col min="8" max="8" width="32.25" customWidth="1"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D1" t="s">
-        <v>460</v>
-      </c>
-      <c r="E1" t="s">
-        <v>461</v>
-      </c>
-      <c r="F1" t="s">
-        <v>462</v>
-      </c>
-      <c r="G1" t="s">
-        <v>463</v>
-      </c>
-      <c r="H1" t="s">
-        <v>464</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="B1" s="2" t="s">
         <v>465</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>472</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F2" t="s">
-        <v>470</v>
-      </c>
-      <c r="G2" t="s">
-        <v>471</v>
-      </c>
-      <c r="H2" t="s">
-        <v>472</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="B2" s="2" t="s">
         <v>473</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>480</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>474</v>
-      </c>
-      <c r="C4">
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>475</v>
-      </c>
-      <c r="E4" t="s">
-        <v>476</v>
-      </c>
-      <c r="F4" t="s">
-        <v>477</v>
-      </c>
-      <c r="G4" t="s">
-        <v>478</v>
-      </c>
-      <c r="H4" t="s">
-        <v>479</v>
-      </c>
-      <c r="I4" t="s">
-        <v>480</v>
+      <c r="D4" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
   <si>
     <t>Id</t>
   </si>
@@ -670,6 +670,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -1834,11 +1840,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -2152,30 +2161,30 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2188,7 +2197,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV5"/>
+  <dimension ref="A1:BX5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2258,13 +2267,15 @@
     <col min="65" max="65" width="9" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2436,6 +2447,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2656,6 +2669,12 @@
       <c r="BV2" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2665,7 +2684,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2673,206 +2692,212 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="AF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="AQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AS3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="BA3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="BB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX3" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="4">
@@ -2950,19 +2975,21 @@
       <c r="BT4" s="2"/>
       <c r="BU4" s="2"/>
       <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -3023,21 +3050,21 @@
         <v>4</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AR5" s="2">
         <v>2</v>
@@ -3059,49 +3086,51 @@
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BF5" s="2"/>
       <c r="BG5" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BH5" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BI5" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BJ5" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BK5" s="2">
         <v>6</v>
       </c>
       <c r="BL5" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BM5" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BN5" s="2"/>
       <c r="BO5" s="2"/>
-      <c r="BP5" s="2" t="s">
-        <v>147</v>
-      </c>
+      <c r="BP5" s="2"/>
       <c r="BQ5" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2" t="s">
         <v>149</v>
       </c>
+      <c r="BR5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BS5" s="2"/>
       <c r="BT5" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BU5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BV5" s="2">
+        <v>151</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3119,1299 +3148,1299 @@
   <dimension ref="A1:DI704"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="20.58203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="10.75" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="113" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1" style="3"/>
+    <col min="9" max="9" width="10.75" customWidth="1" style="3"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
+    <col min="40" max="40" width="15" customWidth="1" style="3"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="3"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="3"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9" customWidth="1" style="3"/>
+    <col min="52" max="52" width="7" customWidth="1" style="3"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="3"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
+    <col min="72" max="73" width="8" customWidth="1" style="3"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
+    <col min="86" max="86" width="9" customWidth="1" style="3"/>
+    <col min="87" max="87" width="16" customWidth="1" style="3"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="3"/>
+    <col min="93" max="98" width="9" customWidth="1" style="3"/>
+    <col min="99" max="99" width="14" customWidth="1" style="3"/>
+    <col min="100" max="100" width="8" customWidth="1" style="3"/>
+    <col min="101" max="101" width="9" customWidth="1" style="3"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
+    <col min="104" max="109" width="9" customWidth="1" style="3"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
+    <col min="111" max="113" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="U1" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="BK1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BT1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BV1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BW1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BX1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="BY1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CA1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CB1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CC1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CD1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CE1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CF1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CG1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CI1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CK1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CL1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CM1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CN1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CO1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CP1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CR1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="CS1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="DA1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DD1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DE1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DF1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DG1" s="3" t="s">
         <v>256</v>
+      </c>
+      <c r="DH1" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AG2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AI2" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AK2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AL2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AM2" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AN2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AO2" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AP2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AU2" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AV2" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AW2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AX2" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="AY2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BA2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BB2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BC2" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BE2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BG2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BH2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BI2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BK2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BL2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BM2" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="BP2" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BP2" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BQ2" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BR2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BS2" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="BU2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BV2" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BW2" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BX2" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="BY2" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="BZ2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CA2" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CB2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CC2" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CD2" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CE2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CF2" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CG2" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CH2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CI2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CJ2" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CK2" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CL2" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CM2" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CN2" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CO2" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CP2" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CQ2" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CR2" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CS2" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CT2" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CU2" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CV2" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CW2" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CX2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="CY2" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="CZ2" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DA2" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DB2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DC2" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DD2" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DE2" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DF2" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DG2" s="3" t="s">
         <v>362</v>
+      </c>
+      <c r="DH2" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="DI2" s="3" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="U3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="V3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="W3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AW3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BA3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="BP3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="BQ3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="BS3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="BT3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY3" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="BZ3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CA3" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="CB3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CC3" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="CD3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CE3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="CH3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="CI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="CK3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="CL3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AJ3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="CH3" s="2" t="s">
+      <c r="CN3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CP3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR3" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="CI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>122</v>
+      <c r="CS3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CT3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CU3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CV3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="CW3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="CX3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="CY3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="CZ3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="DA3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="DB3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="DC3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="DD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DI3" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>380</v>
+      <c r="A4" s="3" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="K6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="C6" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="AC6" s="3">
         <v>4</v>
       </c>
-      <c r="AJ6" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AN6" s="2">
+      <c r="AJ6" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AN6" s="3">
         <v>1</v>
       </c>
-      <c r="AO6" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AV6" s="2">
+      <c r="AO6" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AV6" s="3">
         <v>15</v>
       </c>
-      <c r="AX6" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="AZ6" s="2">
+      <c r="AX6" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="AZ6" s="3">
         <v>0</v>
       </c>
-      <c r="BB6" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD6" s="2">
+      <c r="BB6" s="3">
+        <v>2</v>
+      </c>
+      <c r="BD6" s="3">
         <v>1</v>
       </c>
-      <c r="CB6" s="2" t="s">
+      <c r="CB6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="CG6" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CH6" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CI6" s="2" t="s">
+      <c r="CG6" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="CN6" s="2" t="s">
+      <c r="CH6" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="CY6" s="2" t="s">
+      <c r="CI6" s="3" t="s">
         <v>391</v>
+      </c>
+      <c r="CN6" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="CY6" s="3" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="AC7" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="2">
+      <c r="C7" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="3">
         <v>1</v>
       </c>
-      <c r="AO7" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AV7" s="2">
+      <c r="AO7" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AV7" s="3">
         <v>2.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="A8" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="AX8" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="AZ8" s="2">
+      <c r="L8" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="AX8" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="AZ8" s="3">
         <v>0</v>
       </c>
-      <c r="BB8" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD8" s="2">
+      <c r="BB8" s="3">
+        <v>2</v>
+      </c>
+      <c r="BD8" s="3">
         <v>1</v>
       </c>
-      <c r="CL8" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="CY8" s="2" t="s">
-        <v>400</v>
+      <c r="CL8" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="CY8" s="3" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="AC10" s="2">
+      <c r="A10" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="AC10" s="3">
         <v>1</v>
       </c>
-      <c r="AG10" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="BD10" s="2">
+      <c r="AG10" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="BD10" s="3">
         <v>1</v>
       </c>
-      <c r="BT10" s="2">
+      <c r="BT10" s="3">
         <v>0.1</v>
       </c>
-      <c r="CN10" s="2" t="s">
-        <v>404</v>
+      <c r="CN10" s="3" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="684">
-      <c r="CL684" s="2">
+      <c r="CL684" s="3">
         <v>0.15</v>
       </c>
     </row>
     <row r="686">
-      <c r="CL686" s="2">
+      <c r="CL686" s="3">
         <v>0.2</v>
       </c>
     </row>
     <row r="687">
-      <c r="CL687" s="2">
+      <c r="CL687" s="3">
         <v>0.1</v>
       </c>
     </row>
     <row r="689">
-      <c r="CL689" s="2">
+      <c r="CL689" s="3">
         <v>0.2</v>
       </c>
     </row>
     <row r="696">
-      <c r="CL696" s="2">
+      <c r="CL696" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="698">
-      <c r="CL698" s="2">
+      <c r="CL698" s="3">
         <v>0.4</v>
       </c>
     </row>
     <row r="699">
-      <c r="CL699" s="2">
+      <c r="CL699" s="3">
         <v>0.6</v>
       </c>
     </row>
     <row r="702">
-      <c r="CL702" s="2">
+      <c r="CL702" s="3">
         <v>0.5</v>
       </c>
     </row>
     <row r="703">
-      <c r="CL703" s="2">
+      <c r="CL703" s="3">
         <v>0.667</v>
       </c>
     </row>
     <row r="704">
-      <c r="CL704" s="2">
+      <c r="CL704" s="3">
         <v>0.2</v>
       </c>
     </row>
@@ -4429,171 +4458,171 @@
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1" style="3"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
+    <col min="3" max="6" width="9" customWidth="1" style="3"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
+    <col min="8" max="8" width="15" customWidth="1" style="3"/>
+    <col min="9" max="13" width="9" customWidth="1" style="3"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="3"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>415</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>348</v>
+      <c r="O2" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>132</v>
+      <c r="L3" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="K4" s="2">
+      <c r="A4" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="K4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>428</v>
+      <c r="Q4" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -4609,46 +4638,46 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9" customWidth="1" style="3"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>429</v>
+      <c r="C1" s="3" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>348</v>
+      <c r="C2" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>132</v>
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4664,117 +4693,117 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="9" customWidth="1" style="3"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="I1" s="2" t="s">
-        <v>233</v>
+      <c r="I1" s="3" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>348</v>
+      <c r="G2" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>132</v>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="E4" s="2">
+      <c r="B4" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>438</v>
+      <c r="J4" s="3" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>10</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>440</v>
+      <c r="J5" s="3" t="s">
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -4790,123 +4819,123 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="28" customWidth="1" style="3"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>450</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -4923,45 +4952,45 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
+    <col min="7" max="9" width="9" customWidth="1" style="3"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4979,22 +5008,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -5009,128 +5038,128 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1" style="3"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1" style="3"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="39.5" customWidth="1" style="3"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="32.25" customWidth="1" style="3"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>472</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>480</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="A4" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>487</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBAB61F-781A-4110-9008-D196737AEC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C269FA-FD07-4F4F-B674-D1DE64F396FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="509">
   <si>
     <t>Id</t>
   </si>
@@ -1484,9 +1484,6 @@
   </si>
   <si>
     <t>Muzzle</t>
-  </si>
-  <si>
-    <t>神经损伤麻痹</t>
   </si>
   <si>
     <t>拉普兰德近战击中</t>
@@ -1829,10 +1826,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"Expression":"Buff.Skill.SkillData.DamageRate = Buff.Duration.value","绑定进度条":"圆环"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>数值变化</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1843,10 +1836,6 @@
     <t>{"t":["AgiAddFin"]}</t>
   </si>
   <si>
-    <t>{"绑定进度条":"入梦"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>CCB攻击叠层</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1875,6 +1864,14 @@
   </si>
   <si>
     <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Expression":"Buff.Skill.SkillData.DamageRate = Buff.Duration.value","绑定进度条":"圆"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"绑定进度条":"三角"}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2953,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -2998,16 +2995,16 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AN5" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="AO5" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="AO5" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="AQ5" t="s">
         <v>138</v>
@@ -3573,7 +3570,7 @@
         <v>277</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AC2" t="s">
         <v>278</v>
@@ -4194,7 +4191,7 @@
         <v>382</v>
       </c>
       <c r="AV6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="s">
         <v>383</v>
@@ -4217,28 +4214,25 @@
       <c r="CI6" t="s">
         <v>386</v>
       </c>
-      <c r="CN6" t="s">
+      <c r="CU6" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="CY6" t="s">
         <v>387</v>
-      </c>
-      <c r="CU6" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="CY6" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C7" t="s">
         <v>380</v>
       </c>
       <c r="J7" t="s">
+        <v>389</v>
+      </c>
+      <c r="K7" t="s">
         <v>390</v>
-      </c>
-      <c r="K7" t="s">
-        <v>391</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -4255,22 +4249,22 @@
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" t="s">
         <v>392</v>
       </c>
-      <c r="C8" t="s">
+      <c r="K8" t="s">
+        <v>390</v>
+      </c>
+      <c r="L8" t="s">
         <v>393</v>
       </c>
-      <c r="K8" t="s">
-        <v>391</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="AC8">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="s">
         <v>394</v>
-      </c>
-      <c r="AC8">
-        <v>2</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>395</v>
       </c>
       <c r="AX8" t="s">
         <v>383</v>
@@ -4285,30 +4279,30 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
+        <v>395</v>
+      </c>
+      <c r="CY8" t="s">
         <v>396</v>
-      </c>
-      <c r="CY8" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C10" t="s">
         <v>380</v>
       </c>
       <c r="K10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="BD10">
         <v>1</v>
@@ -4317,21 +4311,21 @@
         <v>0.1</v>
       </c>
       <c r="CN10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="J12" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="AB12">
         <v>1</v>
@@ -4343,10 +4337,10 @@
         <v>382</v>
       </c>
       <c r="AV12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX12" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AZ12">
         <v>2.5</v>
@@ -4355,7 +4349,7 @@
         <v>3</v>
       </c>
       <c r="BT12">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="BV12">
         <v>0</v>
@@ -4367,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="BY12" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="CB12" t="s">
         <v>61</v>
@@ -4382,30 +4376,30 @@
         <v>386</v>
       </c>
       <c r="CU12" s="2" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="CY12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="AC13">
         <v>1</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -4423,10 +4417,10 @@
         <v>1</v>
       </c>
       <c r="BY13" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="CO13">
         <v>100</v>
@@ -4437,22 +4431,22 @@
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="AC14">
         <v>1</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="BD14">
         <v>1</v>
@@ -4470,16 +4464,16 @@
         <v>1</v>
       </c>
       <c r="BY14" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="CN14" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="CR14">
         <v>9999</v>
       </c>
       <c r="CU14" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="684" spans="90:90" x14ac:dyDescent="0.25">
@@ -4565,37 +4559,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F1" t="s">
         <v>402</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>403</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>404</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>405</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>406</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>407</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>408</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>409</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>410</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>411</v>
-      </c>
-      <c r="P1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -4609,40 +4603,40 @@
         <v>83</v>
       </c>
       <c r="E2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F2" t="s">
         <v>413</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>414</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>415</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>416</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>417</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>418</v>
-      </c>
-      <c r="K2" t="s">
-        <v>419</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
       </c>
       <c r="M2" t="s">
+        <v>419</v>
+      </c>
+      <c r="N2" t="s">
         <v>420</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>421</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>422</v>
-      </c>
-      <c r="P2" t="s">
-        <v>423</v>
       </c>
       <c r="Q2" t="s">
         <v>346</v>
@@ -4700,41 +4694,41 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="J5" t="s">
+        <v>497</v>
+      </c>
+      <c r="Q5" t="s">
         <v>498</v>
-      </c>
-      <c r="J5" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -4763,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -4774,7 +4768,7 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D2" t="s">
         <v>346</v>
@@ -4829,19 +4823,19 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E2" t="s">
         <v>76</v>
       </c>
       <c r="F2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G2" t="s">
         <v>428</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>429</v>
-      </c>
-      <c r="H2" t="s">
-        <v>430</v>
       </c>
       <c r="I2" t="s">
         <v>335</v>
@@ -4884,13 +4878,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B4" t="s">
         <v>431</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>432</v>
-      </c>
-      <c r="C4" t="s">
-        <v>433</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -4899,7 +4893,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4907,16 +4901,16 @@
         <v>385</v>
       </c>
       <c r="B5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -4944,34 +4938,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C1" t="s">
         <v>437</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>438</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>439</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>440</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>441</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>442</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>443</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>444</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>445</v>
-      </c>
-      <c r="L1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -4979,34 +4973,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C2" t="s">
         <v>447</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>448</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>449</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>450</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>451</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>452</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>453</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>454</v>
       </c>
-      <c r="J2" t="s">
-        <v>455</v>
-      </c>
       <c r="K2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L2" t="s">
         <v>103</v>
@@ -5084,22 +5078,22 @@
         <v>83</v>
       </c>
       <c r="D2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E2" t="s">
         <v>456</v>
-      </c>
-      <c r="E2" t="s">
-        <v>457</v>
       </c>
       <c r="F2" t="s">
         <v>85</v>
       </c>
       <c r="G2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2" t="s">
         <v>284</v>
       </c>
       <c r="I2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J2" t="s">
         <v>58</v>
@@ -5128,7 +5122,7 @@
         <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>127</v>
@@ -5164,28 +5158,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C1" t="s">
         <v>461</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>462</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>463</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>464</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>465</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>466</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>467</v>
-      </c>
-      <c r="I1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -5193,28 +5187,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C2" t="s">
         <v>469</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>470</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>471</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>472</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>473</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>474</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>475</v>
-      </c>
-      <c r="I2" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -5248,28 +5242,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" t="s">
         <v>478</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>479</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>480</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>481</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>482</v>
-      </c>
-      <c r="I4" t="s">
-        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C269FA-FD07-4F4F-B674-D1DE64F396FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CDD909-CED9-4DC0-A9D5-63FD153EDF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2325,7 +2325,8 @@
     <col min="36" max="36" width="15.83203125" customWidth="1"/>
     <col min="37" max="37" width="13.83203125" customWidth="1"/>
     <col min="38" max="38" width="34.5" customWidth="1"/>
-    <col min="39" max="41" width="9.83203125" customWidth="1"/>
+    <col min="39" max="39" width="16.5" customWidth="1"/>
+    <col min="40" max="41" width="9.83203125" customWidth="1"/>
     <col min="42" max="45" width="9" customWidth="1"/>
     <col min="46" max="46" width="12.5" customWidth="1"/>
     <col min="47" max="52" width="9" customWidth="1"/>
@@ -4405,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="BT13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BV13">
         <v>0</v>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CDD909-CED9-4DC0-A9D5-63FD153EDF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D8DA7C-E908-4A01-A933-8962EB5CB259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="527">
   <si>
     <t>Id</t>
   </si>
@@ -1872,6 +1872,72 @@
   </si>
   <si>
     <t>{"绑定进度条":"三角"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤小弟</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人</t>
+  </si>
+  <si>
+    <t>dsbow</t>
+  </si>
+  <si>
+    <t>普通,远程,海怪</t>
+  </si>
+  <si>
+    <t>神秘的恐鱼。在海中能以更快的初速喷吐，足以摧毁礁石。</t>
+  </si>
+  <si>
+    <t>Move</t>
+  </si>
+  <si>
+    <t>CCB小弟</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:蓝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_2_Loop_A,Skill_2_Loop_B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小弟普攻</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通法球</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"CCB小弟","召唤位置":"使用本技能索敌位置"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ShowRange":1,"Color":"#45b787"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小弟技能</t>
+  </si>
+  <si>
+    <t>小弟技能</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:绿</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -1879,7 +1945,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1914,6 +1980,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1940,7 +2013,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1948,6 +2021,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2293,7 +2369,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BX5"/>
+  <dimension ref="A1:BX7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -3059,6 +3135,110 @@
         <v>149</v>
       </c>
       <c r="BX5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1149</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f t="shared" ref="F7" si="0">"enemy_"&amp;E7&amp;"_"&amp;D7</f>
+        <v>enemy_1149_dsbow</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>4400</v>
+      </c>
+      <c r="N7" s="1">
+        <v>280</v>
+      </c>
+      <c r="P7" s="1">
+        <v>160</v>
+      </c>
+      <c r="R7" s="1">
+        <v>20</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="AN7" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="BG7" s="1" t="str">
+        <f t="shared" ref="BG7" si="1">"enemy_"&amp;E7&amp;"_"&amp;D7</f>
+        <v>enemy_1149_dsbow</v>
+      </c>
+      <c r="BM7" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="BN7" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="BP7"/>
+      <c r="BQ7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="BR7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="BS7" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="BT7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BX7" s="1">
         <v>1</v>
       </c>
     </row>
@@ -4185,9 +4365,6 @@
       <c r="AC6">
         <v>2</v>
       </c>
-      <c r="AN6">
-        <v>1</v>
-      </c>
       <c r="AO6" t="s">
         <v>382</v>
       </c>
@@ -4203,8 +4380,8 @@
       <c r="BD6">
         <v>1</v>
       </c>
-      <c r="CB6" t="s">
-        <v>61</v>
+      <c r="CB6" s="2" t="s">
+        <v>519</v>
       </c>
       <c r="CG6" t="s">
         <v>384</v>
@@ -4349,6 +4526,9 @@
       <c r="BD12">
         <v>3</v>
       </c>
+      <c r="BP12" s="2" t="s">
+        <v>509</v>
+      </c>
       <c r="BT12">
         <v>0.1</v>
       </c>
@@ -4475,6 +4655,131 @@
       </c>
       <c r="CU14" s="2" t="s">
         <v>505</v>
+      </c>
+    </row>
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC16">
+        <v>2</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>382</v>
+      </c>
+      <c r="AV16">
+        <v>8</v>
+      </c>
+      <c r="BD16">
+        <v>1</v>
+      </c>
+      <c r="BT16">
+        <v>0.1</v>
+      </c>
+      <c r="CU16" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="18" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="AC18">
+        <v>2</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>382</v>
+      </c>
+      <c r="AV18">
+        <v>3.5</v>
+      </c>
+      <c r="AX18" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="AZ18">
+        <v>1</v>
+      </c>
+      <c r="BD18">
+        <v>2</v>
+      </c>
+      <c r="BY18" s="2"/>
+      <c r="CB18" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG18" t="s">
+        <v>384</v>
+      </c>
+      <c r="CH18" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="CI18" t="s">
+        <v>386</v>
+      </c>
+      <c r="CU18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="CY18" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="19" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="BT19">
+        <v>3</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>5</v>
+      </c>
+      <c r="BX19">
+        <v>1</v>
+      </c>
+      <c r="BY19" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="CN19" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="CO19">
+        <v>100</v>
+      </c>
+      <c r="CR19">
+        <v>5</v>
       </c>
     </row>
     <row r="684" spans="90:90" x14ac:dyDescent="0.25">

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D8DA7C-E908-4A01-A933-8962EB5CB259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DB44FF-15DE-4C8F-B814-D67CBBB03419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="527">
   <si>
     <t>Id</t>
   </si>
@@ -1931,13 +1931,14 @@
   </si>
   <si>
     <t>小弟技能</t>
-  </si>
-  <si>
-    <t>小弟技能</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>小型:绿</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小弟普攻,小弟技能</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3195,16 +3196,13 @@
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="AM7" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN7" s="3" t="s">
         <v>518</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AR7" s="1">
         <v>1</v>
@@ -4737,7 +4735,7 @@
     </row>
     <row r="19" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>487</v>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DB44FF-15DE-4C8F-B814-D67CBBB03419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885D786E-404E-4D5F-8EA2-DF7AE2F2F385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="538">
   <si>
     <t>Id</t>
   </si>
@@ -1840,10 +1840,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>0.5,0.8,0.5</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>CCB叠层</t>
   </si>
   <si>
@@ -1855,10 +1851,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"maxLevel":3,"BuffId":"隐身","LastTime":5,"绑定进度条":"恐惧"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>{"绑定进度条":"弹药"}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1939,6 +1931,55 @@
   </si>
   <si>
     <t>小弟普攻,小弟技能</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤位置":"使用本技能索敌位置","部署模式":"位移","范围":0.25}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身距离降序</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB攻击印记</t>
+  </si>
+  <si>
+    <t>CCB攻击印记</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通Buff</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>冒黑雾</t>
+  </si>
+  <si>
+    <t>CCB回血</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>治愈</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塞雷娅击中</t>
+  </si>
+  <si>
+    <t>{"DamageBase":1,"TriggerTime":0.5,"HpLess":0.5,"HpLessRate":1.5}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB加攻速,CCB回血</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>-CCB攻击印记</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"maxLevel":3,"BuffId":"隐身","LastTime":6,"绑定进度条":"恐惧"}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2014,7 +2055,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2025,6 +2066,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3027,9 +3071,7 @@
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>500</v>
-      </c>
+      <c r="H5" s="2"/>
       <c r="J5">
         <v>2</v>
       </c>
@@ -3073,7 +3115,7 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AM5" s="2" t="s">
         <v>492</v>
@@ -3141,13 +3183,13 @@
     </row>
     <row r="7" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E7" s="1">
         <v>1149</v>
@@ -3190,19 +3232,19 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AK7" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AR7" s="1">
         <v>1</v>
@@ -3218,10 +3260,10 @@
         <v>enemy_1149_dsbow</v>
       </c>
       <c r="BM7" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="1" t="s">
@@ -3231,7 +3273,7 @@
         <v>147</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="BT7" s="1" t="s">
         <v>148</v>
@@ -4379,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="CB6" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="CG6" t="s">
         <v>384</v>
@@ -4389,6 +4431,12 @@
       </c>
       <c r="CI6" t="s">
         <v>386</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>527</v>
+      </c>
+      <c r="CR6">
+        <v>12</v>
       </c>
       <c r="CU6" s="2" t="s">
         <v>485</v>
@@ -4525,7 +4573,7 @@
         <v>3</v>
       </c>
       <c r="BP12" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="BT12">
         <v>0.1</v>
@@ -4555,7 +4603,7 @@
         <v>386</v>
       </c>
       <c r="CU12" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="CY12" t="s">
         <v>387</v>
@@ -4599,13 +4647,16 @@
         <v>488</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>495</v>
+        <v>535</v>
       </c>
       <c r="CO13">
-        <v>100</v>
+        <v>200</v>
+      </c>
+      <c r="CP13">
+        <v>0.8</v>
       </c>
       <c r="CR13">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
@@ -4646,30 +4697,33 @@
         <v>490</v>
       </c>
       <c r="CN14" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="CR14">
         <v>9999</v>
       </c>
       <c r="CU14" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="AC16">
         <v>2</v>
       </c>
-      <c r="AO16" t="s">
-        <v>382</v>
+      <c r="AO16" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="AR16" s="4" t="s">
+        <v>536</v>
       </c>
       <c r="AV16">
         <v>8</v>
@@ -4681,12 +4735,17 @@
         <v>0.1</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="17" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="CU17" s="2" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="18" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>487</v>
@@ -4721,13 +4780,13 @@
         <v>384</v>
       </c>
       <c r="CH18" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="CI18" t="s">
         <v>386</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="CY18" t="s">
         <v>387</v>
@@ -4735,7 +4794,7 @@
     </row>
     <row r="19" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>487</v>
@@ -4840,7 +4899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5007,7 +5066,7 @@
         <v>5</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -5026,17 +5085,39 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>503</v>
-      </c>
       <c r="Q6" s="2" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="J7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="J8" t="s">
+        <v>533</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>534</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885D786E-404E-4D5F-8EA2-DF7AE2F2F385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50530286-D395-4AD1-8E84-0BF70A20DB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="541">
   <si>
     <t>Id</t>
   </si>
@@ -1855,10 +1855,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>{"Expression":"Buff.Skill.SkillData.DamageRate = Buff.Duration.value","绑定进度条":"圆"}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1882,9 +1878,6 @@
     <t>敌人</t>
   </si>
   <si>
-    <t>dsbow</t>
-  </si>
-  <si>
     <t>普通,远程,海怪</t>
   </si>
   <si>
@@ -1914,10 +1907,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"召唤物ID":"CCB小弟","召唤位置":"使用本技能索敌位置"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>{"ShowRange":1,"Color":"#45b787"}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1926,10 +1915,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>小型:绿</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>小弟普攻,小弟技能</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1980,6 +1965,33 @@
   </si>
   <si>
     <t>{"maxLevel":3,"BuffId":"隐身","LastTime":6,"绑定进度条":"恐惧"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>dsjely</t>
+  </si>
+  <si>
+    <t>位移</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>手动</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,-2#-2,0#2,0#0,2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层,CCB呼吸强化</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"绑定进度条":"Boss"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"CCB小弟","召唤位置":"使用干员攻击范围位置","范围":0.5,"数量":2}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3115,10 +3127,10 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="AN5" s="2" t="s">
         <v>483</v>
@@ -3183,20 +3195,20 @@
     </row>
     <row r="7" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>511</v>
+        <v>534</v>
       </c>
       <c r="E7" s="1">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F7" s="1" t="str">
         <f t="shared" ref="F7" si="0">"enemy_"&amp;E7&amp;"_"&amp;D7</f>
-        <v>enemy_1149_dsbow</v>
+        <v>enemy_1150_dsjely</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -3205,7 +3217,7 @@
         <v>4400</v>
       </c>
       <c r="N7" s="1">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="P7" s="1">
         <v>160</v>
@@ -3232,19 +3244,19 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AK7" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>523</v>
+        <v>514</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>1</v>
       </c>
       <c r="AR7" s="1">
         <v>1</v>
@@ -3257,13 +3269,13 @@
       </c>
       <c r="BG7" s="1" t="str">
         <f t="shared" ref="BG7" si="1">"enemy_"&amp;E7&amp;"_"&amp;D7</f>
-        <v>enemy_1149_dsbow</v>
+        <v>enemy_1150_dsjely</v>
       </c>
       <c r="BM7" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="1" t="s">
@@ -3273,7 +3285,7 @@
         <v>147</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="BT7" s="1" t="s">
         <v>148</v>
@@ -4421,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="CB6" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="CG6" t="s">
         <v>384</v>
@@ -4433,7 +4445,7 @@
         <v>386</v>
       </c>
       <c r="CN6" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="CR6">
         <v>12</v>
@@ -4573,7 +4585,7 @@
         <v>3</v>
       </c>
       <c r="BP12" s="2" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="BT12">
         <v>0.1</v>
@@ -4603,7 +4615,7 @@
         <v>386</v>
       </c>
       <c r="CU12" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CY12" t="s">
         <v>387</v>
@@ -4647,7 +4659,7 @@
         <v>488</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="CO13">
         <v>200</v>
@@ -4657,6 +4669,9 @@
       </c>
       <c r="CR13">
         <v>3</v>
+      </c>
+      <c r="CU13" s="2" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
@@ -4708,22 +4723,22 @@
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>509</v>
-      </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AV16">
         <v>8</v>
@@ -4735,17 +4750,58 @@
         <v>0.1</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="17" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="AC17">
+        <v>2</v>
+      </c>
+      <c r="AO17" s="2"/>
+      <c r="AR17" s="4"/>
+      <c r="AT17" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="BT17">
+        <v>0.1</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>8</v>
+      </c>
+      <c r="BX17">
+        <v>1</v>
+      </c>
+      <c r="BY17" s="2" t="s">
+        <v>490</v>
+      </c>
       <c r="CU17" s="2" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>487</v>
@@ -4780,13 +4836,13 @@
         <v>384</v>
       </c>
       <c r="CH18" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="CI18" t="s">
         <v>386</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="CY18" t="s">
         <v>387</v>
@@ -4794,7 +4850,7 @@
     </row>
     <row r="19" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>487</v>
@@ -5066,7 +5122,7 @@
         <v>5</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -5091,32 +5147,32 @@
         <v>502</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="J7" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="J8" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50530286-D395-4AD1-8E84-0BF70A20DB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7851D0-FB9F-439D-919E-E7C202554035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="547">
   <si>
     <t>Id</t>
   </si>
@@ -1622,9 +1622,6 @@
   </si>
   <si>
     <t>frostl_attack_01_trail</t>
-  </si>
-  <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":10,"ReductionRate":0.25,"SkillId":"链式弹道索敌","CanBack":"false"}</t>
   </si>
   <si>
     <t>大飞镖</t>
@@ -1919,10 +1916,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"召唤位置":"使用本技能索敌位置","部署模式":"位移","范围":0.25}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>自身距离降序</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1992,6 +1985,36 @@
   </si>
   <si>
     <t>{"召唤物ID":"CCB小弟","召唤位置":"使用干员攻击范围位置","范围":0.5,"数量":2}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤位置":"使用本技能索敌位置","部署模式":"位移","范围":0.25,"位移速度":"30"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB链式弹道</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动弹道</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>棘刺2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>aglina_attack_01_trail</t>
+  </si>
+  <si>
+    <t>amiya_skill_03_trail</t>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxLinkNum":10,"ReductionRate":0.25,"SkillId":"链式弹道索敌","CanBack":"false"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxRadius":3,"InitRadius":3}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3127,16 +3150,16 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AN5" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="AO5" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="AO5" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="AQ5" t="s">
         <v>138</v>
@@ -3195,13 +3218,13 @@
     </row>
     <row r="7" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E7" s="1">
         <v>1150</v>
@@ -3244,16 +3267,16 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AK7" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -3272,10 +3295,10 @@
         <v>enemy_1150_dsjely</v>
       </c>
       <c r="BM7" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="BN7" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="BN7" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="1" t="s">
@@ -3285,7 +3308,7 @@
         <v>147</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="BT7" s="1" t="s">
         <v>148</v>
@@ -3803,7 +3826,7 @@
         <v>277</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AC2" t="s">
         <v>278</v>
@@ -4433,25 +4456,25 @@
         <v>1</v>
       </c>
       <c r="CB6" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="CG6" t="s">
         <v>384</v>
       </c>
-      <c r="CH6" t="s">
-        <v>385</v>
+      <c r="CH6" s="2" t="s">
+        <v>516</v>
       </c>
       <c r="CI6" t="s">
         <v>386</v>
       </c>
       <c r="CN6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="CR6">
         <v>12</v>
       </c>
       <c r="CU6" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="CY6" t="s">
         <v>387</v>
@@ -4552,16 +4575,16 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="J12" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="AB12">
         <v>1</v>
@@ -4576,7 +4599,7 @@
         <v>8</v>
       </c>
       <c r="AX12" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AZ12">
         <v>2.5</v>
@@ -4585,7 +4608,7 @@
         <v>3</v>
       </c>
       <c r="BP12" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="BT12">
         <v>0.1</v>
@@ -4600,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="BY12" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="CB12" t="s">
         <v>61</v>
@@ -4609,13 +4632,13 @@
         <v>384</v>
       </c>
       <c r="CH12" t="s">
-        <v>385</v>
+        <v>430</v>
       </c>
       <c r="CI12" t="s">
         <v>386</v>
       </c>
       <c r="CU12" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="CY12" t="s">
         <v>387</v>
@@ -4623,22 +4646,22 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="AC13">
         <v>1</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -4656,10 +4679,10 @@
         <v>1</v>
       </c>
       <c r="BY13" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="CO13">
         <v>200</v>
@@ -4671,27 +4694,27 @@
         <v>3</v>
       </c>
       <c r="CU13" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="AC14">
         <v>1</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="BD14">
         <v>1</v>
@@ -4709,36 +4732,36 @@
         <v>1</v>
       </c>
       <c r="BY14" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="CN14" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="CR14">
         <v>9999</v>
       </c>
       <c r="CU14" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AV16">
         <v>8</v>
@@ -4750,21 +4773,21 @@
         <v>0.1</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
     </row>
     <row r="17" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="X17">
         <v>1</v>
@@ -4775,7 +4798,7 @@
       <c r="AO17" s="2"/>
       <c r="AR17" s="4"/>
       <c r="AT17" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="BD17">
         <v>1</v>
@@ -4793,22 +4816,22 @@
         <v>1</v>
       </c>
       <c r="BY17" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="CU17" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="18" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AC18">
         <v>2</v>
@@ -4820,7 +4843,7 @@
         <v>3.5</v>
       </c>
       <c r="AX18" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AZ18">
         <v>1</v>
@@ -4836,13 +4859,13 @@
         <v>384</v>
       </c>
       <c r="CH18" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="CI18" t="s">
         <v>386</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="CY18" t="s">
         <v>387</v>
@@ -4850,22 +4873,22 @@
     </row>
     <row r="19" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="BD19">
         <v>1</v>
@@ -4883,10 +4906,10 @@
         <v>1</v>
       </c>
       <c r="BY19" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="CN19" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="CO19">
         <v>100</v>
@@ -5122,57 +5145,57 @@
         <v>5</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="J5" t="s">
         <v>496</v>
       </c>
-      <c r="J5" t="s">
+      <c r="Q5" t="s">
         <v>497</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>502</v>
-      </c>
       <c r="Q6" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J7" t="s">
         <v>524</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="J7" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="J8" t="s">
         <v>527</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="J8" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -5238,7 +5261,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -5318,14 +5341,14 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>430</v>
+      <c r="A4" s="2" t="s">
+        <v>540</v>
       </c>
       <c r="B4" t="s">
         <v>431</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>543</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -5333,8 +5356,8 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>433</v>
+      <c r="J4" s="2" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5342,7 +5365,7 @@
         <v>385</v>
       </c>
       <c r="B5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C5" t="s">
         <v>432</v>
@@ -5351,7 +5374,24 @@
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>435</v>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C6" t="s">
+        <v>544</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -5379,34 +5419,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C1" t="s">
         <v>436</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>437</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>438</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>439</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>440</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>441</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>442</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>443</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>444</v>
-      </c>
-      <c r="L1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -5414,31 +5454,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" t="s">
         <v>446</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>447</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>448</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>449</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>450</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>451</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>452</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>453</v>
-      </c>
-      <c r="J2" t="s">
-        <v>454</v>
       </c>
       <c r="K2" t="s">
         <v>427</v>
@@ -5519,22 +5559,22 @@
         <v>83</v>
       </c>
       <c r="D2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E2" t="s">
         <v>455</v>
-      </c>
-      <c r="E2" t="s">
-        <v>456</v>
       </c>
       <c r="F2" t="s">
         <v>85</v>
       </c>
       <c r="G2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2" t="s">
         <v>284</v>
       </c>
       <c r="I2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J2" t="s">
         <v>58</v>
@@ -5563,7 +5603,7 @@
         <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>127</v>
@@ -5599,28 +5639,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C1" t="s">
         <v>460</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>461</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>462</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>463</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>464</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>465</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>466</v>
-      </c>
-      <c r="I1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -5628,28 +5668,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C2" t="s">
         <v>468</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>469</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>470</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>471</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>472</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>473</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>474</v>
-      </c>
-      <c r="I2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -5683,28 +5723,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E4" t="s">
         <v>477</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>478</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>479</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>480</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>481</v>
-      </c>
-      <c r="I4" t="s">
-        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7851D0-FB9F-439D-919E-E7C202554035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023FF8BC-2789-40E9-9C39-DC29FBAF8F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="549">
   <si>
     <t>Id</t>
   </si>
@@ -1487,9 +1487,6 @@
   </si>
   <si>
     <t>拉普兰德近战击中</t>
-  </si>
-  <si>
-    <t>链式弹道索敌</t>
   </si>
   <si>
     <t>禁止主动</t>
@@ -1868,10 +1865,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>被动</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>敌人</t>
   </si>
   <si>
@@ -1968,30 +1961,14 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>手动</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>0,-2#-2,0#2,0#0,2</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层,CCB呼吸强化</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>{"绑定进度条":"Boss"}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"召唤物ID":"CCB小弟","召唤位置":"使用干员攻击范围位置","范围":0.5,"数量":2}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"召唤位置":"使用本技能索敌位置","部署模式":"位移","范围":0.25,"位移速度":"30"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>CCB链式弹道</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2010,11 +1987,42 @@
     <t>amiya_skill_03_trail</t>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":10,"ReductionRate":0.25,"SkillId":"链式弹道索敌","CanBack":"false"}</t>
+    <t>移动弹道</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxRadius":3,"InitRadius":3}</t>
+    <t>{"召唤物ID":"CCB小弟","召唤位置":"使用干员攻击范围位置","范围":0.5,"数量":1}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxRadius":1.5,"InitRadius":1.5}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤位置":"使用本技能索敌位置","部署模式":"位移","范围":0.25,"位移速度":"10"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB减攻速</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>降防</t>
+  </si>
+  <si>
+    <t>CCB弹道索敌</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxLinkNum":3,"ReductionRate":0.25,"SkillId":"CCB弹道索敌","CanBack":0}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3150,16 +3158,16 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="AN5" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="AO5" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="AO5" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="AQ5" t="s">
         <v>138</v>
@@ -3216,15 +3224,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="AM6" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
     <row r="7" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E7" s="1">
         <v>1150</v>
@@ -3267,16 +3280,16 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AK7" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -3295,10 +3308,10 @@
         <v>enemy_1150_dsjely</v>
       </c>
       <c r="BM7" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="1" t="s">
@@ -3308,7 +3321,7 @@
         <v>147</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="BT7" s="1" t="s">
         <v>148</v>
@@ -3826,7 +3839,7 @@
         <v>277</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AC2" t="s">
         <v>278</v>
@@ -4456,42 +4469,42 @@
         <v>1</v>
       </c>
       <c r="CB6" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="CG6" t="s">
         <v>384</v>
       </c>
       <c r="CH6" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="CI6" t="s">
         <v>386</v>
       </c>
       <c r="CN6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="CR6">
         <v>12</v>
       </c>
       <c r="CU6" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="CY6" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>388</v>
+      <c r="A7" s="2" t="s">
+        <v>547</v>
       </c>
       <c r="C7" t="s">
         <v>380</v>
       </c>
       <c r="J7" t="s">
+        <v>388</v>
+      </c>
+      <c r="K7" t="s">
         <v>389</v>
-      </c>
-      <c r="K7" t="s">
-        <v>390</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -4505,25 +4518,29 @@
       <c r="AV7">
         <v>2.5</v>
       </c>
+      <c r="BD7">
+        <v>99</v>
+      </c>
+      <c r="CU7" s="2"/>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C8" t="s">
         <v>391</v>
       </c>
-      <c r="C8" t="s">
+      <c r="K8" t="s">
+        <v>389</v>
+      </c>
+      <c r="L8" t="s">
         <v>392</v>
       </c>
-      <c r="K8" t="s">
-        <v>390</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="AC8">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="s">
         <v>393</v>
-      </c>
-      <c r="AC8">
-        <v>2</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>394</v>
       </c>
       <c r="AX8" t="s">
         <v>383</v>
@@ -4538,30 +4555,30 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
+        <v>394</v>
+      </c>
+      <c r="CY8" t="s">
         <v>395</v>
-      </c>
-      <c r="CY8" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C10" t="s">
         <v>380</v>
       </c>
       <c r="K10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="BD10">
         <v>1</v>
@@ -4570,24 +4587,21 @@
         <v>0.1</v>
       </c>
       <c r="CN10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="J12" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="AB12">
-        <v>1</v>
       </c>
       <c r="AC12">
         <v>2</v>
@@ -4599,17 +4613,15 @@
         <v>8</v>
       </c>
       <c r="AX12" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AZ12">
         <v>2.5</v>
       </c>
       <c r="BD12">
-        <v>3</v>
-      </c>
-      <c r="BP12" s="2" t="s">
-        <v>533</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BP12" s="2"/>
       <c r="BT12">
         <v>0.1</v>
       </c>
@@ -4623,7 +4635,7 @@
         <v>1</v>
       </c>
       <c r="BY12" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="CB12" t="s">
         <v>61</v>
@@ -4632,13 +4644,13 @@
         <v>384</v>
       </c>
       <c r="CH12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="CI12" t="s">
         <v>386</v>
       </c>
       <c r="CU12" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="CY12" t="s">
         <v>387</v>
@@ -4646,22 +4658,22 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="AC13">
         <v>1</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -4679,10 +4691,10 @@
         <v>1</v>
       </c>
       <c r="BY13" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="CO13">
         <v>200</v>
@@ -4694,27 +4706,27 @@
         <v>3</v>
       </c>
       <c r="CU13" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="AC14">
         <v>1</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="BD14">
         <v>1</v>
@@ -4732,62 +4744,95 @@
         <v>1</v>
       </c>
       <c r="BY14" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="CN14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="CR14">
         <v>9999</v>
       </c>
       <c r="CU14" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AV16">
         <v>8</v>
       </c>
+      <c r="AX16" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="AZ16">
+        <v>1.5</v>
+      </c>
       <c r="BD16">
         <v>1</v>
       </c>
       <c r="BT16">
         <v>0.1</v>
       </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>4</v>
+      </c>
+      <c r="BX16">
+        <v>1</v>
+      </c>
+      <c r="BY16" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="CH16" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="CN16" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="CO16">
+        <v>-50</v>
+      </c>
+      <c r="CR16">
+        <v>3</v>
+      </c>
       <c r="CU16" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>534</v>
+        <v>486</v>
       </c>
       <c r="X17">
         <v>1</v>
@@ -4798,11 +4843,17 @@
       <c r="AO17" s="2"/>
       <c r="AR17" s="4"/>
       <c r="AT17" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="BD17">
         <v>1</v>
       </c>
+      <c r="BE17">
+        <v>1</v>
+      </c>
+      <c r="BF17">
+        <v>2</v>
+      </c>
       <c r="BT17">
         <v>0.1</v>
       </c>
@@ -4816,22 +4867,22 @@
         <v>1</v>
       </c>
       <c r="BY17" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="CU17" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AC18">
         <v>2</v>
@@ -4843,7 +4894,7 @@
         <v>3.5</v>
       </c>
       <c r="AX18" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AZ18">
         <v>1</v>
@@ -4859,13 +4910,13 @@
         <v>384</v>
       </c>
       <c r="CH18" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="CI18" t="s">
         <v>386</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="CY18" t="s">
         <v>387</v>
@@ -4873,22 +4924,22 @@
     </row>
     <row r="19" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="BD19">
         <v>1</v>
@@ -4906,10 +4957,10 @@
         <v>1</v>
       </c>
       <c r="BY19" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="CN19" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="CO19">
         <v>100</v>
@@ -4978,7 +5029,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5001,37 +5052,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F1" t="s">
         <v>401</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>402</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>403</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>404</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>405</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>406</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>407</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>408</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>409</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>410</v>
-      </c>
-      <c r="P1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -5045,40 +5096,40 @@
         <v>83</v>
       </c>
       <c r="E2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F2" t="s">
         <v>412</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>413</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>414</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>415</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>416</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>417</v>
-      </c>
-      <c r="K2" t="s">
-        <v>418</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
       </c>
       <c r="M2" t="s">
+        <v>418</v>
+      </c>
+      <c r="N2" t="s">
         <v>419</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>420</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>421</v>
-      </c>
-      <c r="P2" t="s">
-        <v>422</v>
       </c>
       <c r="Q2" t="s">
         <v>346</v>
@@ -5136,66 +5187,80 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="J5" t="s">
         <v>495</v>
       </c>
-      <c r="J5" t="s">
+      <c r="Q5" t="s">
         <v>496</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>501</v>
-      </c>
       <c r="Q6" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J7" t="s">
         <v>522</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="J7" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="J8" t="s">
         <v>525</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="J8" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>528</v>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="J10" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -5221,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -5232,7 +5297,7 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D2" t="s">
         <v>346</v>
@@ -5287,19 +5352,19 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E2" t="s">
         <v>76</v>
       </c>
       <c r="F2" t="s">
+        <v>426</v>
+      </c>
+      <c r="G2" t="s">
         <v>427</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>428</v>
-      </c>
-      <c r="H2" t="s">
-        <v>429</v>
       </c>
       <c r="I2" t="s">
         <v>335</v>
@@ -5342,22 +5407,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C4" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5365,33 +5430,33 @@
         <v>385</v>
       </c>
       <c r="B5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="C6" t="s">
-        <v>544</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -5419,34 +5484,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" t="s">
         <v>435</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>436</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>437</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>438</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>439</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>440</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>441</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>442</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>443</v>
-      </c>
-      <c r="L1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -5454,34 +5519,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" t="s">
         <v>445</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>446</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>447</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>448</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>449</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>450</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>451</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>452</v>
       </c>
-      <c r="J2" t="s">
-        <v>453</v>
-      </c>
       <c r="K2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L2" t="s">
         <v>103</v>
@@ -5559,22 +5624,22 @@
         <v>83</v>
       </c>
       <c r="D2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E2" t="s">
         <v>454</v>
-      </c>
-      <c r="E2" t="s">
-        <v>455</v>
       </c>
       <c r="F2" t="s">
         <v>85</v>
       </c>
       <c r="G2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2" t="s">
         <v>284</v>
       </c>
       <c r="I2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J2" t="s">
         <v>58</v>
@@ -5603,7 +5668,7 @@
         <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>127</v>
@@ -5639,28 +5704,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1" t="s">
         <v>459</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>460</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>461</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>462</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>463</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>464</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>465</v>
-      </c>
-      <c r="I1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -5668,28 +5733,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C2" t="s">
         <v>467</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>468</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>469</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>470</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>471</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>472</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>473</v>
-      </c>
-      <c r="I2" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -5723,28 +5788,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>475</v>
+      </c>
+      <c r="E4" t="s">
         <v>476</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>477</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>478</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>479</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>480</v>
-      </c>
-      <c r="I4" t="s">
-        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023FF8BC-2789-40E9-9C39-DC29FBAF8F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE36214-B263-48EE-AF53-071C15BE61F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="571">
   <si>
     <t>Id</t>
   </si>
@@ -1897,18 +1897,10 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"ShowRange":1,"Color":"#45b787"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>小弟技能</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>小弟普攻,小弟技能</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>自身距离降序</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1950,10 +1942,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"maxLevel":3,"BuffId":"隐身","LastTime":6,"绑定进度条":"恐惧"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>dsjely</t>
   </si>
   <si>
@@ -1961,14 +1949,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>0,-2#-2,0#2,0#0,2</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"绑定进度条":"Boss"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>CCB链式弹道</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1991,10 +1971,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"召唤物ID":"CCB小弟","召唤位置":"使用干员攻击范围位置","范围":0.5,"数量":1}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>{"MoveHeight":0,"MaxRadius":1.5,"InitRadius":1.5}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2003,10 +1979,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>CCB减攻速</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2022,7 +1994,118 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":3,"ReductionRate":0.25,"SkillId":"CCB弹道索敌","CanBack":0}</t>
+    <t>{"MoveHeight":0,"MaxLinkNum":3,"ReductionRate":0.25,"SkillId":"CCB弹道索敌","CanBack":0,"ShowRange":1,"Color":"#ed3333"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB强力击标记</t>
+  </si>
+  <si>
+    <t>CCB强力击标记</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>CCB增伤</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB减攻速</t>
+  </si>
+  <si>
+    <t>{"DamageRate":1.5}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱点伤害</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐身</t>
+  </si>
+  <si>
+    <t>对buff伤害</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB隐身</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"HideTime":0,"无视阻挡":1}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"maxLevel":3,"BuffId":"CCB隐身","LastTime":6,"绑定进度条":"恐惧"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB隐身</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB减攻速,减速</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小弟自流血</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>LoseHP</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层,位移,召唤小弟</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"CCB小弟","召唤位置":"使用本技能索敌位置","范围":0.5,"数量":1}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>被击</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小弟减速</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值变化</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小弟减速,CCB攻击印记</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ShowRange":1,"Color":"#45b787","Alpha":0.25}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"t":["SpeedRate"]}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小弟技能</t>
+  </si>
+  <si>
+    <t>小弟普攻,小弟自流血</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:绿</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3158,7 +3241,7 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="AM5" s="2" t="s">
         <v>490</v>
@@ -3237,7 +3320,7 @@
         <v>506</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E7" s="1">
         <v>1150</v>
@@ -3286,10 +3369,16 @@
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>517</v>
+        <v>569</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>568</v>
       </c>
       <c r="AN7" s="3" t="s">
         <v>511</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>570</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -4480,8 +4569,11 @@
       <c r="CI6" t="s">
         <v>386</v>
       </c>
-      <c r="CN6" t="s">
-        <v>519</v>
+      <c r="CJ6" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>518</v>
       </c>
       <c r="CR6">
         <v>12</v>
@@ -4495,7 +4587,7 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="C7" t="s">
         <v>380</v>
@@ -4505,6 +4597,9 @@
       </c>
       <c r="K7" t="s">
         <v>389</v>
+      </c>
+      <c r="R7" t="s">
+        <v>542</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -4619,7 +4714,7 @@
         <v>2.5</v>
       </c>
       <c r="BD12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP12" s="2"/>
       <c r="BT12">
@@ -4649,6 +4744,12 @@
       <c r="CI12" t="s">
         <v>386</v>
       </c>
+      <c r="CJ12" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="CN12" s="2" t="s">
+        <v>543</v>
+      </c>
       <c r="CU12" s="2" t="s">
         <v>503</v>
       </c>
@@ -4694,7 +4795,7 @@
         <v>486</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="CO13">
         <v>200</v>
@@ -4703,11 +4804,9 @@
         <v>0.8</v>
       </c>
       <c r="CR13">
-        <v>3</v>
-      </c>
-      <c r="CU13" s="2" t="s">
-        <v>533</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="CU13" s="2"/>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -4749,40 +4848,38 @@
       <c r="CN14" t="s">
         <v>498</v>
       </c>
-      <c r="CR14">
-        <v>9999</v>
-      </c>
       <c r="CU14" s="2" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>491</v>
-      </c>
+      <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
         <v>486</v>
       </c>
+      <c r="O16" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AV16">
         <v>8</v>
       </c>
       <c r="AX16" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="AZ16">
         <v>1.5</v>
@@ -4790,90 +4887,64 @@
       <c r="BD16">
         <v>1</v>
       </c>
-      <c r="BT16">
-        <v>0.1</v>
-      </c>
-      <c r="BV16">
-        <v>0</v>
-      </c>
-      <c r="BW16">
-        <v>4</v>
-      </c>
-      <c r="BX16">
-        <v>1</v>
-      </c>
-      <c r="BY16" s="2" t="s">
-        <v>488</v>
-      </c>
+      <c r="BS16">
+        <v>6</v>
+      </c>
+      <c r="BY16" s="2"/>
       <c r="CH16" s="2" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="CN16" s="2" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="CO16">
         <v>-50</v>
       </c>
+      <c r="CP16">
+        <v>-0.8</v>
+      </c>
       <c r="CR16">
         <v>3</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="17" spans="1:103" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>504</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>491</v>
-      </c>
+      <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="X17">
+        <v>556</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="AC17">
+        <v>2</v>
+      </c>
+      <c r="AE17">
         <v>1</v>
-      </c>
-      <c r="AC17">
-        <v>2</v>
       </c>
       <c r="AO17" s="2"/>
       <c r="AR17" s="4"/>
-      <c r="AT17" s="2" t="s">
-        <v>532</v>
-      </c>
+      <c r="AT17" s="2"/>
       <c r="BD17">
         <v>1</v>
       </c>
-      <c r="BE17">
-        <v>1</v>
-      </c>
-      <c r="BF17">
-        <v>2</v>
-      </c>
-      <c r="BT17">
-        <v>0.1</v>
-      </c>
-      <c r="BV17">
-        <v>0</v>
-      </c>
-      <c r="BW17">
-        <v>8</v>
-      </c>
-      <c r="BX17">
-        <v>1</v>
-      </c>
-      <c r="BY17" s="2" t="s">
-        <v>488</v>
-      </c>
+      <c r="BY17" s="2"/>
       <c r="CU17" s="2" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="18" spans="1:103" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>513</v>
       </c>
@@ -4915,16 +4986,22 @@
       <c r="CI18" t="s">
         <v>386</v>
       </c>
+      <c r="CN18" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="CO18">
+        <v>-0.8</v>
+      </c>
       <c r="CU18" s="2" t="s">
-        <v>515</v>
+        <v>566</v>
       </c>
       <c r="CY18" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="19" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>485</v>
@@ -4967,6 +5044,56 @@
       </c>
       <c r="CR19">
         <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="AX20" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="AZ20">
+        <v>0.05</v>
+      </c>
+      <c r="BB20">
+        <v>1</v>
+      </c>
+      <c r="BD20">
+        <v>1</v>
+      </c>
+      <c r="BS20">
+        <v>0.5</v>
+      </c>
+      <c r="CY20" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="DD20">
+        <v>1</v>
+      </c>
+      <c r="DG20">
+        <v>1</v>
+      </c>
+      <c r="DH20">
+        <v>1</v>
       </c>
     </row>
     <row r="684" spans="90:90" x14ac:dyDescent="0.25">
@@ -5029,7 +5156,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5220,47 +5347,92 @@
       <c r="C6" s="2" t="s">
         <v>500</v>
       </c>
+      <c r="K6">
+        <v>99999</v>
+      </c>
       <c r="Q6" s="2" t="s">
-        <v>529</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="J7" t="s">
         <v>520</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="J7" t="s">
-        <v>522</v>
+      <c r="K7">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="J8" t="s">
         <v>523</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="J8" t="s">
-        <v>525</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>526</v>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="J9" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>494</v>
       </c>
       <c r="J10" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="Q10" t="s">
         <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="K11">
+        <v>0.8</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C12" t="s">
+        <v>549</v>
+      </c>
+      <c r="J12" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -5272,7 +5444,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -5315,6 +5487,20 @@
       </c>
       <c r="D3" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C5" t="s">
+        <v>546</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -5407,13 +5593,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B4" t="s">
         <v>430</v>
       </c>
       <c r="C4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -5422,7 +5608,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5444,19 +5630,19 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C6" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE36214-B263-48EE-AF53-071C15BE61F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2991A37F-6622-4A29-9C95-AB8373F53943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="571">
   <si>
     <t>Id</t>
   </si>
@@ -1975,10 +1975,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"召唤位置":"使用本技能索敌位置","部署模式":"位移","范围":0.25,"位移速度":"10"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>CCB减攻速</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1991,10 +1987,6 @@
   </si>
   <si>
     <t>CCB弹道索敌</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":3,"ReductionRate":0.25,"SkillId":"CCB弹道索敌","CanBack":0,"ShowRange":1,"Color":"#ed3333"}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
@@ -2106,6 +2098,14 @@
   </si>
   <si>
     <t>小型:绿</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤位置":"使用本技能索敌位置","部署模式":"位移","位移速度":"10"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxLinkNum":6,"ReductionRate":0.25,"SkillId":"CCB弹道索敌","CanBack":1,"ShowRange":1,"Color":"#ed3333"}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3241,7 +3241,7 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AM5" s="2" t="s">
         <v>490</v>
@@ -3369,16 +3369,16 @@
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AN7" s="3" t="s">
         <v>511</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -4570,7 +4570,7 @@
         <v>386</v>
       </c>
       <c r="CJ6" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="CN6" s="2" t="s">
         <v>518</v>
@@ -4587,7 +4587,7 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C7" t="s">
         <v>380</v>
@@ -4599,7 +4599,7 @@
         <v>389</v>
       </c>
       <c r="R7" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -4745,10 +4745,10 @@
         <v>386</v>
       </c>
       <c r="CJ12" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="CN12" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="CU12" s="2" t="s">
         <v>503</v>
@@ -4864,7 +4864,7 @@
         <v>486</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AC16">
         <v>2</v>
@@ -4879,7 +4879,7 @@
         <v>8</v>
       </c>
       <c r="AX16" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AZ16">
         <v>1.5</v>
@@ -4895,7 +4895,7 @@
         <v>534</v>
       </c>
       <c r="CN16" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="CO16">
         <v>-50</v>
@@ -4907,7 +4907,7 @@
         <v>3</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
@@ -4919,10 +4919,10 @@
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>517</v>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="BY17" s="2"/>
       <c r="CU17" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
@@ -4961,6 +4961,9 @@
       <c r="AO18" t="s">
         <v>382</v>
       </c>
+      <c r="AR18" s="4" t="s">
+        <v>526</v>
+      </c>
       <c r="AV18">
         <v>3.5</v>
       </c>
@@ -4987,13 +4990,13 @@
         <v>386</v>
       </c>
       <c r="CN18" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="CO18">
         <v>-0.8</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="CY18" t="s">
         <v>387</v>
@@ -5048,7 +5051,7 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>485</v>
@@ -5069,7 +5072,7 @@
         <v>492</v>
       </c>
       <c r="AX20" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="AZ20">
         <v>0.05</v>
@@ -5084,7 +5087,7 @@
         <v>0.5</v>
       </c>
       <c r="CY20" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="DD20">
         <v>1</v>
@@ -5351,7 +5354,7 @@
         <v>99999</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -5384,24 +5387,24 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>519</v>
       </c>
       <c r="J9" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>494</v>
       </c>
       <c r="J10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q10" t="s">
         <v>496</v>
@@ -5409,30 +5412,30 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="K11">
         <v>0.8</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C12" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J12" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -5491,16 +5494,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C5" t="s">
+        <v>544</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="C5" t="s">
-        <v>546</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -5608,7 +5611,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>541</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2991A37F-6622-4A29-9C95-AB8373F53943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00ADF66C-69F5-43F9-85A2-61E0A01BE430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="585">
   <si>
     <t>Id</t>
   </si>
@@ -2058,10 +2058,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层,位移,召唤小弟</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>{"召唤物ID":"CCB小弟","召唤位置":"使用本技能索敌位置","范围":0.5,"数量":1}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2106,6 +2102,62 @@
   </si>
   <si>
     <t>{"MoveHeight":0,"MaxLinkNum":6,"ReductionRate":0.25,"SkillId":"CCB弹道索敌","CanBack":1,"ShowRange":1,"Color":"#ed3333"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>涨潮</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>中立单位</t>
+  </si>
+  <si>
+    <t>通用地板</t>
+  </si>
+  <si>
+    <t>全地形</t>
+  </si>
+  <si>
+    <t>辅助</t>
+  </si>
+  <si>
+    <t>海水</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓无敌</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"TexturePath":"Icon/头像_浊心斯卡蒂.png","Alpha":0.5}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤地板</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署装置</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>手动</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层,位移,召唤小弟,CCB呼吸强化</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤地板</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"涨潮","召唤位置":"使用自身位置","持续":15}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2540,7 +2592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BX7"/>
+  <dimension ref="A1:BX9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -3241,10 +3293,10 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>490</v>
+        <v>583</v>
       </c>
       <c r="AN5" s="2" t="s">
         <v>481</v>
@@ -3369,16 +3421,16 @@
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AN7" s="3" t="s">
         <v>511</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -3417,6 +3469,89 @@
       </c>
       <c r="BX7" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B9" t="s">
+        <v>571</v>
+      </c>
+      <c r="F9" t="s">
+        <v>572</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>90</v>
+      </c>
+      <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0.05</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>573</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0.5</v>
+      </c>
+      <c r="AT9">
+        <v>1</v>
+      </c>
+      <c r="AZ9">
+        <v>0.25</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>574</v>
+      </c>
+      <c r="BO9" s="2" t="s">
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -4907,7 +5042,7 @@
         <v>3</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
@@ -4922,7 +5057,7 @@
         <v>554</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>517</v>
@@ -4941,7 +5076,7 @@
       </c>
       <c r="BY17" s="2"/>
       <c r="CU17" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
@@ -4990,13 +5125,13 @@
         <v>386</v>
       </c>
       <c r="CN18" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="CO18">
         <v>-0.8</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="CY18" t="s">
         <v>387</v>
@@ -5097,6 +5232,44 @@
       </c>
       <c r="DH20">
         <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="BT22">
+        <v>0.1</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>1</v>
+      </c>
+      <c r="BX22">
+        <v>1</v>
+      </c>
+      <c r="BY22" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="CU22" s="2" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="684" spans="90:90" x14ac:dyDescent="0.25">
@@ -5412,16 +5585,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="K11">
         <v>0.8</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -5611,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00ADF66C-69F5-43F9-85A2-61E0A01BE430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC081F18-D63C-42BB-A1CE-2CF2B38F137C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="593">
   <si>
     <t>Id</t>
   </si>
@@ -2125,39 +2125,70 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
+    <t>召唤地板</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署装置</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>手动</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层,位移,召唤小弟,CCB呼吸强化</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤地板</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>潮起</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通技能</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅自己</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>涨潮</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"涨潮","召唤位置":"使用自身位置","持续":20}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>重设高度</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
     <t>萃蔓无敌</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"TexturePath":"Icon/头像_浊心斯卡蒂.png","Alpha":0.5}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>召唤地板</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>部署装置</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>手动</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层,位移,召唤小弟,CCB呼吸强化</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>召唤地板</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"召唤物ID":"涨潮","召唤位置":"使用自身位置","持续":15}</t>
+    <t>潮起</t>
+  </si>
+  <si>
+    <t>{"TexturePath":"Icon/otto.png","Alpha":0.5}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Fly":4,"Time":2}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己入场</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3293,10 +3324,10 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AN5" s="2" t="s">
         <v>481</v>
@@ -3408,12 +3439,6 @@
       <c r="AC7" s="1">
         <v>0.75</v>
       </c>
-      <c r="AH7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="1">
-        <v>0</v>
-      </c>
       <c r="AJ7" s="1" t="s">
         <v>510</v>
       </c>
@@ -3530,8 +3555,12 @@
         <v>137</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>576</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>589</v>
+      </c>
+      <c r="AO9" s="1"/>
       <c r="AQ9" t="s">
         <v>573</v>
       </c>
@@ -3551,7 +3580,7 @@
         <v>574</v>
       </c>
       <c r="BO9" s="2" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -5236,16 +5265,16 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>491</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -5266,10 +5295,50 @@
         <v>1</v>
       </c>
       <c r="BY22" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="CU22" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="AC23">
+        <v>7</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AG23" s="2" t="s">
         <v>584</v>
+      </c>
+      <c r="AN23">
+        <v>1</v>
+      </c>
+      <c r="BD23">
+        <v>1</v>
+      </c>
+      <c r="BY23" s="2"/>
+      <c r="CN23" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="CR23">
+        <v>10</v>
+      </c>
+      <c r="DH23">
+        <v>1</v>
       </c>
     </row>
     <row r="684" spans="90:90" x14ac:dyDescent="0.25">
@@ -5332,7 +5401,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5609,6 +5678,17 @@
       </c>
       <c r="Q12" s="2" t="s">
         <v>550</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>591</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC081F18-D63C-42BB-A1CE-2CF2B38F137C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F88B8F-6CC1-4027-B8DF-87C5644F933F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="595">
   <si>
     <t>Id</t>
   </si>
@@ -1927,9 +1927,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>塞雷娅击中</t>
-  </si>
-  <si>
     <t>{"DamageBase":1,"TriggerTime":0.5,"HpLess":0.5,"HpLessRate":1.5}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2189,6 +2186,17 @@
   </si>
   <si>
     <t>自己入场</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>agoat2_skill_03_buff_01</t>
+  </si>
+  <si>
+    <t>纯烬艾雅法拉3加成</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯烬艾雅法拉3加成</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3324,10 +3332,10 @@
         <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="AM5" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="AM5" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="AN5" s="2" t="s">
         <v>481</v>
@@ -3403,7 +3411,7 @@
         <v>506</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E7" s="1">
         <v>1150</v>
@@ -3446,16 +3454,16 @@
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AN7" s="3" t="s">
         <v>511</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -3498,13 +3506,13 @@
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B9" t="s">
         <v>570</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
         <v>571</v>
-      </c>
-      <c r="F9" t="s">
-        <v>572</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -3549,20 +3557,20 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AK9" t="s">
         <v>137</v>
       </c>
       <c r="AL9" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="AM9" t="s">
         <v>588</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>589</v>
       </c>
       <c r="AO9" s="1"/>
       <c r="AQ9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3577,10 +3585,10 @@
         <v>0.25</v>
       </c>
       <c r="BE9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BO9" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -4734,7 +4742,7 @@
         <v>386</v>
       </c>
       <c r="CJ6" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="CN6" s="2" t="s">
         <v>518</v>
@@ -4751,7 +4759,7 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C7" t="s">
         <v>380</v>
@@ -4763,7 +4771,7 @@
         <v>389</v>
       </c>
       <c r="R7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -4909,10 +4917,10 @@
         <v>386</v>
       </c>
       <c r="CJ12" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="CN12" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CU12" s="2" t="s">
         <v>503</v>
@@ -4959,7 +4967,7 @@
         <v>486</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="CO13">
         <v>200</v>
@@ -5018,7 +5026,7 @@
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>505</v>
@@ -5028,7 +5036,7 @@
         <v>486</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AC16">
         <v>2</v>
@@ -5037,13 +5045,13 @@
         <v>516</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AV16">
         <v>8</v>
       </c>
       <c r="AX16" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AZ16">
         <v>1.5</v>
@@ -5056,10 +5064,10 @@
       </c>
       <c r="BY16" s="2"/>
       <c r="CH16" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="CN16" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="CO16">
         <v>-50</v>
@@ -5071,7 +5079,7 @@
         <v>3</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
@@ -5083,10 +5091,10 @@
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>517</v>
@@ -5105,7 +5113,7 @@
       </c>
       <c r="BY17" s="2"/>
       <c r="CU17" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
@@ -5126,7 +5134,7 @@
         <v>382</v>
       </c>
       <c r="AR18" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AV18">
         <v>3.5</v>
@@ -5154,13 +5162,13 @@
         <v>386</v>
       </c>
       <c r="CN18" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CO18">
         <v>-0.8</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="CY18" t="s">
         <v>387</v>
@@ -5215,7 +5223,7 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>485</v>
@@ -5236,7 +5244,7 @@
         <v>492</v>
       </c>
       <c r="AX20" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AZ20">
         <v>0.05</v>
@@ -5251,7 +5259,7 @@
         <v>0.5</v>
       </c>
       <c r="CY20" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="DD20">
         <v>1</v>
@@ -5265,16 +5273,16 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>491</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -5295,25 +5303,25 @@
         <v>1</v>
       </c>
       <c r="BY22" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="CU22" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -5322,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AN23">
         <v>1</v>
@@ -5332,7 +5340,7 @@
       </c>
       <c r="BY23" s="2"/>
       <c r="CN23" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="CR23">
         <v>10</v>
@@ -5596,7 +5604,7 @@
         <v>99999</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -5620,33 +5628,33 @@
       <c r="C8" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>519</v>
       </c>
       <c r="J9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>494</v>
       </c>
       <c r="J10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Q10" t="s">
         <v>496</v>
@@ -5654,41 +5662,41 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="K11">
         <v>0.8</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C12" t="s">
+        <v>546</v>
+      </c>
+      <c r="J12" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q12" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="C12" t="s">
-        <v>547</v>
-      </c>
-      <c r="J12" t="s">
-        <v>547</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -5747,16 +5755,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C5" t="s">
         <v>543</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -5849,13 +5857,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B4" t="s">
         <v>430</v>
       </c>
       <c r="C4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -5864,7 +5872,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5886,19 +5894,19 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="C6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -5910,7 +5918,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -6030,6 +6038,23 @@
       </c>
       <c r="L3" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B5" t="s">
+        <v>592</v>
+      </c>
+      <c r="K5">
+        <v>60</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F88B8F-6CC1-4027-B8DF-87C5644F933F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0335DFAF-2BC6-46E8-A103-940B75FE318C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="595">
   <si>
     <t>Id</t>
   </si>
@@ -1216,9 +1216,6 @@
     <t>AttackPoint</t>
   </si>
   <si>
-    <t>AttackRange</t>
-  </si>
-  <si>
     <t>AttackAreaWithMain</t>
   </si>
   <si>
@@ -1325,9 +1322,6 @@
   </si>
   <si>
     <t>Bullet</t>
-  </si>
-  <si>
-    <t>ShootPoint</t>
   </si>
   <si>
     <t>Modifys</t>
@@ -1885,10 +1879,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_2_Loop_A,Skill_2_Loop_B</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>小弟普攻</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2098,10 +2088,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":6,"ReductionRate":0.25,"SkillId":"CCB弹道索敌","CanBack":1,"ShowRange":1,"Color":"#ed3333"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>涨潮</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2139,10 +2125,6 @@
   </si>
   <si>
     <t>CCB普攻,起飞,CCB强力击,CCB攻击叠层,位移,召唤小弟,CCB呼吸强化</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>召唤地板</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
@@ -2197,6 +2179,26 @@
   </si>
   <si>
     <t>纯烬艾雅法拉3加成</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_1350_mgcshp_2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShootPoint</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>C_Head</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackRange</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0.5,"MaxLinkNum":-1,"SkillId":"CCB弹道索敌","CanBack":1}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3282,8 +3284,8 @@
       <c r="B5" t="s">
         <v>135</v>
       </c>
-      <c r="F5" t="s">
-        <v>136</v>
+      <c r="F5" s="2" t="s">
+        <v>590</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3331,17 +3333,15 @@
       <c r="AK5" t="s">
         <v>137</v>
       </c>
-      <c r="AL5" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="AM5" s="2" t="s">
-        <v>580</v>
-      </c>
+      <c r="AL5" t="s">
+        <v>377</v>
+      </c>
+      <c r="AM5" s="2"/>
       <c r="AN5" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AQ5" t="s">
         <v>138</v>
@@ -3399,19 +3399,23 @@
       </c>
     </row>
     <row r="6" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="AM6" s="2" t="s">
-        <v>504</v>
-      </c>
+      <c r="F6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="AM6" s="2"/>
     </row>
     <row r="7" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E7" s="1">
         <v>1150</v>
@@ -3448,22 +3452,22 @@
         <v>0.75</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AK7" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -3482,10 +3486,10 @@
         <v>enemy_1150_dsjely</v>
       </c>
       <c r="BM7" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="1" t="s">
@@ -3495,7 +3499,7 @@
         <v>147</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="BT7" s="1" t="s">
         <v>148</v>
@@ -3506,13 +3510,13 @@
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B9" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F9" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -3557,20 +3561,20 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AK9" t="s">
         <v>137</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AM9" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="AO9" s="1"/>
       <c r="AQ9" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3585,10 +3589,10 @@
         <v>0.25</v>
       </c>
       <c r="BE9" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="BO9" s="2" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
@@ -4100,7 +4104,7 @@
         <v>277</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AC2" t="s">
         <v>278</v>
@@ -4159,203 +4163,203 @@
       <c r="AU2" t="s">
         <v>296</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AV2" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="AW2" t="s">
         <v>297</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>298</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>299</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>300</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>301</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>302</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>303</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>304</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>305</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>306</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>307</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>308</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>309</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>310</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>311</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>312</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>313</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BN2" t="s">
         <v>314</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>315</v>
       </c>
       <c r="BO2" t="s">
         <v>85</v>
       </c>
       <c r="BP2" t="s">
+        <v>315</v>
+      </c>
+      <c r="BQ2" t="s">
         <v>316</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>317</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>318</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BT2" t="s">
         <v>319</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>320</v>
       </c>
       <c r="BU2" t="s">
         <v>101</v>
       </c>
       <c r="BV2" t="s">
+        <v>320</v>
+      </c>
+      <c r="BW2" t="s">
         <v>321</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BX2" t="s">
         <v>322</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BY2" t="s">
         <v>323</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BZ2" t="s">
         <v>324</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
         <v>325</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CB2" t="s">
         <v>326</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>327</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>328</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>329</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>330</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>331</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>332</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="CJ2" t="s">
         <v>333</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CK2" t="s">
         <v>334</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CL2" t="s">
         <v>335</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CM2" t="s">
         <v>336</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CN2" t="s">
         <v>337</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CO2" t="s">
         <v>338</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CP2" t="s">
         <v>339</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CQ2" t="s">
         <v>340</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>341</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>342</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>343</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CU2" t="s">
         <v>344</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CV2" t="s">
         <v>345</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CW2" t="s">
         <v>346</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CX2" t="s">
         <v>347</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CY2" t="s">
         <v>348</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CZ2" t="s">
         <v>349</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DA2" t="s">
         <v>350</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DB2" t="s">
         <v>351</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DC2" t="s">
         <v>352</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DD2" t="s">
         <v>353</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DE2" t="s">
         <v>354</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DF2" t="s">
         <v>355</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DG2" t="s">
         <v>356</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DH2" t="s">
         <v>357</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DI2" t="s">
         <v>358</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>359</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -4384,13 +4388,13 @@
         <v>124</v>
       </c>
       <c r="J3" t="s">
+        <v>359</v>
+      </c>
+      <c r="K3" t="s">
+        <v>360</v>
+      </c>
+      <c r="L3" t="s">
         <v>361</v>
-      </c>
-      <c r="K3" t="s">
-        <v>362</v>
-      </c>
-      <c r="L3" t="s">
-        <v>363</v>
       </c>
       <c r="M3" t="s">
         <v>127</v>
@@ -4453,7 +4457,7 @@
         <v>124</v>
       </c>
       <c r="AG3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AH3" t="s">
         <v>124</v>
@@ -4477,10 +4481,10 @@
         <v>124</v>
       </c>
       <c r="AO3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AP3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
@@ -4492,7 +4496,7 @@
         <v>2</v>
       </c>
       <c r="AT3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AU3" t="s">
         <v>124</v>
@@ -4504,7 +4508,7 @@
         <v>124</v>
       </c>
       <c r="AX3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AY3" t="s">
         <v>124</v>
@@ -4534,7 +4538,7 @@
         <v>124</v>
       </c>
       <c r="BH3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="BI3" t="s">
         <v>124</v>
@@ -4561,10 +4565,10 @@
         <v>128</v>
       </c>
       <c r="BQ3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="BR3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="BS3" t="s">
         <v>125</v>
@@ -4585,19 +4589,19 @@
         <v>127</v>
       </c>
       <c r="BY3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="CB3" t="s">
         <v>129</v>
       </c>
       <c r="CC3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="CD3" t="s">
         <v>129</v>
@@ -4609,19 +4613,19 @@
         <v>129</v>
       </c>
       <c r="CG3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="CH3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="CK3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="CL3" t="s">
         <v>134</v>
@@ -4642,7 +4646,7 @@
         <v>133</v>
       </c>
       <c r="CR3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="CS3" t="s">
         <v>133</v>
@@ -4654,28 +4658,28 @@
         <v>134</v>
       </c>
       <c r="CV3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="CW3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="CX3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="CY3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="CZ3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="DA3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="DB3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="DC3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="DD3" t="s">
         <v>124</v>
@@ -4698,30 +4702,30 @@
     </row>
     <row r="4" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" t="s">
+        <v>378</v>
+      </c>
+      <c r="K6" t="s">
         <v>379</v>
-      </c>
-      <c r="C6" t="s">
-        <v>380</v>
-      </c>
-      <c r="K6" t="s">
-        <v>381</v>
       </c>
       <c r="AC6">
         <v>2</v>
       </c>
       <c r="AO6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AV6">
         <v>8</v>
       </c>
       <c r="AX6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AZ6">
         <v>1</v>
@@ -4729,49 +4733,58 @@
       <c r="BD6">
         <v>1</v>
       </c>
-      <c r="CB6" s="2" t="s">
-        <v>512</v>
+      <c r="CB6" t="s">
+        <v>61</v>
       </c>
       <c r="CG6" t="s">
-        <v>384</v>
-      </c>
-      <c r="CH6" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>386</v>
+        <v>382</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>427</v>
+      </c>
+      <c r="CI6" s="2" t="s">
+        <v>592</v>
       </c>
       <c r="CJ6" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="CN6" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="CR6">
         <v>12</v>
       </c>
       <c r="CU6" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="CY6" t="s">
-        <v>387</v>
+        <v>385</v>
+      </c>
+      <c r="DD6">
+        <v>1</v>
+      </c>
+      <c r="DG6">
+        <v>1</v>
+      </c>
+      <c r="DH6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="K7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="R7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -4780,37 +4793,40 @@
         <v>1</v>
       </c>
       <c r="AO7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AV7">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="BD7">
         <v>99</v>
       </c>
+      <c r="CH7" s="2" t="s">
+        <v>511</v>
+      </c>
       <c r="CU7" s="2"/>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K8" t="s">
+        <v>387</v>
+      </c>
+      <c r="L8" t="s">
         <v>390</v>
-      </c>
-      <c r="C8" t="s">
-        <v>391</v>
-      </c>
-      <c r="K8" t="s">
-        <v>389</v>
-      </c>
-      <c r="L8" t="s">
-        <v>392</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AO8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AX8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -4822,30 +4838,30 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="CY8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="L10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="BD10">
         <v>1</v>
@@ -4854,33 +4870,33 @@
         <v>0.1</v>
       </c>
       <c r="CN10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="AC12">
         <v>2</v>
       </c>
       <c r="AO12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AV12">
         <v>8</v>
       </c>
       <c r="AX12" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AZ12">
         <v>2.5</v>
@@ -4902,51 +4918,51 @@
         <v>1</v>
       </c>
       <c r="BY12" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="CB12" t="s">
         <v>61</v>
       </c>
       <c r="CG12" t="s">
+        <v>382</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>427</v>
+      </c>
+      <c r="CI12" t="s">
         <v>384</v>
       </c>
-      <c r="CH12" t="s">
-        <v>429</v>
-      </c>
-      <c r="CI12" t="s">
-        <v>386</v>
-      </c>
       <c r="CJ12" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="CN12" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="CU12" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="CY12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC13">
         <v>1</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -4964,10 +4980,10 @@
         <v>1</v>
       </c>
       <c r="BY13" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="CO13">
         <v>200</v>
@@ -4982,22 +4998,22 @@
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC14">
         <v>1</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="BD14">
         <v>1</v>
@@ -5015,43 +5031,43 @@
         <v>1</v>
       </c>
       <c r="BY14" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="CN14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="CU14" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="AV16">
         <v>8</v>
       </c>
       <c r="AX16" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="AZ16">
         <v>1.5</v>
@@ -5064,10 +5080,10 @@
       </c>
       <c r="BY16" s="2"/>
       <c r="CH16" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="CN16" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="CO16">
         <v>-50</v>
@@ -5079,25 +5095,25 @@
         <v>3</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AC17">
         <v>2</v>
@@ -5113,34 +5129,34 @@
       </c>
       <c r="BY17" s="2"/>
       <c r="CU17" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC18">
         <v>2</v>
       </c>
       <c r="AO18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AR18" s="4" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="AV18">
         <v>3.5</v>
       </c>
       <c r="AX18" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AZ18">
         <v>1</v>
@@ -5153,45 +5169,45 @@
         <v>61</v>
       </c>
       <c r="CG18" t="s">
+        <v>382</v>
+      </c>
+      <c r="CH18" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="CI18" t="s">
         <v>384</v>
       </c>
-      <c r="CH18" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="CI18" t="s">
-        <v>386</v>
-      </c>
       <c r="CN18" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="CO18">
         <v>-0.8</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="CY18" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="BD19">
         <v>1</v>
@@ -5209,10 +5225,10 @@
         <v>1</v>
       </c>
       <c r="BY19" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="CN19" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="CO19">
         <v>100</v>
@@ -5223,16 +5239,16 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC20">
         <v>1</v>
@@ -5241,10 +5257,10 @@
         <v>1</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AX20" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AZ20">
         <v>0.05</v>
@@ -5259,7 +5275,7 @@
         <v>0.5</v>
       </c>
       <c r="CY20" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="DD20">
         <v>1</v>
@@ -5273,16 +5289,16 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -5303,25 +5319,25 @@
         <v>1</v>
       </c>
       <c r="BY22" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="CU22" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -5330,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AN23">
         <v>1</v>
@@ -5340,7 +5356,7 @@
       </c>
       <c r="BY23" s="2"/>
       <c r="CN23" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="CR23">
         <v>10</v>
@@ -5432,37 +5448,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G1" t="s">
         <v>400</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>401</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>402</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>403</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>404</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>405</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>406</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>407</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>408</v>
-      </c>
-      <c r="O1" t="s">
-        <v>409</v>
-      </c>
-      <c r="P1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -5476,43 +5492,43 @@
         <v>83</v>
       </c>
       <c r="E2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G2" t="s">
         <v>411</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>412</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>413</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>414</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>415</v>
-      </c>
-      <c r="J2" t="s">
-        <v>416</v>
-      </c>
-      <c r="K2" t="s">
-        <v>417</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
       </c>
       <c r="M2" t="s">
+        <v>416</v>
+      </c>
+      <c r="N2" t="s">
+        <v>417</v>
+      </c>
+      <c r="O2" t="s">
         <v>418</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>419</v>
       </c>
-      <c r="O2" t="s">
-        <v>420</v>
-      </c>
-      <c r="P2" t="s">
-        <v>421</v>
-      </c>
       <c r="Q2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -5541,13 +5557,13 @@
         <v>124</v>
       </c>
       <c r="J3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K3" t="s">
         <v>125</v>
       </c>
       <c r="L3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M3" t="s">
         <v>124</v>
@@ -5556,7 +5572,7 @@
         <v>124</v>
       </c>
       <c r="O3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P3" t="s">
         <v>124</v>
@@ -5567,55 +5583,55 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="J5" t="s">
         <v>493</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="Q5" t="s">
         <v>494</v>
-      </c>
-      <c r="J5" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K6">
         <v>99999</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="K7">
         <v>12</v>
@@ -5623,80 +5639,80 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J9" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="J10" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q10" t="s">
         <v>494</v>
-      </c>
-      <c r="J10" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="K11">
         <v>0.8</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C12" t="s">
+        <v>543</v>
+      </c>
+      <c r="J12" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q12" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="J12" t="s">
-        <v>546</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -5722,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -5733,10 +5749,10 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5747,7 +5763,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D3" t="s">
         <v>134</v>
@@ -5755,16 +5771,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C5" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -5776,7 +5792,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -5802,25 +5818,25 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
         <v>76</v>
       </c>
       <c r="F2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H2" t="s">
         <v>426</v>
       </c>
-      <c r="G2" t="s">
-        <v>427</v>
-      </c>
-      <c r="H2" t="s">
-        <v>428</v>
-      </c>
       <c r="I2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -5849,7 +5865,7 @@
         <v>127</v>
       </c>
       <c r="I3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J3" t="s">
         <v>134</v>
@@ -5857,56 +5873,58 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>568</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="C6" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -5934,34 +5952,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D1" t="s">
         <v>434</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>435</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>436</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>437</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>438</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>439</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>440</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>441</v>
-      </c>
-      <c r="K1" t="s">
-        <v>442</v>
-      </c>
-      <c r="L1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -5969,34 +5987,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D2" t="s">
         <v>444</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>445</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>446</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>447</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>448</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>449</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>450</v>
       </c>
-      <c r="I2" t="s">
-        <v>451</v>
-      </c>
-      <c r="J2" t="s">
-        <v>452</v>
-      </c>
       <c r="K2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L2" t="s">
         <v>103</v>
@@ -6045,10 +6063,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="K5">
         <v>60</v>
@@ -6091,22 +6109,22 @@
         <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F2" t="s">
         <v>85</v>
       </c>
       <c r="G2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H2" t="s">
         <v>284</v>
       </c>
       <c r="I2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J2" t="s">
         <v>58</v>
@@ -6135,7 +6153,7 @@
         <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>127</v>
@@ -6171,28 +6189,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1" t="s">
         <v>458</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>459</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>460</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>461</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>462</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>463</v>
-      </c>
-      <c r="H1" t="s">
-        <v>464</v>
-      </c>
-      <c r="I1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -6200,28 +6218,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D2" t="s">
         <v>466</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>467</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>468</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>469</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>470</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>471</v>
-      </c>
-      <c r="H2" t="s">
-        <v>472</v>
-      </c>
-      <c r="I2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6255,28 +6273,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E4" t="s">
+        <v>474</v>
+      </c>
+      <c r="F4" t="s">
         <v>475</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>476</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>477</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>478</v>
-      </c>
-      <c r="H4" t="s">
-        <v>479</v>
-      </c>
-      <c r="I4" t="s">
-        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC081F18-D63C-42BB-A1CE-2CF2B38F137C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0335DFAF-2BC6-46E8-A103-940B75FE318C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="595">
   <si>
     <t>Id</t>
   </si>
@@ -1216,9 +1216,6 @@
     <t>AttackPoint</t>
   </si>
   <si>
-    <t>AttackRange</t>
-  </si>
-  <si>
     <t>AttackAreaWithMain</t>
   </si>
   <si>
@@ -1325,9 +1322,6 @@
   </si>
   <si>
     <t>Bullet</t>
-  </si>
-  <si>
-    <t>ShootPoint</t>
   </si>
   <si>
     <t>Modifys</t>
@@ -1885,10 +1879,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_2_Loop_A,Skill_2_Loop_B</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>小弟普攻</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1925,9 +1915,6 @@
   <si>
     <t>治愈</t>
     <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>塞雷娅击中</t>
   </si>
   <si>
     <t>{"DamageBase":1,"TriggerTime":0.5,"HpLess":0.5,"HpLessRate":1.5}</t>
@@ -2101,10 +2088,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":6,"ReductionRate":0.25,"SkillId":"CCB弹道索敌","CanBack":1,"ShowRange":1,"Color":"#ed3333"}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>涨潮</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2145,10 +2128,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>召唤地板</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>潮起</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2189,6 +2168,37 @@
   </si>
   <si>
     <t>自己入场</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>agoat2_skill_03_buff_01</t>
+  </si>
+  <si>
+    <t>纯烬艾雅法拉3加成</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯烬艾雅法拉3加成</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_1350_mgcshp_2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShootPoint</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>C_Head</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackRange</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0.5,"MaxLinkNum":-1,"SkillId":"CCB弹道索敌","CanBack":1}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3274,8 +3284,8 @@
       <c r="B5" t="s">
         <v>135</v>
       </c>
-      <c r="F5" t="s">
-        <v>136</v>
+      <c r="F5" s="2" t="s">
+        <v>590</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3323,17 +3333,15 @@
       <c r="AK5" t="s">
         <v>137</v>
       </c>
-      <c r="AL5" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="AM5" s="2" t="s">
-        <v>581</v>
-      </c>
+      <c r="AL5" t="s">
+        <v>377</v>
+      </c>
+      <c r="AM5" s="2"/>
       <c r="AN5" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AQ5" t="s">
         <v>138</v>
@@ -3391,19 +3399,23 @@
       </c>
     </row>
     <row r="6" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="AM6" s="2" t="s">
-        <v>504</v>
-      </c>
+      <c r="F6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="AM6" s="2"/>
     </row>
     <row r="7" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E7" s="1">
         <v>1150</v>
@@ -3440,22 +3452,22 @@
         <v>0.75</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AK7" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -3474,10 +3486,10 @@
         <v>enemy_1150_dsjely</v>
       </c>
       <c r="BM7" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="1" t="s">
@@ -3487,7 +3499,7 @@
         <v>147</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="BT7" s="1" t="s">
         <v>148</v>
@@ -3498,13 +3510,13 @@
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B9" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="F9" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -3549,20 +3561,20 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="AK9" t="s">
         <v>137</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="AM9" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="AO9" s="1"/>
       <c r="AQ9" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3577,10 +3589,10 @@
         <v>0.25</v>
       </c>
       <c r="BE9" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="BO9" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
@@ -4092,7 +4104,7 @@
         <v>277</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AC2" t="s">
         <v>278</v>
@@ -4151,203 +4163,203 @@
       <c r="AU2" t="s">
         <v>296</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AV2" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="AW2" t="s">
         <v>297</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>298</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>299</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>300</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>301</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>302</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>303</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>304</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>305</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>306</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>307</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>308</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>309</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>310</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>311</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>312</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>313</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BN2" t="s">
         <v>314</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>315</v>
       </c>
       <c r="BO2" t="s">
         <v>85</v>
       </c>
       <c r="BP2" t="s">
+        <v>315</v>
+      </c>
+      <c r="BQ2" t="s">
         <v>316</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>317</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>318</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BT2" t="s">
         <v>319</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>320</v>
       </c>
       <c r="BU2" t="s">
         <v>101</v>
       </c>
       <c r="BV2" t="s">
+        <v>320</v>
+      </c>
+      <c r="BW2" t="s">
         <v>321</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BX2" t="s">
         <v>322</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BY2" t="s">
         <v>323</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BZ2" t="s">
         <v>324</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
         <v>325</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CB2" t="s">
         <v>326</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>327</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>328</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>329</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>330</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>331</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>332</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="CJ2" t="s">
         <v>333</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CK2" t="s">
         <v>334</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CL2" t="s">
         <v>335</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CM2" t="s">
         <v>336</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CN2" t="s">
         <v>337</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CO2" t="s">
         <v>338</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CP2" t="s">
         <v>339</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CQ2" t="s">
         <v>340</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>341</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>342</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>343</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CU2" t="s">
         <v>344</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CV2" t="s">
         <v>345</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CW2" t="s">
         <v>346</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CX2" t="s">
         <v>347</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CY2" t="s">
         <v>348</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CZ2" t="s">
         <v>349</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DA2" t="s">
         <v>350</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DB2" t="s">
         <v>351</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DC2" t="s">
         <v>352</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DD2" t="s">
         <v>353</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DE2" t="s">
         <v>354</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DF2" t="s">
         <v>355</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DG2" t="s">
         <v>356</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DH2" t="s">
         <v>357</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DI2" t="s">
         <v>358</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>359</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -4376,13 +4388,13 @@
         <v>124</v>
       </c>
       <c r="J3" t="s">
+        <v>359</v>
+      </c>
+      <c r="K3" t="s">
+        <v>360</v>
+      </c>
+      <c r="L3" t="s">
         <v>361</v>
-      </c>
-      <c r="K3" t="s">
-        <v>362</v>
-      </c>
-      <c r="L3" t="s">
-        <v>363</v>
       </c>
       <c r="M3" t="s">
         <v>127</v>
@@ -4445,7 +4457,7 @@
         <v>124</v>
       </c>
       <c r="AG3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AH3" t="s">
         <v>124</v>
@@ -4469,10 +4481,10 @@
         <v>124</v>
       </c>
       <c r="AO3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AP3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
@@ -4484,7 +4496,7 @@
         <v>2</v>
       </c>
       <c r="AT3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AU3" t="s">
         <v>124</v>
@@ -4496,7 +4508,7 @@
         <v>124</v>
       </c>
       <c r="AX3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AY3" t="s">
         <v>124</v>
@@ -4526,7 +4538,7 @@
         <v>124</v>
       </c>
       <c r="BH3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="BI3" t="s">
         <v>124</v>
@@ -4553,10 +4565,10 @@
         <v>128</v>
       </c>
       <c r="BQ3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="BR3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="BS3" t="s">
         <v>125</v>
@@ -4577,19 +4589,19 @@
         <v>127</v>
       </c>
       <c r="BY3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="CB3" t="s">
         <v>129</v>
       </c>
       <c r="CC3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="CD3" t="s">
         <v>129</v>
@@ -4601,19 +4613,19 @@
         <v>129</v>
       </c>
       <c r="CG3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="CH3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="CK3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="CL3" t="s">
         <v>134</v>
@@ -4634,7 +4646,7 @@
         <v>133</v>
       </c>
       <c r="CR3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="CS3" t="s">
         <v>133</v>
@@ -4646,28 +4658,28 @@
         <v>134</v>
       </c>
       <c r="CV3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="CW3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="CX3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="CY3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="CZ3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="DA3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="DB3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="DC3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="DD3" t="s">
         <v>124</v>
@@ -4690,30 +4702,30 @@
     </row>
     <row r="4" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" t="s">
+        <v>378</v>
+      </c>
+      <c r="K6" t="s">
         <v>379</v>
-      </c>
-      <c r="C6" t="s">
-        <v>380</v>
-      </c>
-      <c r="K6" t="s">
-        <v>381</v>
       </c>
       <c r="AC6">
         <v>2</v>
       </c>
       <c r="AO6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AV6">
         <v>8</v>
       </c>
       <c r="AX6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AZ6">
         <v>1</v>
@@ -4721,49 +4733,58 @@
       <c r="BD6">
         <v>1</v>
       </c>
-      <c r="CB6" s="2" t="s">
-        <v>512</v>
+      <c r="CB6" t="s">
+        <v>61</v>
       </c>
       <c r="CG6" t="s">
-        <v>384</v>
-      </c>
-      <c r="CH6" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>386</v>
+        <v>382</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>427</v>
+      </c>
+      <c r="CI6" s="2" t="s">
+        <v>592</v>
       </c>
       <c r="CJ6" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="CN6" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="CR6">
         <v>12</v>
       </c>
       <c r="CU6" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="CY6" t="s">
-        <v>387</v>
+        <v>385</v>
+      </c>
+      <c r="DD6">
+        <v>1</v>
+      </c>
+      <c r="DG6">
+        <v>1</v>
+      </c>
+      <c r="DH6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="K7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="R7" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -4772,37 +4793,40 @@
         <v>1</v>
       </c>
       <c r="AO7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AV7">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="BD7">
         <v>99</v>
       </c>
+      <c r="CH7" s="2" t="s">
+        <v>511</v>
+      </c>
       <c r="CU7" s="2"/>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K8" t="s">
+        <v>387</v>
+      </c>
+      <c r="L8" t="s">
         <v>390</v>
-      </c>
-      <c r="C8" t="s">
-        <v>391</v>
-      </c>
-      <c r="K8" t="s">
-        <v>389</v>
-      </c>
-      <c r="L8" t="s">
-        <v>392</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AO8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AX8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -4814,30 +4838,30 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="CY8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="L10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="BD10">
         <v>1</v>
@@ -4846,33 +4870,33 @@
         <v>0.1</v>
       </c>
       <c r="CN10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="AC12">
         <v>2</v>
       </c>
       <c r="AO12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AV12">
         <v>8</v>
       </c>
       <c r="AX12" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AZ12">
         <v>2.5</v>
@@ -4894,51 +4918,51 @@
         <v>1</v>
       </c>
       <c r="BY12" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="CB12" t="s">
         <v>61</v>
       </c>
       <c r="CG12" t="s">
+        <v>382</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>427</v>
+      </c>
+      <c r="CI12" t="s">
         <v>384</v>
       </c>
-      <c r="CH12" t="s">
-        <v>429</v>
-      </c>
-      <c r="CI12" t="s">
-        <v>386</v>
-      </c>
       <c r="CJ12" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="CN12" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="CU12" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="CY12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC13">
         <v>1</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -4956,10 +4980,10 @@
         <v>1</v>
       </c>
       <c r="BY13" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="CO13">
         <v>200</v>
@@ -4974,22 +4998,22 @@
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC14">
         <v>1</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="BD14">
         <v>1</v>
@@ -5007,43 +5031,43 @@
         <v>1</v>
       </c>
       <c r="BY14" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="CN14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="CU14" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AV16">
         <v>8</v>
       </c>
       <c r="AX16" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AZ16">
         <v>1.5</v>
@@ -5056,10 +5080,10 @@
       </c>
       <c r="BY16" s="2"/>
       <c r="CH16" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="CN16" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="CO16">
         <v>-50</v>
@@ -5071,25 +5095,25 @@
         <v>3</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AC17">
         <v>2</v>
@@ -5105,34 +5129,34 @@
       </c>
       <c r="BY17" s="2"/>
       <c r="CU17" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC18">
         <v>2</v>
       </c>
       <c r="AO18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AR18" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AV18">
         <v>3.5</v>
       </c>
       <c r="AX18" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AZ18">
         <v>1</v>
@@ -5145,45 +5169,45 @@
         <v>61</v>
       </c>
       <c r="CG18" t="s">
+        <v>382</v>
+      </c>
+      <c r="CH18" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="CI18" t="s">
         <v>384</v>
       </c>
-      <c r="CH18" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="CI18" t="s">
-        <v>386</v>
-      </c>
       <c r="CN18" s="2" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="CO18">
         <v>-0.8</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="CY18" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="BD19">
         <v>1</v>
@@ -5201,10 +5225,10 @@
         <v>1</v>
       </c>
       <c r="BY19" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="CN19" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="CO19">
         <v>100</v>
@@ -5215,16 +5239,16 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AC20">
         <v>1</v>
@@ -5233,10 +5257,10 @@
         <v>1</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AX20" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AZ20">
         <v>0.05</v>
@@ -5251,7 +5275,7 @@
         <v>0.5</v>
       </c>
       <c r="CY20" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="DD20">
         <v>1</v>
@@ -5265,16 +5289,16 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -5295,25 +5319,25 @@
         <v>1</v>
       </c>
       <c r="BY22" s="2" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="CU22" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -5322,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="AN23">
         <v>1</v>
@@ -5332,7 +5356,7 @@
       </c>
       <c r="BY23" s="2"/>
       <c r="CN23" s="2" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="CR23">
         <v>10</v>
@@ -5424,37 +5448,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G1" t="s">
         <v>400</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>401</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>402</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>403</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>404</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>405</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>406</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>407</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>408</v>
-      </c>
-      <c r="O1" t="s">
-        <v>409</v>
-      </c>
-      <c r="P1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -5468,43 +5492,43 @@
         <v>83</v>
       </c>
       <c r="E2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G2" t="s">
         <v>411</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>412</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>413</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>414</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>415</v>
-      </c>
-      <c r="J2" t="s">
-        <v>416</v>
-      </c>
-      <c r="K2" t="s">
-        <v>417</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
       </c>
       <c r="M2" t="s">
+        <v>416</v>
+      </c>
+      <c r="N2" t="s">
+        <v>417</v>
+      </c>
+      <c r="O2" t="s">
         <v>418</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>419</v>
       </c>
-      <c r="O2" t="s">
-        <v>420</v>
-      </c>
-      <c r="P2" t="s">
-        <v>421</v>
-      </c>
       <c r="Q2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -5533,13 +5557,13 @@
         <v>124</v>
       </c>
       <c r="J3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K3" t="s">
         <v>125</v>
       </c>
       <c r="L3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M3" t="s">
         <v>124</v>
@@ -5548,7 +5572,7 @@
         <v>124</v>
       </c>
       <c r="O3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P3" t="s">
         <v>124</v>
@@ -5559,55 +5583,55 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="J5" t="s">
         <v>493</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="Q5" t="s">
         <v>494</v>
-      </c>
-      <c r="J5" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K6">
         <v>99999</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="K7">
         <v>12</v>
@@ -5615,80 +5639,80 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="J8" t="s">
-        <v>523</v>
+        <v>519</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>589</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J9" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="J10" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q10" t="s">
         <v>494</v>
-      </c>
-      <c r="J10" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="K11">
         <v>0.8</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C12" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="J12" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q14" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -5714,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -5725,10 +5749,10 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5739,7 +5763,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D3" t="s">
         <v>134</v>
@@ -5747,16 +5771,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C5" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -5768,7 +5792,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -5794,25 +5818,25 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
         <v>76</v>
       </c>
       <c r="F2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H2" t="s">
         <v>426</v>
       </c>
-      <c r="G2" t="s">
-        <v>427</v>
-      </c>
-      <c r="H2" t="s">
-        <v>428</v>
-      </c>
       <c r="I2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -5841,7 +5865,7 @@
         <v>127</v>
       </c>
       <c r="I3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J3" t="s">
         <v>134</v>
@@ -5849,56 +5873,58 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" t="s">
         <v>529</v>
       </c>
-      <c r="B4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C4" t="s">
-        <v>532</v>
-      </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>569</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C6" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -5910,7 +5936,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -5926,34 +5952,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D1" t="s">
         <v>434</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>435</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>436</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>437</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>438</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>439</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>440</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>441</v>
-      </c>
-      <c r="K1" t="s">
-        <v>442</v>
-      </c>
-      <c r="L1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -5961,34 +5987,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D2" t="s">
         <v>444</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>445</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>446</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>447</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>448</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>449</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>450</v>
       </c>
-      <c r="I2" t="s">
-        <v>451</v>
-      </c>
-      <c r="J2" t="s">
-        <v>452</v>
-      </c>
       <c r="K2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L2" t="s">
         <v>103</v>
@@ -6030,6 +6056,23 @@
       </c>
       <c r="L3" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B5" t="s">
+        <v>587</v>
+      </c>
+      <c r="K5">
+        <v>60</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6066,22 +6109,22 @@
         <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F2" t="s">
         <v>85</v>
       </c>
       <c r="G2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H2" t="s">
         <v>284</v>
       </c>
       <c r="I2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J2" t="s">
         <v>58</v>
@@ -6110,7 +6153,7 @@
         <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>127</v>
@@ -6146,28 +6189,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1" t="s">
         <v>458</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>459</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>460</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>461</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>462</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>463</v>
-      </c>
-      <c r="H1" t="s">
-        <v>464</v>
-      </c>
-      <c r="I1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -6175,28 +6218,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D2" t="s">
         <v>466</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>467</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>468</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>469</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>470</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>471</v>
-      </c>
-      <c r="H2" t="s">
-        <v>472</v>
-      </c>
-      <c r="I2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6230,28 +6273,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E4" t="s">
+        <v>474</v>
+      </c>
+      <c r="F4" t="s">
         <v>475</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>476</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>477</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>478</v>
-      </c>
-      <c r="H4" t="s">
-        <v>479</v>
-      </c>
-      <c r="I4" t="s">
-        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0335DFAF-2BC6-46E8-A103-940B75FE318C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF516D8-EDEA-4271-AC66-45AD03AD407E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="596">
   <si>
     <t>Id</t>
   </si>
@@ -2198,7 +2198,11 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"MoveHeight":0.5,"MaxLinkNum":-1,"SkillId":"CCB弹道索敌","CanBack":1}</t>
+    <t>CCB增伤,弱点伤害</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0.5,"MaxLinkNum":60,"SkillId":"CCB弹道索敌","CanBack":1,"ShowRange":1,"Color":"#EE3527"}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -4746,7 +4750,7 @@
         <v>592</v>
       </c>
       <c r="CJ6" s="2" t="s">
-        <v>539</v>
+        <v>594</v>
       </c>
       <c r="CN6" s="2" t="s">
         <v>515</v>
@@ -4796,7 +4800,7 @@
         <v>380</v>
       </c>
       <c r="AV7">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="BD7">
         <v>99</v>
@@ -5888,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF516D8-EDEA-4271-AC66-45AD03AD407E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB92FAF7-C848-469C-9948-F6B6C9DFD217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2202,7 +2202,7 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"MoveHeight":0.5,"MaxLinkNum":60,"SkillId":"CCB弹道索敌","CanBack":1,"ShowRange":1,"Color":"#EE3527"}</t>
+    <t>{"MoveHeight":0,"MaxLinkNum":60,"SkillId":"CCB弹道索敌","CanBack":1,"ShowRange":1,"Color":"#EE3527","Homing":1,"LifeTime":15,"NavigationConstant":2}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB92FAF7-C848-469C-9948-F6B6C9DFD217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C6860A-B00A-4A0A-8DFA-E0AEE2C6DA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="600">
   <si>
     <t>Id</t>
   </si>
@@ -739,9 +739,6 @@
     <t>Hip</t>
   </si>
   <si>
-    <t>地面位</t>
-  </si>
-  <si>
     <t>先锋</t>
   </si>
   <si>
@@ -1767,10 +1764,6 @@
   </si>
   <si>
     <t>小型:紫</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"ShowRange":1}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
@@ -2202,7 +2195,30 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":60,"SkillId":"CCB弹道索敌","CanBack":1,"ShowRange":1,"Color":"#EE3527","Homing":1,"LifeTime":15,"NavigationConstant":2}</t>
+    <t>弩箭</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身距离升序</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxLinkNum":-1,"SkillId":"CCB弹道索敌","CanBack":0,"ShowRange":0,"Color":"#EE3527","Homing":1,"LifeTime":90,"NavigationConstant":3,"HomingDelay":0.5,"MaxTurnRate":2160}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB棘刺2弹道</t>
+  </si>
+  <si>
+    <t>CCB棘刺2弹道</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ShowRange":1,"Line":4,"MaxLine":60,"BaseAngle": 0,"FanRange":60}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxRadius":1.5,"InitRadius":0.75,"RadiusExponentRate":0.25,"Trigger":0.1,"MaxTargetCount":6,"LifeTime":15}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -3289,7 +3305,7 @@
         <v>135</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3326,7 +3342,7 @@
         <v>0.05</v>
       </c>
       <c r="AA5">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AD5">
         <v>1</v>
@@ -3338,17 +3354,17 @@
         <v>137</v>
       </c>
       <c r="AL5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="AO5" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="AO5" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="AQ5" t="s">
-        <v>138</v>
+        <v>566</v>
       </c>
       <c r="AR5">
         <v>2</v>
@@ -3360,43 +3376,43 @@
         <v>0.25</v>
       </c>
       <c r="BE5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BG5" t="s">
         <v>139</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BH5" t="s">
         <v>140</v>
       </c>
-      <c r="BH5" t="s">
+      <c r="BI5" t="s">
         <v>141</v>
       </c>
-      <c r="BI5" t="s">
+      <c r="BJ5" t="s">
         <v>142</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>143</v>
       </c>
       <c r="BK5">
         <v>6</v>
       </c>
       <c r="BL5" t="s">
+        <v>143</v>
+      </c>
+      <c r="BM5" t="s">
         <v>144</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BQ5" t="s">
         <v>145</v>
       </c>
-      <c r="BQ5" t="s">
+      <c r="BR5" t="s">
         <v>146</v>
       </c>
-      <c r="BR5" t="s">
+      <c r="BT5" t="s">
         <v>147</v>
       </c>
-      <c r="BT5" t="s">
+      <c r="BU5" t="s">
+        <v>147</v>
+      </c>
+      <c r="BV5" t="s">
         <v>148</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>148</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>149</v>
       </c>
       <c r="BX5">
         <v>1</v>
@@ -3407,19 +3423,19 @@
         <v>136</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AM6" s="2"/>
     </row>
     <row r="7" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E7" s="1">
         <v>1150</v>
@@ -3456,22 +3472,22 @@
         <v>0.75</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AK7" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AM7" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="AN7" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="AO7" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="AN7" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -3490,23 +3506,23 @@
         <v>enemy_1150_dsjely</v>
       </c>
       <c r="BM7" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="BR7" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="BR7" s="1" t="s">
+      <c r="BS7" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="BT7" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="BS7" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="BT7" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="BX7" s="1">
         <v>1</v>
@@ -3514,13 +3530,13 @@
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B9" t="s">
+        <v>564</v>
+      </c>
+      <c r="F9" t="s">
         <v>565</v>
-      </c>
-      <c r="B9" t="s">
-        <v>566</v>
-      </c>
-      <c r="F9" t="s">
-        <v>567</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -3565,20 +3581,20 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AK9" t="s">
         <v>137</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AM9" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AO9" s="1"/>
       <c r="AQ9" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3593,10 +3609,10 @@
         <v>0.25</v>
       </c>
       <c r="BE9" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="BO9" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -3698,334 +3714,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1" t="s">
         <v>150</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>151</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>152</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>153</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>154</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>155</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>156</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>157</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>158</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>159</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>160</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>161</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>162</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>163</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>164</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>165</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>166</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
+        <v>166</v>
+      </c>
+      <c r="V1" t="s">
         <v>167</v>
       </c>
-      <c r="U1" t="s">
-        <v>167</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>168</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>169</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>170</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>171</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>172</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>173</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>174</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>175</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>176</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>177</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>178</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>179</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>180</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>181</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>182</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>183</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>184</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>185</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>186</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>187</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>188</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>189</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>190</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>191</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>192</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>193</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>194</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>195</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>196</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>197</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>198</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>199</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>200</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>201</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>202</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>203</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>204</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>205</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK1" t="s">
         <v>206</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>206</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>207</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>208</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>209</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>210</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>211</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>212</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>213</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>214</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>215</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>216</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>217</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>218</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>219</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>220</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>221</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>222</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>223</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>224</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>225</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>226</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>227</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>228</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>229</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>230</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>231</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>232</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>233</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>234</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>235</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>236</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>237</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>238</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
+        <v>215</v>
+      </c>
+      <c r="CS1" t="s">
         <v>239</v>
       </c>
-      <c r="CR1" t="s">
-        <v>216</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>240</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>241</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>242</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>243</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>244</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>245</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
+        <v>244</v>
+      </c>
+      <c r="DA1" t="s">
         <v>246</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>245</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>247</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>248</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>249</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>250</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>251</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>252</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DH1" t="s">
         <v>253</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DI1" t="s">
         <v>254</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -4039,331 +4055,331 @@
         <v>83</v>
       </c>
       <c r="E2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" t="s">
         <v>256</v>
-      </c>
-      <c r="F2" t="s">
-        <v>257</v>
       </c>
       <c r="G2" t="s">
         <v>57</v>
       </c>
       <c r="H2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" t="s">
         <v>258</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>259</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>260</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>261</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>262</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>263</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>264</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>265</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>266</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>267</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>268</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>269</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>270</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>271</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>272</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>273</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>274</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>275</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="AC2" t="s">
         <v>277</v>
       </c>
-      <c r="AB2" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>278</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>279</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>280</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>281</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>282</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>283</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>284</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>285</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>286</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>287</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>288</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>289</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>290</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>291</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>292</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>293</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>294</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>295</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="AW2" t="s">
         <v>296</v>
       </c>
-      <c r="AV2" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>297</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>298</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>299</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>300</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>301</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>302</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>303</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>304</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>305</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>306</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>307</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>308</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>309</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>310</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>311</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>312</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BN2" t="s">
         <v>313</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>314</v>
       </c>
       <c r="BO2" t="s">
         <v>85</v>
       </c>
       <c r="BP2" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ2" t="s">
         <v>315</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>316</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>317</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BT2" t="s">
         <v>318</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>319</v>
       </c>
       <c r="BU2" t="s">
         <v>101</v>
       </c>
       <c r="BV2" t="s">
+        <v>319</v>
+      </c>
+      <c r="BW2" t="s">
         <v>320</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BX2" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BY2" t="s">
         <v>322</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BZ2" t="s">
         <v>323</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
         <v>324</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CB2" t="s">
         <v>325</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>326</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>327</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>328</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>329</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>330</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>331</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="CJ2" t="s">
         <v>332</v>
       </c>
-      <c r="CI2" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="CJ2" t="s">
+      <c r="CK2" t="s">
         <v>333</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CL2" t="s">
         <v>334</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CM2" t="s">
         <v>335</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CN2" t="s">
         <v>336</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CO2" t="s">
         <v>337</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
         <v>338</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CQ2" t="s">
         <v>339</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CR2" t="s">
         <v>340</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
         <v>341</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CT2" t="s">
         <v>342</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CU2" t="s">
         <v>343</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CV2" t="s">
         <v>344</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CW2" t="s">
         <v>345</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CX2" t="s">
         <v>346</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CY2" t="s">
         <v>347</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CZ2" t="s">
         <v>348</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DA2" t="s">
         <v>349</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DB2" t="s">
         <v>350</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DC2" t="s">
         <v>351</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>352</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>353</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DF2" t="s">
         <v>354</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DG2" t="s">
         <v>355</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DH2" t="s">
         <v>356</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DI2" t="s">
         <v>357</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -4392,13 +4408,13 @@
         <v>124</v>
       </c>
       <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
         <v>359</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>360</v>
-      </c>
-      <c r="L3" t="s">
-        <v>361</v>
       </c>
       <c r="M3" t="s">
         <v>127</v>
@@ -4461,7 +4477,7 @@
         <v>124</v>
       </c>
       <c r="AG3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AH3" t="s">
         <v>124</v>
@@ -4485,10 +4501,10 @@
         <v>124</v>
       </c>
       <c r="AO3" t="s">
+        <v>362</v>
+      </c>
+      <c r="AP3" t="s">
         <v>363</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>364</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
@@ -4500,7 +4516,7 @@
         <v>2</v>
       </c>
       <c r="AT3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AU3" t="s">
         <v>124</v>
@@ -4512,7 +4528,7 @@
         <v>124</v>
       </c>
       <c r="AX3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AY3" t="s">
         <v>124</v>
@@ -4542,7 +4558,7 @@
         <v>124</v>
       </c>
       <c r="BH3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="BI3" t="s">
         <v>124</v>
@@ -4569,10 +4585,10 @@
         <v>128</v>
       </c>
       <c r="BQ3" t="s">
+        <v>366</v>
+      </c>
+      <c r="BR3" t="s">
         <v>367</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>368</v>
       </c>
       <c r="BS3" t="s">
         <v>125</v>
@@ -4593,19 +4609,19 @@
         <v>127</v>
       </c>
       <c r="BY3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="CB3" t="s">
         <v>129</v>
       </c>
       <c r="CC3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="CD3" t="s">
         <v>129</v>
@@ -4617,19 +4633,19 @@
         <v>129</v>
       </c>
       <c r="CG3" t="s">
+        <v>370</v>
+      </c>
+      <c r="CH3" t="s">
         <v>371</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>372</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="CK3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="CL3" t="s">
         <v>134</v>
@@ -4650,7 +4666,7 @@
         <v>133</v>
       </c>
       <c r="CR3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="CS3" t="s">
         <v>133</v>
@@ -4662,28 +4678,28 @@
         <v>134</v>
       </c>
       <c r="CV3" t="s">
+        <v>373</v>
+      </c>
+      <c r="CW3" t="s">
         <v>374</v>
       </c>
-      <c r="CW3" t="s">
-        <v>375</v>
-      </c>
       <c r="CX3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="CY3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="CZ3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="DA3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="DB3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="DC3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="DD3" t="s">
         <v>124</v>
@@ -4706,33 +4722,33 @@
     </row>
     <row r="4" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>377</v>
-      </c>
-      <c r="C6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="K6" t="s">
         <v>378</v>
       </c>
-      <c r="K6" t="s">
-        <v>379</v>
+      <c r="X6">
+        <v>1</v>
       </c>
       <c r="AC6">
         <v>2</v>
       </c>
       <c r="AO6" t="s">
+        <v>379</v>
+      </c>
+      <c r="AX6" t="s">
         <v>380</v>
       </c>
-      <c r="AV6">
-        <v>8</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>381</v>
-      </c>
       <c r="AZ6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BD6">
         <v>1</v>
@@ -4741,28 +4757,28 @@
         <v>61</v>
       </c>
       <c r="CG6" t="s">
-        <v>382</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>427</v>
+        <v>381</v>
+      </c>
+      <c r="CH6" s="2" t="s">
+        <v>596</v>
       </c>
       <c r="CI6" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="CJ6" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="CJ6" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="CN6" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="CR6">
         <v>12</v>
       </c>
       <c r="CU6" s="2" t="s">
-        <v>481</v>
+        <v>598</v>
       </c>
       <c r="CY6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="DD6">
         <v>1</v>
@@ -4776,19 +4792,19 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J7" t="s">
+        <v>385</v>
+      </c>
+      <c r="K7" t="s">
         <v>386</v>
       </c>
-      <c r="K7" t="s">
-        <v>387</v>
-      </c>
       <c r="R7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -4796,41 +4812,41 @@
       <c r="AD7">
         <v>1</v>
       </c>
-      <c r="AO7" t="s">
-        <v>380</v>
+      <c r="AO7" s="2" t="s">
+        <v>594</v>
       </c>
       <c r="AV7">
-        <v>1.5</v>
+        <v>16</v>
       </c>
       <c r="BD7">
         <v>99</v>
       </c>
       <c r="CH7" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="CU7" s="2"/>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>387</v>
+      </c>
+      <c r="C8" t="s">
         <v>388</v>
       </c>
-      <c r="C8" t="s">
+      <c r="K8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L8" t="s">
         <v>389</v>
-      </c>
-      <c r="K8" t="s">
-        <v>387</v>
-      </c>
-      <c r="L8" t="s">
-        <v>390</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AO8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AX8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -4842,30 +4858,30 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
+        <v>391</v>
+      </c>
+      <c r="CY8" t="s">
         <v>392</v>
-      </c>
-      <c r="CY8" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C10" t="s">
+        <v>377</v>
+      </c>
+      <c r="K10" t="s">
+        <v>386</v>
+      </c>
+      <c r="L10" t="s">
         <v>394</v>
-      </c>
-      <c r="C10" t="s">
-        <v>378</v>
-      </c>
-      <c r="K10" t="s">
-        <v>387</v>
-      </c>
-      <c r="L10" t="s">
-        <v>395</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="BD10">
         <v>1</v>
@@ -4874,33 +4890,33 @@
         <v>0.1</v>
       </c>
       <c r="CN10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="AC12">
         <v>2</v>
       </c>
       <c r="AO12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AV12">
         <v>8</v>
       </c>
       <c r="AX12" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AZ12">
         <v>2.5</v>
@@ -4922,51 +4938,51 @@
         <v>1</v>
       </c>
       <c r="BY12" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="CB12" t="s">
         <v>61</v>
       </c>
       <c r="CG12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="CH12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="CI12" t="s">
+        <v>383</v>
+      </c>
+      <c r="CJ12" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="CN12" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="CU12" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="CY12" t="s">
         <v>384</v>
-      </c>
-      <c r="CJ12" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="CN12" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="CU12" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="CY12" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AC13">
         <v>1</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -4984,10 +5000,10 @@
         <v>1</v>
       </c>
       <c r="BY13" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="CN13" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="CO13">
         <v>200</v>
@@ -5002,22 +5018,22 @@
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AC14">
         <v>1</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="BD14">
         <v>1</v>
@@ -5035,43 +5051,43 @@
         <v>1</v>
       </c>
       <c r="BY14" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="CN14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="CU14" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AV16">
         <v>8</v>
       </c>
       <c r="AX16" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AZ16">
         <v>1.5</v>
@@ -5084,10 +5100,10 @@
       </c>
       <c r="BY16" s="2"/>
       <c r="CH16" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="CN16" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="CO16">
         <v>-50</v>
@@ -5099,25 +5115,25 @@
         <v>3</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AC17">
         <v>2</v>
@@ -5133,34 +5149,34 @@
       </c>
       <c r="BY17" s="2"/>
       <c r="CU17" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AC18">
         <v>2</v>
       </c>
       <c r="AO18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AR18" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AV18">
         <v>3.5</v>
       </c>
       <c r="AX18" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AZ18">
         <v>1</v>
@@ -5173,45 +5189,45 @@
         <v>61</v>
       </c>
       <c r="CG18" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="CH18" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="CI18" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="CN18" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="CO18">
         <v>-0.8</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="CY18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="BD19">
         <v>1</v>
@@ -5229,10 +5245,10 @@
         <v>1</v>
       </c>
       <c r="BY19" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="CN19" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="CO19">
         <v>100</v>
@@ -5243,16 +5259,16 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AC20">
         <v>1</v>
@@ -5261,10 +5277,10 @@
         <v>1</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AX20" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AZ20">
         <v>0.05</v>
@@ -5279,7 +5295,7 @@
         <v>0.5</v>
       </c>
       <c r="CY20" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="DD20">
         <v>1</v>
@@ -5293,16 +5309,16 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -5323,25 +5339,25 @@
         <v>1</v>
       </c>
       <c r="BY22" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="CU22" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -5350,7 +5366,7 @@
         <v>1</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AN23">
         <v>1</v>
@@ -5360,7 +5376,7 @@
       </c>
       <c r="BY23" s="2"/>
       <c r="CN23" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="CR23">
         <v>10</v>
@@ -5452,37 +5468,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F1" t="s">
         <v>398</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>399</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>400</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>401</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>402</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>403</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>404</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>405</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>406</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>407</v>
-      </c>
-      <c r="P1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -5496,43 +5512,43 @@
         <v>83</v>
       </c>
       <c r="E2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F2" t="s">
         <v>409</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>410</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>411</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>412</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>413</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>414</v>
-      </c>
-      <c r="K2" t="s">
-        <v>415</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
       </c>
       <c r="M2" t="s">
+        <v>415</v>
+      </c>
+      <c r="N2" t="s">
         <v>416</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>417</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>418</v>
       </c>
-      <c r="P2" t="s">
-        <v>419</v>
-      </c>
       <c r="Q2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -5561,13 +5577,13 @@
         <v>124</v>
       </c>
       <c r="J3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K3" t="s">
         <v>125</v>
       </c>
       <c r="L3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M3" t="s">
         <v>124</v>
@@ -5576,7 +5592,7 @@
         <v>124</v>
       </c>
       <c r="O3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P3" t="s">
         <v>124</v>
@@ -5587,55 +5603,55 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="J5" t="s">
         <v>491</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="Q5" t="s">
         <v>492</v>
-      </c>
-      <c r="J5" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="K6">
         <v>99999</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="J7" t="s">
         <v>515</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="J7" t="s">
-        <v>517</v>
       </c>
       <c r="K7">
         <v>12</v>
@@ -5643,80 +5659,80 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="J9" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="J10" t="s">
         <v>532</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="Q10" t="s">
         <v>492</v>
-      </c>
-      <c r="J10" t="s">
-        <v>534</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="K11">
         <v>0.8</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C12" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J12" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>581</v>
-      </c>
       <c r="Q14" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -5742,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -5753,10 +5769,10 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5767,7 +5783,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
         <v>134</v>
@@ -5775,16 +5791,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C5" t="s">
+        <v>538</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C5" t="s">
-        <v>540</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -5796,19 +5812,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="10" width="9" customWidth="1"/>
+    <col min="5" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -5822,25 +5840,25 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E2" t="s">
         <v>76</v>
       </c>
       <c r="F2" t="s">
+        <v>423</v>
+      </c>
+      <c r="G2" t="s">
         <v>424</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>425</v>
       </c>
-      <c r="H2" t="s">
-        <v>426</v>
-      </c>
       <c r="I2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -5869,7 +5887,7 @@
         <v>127</v>
       </c>
       <c r="I3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J3" t="s">
         <v>134</v>
@@ -5877,19 +5895,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>595</v>
@@ -5897,38 +5912,55 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>528</v>
+        <v>529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C7" t="s">
+        <v>527</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -5956,34 +5988,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C1" t="s">
         <v>432</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>433</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>434</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>435</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>436</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>437</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>438</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>439</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>440</v>
-      </c>
-      <c r="L1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -5991,34 +6023,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C2" t="s">
         <v>442</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>443</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>444</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>445</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>446</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>447</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>448</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>449</v>
       </c>
-      <c r="J2" t="s">
-        <v>450</v>
-      </c>
       <c r="K2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L2" t="s">
         <v>103</v>
@@ -6067,10 +6099,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="K5">
         <v>60</v>
@@ -6107,28 +6139,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
         <v>83</v>
       </c>
       <c r="D2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E2" t="s">
         <v>451</v>
-      </c>
-      <c r="E2" t="s">
-        <v>452</v>
       </c>
       <c r="F2" t="s">
         <v>85</v>
       </c>
       <c r="G2" t="s">
+        <v>452</v>
+      </c>
+      <c r="H2" t="s">
+        <v>283</v>
+      </c>
+      <c r="I2" t="s">
         <v>453</v>
-      </c>
-      <c r="H2" t="s">
-        <v>284</v>
-      </c>
-      <c r="I2" t="s">
-        <v>454</v>
       </c>
       <c r="J2" t="s">
         <v>58</v>
@@ -6157,7 +6189,7 @@
         <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>127</v>
@@ -6193,28 +6225,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C1" t="s">
         <v>456</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>457</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>458</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>459</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>460</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>461</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>462</v>
-      </c>
-      <c r="I1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -6222,28 +6254,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2" t="s">
         <v>464</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>465</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>466</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>467</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>468</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>469</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>470</v>
-      </c>
-      <c r="I2" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6277,28 +6309,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>472</v>
+      </c>
+      <c r="E4" t="s">
         <v>473</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>474</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>475</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>476</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>477</v>
-      </c>
-      <c r="I4" t="s">
-        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF1E0BA-12FB-40E3-B306-6046F679CE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D4420E-925E-4407-89F2-4789DAABDA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="650">
   <si>
     <t>Id</t>
   </si>
@@ -2145,9 +2145,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>agoat2_skill_03_buff_01</t>
-  </si>
-  <si>
     <t>纯烬艾雅法拉3加成</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -2409,6 +2406,13 @@
   </si>
   <si>
     <t>入场</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯烬艾雅法拉3加成</t>
+  </si>
+  <si>
+    <t>agoat2_skill_03_buff_01</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2911,10 +2915,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -3571,19 +3575,19 @@
     </row>
     <row r="5" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3626,16 +3630,16 @@
         <v>1</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AK5" t="s">
         <v>136</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AN5" s="2" t="s">
         <v>473</v>
@@ -3656,10 +3660,10 @@
         <v>0.25</v>
       </c>
       <c r="BE5" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="BF5" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="BF5" s="1" t="s">
-        <v>619</v>
       </c>
       <c r="BG5" s="1" t="str">
         <f t="shared" ref="BG5" si="0">"icon_"&amp;D5</f>
@@ -3903,15 +3907,15 @@
     </row>
     <row r="10" spans="1:76" x14ac:dyDescent="0.25">
       <c r="E10" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>515</v>
@@ -3981,7 +3985,7 @@
         <v>0.25</v>
       </c>
       <c r="BG11" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="BM11" s="1" t="s">
         <v>497</v>
@@ -4008,10 +4012,10 @@
     </row>
     <row r="12" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>515</v>
@@ -4081,7 +4085,7 @@
         <v>0.25</v>
       </c>
       <c r="BG12" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="BM12" s="1" t="s">
         <v>497</v>
@@ -4108,10 +4112,10 @@
     </row>
     <row r="13" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>515</v>
@@ -4181,7 +4185,7 @@
         <v>0.25</v>
       </c>
       <c r="BG13" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="BM13" s="1" t="s">
         <v>497</v>
@@ -4775,7 +4779,7 @@
         <v>290</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AW2" t="s">
         <v>291</v>
@@ -4892,7 +4896,7 @@
         <v>326</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="CJ2" t="s">
         <v>327</v>
@@ -5321,13 +5325,13 @@
         <v>371</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K6" t="s">
         <v>373</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AC6">
         <v>2</v>
@@ -5339,7 +5343,7 @@
         <v>374</v>
       </c>
       <c r="AT6" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AX6" t="s">
         <v>375</v>
@@ -5357,22 +5361,22 @@
         <v>0.25</v>
       </c>
       <c r="BP6" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="BQ6" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="CB6" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="CG6" t="s">
         <v>376</v>
       </c>
       <c r="CH6" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="CI6" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="CJ6" s="2" t="s">
         <v>531</v>
@@ -5384,7 +5388,7 @@
         <v>12</v>
       </c>
       <c r="CU6" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="CY6" t="s">
         <v>379</v>
@@ -5422,7 +5426,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AV7">
         <v>16</v>
@@ -5996,17 +6000,17 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -6024,7 +6028,7 @@
         <v>1</v>
       </c>
       <c r="AX25" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AZ25">
         <v>1.5</v>
@@ -6039,7 +6043,7 @@
         <v>0.04</v>
       </c>
       <c r="BP25" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="BT25">
         <v>2.5</v>
@@ -6054,55 +6058,55 @@
         <v>1</v>
       </c>
       <c r="BY25" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="CB25" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="CE25" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="CF25" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="CG25" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="CH25" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="CI25" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="CE25" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="CF25" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="CG25" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="CH25" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="CI25" s="2" t="s">
-        <v>628</v>
-      </c>
       <c r="CJ25" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="CU25" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="CY25" s="2"/>
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="AC26">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="2" t="s">
-        <v>600</v>
-      </c>
       <c r="BD26">
         <v>1</v>
       </c>
       <c r="CN26" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="CR26">
         <v>3</v>
@@ -6110,25 +6114,25 @@
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K28" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="O28" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="AC28">
         <v>1</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="BT28">
         <v>2.5</v>
@@ -6143,21 +6147,21 @@
         <v>1</v>
       </c>
       <c r="BY28" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C31" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>381</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -6194,21 +6198,21 @@
       <c r="CA31" s="8"/>
       <c r="CN31" s="9"/>
       <c r="CU31" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C32" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>381</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
@@ -6245,21 +6249,21 @@
       <c r="CA32" s="8"/>
       <c r="CN32" s="9"/>
       <c r="CU32" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="33" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C33" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>381</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
@@ -6296,7 +6300,7 @@
       <c r="CA33" s="8"/>
       <c r="CN33" s="9"/>
       <c r="CU33" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="684" spans="90:90" x14ac:dyDescent="0.25">
@@ -6579,7 +6583,7 @@
         <v>511</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>512</v>
@@ -6651,13 +6655,13 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J16" t="s">
-        <v>485</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -6832,7 +6836,7 @@
         <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6868,13 +6872,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>519</v>
       </c>
       <c r="C7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E7">
         <v>2.25</v>
@@ -6883,18 +6887,18 @@
         <v>2</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>519</v>
       </c>
       <c r="C8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -6903,7 +6907,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -6913,7 +6917,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>
@@ -7052,10 +7056,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="B5" t="s">
         <v>579</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="K5">
         <v>60</v>
@@ -7066,10 +7070,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B7" t="s">
         <v>614</v>
-      </c>
-      <c r="B7" t="s">
-        <v>615</v>
       </c>
       <c r="K7">
         <v>60</v>
